--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>D-2</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F760D-EED6-49F6-BC6D-899349450A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D6F1A05-4F49-49E3-A76A-D68BA2D3793F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FD40498-10AB-4B2A-8A53-DFCC458E99F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0EE0671F-CCB6-4E59-BDF2-9AEEC94866AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="238">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,562 +95,664 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Semipresencial</t>
+  </si>
+  <si>
+    <t>0010620-68.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>Marcio Aragao De Melo</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               35.458,88</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010484-64.2026.5.03.0031</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Kaio Rodrigo Goncalves Da Cruz</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               15.171,44</t>
+  </si>
+  <si>
+    <t>JRT</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt3.contagem</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>0000235-34.2024.5.05.0010</t>
+  </si>
+  <si>
+    <t>Empresa Brasileira De Correios E Telégrafos</t>
+  </si>
+  <si>
+    <t>Bruno Dorotea Carvalho</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>04ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             300.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/j/81673214114?pwd=KqDZYEX0bwqYaAEm1kji5uS54hN9fb.1 ID da reunião: 816 7321 4114 Senha: 381576</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0021010-86.2025.5.04.0261</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Ereni Lucia Merelles</t>
+  </si>
+  <si>
+    <t>MONTENEGRO</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>R$               90.863,10</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>https://trt4-jus-br.zoom.us/my/varamontenegrojt</t>
+  </si>
+  <si>
+    <t>0021011-71.2025.5.04.0261</t>
+  </si>
+  <si>
+    <t>R$               81.145,00</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000798-22.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Wemerson Sarbos Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             467.744,00</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>JJS</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1000238-71.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Marcos Vinicius Aureliano Da Silva</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             154.338,18</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>1000540-73.2026.5.02.0055</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Rodrigo De Souza Carvalho</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>55ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             187.199,20</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>1001034-62.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Guilherme Arenghi</t>
+  </si>
+  <si>
+    <t>R$               31.203,97</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012382-27.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Fabio Jose Da Silva</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$             726.201,97</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>1000661-53.2026.5.02.0362</t>
+  </si>
+  <si>
+    <t>Telefonica Transportes E Logistica Ltda</t>
+  </si>
+  <si>
+    <t>Leandro Guerra Martins</t>
+  </si>
+  <si>
+    <t>MAUÁ</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             609.505,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81888793195?pwd=zaKVkkSJIGnQZm0NWHNP3Dvd0XynH6.1 ID da reunião: 818 8879 3195 Senha de acesso: 489121</t>
+  </si>
+  <si>
+    <t>0011002-62.2025.5.15.0061</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Jose Donizete Gregorio De Barros</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             239.250,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Zalaf</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>1000511-51.2026.5.02.0466</t>
+  </si>
+  <si>
+    <t>Lucas Costa De Souza</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>Ação Revisional</t>
+  </si>
+  <si>
+    <t>R$               17.133,76</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>0012342-45.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Wellington Eduardo Antonio</t>
+  </si>
+  <si>
+    <t>R$             807.325,10</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0010934-15.2026.5.15.0082</t>
+    <t>0000007-07.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Anderson Felipe Ferri</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$               88.000,00</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/s6t0x ID da Reunião: 86331122339 Senha: AjcTXjEOTP</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011152-45.2023.5.15.0083</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Alexandre De Paula Silva</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$               93.500,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>1000983-48.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Junior Duarte Da Silva De Lima</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.253.619,24</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>1000708-14.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Ricardo Gabriel Rigonatt</t>
+  </si>
+  <si>
+    <t>R$          1.040.664,19</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>1000112-75.2026.5.02.0028</t>
+  </si>
+  <si>
+    <t>Bit Services Inovacao E Tecnologia Ltda</t>
+  </si>
+  <si>
+    <t>Rosana Aparecida Rodrigues Soares</t>
+  </si>
+  <si>
+    <t>28ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             403.222,02</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010335-20.2026.5.15.0133</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
-    <t>Genival Barbosa De Souza</t>
+    <t>Renato Jose Dias</t>
   </si>
   <si>
     <t>SÃO JOSÉ DO RIO PRETO</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Ação de Consignação em Pagamento</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               18.722,63</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0010932-15.2026.5.15.0092</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A</t>
-  </si>
-  <si>
-    <t>Yves Antoine Morisseau</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>R$               24.928,50</t>
-  </si>
-  <si>
-    <t>FCG</t>
+    <t>R$             418.460,00</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>1001486-47.2025.5.02.0001</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Luciene Vicentina Pereira Barros</t>
+  </si>
+  <si>
+    <t>15ª TURMA</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$             360.084,51</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000385-50.2019.5.02.0432</t>
+  </si>
+  <si>
+    <t>Josafa Correia Da Silva</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               44.493,44</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/86338540319?pwd=YXVKQ3hRYjBjQXV1L1pZa2hjUS9xdz09 ID da reunião: 863 3854 0319 Senha de acesso: 464616</t>
+  </si>
+  <si>
+    <t>0012911-33.2024.5.15.0140</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Fabio De Moura Laurindo</t>
+  </si>
+  <si>
+    <t>ATIBAIA</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               70.026,90</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011704-65.2024.5.03.0129</t>
+  </si>
+  <si>
+    <t>Sociedade Fogas Ltda.</t>
+  </si>
+  <si>
+    <t>Joel Santiago Pereira</t>
+  </si>
+  <si>
+    <t>POUSO ALEGRE</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             346.272,00</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/trt3.turma3</t>
+  </si>
+  <si>
+    <t>1000597-21.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Rogerio Medeiros</t>
+  </si>
+  <si>
+    <t>R$          1.502.000,00</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0001578-56.2025.5.09.0095</t>
+  </si>
+  <si>
+    <t>Allan Ferreira Silva</t>
+  </si>
+  <si>
+    <t>FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>R$               66.145,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/9x465 ID da Reunião: 87286990916 Senha: 1LQMvJnlUg</t>
+  </si>
+  <si>
+    <t>0011838-87.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Ederson Claudinei Dos Santos Rosa Silva</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$             151.517,15</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>0010164-88.2026.5.03.0071</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Paulo Henrique De Castro Alves</t>
+  </si>
+  <si>
+    <t>PATOS DE MINAS</t>
+  </si>
+  <si>
+    <t>R$               40.213,83</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patosdeminas</t>
+  </si>
+  <si>
+    <t>0010287-79.2026.5.15.0030</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Edimar Jose Dos Santos</t>
+  </si>
+  <si>
+    <t>OURINHOS</t>
+  </si>
+  <si>
+    <t>R$             201.367,91</t>
   </si>
   <si>
     <t>CAL</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/81373986659?pwd=QzVUTjNjQkZ6SzFMenZWemcreHB5Zz09 ID da reunião: 813 7398 6659 Senha: 386734</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000255-19.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Sizelando Cambui Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$               37.874,10</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>JJS</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Semipresencial</t>
-  </si>
-  <si>
-    <t>0010591-18.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Allyson Hian Ladeia Lira De Souza</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               63.021,36</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09  ID da reunião: 875 2756 4652  Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000126-33.2020.5.02.0040</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Cristiane Aparecida Benedito Souza</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>CEJUSC TST</t>
-  </si>
-  <si>
-    <t>Recursal TST</t>
-  </si>
-  <si>
-    <t>R$             636.603,96</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>bit.ly/Cejusc2026</t>
-  </si>
-  <si>
-    <t>0010421-41.2020.5.15.0152</t>
-  </si>
-  <si>
-    <t>Wickbold &amp; Nosso Pão Indústrias Alimentícias Ltda</t>
-  </si>
-  <si>
-    <t>Carlos Eduardo Ferreira Soares</t>
-  </si>
-  <si>
-    <t>HORTOLÂNDIA</t>
-  </si>
-  <si>
-    <t>CEJUSC LIMEIRA</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$               58.707,85</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>https://bit.ly/cejusclimeirasala2 ID da reunião: 649 704 1087 senha: 521311</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010231-75.2026.5.03.0096</t>
-  </si>
-  <si>
-    <t>Agrocerrado Produtos Agrícolas E Assistência Técnica Ltda.</t>
-  </si>
-  <si>
-    <t>Leonardo Pereira Dos Santos</t>
-  </si>
-  <si>
-    <t>UNAÍ</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             127.762,61</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>DPR</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.unai</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0011580-45.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda</t>
-  </si>
-  <si>
-    <t>Joao Vitor Vieira Cezar</t>
-  </si>
-  <si>
-    <t>CAÇAPAVA</t>
-  </si>
-  <si>
-    <t>R$               47.500,00</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>JRT</t>
-  </si>
-  <si>
-    <t>0010546-54.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Jose Rodrigues Dos Reis</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$               94.031,96</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0010096-25.2026.5.15.0130</t>
-  </si>
-  <si>
-    <t>David Savassa Da Silva</t>
-  </si>
-  <si>
-    <t>11ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               34.155,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Correspondente - Dra. Juliana da Silva, (19) 98743-4081.</t>
+    <t>https://trt15-jus-br.zoom.us/j/85209397799?pwd=WjA5VVN3clJWR2c3dFZ4eUhOMjU5Zz0 ID da reunião: 85209397799 e Senha: 353827</t>
+  </si>
+  <si>
+    <t>0011759-61.2025.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Rafael Pereira Da Silva</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$               86.113,94</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
   </si>
   <si>
     <t>Audiência Inicial - Telepresencial</t>
   </si>
   <si>
-    <t>0010374-66.2026.5.03.0160</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S/A</t>
-  </si>
-  <si>
-    <t>Neliton Pereira Pedrosa</t>
-  </si>
-  <si>
-    <t>FORMIGA</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             135.000,00</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt2formiga</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011224-77.2025.5.15.0013</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Joao Paulo Dias De Faria</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               92.820,08</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>1000915-10.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Leandro Santa Rosa Da Silva Monteiro</t>
-  </si>
-  <si>
-    <t>R$          1.230.271,69</t>
-  </si>
-  <si>
-    <t>0010221-45.2025.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Gelson Pinto</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>R$               60.841,75</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1001909-72.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Samuel Da Silva</t>
-  </si>
-  <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             185.780,50</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0011164-38.2025.5.03.0143</t>
-  </si>
-  <si>
-    <t>Empresa Brasileira De Correios E Telégrafos</t>
-  </si>
-  <si>
-    <t>Nelida Larisa Faria Figueiredo</t>
-  </si>
-  <si>
-    <t>JUIZ DE FORA</t>
-  </si>
-  <si>
-    <t>R$          2.353.657,08</t>
-  </si>
-  <si>
-    <t>Dispensada a presença de partes e procuradores</t>
-  </si>
-  <si>
-    <t>0010376-28.2024.5.15.0045</t>
-  </si>
-  <si>
-    <t>Anderson Rodrigo Da Costa</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>Recursal TRT</t>
-  </si>
-  <si>
-    <t>R$          1.205.489,64</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>bit.ly/cejusc2grau</t>
-  </si>
-  <si>
-    <t>0011301-91.2022.5.15.0013</t>
-  </si>
-  <si>
-    <t>Wagner Jose Goulart</t>
-  </si>
-  <si>
-    <t>R$             500.000,00</t>
-  </si>
-  <si>
-    <t>0011696-51.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Cicero De Souza</t>
-  </si>
-  <si>
-    <t>R$             112.873,57</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85877224676?pwd=SzhWaXM1NGRneVVxTW9na2lUWGl1Zz09</t>
-  </si>
-  <si>
-    <t>0010616-85.2026.5.03.0043</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Mariana Cristina Abraao Silva</t>
-  </si>
-  <si>
-    <t>UBERLÂNDIA</t>
-  </si>
-  <si>
-    <t>R$               73.023,60</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1.uberlandia</t>
-  </si>
-  <si>
-    <t>0011061-55.2025.5.15.0124</t>
-  </si>
-  <si>
-    <t>Epifanio Pereira</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$             240.908,10</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
-  </si>
-  <si>
-    <t>0010186-98.2023.5.15.0013</t>
-  </si>
-  <si>
-    <t>Frediano Da Silva Pinheiro</t>
-  </si>
-  <si>
-    <t>R$             102.500,00</t>
-  </si>
-  <si>
-    <t>0010498-75.2023.5.15.0045</t>
-  </si>
-  <si>
-    <t>Jose Benedito Azevedo De Castro</t>
-  </si>
-  <si>
-    <t>R$             204.483,46</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0010960-67.2023.5.15.0001</t>
-  </si>
-  <si>
-    <t>Enore Zonzini</t>
-  </si>
-  <si>
-    <t>02ª TURMA</t>
-  </si>
-  <si>
-    <t>R$          1.060.864,00</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/launch/jc/86828801471 ID da reunião: 868 2880 1471 Senha: 997231</t>
-  </si>
-  <si>
-    <t>0010997-58.2023.5.15.0013</t>
-  </si>
-  <si>
-    <t>Anderson Deive Rodrigues Alves</t>
-  </si>
-  <si>
-    <t>Marcos Eduardo Ribeiro</t>
-  </si>
-  <si>
-    <t>05ª TURMA</t>
-  </si>
-  <si>
-    <t>R$               93.500,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/84034239737?pwd=qpEEecbdXlhjIa8zjjb8srJaltqYbh.1</t>
+    <t>0010289-49.2026.5.15.0030</t>
+  </si>
+  <si>
+    <t>Wiliam Machado Leal</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85209397799?pwd=WjA5VVN3clJWR2c3dFZ4eUhOMjU5Zz09  ID da reunião: 85209397799 e Senha:353827</t>
   </si>
 </sst>
 </file>
@@ -1128,11 +1230,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF21AB92-9416-419C-965B-4C29B394F6B4}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE714E1C-EF1E-4220-BC30-903B22BAFB26}">
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,15 +1293,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104697</v>
+        <v>104967</v>
       </c>
       <c r="B2" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.34375</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1238,60 +1343,60 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104966</v>
+        <v>104484</v>
       </c>
       <c r="B3" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C3" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>41</v>
@@ -1300,15 +1405,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>104226</v>
+        <v>100254</v>
       </c>
       <c r="B4" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C4" s="6">
-        <v>0.36805555555555558</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>43</v>
@@ -1326,1165 +1431,1165 @@
         <v>47</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>104922</v>
+        <v>102033</v>
       </c>
       <c r="B5" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C5" s="6">
-        <v>0.375</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>102059</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>104136</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46189</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.38333333333333336</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J6" s="7" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>104861</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>85432</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46189</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.38680555555555557</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>104039</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="H8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>104381</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46189</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="K8" s="7" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>105031</v>
+        <v>104661</v>
       </c>
       <c r="B9" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4201388888888889</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105081</v>
+        <v>105186</v>
       </c>
       <c r="B10" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C10" s="6">
-        <v>0.4375</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>103821</v>
+        <v>99425</v>
       </c>
       <c r="B11" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C11" s="6">
-        <v>0.4375</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>104921</v>
+        <v>105064</v>
       </c>
       <c r="B12" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C12" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>101340</v>
+        <v>102178</v>
       </c>
       <c r="B13" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C13" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>104997</v>
+        <v>104641</v>
       </c>
       <c r="B14" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C14" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="G14" s="7" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>100215</v>
+        <v>99426</v>
       </c>
       <c r="B15" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C15" s="6">
-        <v>0.51388888888888884</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>102988</v>
+        <v>103743</v>
       </c>
       <c r="B16" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C16" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>103003</v>
+        <v>94994</v>
       </c>
       <c r="B17" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C17" s="6">
-        <v>0.55138888888888893</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="P17" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>105060</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>97435</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46189</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>93942</v>
+        <v>104740</v>
       </c>
       <c r="B19" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C19" s="6">
-        <v>0.59305555555555556</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>103562</v>
+        <v>103894</v>
       </c>
       <c r="B20" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C20" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>104755</v>
+        <v>104554</v>
       </c>
       <c r="B21" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C21" s="6">
-        <v>0.60763888888888884</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>103194</v>
+        <v>104395</v>
       </c>
       <c r="B22" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C22" s="6">
-        <v>0.61111111111111116</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>55</v>
+        <v>172</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>38</v>
+        <v>175</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>97287</v>
+        <v>66615</v>
       </c>
       <c r="B23" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C23" s="6">
-        <v>0.62083333333333335</v>
+        <v>0.54513888888888884</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>99056</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
-        <v>91987</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46189</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.64861111111111114</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P24" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="Q24" s="7" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>104157</v>
+        <v>102819</v>
       </c>
       <c r="B25" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C25" s="6">
-        <v>0.65972222222222221</v>
+        <v>0.5625</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>191</v>
@@ -2493,116 +2598,453 @@
         <v>192</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>100844</v>
+        <v>104638</v>
       </c>
       <c r="B26" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C26" s="6">
-        <v>0.66666666666666663</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>200</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>103586</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="O26" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q26" s="7" t="s">
+      <c r="E27" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="R26" s="8" t="s">
-        <v>203</v>
+      <c r="J27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>98536</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>103976</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>104533</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>103526</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>104294</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46190</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{D0C44EAA-C575-41AB-A006-72C753517124}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/81373986659?pwd=QzVUTjNjQkZ6SzFMenZWemcreHB5Zz09%20ID%20da%20reunião:%20813%207398%206659%20Senha:%20386734" xr:uid="{4144CE7F-99EA-4A19-B23A-53D6C4194870}"/>
-    <hyperlink ref="R5" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20%20ID%20da%20reunião:%20875%202756%204652%20%20Senha%20de%20acesso:%20246680" xr:uid="{6019A524-25BF-457D-AEFF-138C1B45A586}"/>
-    <hyperlink ref="R7" r:id="rId4" xr:uid="{7BC0DC9C-255F-4483-B359-366B48377B1E}"/>
-    <hyperlink ref="R8" r:id="rId5" xr:uid="{1E7458E7-CB62-43A3-BF11-CAFF2CEC0785}"/>
-    <hyperlink ref="R10" r:id="rId6" xr:uid="{28C5E655-DD24-4B22-A111-F52C3A89054A}"/>
-    <hyperlink ref="R12" r:id="rId7" xr:uid="{BED8E0F3-536B-4864-93D2-BD45F784A2CA}"/>
-    <hyperlink ref="R15" r:id="rId8" xr:uid="{D3B6E344-AC2C-494D-B9BA-8E3FE4F86D02}"/>
-    <hyperlink ref="R20" r:id="rId9" xr:uid="{0F670622-AD2D-44DF-8EBA-8E578B790E5F}"/>
-    <hyperlink ref="R21" r:id="rId10" xr:uid="{04CCE6AA-9099-4EBF-A70A-1438872A856E}"/>
-    <hyperlink ref="R22" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{D92CDCBB-A325-41B0-98B3-136838810A85}"/>
-    <hyperlink ref="R25" r:id="rId12" xr:uid="{A2FA4682-218E-4240-8F39-1270DAC94ACE}"/>
-    <hyperlink ref="R26" r:id="rId13" xr:uid="{91786964-AA4B-4634-9617-FE62CCDC4CE2}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{7A58F037-CEEC-4391-9AD5-27180FFAC830}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{60B3EE2E-755A-4F01-AB3C-5396F3FDEB42}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://trt5-jus-br.zoom.us/j/81673214114?pwd=KqDZYEX0bwqYaAEm1kji5uS54hN9fb.1%20ID%20da%20reunião:%20816%207321%204114%20Senha:%20381576" xr:uid="{12023888-1176-4A76-9DB7-D6D9A16A517C}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{3144A8B9-9355-470C-92E0-18541F97C469}"/>
+    <hyperlink ref="R6" r:id="rId5" xr:uid="{45B24127-8FBF-4422-9522-2F1135FA4A41}"/>
+    <hyperlink ref="R12" r:id="rId6" display="https://trt2-jus-br.zoom.us/j/81888793195?pwd=zaKVkkSJIGnQZm0NWHNP3Dvd0XynH6.1%20ID%20da%20reunião:%20818%208879%203195%20Senha%20de%20acesso:%20489121" xr:uid="{707F3C4F-54B6-4893-8618-E10DCBF1E8C0}"/>
+    <hyperlink ref="R16" r:id="rId7" xr:uid="{202C8D39-A899-4DCD-902F-989A50064B66}"/>
+    <hyperlink ref="R23" r:id="rId8" display="https://trt2-jus-br.zoom.us/j/86338540319?pwd=YXVKQ3hRYjBjQXV1L1pZa2hjUS9xdz09%20ID%20da%20reunião:%20863%203854%200319%20Senha%20de%20acesso:%20464616" xr:uid="{DCFE1D9F-244E-444B-8D99-F18BD2AC9BF6}"/>
+    <hyperlink ref="R25" r:id="rId9" xr:uid="{85926BB9-82B8-42F3-917E-FAFD9A9784B2}"/>
+    <hyperlink ref="R27" r:id="rId10" xr:uid="{16E2299E-ED61-4B1F-854E-B6B02425FF28}"/>
+    <hyperlink ref="R29" r:id="rId11" xr:uid="{15BA15F9-F1F8-4503-93D4-D3199A873627}"/>
+    <hyperlink ref="R30" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/85209397799?pwd=WjA5VVN3clJWR2c3dFZ4eUhOMjU5Zz0%20ID%20da%20reunião:%2085209397799%20e%20Senha:%20353827" xr:uid="{0B968083-9F24-4107-B956-6081A2A23801}"/>
+    <hyperlink ref="R31" r:id="rId13" xr:uid="{DB82136A-1D70-47D8-903C-5D4599980FF3}"/>
+    <hyperlink ref="R32" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/85209397799?pwd=WjA5VVN3clJWR2c3dFZ4eUhOMjU5Zz09%20%20ID%20da%20reunião:%2085209397799%20e%20Senha:353827" xr:uid="{E5788123-8267-40C3-B0DA-FEF05CAE30D0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -759,7 +759,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1232,12 +1232,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE714E1C-EF1E-4220-BC30-903B22BAFB26}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="16.149999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A2" s="4">
         <v>104967</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A3" s="4">
         <v>104484</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="4">
         <v>100254</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A5" s="4">
         <v>102033</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A6" s="4">
         <v>102059</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A7" s="4">
         <v>104861</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A8" s="4">
         <v>104039</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A9" s="4">
         <v>104661</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A10" s="4">
         <v>105186</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A11" s="4">
         <v>99425</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A12" s="4">
         <v>105064</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A13" s="4">
         <v>102178</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A14" s="4">
         <v>104641</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A15" s="4">
         <v>99426</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A16" s="4">
         <v>103743</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A17" s="4">
         <v>94994</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A18" s="4">
         <v>105060</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A19" s="4">
         <v>104740</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A20" s="4">
         <v>103894</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A21" s="4">
         <v>104554</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A22" s="4">
         <v>104395</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A23" s="4">
         <v>66615</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A24" s="4">
         <v>99056</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A25" s="4">
         <v>102819</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A26" s="4">
         <v>104638</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A27" s="4">
         <v>103586</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A28" s="4">
         <v>98536</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A29" s="4">
         <v>103976</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A30" s="4">
         <v>104533</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A31" s="4">
         <v>103526</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A32" s="4">
         <v>104294</v>
       </c>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>JPE</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -6875,7 +6875,7 @@
         <v>46199</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
         <v>55</v>
@@ -6907,7 +6907,7 @@
         <v>46199</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D96" t="s">
         <v>55</v>
@@ -6939,7 +6939,7 @@
         <v>46199</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
         <v>56</v>
@@ -6971,7 +6971,7 @@
         <v>46199</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
         <v>43</v>
@@ -7006,7 +7006,7 @@
         <v>46199</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
@@ -7041,7 +7041,7 @@
         <v>46199</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
         <v>39</v>
@@ -7076,7 +7076,7 @@
         <v>46199</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
         <v>58</v>
@@ -7108,7 +7108,7 @@
         <v>46199</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7143,7 +7143,7 @@
         <v>46199</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>44</v>
@@ -7178,7 +7178,7 @@
         <v>46199</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D104" t="s">
         <v>61</v>
@@ -7210,7 +7210,7 @@
         <v>46199</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D105" t="s">
         <v>55</v>
@@ -7242,7 +7242,7 @@
         <v>46199</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D106" t="s">
         <v>58</v>
@@ -7274,7 +7274,7 @@
         <v>46199</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
         <v>45</v>
@@ -7309,7 +7309,7 @@
         <v>46199</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D108" t="s">
         <v>57</v>
@@ -7341,7 +7341,7 @@
         <v>46199</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D109" t="s">
         <v>55</v>
@@ -7373,7 +7373,7 @@
         <v>46199</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D110" t="s">
         <v>55</v>
@@ -7405,7 +7405,7 @@
         <v>46199</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
         <v>37</v>
@@ -7440,7 +7440,7 @@
         <v>46199</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
         <v>37</v>
@@ -7475,7 +7475,7 @@
         <v>46199</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D113" t="s">
         <v>55</v>
@@ -7507,7 +7507,7 @@
         <v>46199</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
         <v>37</v>
@@ -7542,7 +7542,7 @@
         <v>46199</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D115" t="s">
         <v>58</v>
@@ -7574,7 +7574,7 @@
         <v>46199</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D116" t="s">
         <v>56</v>
@@ -7606,7 +7606,7 @@
         <v>46199</v>
       </c>
       <c r="B117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D117" t="s">
         <v>56</v>
@@ -7638,7 +7638,7 @@
         <v>46199</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D118" t="s">
         <v>56</v>
@@ -7670,7 +7670,7 @@
         <v>46199</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D119" t="s">
         <v>61</v>
@@ -7702,7 +7702,7 @@
         <v>46199</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D120" t="s">
         <v>62</v>
@@ -7734,7 +7734,7 @@
         <v>46199</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D121" t="s">
         <v>56</v>
@@ -7766,7 +7766,7 @@
         <v>46199</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D122" t="s">
         <v>56</v>
@@ -7798,7 +7798,7 @@
         <v>46199</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D123" t="s">
         <v>55</v>
@@ -7830,7 +7830,7 @@
         <v>46199</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D124" t="s">
         <v>56</v>
@@ -7862,7 +7862,7 @@
         <v>46199</v>
       </c>
       <c r="B125" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D125" t="s">
         <v>55</v>
@@ -7894,7 +7894,7 @@
         <v>46199</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D126" t="s">
         <v>55</v>
@@ -7926,7 +7926,7 @@
         <v>46199</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D127" t="s">
         <v>56</v>
@@ -7958,7 +7958,7 @@
         <v>46199</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
         <v>57</v>
@@ -7990,7 +7990,7 @@
         <v>46199</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D129" t="s">
         <v>56</v>
@@ -8022,7 +8022,7 @@
         <v>46202</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C130" t="s">
         <v>46</v>
@@ -8057,7 +8057,7 @@
         <v>46202</v>
       </c>
       <c r="B131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D131" t="s">
         <v>63</v>
@@ -8089,7 +8089,7 @@
         <v>46202</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
         <v>56</v>
@@ -8121,7 +8121,7 @@
         <v>46202</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
         <v>58</v>
@@ -8153,7 +8153,7 @@
         <v>46202</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
         <v>29</v>
@@ -8188,7 +8188,7 @@
         <v>46202</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D135" t="s">
         <v>58</v>
@@ -8220,7 +8220,7 @@
         <v>46202</v>
       </c>
       <c r="B136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C136" t="s">
         <v>47</v>
@@ -8255,7 +8255,7 @@
         <v>46202</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
         <v>36</v>
@@ -8290,7 +8290,7 @@
         <v>46202</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138" t="s">
         <v>48</v>
@@ -8325,7 +8325,7 @@
         <v>46202</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>16</v>
@@ -8360,7 +8360,7 @@
         <v>46202</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
         <v>27</v>
@@ -8395,7 +8395,7 @@
         <v>46202</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
         <v>37</v>
@@ -8430,7 +8430,7 @@
         <v>46202</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
         <v>33</v>
@@ -8465,7 +8465,7 @@
         <v>46202</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
         <v>49</v>
@@ -8500,7 +8500,7 @@
         <v>46202</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -8535,7 +8535,7 @@
         <v>46202</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D145" t="s">
         <v>55</v>
@@ -8567,7 +8567,7 @@
         <v>46202</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
         <v>32</v>
@@ -8602,7 +8602,7 @@
         <v>46202</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
         <v>40</v>
@@ -8637,7 +8637,7 @@
         <v>46202</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
         <v>25</v>
@@ -8672,7 +8672,7 @@
         <v>46202</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
         <v>38</v>
@@ -8707,7 +8707,7 @@
         <v>46202</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
         <v>55</v>
@@ -8739,7 +8739,7 @@
         <v>46202</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D151" t="s">
         <v>55</v>
@@ -8771,7 +8771,7 @@
         <v>46202</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
         <v>26</v>
@@ -8806,7 +8806,7 @@
         <v>46202</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
         <v>48</v>
@@ -8841,7 +8841,7 @@
         <v>46202</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
         <v>56</v>
@@ -8873,7 +8873,7 @@
         <v>46202</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D155" t="s">
         <v>62</v>
@@ -8905,7 +8905,7 @@
         <v>46202</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" t="s">
         <v>56</v>
@@ -8937,7 +8937,7 @@
         <v>46202</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D157" t="s">
         <v>57</v>
@@ -8969,7 +8969,7 @@
         <v>46202</v>
       </c>
       <c r="B158" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
@@ -9004,7 +9004,7 @@
         <v>46202</v>
       </c>
       <c r="B159" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D159" t="s">
         <v>55</v>
@@ -9036,7 +9036,7 @@
         <v>46202</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D160" t="s">
         <v>55</v>
@@ -9068,7 +9068,7 @@
         <v>46202</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D161" t="s">
         <v>56</v>
@@ -9100,7 +9100,7 @@
         <v>46202</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C162" t="s">
         <v>18</v>
@@ -9135,7 +9135,7 @@
         <v>46202</v>
       </c>
       <c r="B163" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D163" t="s">
         <v>58</v>
@@ -9167,7 +9167,7 @@
         <v>46203</v>
       </c>
       <c r="B164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D164" t="s">
         <v>56</v>
@@ -9199,7 +9199,7 @@
         <v>46203</v>
       </c>
       <c r="B165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D165" t="s">
         <v>56</v>
@@ -9231,7 +9231,7 @@
         <v>46203</v>
       </c>
       <c r="B166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D166" t="s">
         <v>56</v>
@@ -9263,7 +9263,7 @@
         <v>46203</v>
       </c>
       <c r="B167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D167" t="s">
         <v>56</v>
@@ -9295,7 +9295,7 @@
         <v>46203</v>
       </c>
       <c r="B168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
         <v>32</v>
@@ -9330,7 +9330,7 @@
         <v>46203</v>
       </c>
       <c r="B169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
         <v>29</v>
@@ -9365,7 +9365,7 @@
         <v>46203</v>
       </c>
       <c r="B170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
         <v>26</v>
@@ -9400,7 +9400,7 @@
         <v>46203</v>
       </c>
       <c r="B171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D171" t="s">
         <v>55</v>
@@ -9432,7 +9432,7 @@
         <v>46203</v>
       </c>
       <c r="B172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
         <v>23</v>
@@ -9467,7 +9467,7 @@
         <v>46203</v>
       </c>
       <c r="B173" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C173" t="s">
         <v>38</v>
@@ -9502,7 +9502,7 @@
         <v>46203</v>
       </c>
       <c r="B174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
         <v>21</v>
@@ -9537,7 +9537,7 @@
         <v>46203</v>
       </c>
       <c r="B175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D175" t="s">
         <v>56</v>
@@ -9569,7 +9569,7 @@
         <v>46203</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D176" t="s">
         <v>58</v>
@@ -9601,7 +9601,7 @@
         <v>46203</v>
       </c>
       <c r="B177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D177" t="s">
         <v>58</v>
@@ -9633,7 +9633,7 @@
         <v>46203</v>
       </c>
       <c r="B178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
         <v>46</v>
@@ -9668,7 +9668,7 @@
         <v>46203</v>
       </c>
       <c r="B179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D179" t="s">
         <v>55</v>
@@ -9700,7 +9700,7 @@
         <v>46203</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D180" t="s">
         <v>58</v>
@@ -9732,7 +9732,7 @@
         <v>46203</v>
       </c>
       <c r="B181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D181" t="s">
         <v>56</v>
@@ -9764,7 +9764,7 @@
         <v>46203</v>
       </c>
       <c r="B182" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C182" t="s">
         <v>45</v>
@@ -9799,7 +9799,7 @@
         <v>46203</v>
       </c>
       <c r="B183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D183" t="s">
         <v>55</v>
@@ -9831,7 +9831,7 @@
         <v>46203</v>
       </c>
       <c r="B184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D184" t="s">
         <v>55</v>
@@ -9863,7 +9863,7 @@
         <v>46203</v>
       </c>
       <c r="B185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
@@ -9898,7 +9898,7 @@
         <v>46203</v>
       </c>
       <c r="B186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -9930,7 +9930,7 @@
         <v>46203</v>
       </c>
       <c r="B187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D187" t="s">
         <v>58</v>
@@ -9962,7 +9962,7 @@
         <v>46203</v>
       </c>
       <c r="B188" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
         <v>51</v>
@@ -9997,7 +9997,7 @@
         <v>46203</v>
       </c>
       <c r="B189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D189" t="s">
         <v>55</v>
@@ -10029,7 +10029,7 @@
         <v>46203</v>
       </c>
       <c r="B190" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D190" t="s">
         <v>61</v>
@@ -10061,7 +10061,7 @@
         <v>46203</v>
       </c>
       <c r="B191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D191" t="s">
         <v>61</v>
@@ -10093,7 +10093,7 @@
         <v>46203</v>
       </c>
       <c r="B192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D192" t="s">
         <v>55</v>
@@ -10125,7 +10125,7 @@
         <v>46203</v>
       </c>
       <c r="B193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -10160,7 +10160,7 @@
         <v>46203</v>
       </c>
       <c r="B194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -10195,7 +10195,7 @@
         <v>46203</v>
       </c>
       <c r="B195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C195" t="s">
         <v>44</v>
@@ -10230,7 +10230,7 @@
         <v>46203</v>
       </c>
       <c r="B196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -10265,7 +10265,7 @@
         <v>46203</v>
       </c>
       <c r="B197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C197" t="s">
         <v>18</v>
@@ -10300,7 +10300,7 @@
         <v>46203</v>
       </c>
       <c r="B198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C198" t="s">
         <v>32</v>
@@ -10335,7 +10335,7 @@
         <v>46203</v>
       </c>
       <c r="B199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D199" t="s">
         <v>56</v>
@@ -10367,7 +10367,7 @@
         <v>46203</v>
       </c>
       <c r="B200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C200" t="s">
         <v>18</v>
@@ -10402,7 +10402,7 @@
         <v>46203</v>
       </c>
       <c r="B201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
@@ -10437,7 +10437,7 @@
         <v>46203</v>
       </c>
       <c r="B202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -10472,7 +10472,7 @@
         <v>46203</v>
       </c>
       <c r="B203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C203" t="s">
         <v>16</v>
@@ -10507,7 +10507,7 @@
         <v>46203</v>
       </c>
       <c r="B204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D204" t="s">
         <v>55</v>
@@ -10539,7 +10539,7 @@
         <v>46203</v>
       </c>
       <c r="B205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -10574,7 +10574,7 @@
         <v>46203</v>
       </c>
       <c r="B206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -10609,7 +10609,7 @@
         <v>46203</v>
       </c>
       <c r="B207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D207" t="s">
         <v>55</v>
@@ -10641,7 +10641,7 @@
         <v>46203</v>
       </c>
       <c r="B208" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
         <v>40</v>
@@ -10676,7 +10676,7 @@
         <v>46203</v>
       </c>
       <c r="B209" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -10711,7 +10711,7 @@
         <v>46203</v>
       </c>
       <c r="B210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
         <v>36</v>
@@ -10746,7 +10746,7 @@
         <v>46203</v>
       </c>
       <c r="B211" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D211" t="s">
         <v>56</v>
@@ -10778,7 +10778,7 @@
         <v>46203</v>
       </c>
       <c r="B212" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D212" t="s">
         <v>55</v>
@@ -10810,7 +10810,7 @@
         <v>46203</v>
       </c>
       <c r="B213" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D213" t="s">
         <v>61</v>
@@ -10842,7 +10842,7 @@
         <v>46203</v>
       </c>
       <c r="B214" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D214" t="s">
         <v>56</v>
@@ -10874,7 +10874,7 @@
         <v>46203</v>
       </c>
       <c r="B215" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D215" t="s">
         <v>56</v>
@@ -10906,7 +10906,7 @@
         <v>46203</v>
       </c>
       <c r="B216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D216" t="s">
         <v>57</v>
@@ -10938,7 +10938,7 @@
         <v>46203</v>
       </c>
       <c r="B217" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D217" t="s">
         <v>56</v>
@@ -10970,7 +10970,7 @@
         <v>46203</v>
       </c>
       <c r="B218" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D218" t="s">
         <v>55</v>
@@ -11002,7 +11002,7 @@
         <v>46203</v>
       </c>
       <c r="B219" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D219" t="s">
         <v>58</v>
@@ -11034,7 +11034,7 @@
         <v>46203</v>
       </c>
       <c r="B220" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -11069,7 +11069,7 @@
         <v>46203</v>
       </c>
       <c r="B221" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D221" t="s">
         <v>63</v>
@@ -11101,7 +11101,7 @@
         <v>46203</v>
       </c>
       <c r="B222" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D222" t="s">
         <v>55</v>
@@ -11133,7 +11133,7 @@
         <v>46203</v>
       </c>
       <c r="B223" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
         <v>35</v>
@@ -11168,7 +11168,7 @@
         <v>46203</v>
       </c>
       <c r="B224" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D224" t="s">
         <v>55</v>
@@ -11200,7 +11200,7 @@
         <v>46203</v>
       </c>
       <c r="B225" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D225" t="s">
         <v>55</v>
@@ -11232,7 +11232,7 @@
         <v>46203</v>
       </c>
       <c r="B226" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D226" t="s">
         <v>55</v>
@@ -11264,7 +11264,7 @@
         <v>46203</v>
       </c>
       <c r="B227" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C227" t="s">
         <v>30</v>
@@ -11299,7 +11299,7 @@
         <v>46203</v>
       </c>
       <c r="B228" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D228" t="s">
         <v>55</v>
@@ -11331,7 +11331,7 @@
         <v>46203</v>
       </c>
       <c r="B229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C229" t="s">
         <v>30</v>
@@ -11366,7 +11366,7 @@
         <v>46203</v>
       </c>
       <c r="B230" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C230" t="s">
         <v>38</v>
@@ -11401,7 +11401,7 @@
         <v>46203</v>
       </c>
       <c r="B231" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C231" t="s">
         <v>37</v>
@@ -11436,7 +11436,7 @@
         <v>46203</v>
       </c>
       <c r="B232" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D232" t="s">
         <v>56</v>
@@ -11468,7 +11468,7 @@
         <v>46203</v>
       </c>
       <c r="B233" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
         <v>24</v>
@@ -11503,7 +11503,7 @@
         <v>46203</v>
       </c>
       <c r="B234" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C234" t="s">
         <v>40</v>
@@ -11538,7 +11538,7 @@
         <v>46203</v>
       </c>
       <c r="B235" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C235" t="s">
         <v>40</v>
@@ -11573,7 +11573,7 @@
         <v>46203</v>
       </c>
       <c r="B236" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C236" t="s">
         <v>27</v>
@@ -11608,7 +11608,7 @@
         <v>46203</v>
       </c>
       <c r="B237" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
         <v>42</v>
@@ -11643,7 +11643,7 @@
         <v>46203</v>
       </c>
       <c r="B238" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C238" t="s">
         <v>16</v>
@@ -11678,7 +11678,7 @@
         <v>46203</v>
       </c>
       <c r="B239" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C239" t="s">
         <v>40</v>
@@ -11713,7 +11713,7 @@
         <v>46203</v>
       </c>
       <c r="B240" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C240" t="s">
         <v>46</v>
@@ -11748,7 +11748,7 @@
         <v>46203</v>
       </c>
       <c r="B241" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D241" t="s">
         <v>57</v>
@@ -11780,7 +11780,7 @@
         <v>46203</v>
       </c>
       <c r="B242" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
         <v>49</v>
@@ -11815,7 +11815,7 @@
         <v>46203</v>
       </c>
       <c r="B243" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -11850,7 +11850,7 @@
         <v>46203</v>
       </c>
       <c r="B244" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D244" t="s">
         <v>56</v>
@@ -11882,7 +11882,7 @@
         <v>46203</v>
       </c>
       <c r="B245" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D245" t="s">
         <v>56</v>
@@ -11914,7 +11914,7 @@
         <v>46203</v>
       </c>
       <c r="B246" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D246" t="s">
         <v>56</v>
@@ -11946,7 +11946,7 @@
         <v>46203</v>
       </c>
       <c r="B247" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D247" t="s">
         <v>56</v>
@@ -11978,7 +11978,7 @@
         <v>46203</v>
       </c>
       <c r="B248" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D248" t="s">
         <v>56</v>
@@ -12010,7 +12010,7 @@
         <v>46203</v>
       </c>
       <c r="B249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D249" t="s">
         <v>55</v>
@@ -12042,7 +12042,7 @@
         <v>46203</v>
       </c>
       <c r="B250" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D250" t="s">
         <v>56</v>
@@ -12074,7 +12074,7 @@
         <v>46203</v>
       </c>
       <c r="B251" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D251" t="s">
         <v>56</v>
@@ -12106,7 +12106,7 @@
         <v>46204</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C252" t="s">
         <v>52</v>
@@ -12141,7 +12141,7 @@
         <v>46204</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C253" t="s">
         <v>19</v>
@@ -12176,7 +12176,7 @@
         <v>46204</v>
       </c>
       <c r="B254" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -12211,7 +12211,7 @@
         <v>46204</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C255" t="s">
         <v>19</v>
@@ -12246,7 +12246,7 @@
         <v>46204</v>
       </c>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C256" t="s">
         <v>26</v>
@@ -12281,7 +12281,7 @@
         <v>46204</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C257" t="s">
         <v>35</v>
@@ -12316,7 +12316,7 @@
         <v>46204</v>
       </c>
       <c r="B258" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C258" t="s">
         <v>48</v>
@@ -12351,7 +12351,7 @@
         <v>46204</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C259" t="s">
         <v>40</v>
@@ -12386,7 +12386,7 @@
         <v>46204</v>
       </c>
       <c r="B260" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C260" t="s">
         <v>53</v>
@@ -12421,7 +12421,7 @@
         <v>46204</v>
       </c>
       <c r="B261" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D261" t="s">
         <v>58</v>
@@ -12453,7 +12453,7 @@
         <v>46204</v>
       </c>
       <c r="B262" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C262" t="s">
         <v>39</v>
@@ -12488,7 +12488,7 @@
         <v>46204</v>
       </c>
       <c r="B263" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C263" t="s">
         <v>29</v>
@@ -12523,7 +12523,7 @@
         <v>46204</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D264" t="s">
         <v>58</v>
@@ -12555,7 +12555,7 @@
         <v>46204</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C265" t="s">
         <v>18</v>
@@ -12590,7 +12590,7 @@
         <v>46204</v>
       </c>
       <c r="B266" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C266" t="s">
         <v>32</v>
@@ -12625,7 +12625,7 @@
         <v>46204</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C267" t="s">
         <v>16</v>
@@ -12660,7 +12660,7 @@
         <v>46204</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C268" t="s">
         <v>33</v>
@@ -12695,7 +12695,7 @@
         <v>46204</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D269" t="s">
         <v>55</v>
@@ -12727,7 +12727,7 @@
         <v>46204</v>
       </c>
       <c r="B270" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D270" t="s">
         <v>55</v>
@@ -12759,7 +12759,7 @@
         <v>46204</v>
       </c>
       <c r="B271" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D271" t="s">
         <v>55</v>
@@ -12791,7 +12791,7 @@
         <v>46204</v>
       </c>
       <c r="B272" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D272" t="s">
         <v>56</v>
@@ -12823,7 +12823,7 @@
         <v>46204</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C273" t="s">
         <v>27</v>
@@ -12858,7 +12858,7 @@
         <v>46204</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D274" t="s">
         <v>56</v>
@@ -12890,7 +12890,7 @@
         <v>46204</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D275" t="s">
         <v>56</v>
@@ -12922,7 +12922,7 @@
         <v>46204</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C276" t="s">
         <v>25</v>
@@ -12957,7 +12957,7 @@
         <v>46204</v>
       </c>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C277" t="s">
         <v>49</v>
@@ -12992,7 +12992,7 @@
         <v>46204</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D278" t="s">
         <v>56</v>
@@ -13024,7 +13024,7 @@
         <v>46204</v>
       </c>
       <c r="B279" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D279" t="s">
         <v>56</v>
@@ -13056,7 +13056,7 @@
         <v>46204</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D280" t="s">
         <v>56</v>
@@ -13088,7 +13088,7 @@
         <v>46204</v>
       </c>
       <c r="B281" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C281" t="s">
         <v>40</v>
@@ -13123,7 +13123,7 @@
         <v>46204</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D282" t="s">
         <v>55</v>
@@ -13155,7 +13155,7 @@
         <v>46204</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C283" t="s">
         <v>38</v>
@@ -13190,7 +13190,7 @@
         <v>46204</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C284" t="s">
         <v>36</v>
@@ -13225,7 +13225,7 @@
         <v>46204</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C285" t="s">
         <v>45</v>
@@ -13260,7 +13260,7 @@
         <v>46204</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C286" t="s">
         <v>40</v>
@@ -13295,7 +13295,7 @@
         <v>46204</v>
       </c>
       <c r="B287" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -13330,7 +13330,7 @@
         <v>46204</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C288" t="s">
         <v>40</v>
@@ -13365,7 +13365,7 @@
         <v>46204</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C289" t="s">
         <v>29</v>
@@ -13400,7 +13400,7 @@
         <v>46204</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C290" t="s">
         <v>23</v>
@@ -13435,7 +13435,7 @@
         <v>46204</v>
       </c>
       <c r="B291" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C291" t="s">
         <v>43</v>
@@ -13470,7 +13470,7 @@
         <v>46204</v>
       </c>
       <c r="B292" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C292" t="s">
         <v>53</v>
@@ -13505,7 +13505,7 @@
         <v>46204</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D293" t="s">
         <v>58</v>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8022,7 +8022,7 @@
         <v>46202</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
         <v>46</v>
@@ -8057,7 +8057,7 @@
         <v>46202</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D131" t="s">
         <v>63</v>
@@ -8089,7 +8089,7 @@
         <v>46202</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132" t="s">
         <v>56</v>
@@ -8121,7 +8121,7 @@
         <v>46202</v>
       </c>
       <c r="B133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D133" t="s">
         <v>58</v>
@@ -8153,7 +8153,7 @@
         <v>46202</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
         <v>29</v>
@@ -8188,7 +8188,7 @@
         <v>46202</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D135" t="s">
         <v>58</v>
@@ -8220,7 +8220,7 @@
         <v>46202</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>47</v>
@@ -8255,7 +8255,7 @@
         <v>46202</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>36</v>
@@ -8290,7 +8290,7 @@
         <v>46202</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>48</v>
@@ -8325,7 +8325,7 @@
         <v>46202</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
         <v>16</v>
@@ -8360,7 +8360,7 @@
         <v>46202</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>27</v>
@@ -8395,7 +8395,7 @@
         <v>46202</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>37</v>
@@ -8430,7 +8430,7 @@
         <v>46202</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
         <v>33</v>
@@ -8465,7 +8465,7 @@
         <v>46202</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
         <v>49</v>
@@ -8500,7 +8500,7 @@
         <v>46202</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -8535,7 +8535,7 @@
         <v>46202</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D145" t="s">
         <v>55</v>
@@ -8567,7 +8567,7 @@
         <v>46202</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>32</v>
@@ -8602,7 +8602,7 @@
         <v>46202</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
         <v>40</v>
@@ -8637,7 +8637,7 @@
         <v>46202</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
         <v>25</v>
@@ -8672,7 +8672,7 @@
         <v>46202</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C149" t="s">
         <v>38</v>
@@ -8707,7 +8707,7 @@
         <v>46202</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D150" t="s">
         <v>55</v>
@@ -8739,7 +8739,7 @@
         <v>46202</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D151" t="s">
         <v>55</v>
@@ -8771,7 +8771,7 @@
         <v>46202</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C152" t="s">
         <v>26</v>
@@ -8806,7 +8806,7 @@
         <v>46202</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C153" t="s">
         <v>48</v>
@@ -8841,7 +8841,7 @@
         <v>46202</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D154" t="s">
         <v>56</v>
@@ -8873,7 +8873,7 @@
         <v>46202</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D155" t="s">
         <v>62</v>
@@ -8905,7 +8905,7 @@
         <v>46202</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D156" t="s">
         <v>56</v>
@@ -8937,7 +8937,7 @@
         <v>46202</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D157" t="s">
         <v>57</v>
@@ -8969,7 +8969,7 @@
         <v>46202</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
@@ -9004,7 +9004,7 @@
         <v>46202</v>
       </c>
       <c r="B159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D159" t="s">
         <v>55</v>
@@ -9036,7 +9036,7 @@
         <v>46202</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D160" t="s">
         <v>55</v>
@@ -9068,7 +9068,7 @@
         <v>46202</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D161" t="s">
         <v>56</v>
@@ -9100,7 +9100,7 @@
         <v>46202</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
         <v>18</v>
@@ -9135,7 +9135,7 @@
         <v>46202</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D163" t="s">
         <v>58</v>
@@ -9167,7 +9167,7 @@
         <v>46203</v>
       </c>
       <c r="B164" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D164" t="s">
         <v>56</v>
@@ -9199,7 +9199,7 @@
         <v>46203</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D165" t="s">
         <v>56</v>
@@ -9231,7 +9231,7 @@
         <v>46203</v>
       </c>
       <c r="B166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D166" t="s">
         <v>56</v>
@@ -9263,7 +9263,7 @@
         <v>46203</v>
       </c>
       <c r="B167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D167" t="s">
         <v>56</v>
@@ -9295,7 +9295,7 @@
         <v>46203</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C168" t="s">
         <v>32</v>
@@ -9330,7 +9330,7 @@
         <v>46203</v>
       </c>
       <c r="B169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C169" t="s">
         <v>29</v>
@@ -9365,7 +9365,7 @@
         <v>46203</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C170" t="s">
         <v>26</v>
@@ -9400,7 +9400,7 @@
         <v>46203</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171" t="s">
         <v>55</v>
@@ -9432,7 +9432,7 @@
         <v>46203</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C172" t="s">
         <v>23</v>
@@ -9467,7 +9467,7 @@
         <v>46203</v>
       </c>
       <c r="B173" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C173" t="s">
         <v>38</v>
@@ -9502,7 +9502,7 @@
         <v>46203</v>
       </c>
       <c r="B174" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C174" t="s">
         <v>21</v>
@@ -9537,7 +9537,7 @@
         <v>46203</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D175" t="s">
         <v>56</v>
@@ -9569,7 +9569,7 @@
         <v>46203</v>
       </c>
       <c r="B176" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D176" t="s">
         <v>58</v>
@@ -9601,7 +9601,7 @@
         <v>46203</v>
       </c>
       <c r="B177" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D177" t="s">
         <v>58</v>
@@ -9633,7 +9633,7 @@
         <v>46203</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C178" t="s">
         <v>46</v>
@@ -9668,7 +9668,7 @@
         <v>46203</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D179" t="s">
         <v>55</v>
@@ -9700,7 +9700,7 @@
         <v>46203</v>
       </c>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D180" t="s">
         <v>58</v>
@@ -9732,7 +9732,7 @@
         <v>46203</v>
       </c>
       <c r="B181" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D181" t="s">
         <v>56</v>
@@ -9764,7 +9764,7 @@
         <v>46203</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C182" t="s">
         <v>45</v>
@@ -9799,7 +9799,7 @@
         <v>46203</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
         <v>55</v>
@@ -9831,7 +9831,7 @@
         <v>46203</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D184" t="s">
         <v>55</v>
@@ -9863,7 +9863,7 @@
         <v>46203</v>
       </c>
       <c r="B185" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
@@ -9898,7 +9898,7 @@
         <v>46203</v>
       </c>
       <c r="B186" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -9930,7 +9930,7 @@
         <v>46203</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D187" t="s">
         <v>58</v>
@@ -9962,7 +9962,7 @@
         <v>46203</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
         <v>51</v>
@@ -9997,7 +9997,7 @@
         <v>46203</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D189" t="s">
         <v>55</v>
@@ -10029,7 +10029,7 @@
         <v>46203</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D190" t="s">
         <v>61</v>
@@ -10061,7 +10061,7 @@
         <v>46203</v>
       </c>
       <c r="B191" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D191" t="s">
         <v>61</v>
@@ -10093,7 +10093,7 @@
         <v>46203</v>
       </c>
       <c r="B192" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D192" t="s">
         <v>55</v>
@@ -10125,7 +10125,7 @@
         <v>46203</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -10160,7 +10160,7 @@
         <v>46203</v>
       </c>
       <c r="B194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -10195,7 +10195,7 @@
         <v>46203</v>
       </c>
       <c r="B195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C195" t="s">
         <v>44</v>
@@ -10230,7 +10230,7 @@
         <v>46203</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -10265,7 +10265,7 @@
         <v>46203</v>
       </c>
       <c r="B197" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C197" t="s">
         <v>18</v>
@@ -10300,7 +10300,7 @@
         <v>46203</v>
       </c>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C198" t="s">
         <v>32</v>
@@ -10335,7 +10335,7 @@
         <v>46203</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D199" t="s">
         <v>56</v>
@@ -10367,7 +10367,7 @@
         <v>46203</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C200" t="s">
         <v>18</v>
@@ -10402,7 +10402,7 @@
         <v>46203</v>
       </c>
       <c r="B201" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
@@ -10437,7 +10437,7 @@
         <v>46203</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -10472,7 +10472,7 @@
         <v>46203</v>
       </c>
       <c r="B203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C203" t="s">
         <v>16</v>
@@ -10507,7 +10507,7 @@
         <v>46203</v>
       </c>
       <c r="B204" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D204" t="s">
         <v>55</v>
@@ -10539,7 +10539,7 @@
         <v>46203</v>
       </c>
       <c r="B205" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -10574,7 +10574,7 @@
         <v>46203</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -10609,7 +10609,7 @@
         <v>46203</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D207" t="s">
         <v>55</v>
@@ -10641,7 +10641,7 @@
         <v>46203</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C208" t="s">
         <v>40</v>
@@ -10676,7 +10676,7 @@
         <v>46203</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -10711,7 +10711,7 @@
         <v>46203</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C210" t="s">
         <v>36</v>
@@ -10746,7 +10746,7 @@
         <v>46203</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D211" t="s">
         <v>56</v>
@@ -10778,7 +10778,7 @@
         <v>46203</v>
       </c>
       <c r="B212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D212" t="s">
         <v>55</v>
@@ -10810,7 +10810,7 @@
         <v>46203</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D213" t="s">
         <v>61</v>
@@ -10842,7 +10842,7 @@
         <v>46203</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D214" t="s">
         <v>56</v>
@@ -10874,7 +10874,7 @@
         <v>46203</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D215" t="s">
         <v>56</v>
@@ -10906,7 +10906,7 @@
         <v>46203</v>
       </c>
       <c r="B216" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D216" t="s">
         <v>57</v>
@@ -10938,7 +10938,7 @@
         <v>46203</v>
       </c>
       <c r="B217" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D217" t="s">
         <v>56</v>
@@ -10970,7 +10970,7 @@
         <v>46203</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D218" t="s">
         <v>55</v>
@@ -11002,7 +11002,7 @@
         <v>46203</v>
       </c>
       <c r="B219" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D219" t="s">
         <v>58</v>
@@ -11034,7 +11034,7 @@
         <v>46203</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -11069,7 +11069,7 @@
         <v>46203</v>
       </c>
       <c r="B221" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D221" t="s">
         <v>63</v>
@@ -11101,7 +11101,7 @@
         <v>46203</v>
       </c>
       <c r="B222" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D222" t="s">
         <v>55</v>
@@ -11133,7 +11133,7 @@
         <v>46203</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C223" t="s">
         <v>35</v>
@@ -11168,7 +11168,7 @@
         <v>46203</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D224" t="s">
         <v>55</v>
@@ -11200,7 +11200,7 @@
         <v>46203</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D225" t="s">
         <v>55</v>
@@ -11232,7 +11232,7 @@
         <v>46203</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D226" t="s">
         <v>55</v>
@@ -11264,7 +11264,7 @@
         <v>46203</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C227" t="s">
         <v>30</v>
@@ -11299,7 +11299,7 @@
         <v>46203</v>
       </c>
       <c r="B228" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D228" t="s">
         <v>55</v>
@@ -11331,7 +11331,7 @@
         <v>46203</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C229" t="s">
         <v>30</v>
@@ -11366,7 +11366,7 @@
         <v>46203</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C230" t="s">
         <v>38</v>
@@ -11401,7 +11401,7 @@
         <v>46203</v>
       </c>
       <c r="B231" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C231" t="s">
         <v>37</v>
@@ -11436,7 +11436,7 @@
         <v>46203</v>
       </c>
       <c r="B232" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D232" t="s">
         <v>56</v>
@@ -11468,7 +11468,7 @@
         <v>46203</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C233" t="s">
         <v>24</v>
@@ -11503,7 +11503,7 @@
         <v>46203</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C234" t="s">
         <v>40</v>
@@ -11538,7 +11538,7 @@
         <v>46203</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C235" t="s">
         <v>40</v>
@@ -11573,7 +11573,7 @@
         <v>46203</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C236" t="s">
         <v>27</v>
@@ -11608,7 +11608,7 @@
         <v>46203</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C237" t="s">
         <v>42</v>
@@ -11643,7 +11643,7 @@
         <v>46203</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C238" t="s">
         <v>16</v>
@@ -11678,7 +11678,7 @@
         <v>46203</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C239" t="s">
         <v>40</v>
@@ -11713,7 +11713,7 @@
         <v>46203</v>
       </c>
       <c r="B240" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C240" t="s">
         <v>46</v>
@@ -11748,7 +11748,7 @@
         <v>46203</v>
       </c>
       <c r="B241" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D241" t="s">
         <v>57</v>
@@ -11780,7 +11780,7 @@
         <v>46203</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C242" t="s">
         <v>49</v>
@@ -11815,7 +11815,7 @@
         <v>46203</v>
       </c>
       <c r="B243" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -11850,7 +11850,7 @@
         <v>46203</v>
       </c>
       <c r="B244" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D244" t="s">
         <v>56</v>
@@ -11882,7 +11882,7 @@
         <v>46203</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D245" t="s">
         <v>56</v>
@@ -11914,7 +11914,7 @@
         <v>46203</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D246" t="s">
         <v>56</v>
@@ -11946,7 +11946,7 @@
         <v>46203</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D247" t="s">
         <v>56</v>
@@ -11978,7 +11978,7 @@
         <v>46203</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D248" t="s">
         <v>56</v>
@@ -12010,7 +12010,7 @@
         <v>46203</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D249" t="s">
         <v>55</v>
@@ -12042,7 +12042,7 @@
         <v>46203</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D250" t="s">
         <v>56</v>
@@ -12074,7 +12074,7 @@
         <v>46203</v>
       </c>
       <c r="B251" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D251" t="s">
         <v>56</v>
@@ -12106,7 +12106,7 @@
         <v>46204</v>
       </c>
       <c r="B252" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C252" t="s">
         <v>52</v>
@@ -12141,7 +12141,7 @@
         <v>46204</v>
       </c>
       <c r="B253" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C253" t="s">
         <v>19</v>
@@ -12176,7 +12176,7 @@
         <v>46204</v>
       </c>
       <c r="B254" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -12211,7 +12211,7 @@
         <v>46204</v>
       </c>
       <c r="B255" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C255" t="s">
         <v>19</v>
@@ -12246,7 +12246,7 @@
         <v>46204</v>
       </c>
       <c r="B256" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C256" t="s">
         <v>26</v>
@@ -12281,7 +12281,7 @@
         <v>46204</v>
       </c>
       <c r="B257" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C257" t="s">
         <v>35</v>
@@ -12316,7 +12316,7 @@
         <v>46204</v>
       </c>
       <c r="B258" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C258" t="s">
         <v>48</v>
@@ -12351,7 +12351,7 @@
         <v>46204</v>
       </c>
       <c r="B259" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C259" t="s">
         <v>40</v>
@@ -12386,7 +12386,7 @@
         <v>46204</v>
       </c>
       <c r="B260" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C260" t="s">
         <v>53</v>
@@ -12421,7 +12421,7 @@
         <v>46204</v>
       </c>
       <c r="B261" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D261" t="s">
         <v>58</v>
@@ -12453,7 +12453,7 @@
         <v>46204</v>
       </c>
       <c r="B262" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C262" t="s">
         <v>39</v>
@@ -12488,7 +12488,7 @@
         <v>46204</v>
       </c>
       <c r="B263" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C263" t="s">
         <v>29</v>
@@ -12523,7 +12523,7 @@
         <v>46204</v>
       </c>
       <c r="B264" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D264" t="s">
         <v>58</v>
@@ -12555,7 +12555,7 @@
         <v>46204</v>
       </c>
       <c r="B265" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
         <v>18</v>
@@ -12590,7 +12590,7 @@
         <v>46204</v>
       </c>
       <c r="B266" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
         <v>32</v>
@@ -12625,7 +12625,7 @@
         <v>46204</v>
       </c>
       <c r="B267" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C267" t="s">
         <v>16</v>
@@ -12660,7 +12660,7 @@
         <v>46204</v>
       </c>
       <c r="B268" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
         <v>33</v>
@@ -12695,7 +12695,7 @@
         <v>46204</v>
       </c>
       <c r="B269" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D269" t="s">
         <v>55</v>
@@ -12727,7 +12727,7 @@
         <v>46204</v>
       </c>
       <c r="B270" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D270" t="s">
         <v>55</v>
@@ -12759,7 +12759,7 @@
         <v>46204</v>
       </c>
       <c r="B271" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D271" t="s">
         <v>55</v>
@@ -12791,7 +12791,7 @@
         <v>46204</v>
       </c>
       <c r="B272" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D272" t="s">
         <v>56</v>
@@ -12823,7 +12823,7 @@
         <v>46204</v>
       </c>
       <c r="B273" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
         <v>27</v>
@@ -12858,7 +12858,7 @@
         <v>46204</v>
       </c>
       <c r="B274" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D274" t="s">
         <v>56</v>
@@ -12890,7 +12890,7 @@
         <v>46204</v>
       </c>
       <c r="B275" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D275" t="s">
         <v>56</v>
@@ -12922,7 +12922,7 @@
         <v>46204</v>
       </c>
       <c r="B276" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C276" t="s">
         <v>25</v>
@@ -12957,7 +12957,7 @@
         <v>46204</v>
       </c>
       <c r="B277" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
         <v>49</v>
@@ -12992,7 +12992,7 @@
         <v>46204</v>
       </c>
       <c r="B278" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D278" t="s">
         <v>56</v>
@@ -13024,7 +13024,7 @@
         <v>46204</v>
       </c>
       <c r="B279" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D279" t="s">
         <v>56</v>
@@ -13056,7 +13056,7 @@
         <v>46204</v>
       </c>
       <c r="B280" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D280" t="s">
         <v>56</v>
@@ -13088,7 +13088,7 @@
         <v>46204</v>
       </c>
       <c r="B281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C281" t="s">
         <v>40</v>
@@ -13123,7 +13123,7 @@
         <v>46204</v>
       </c>
       <c r="B282" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D282" t="s">
         <v>55</v>
@@ -13155,7 +13155,7 @@
         <v>46204</v>
       </c>
       <c r="B283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
         <v>38</v>
@@ -13190,7 +13190,7 @@
         <v>46204</v>
       </c>
       <c r="B284" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
         <v>36</v>
@@ -13225,7 +13225,7 @@
         <v>46204</v>
       </c>
       <c r="B285" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
         <v>45</v>
@@ -13260,7 +13260,7 @@
         <v>46204</v>
       </c>
       <c r="B286" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
         <v>40</v>
@@ -13295,7 +13295,7 @@
         <v>46204</v>
       </c>
       <c r="B287" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -13330,7 +13330,7 @@
         <v>46204</v>
       </c>
       <c r="B288" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
         <v>40</v>
@@ -13365,7 +13365,7 @@
         <v>46204</v>
       </c>
       <c r="B289" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
         <v>29</v>
@@ -13400,7 +13400,7 @@
         <v>46204</v>
       </c>
       <c r="B290" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C290" t="s">
         <v>23</v>
@@ -13435,7 +13435,7 @@
         <v>46204</v>
       </c>
       <c r="B291" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
         <v>43</v>
@@ -13470,7 +13470,7 @@
         <v>46204</v>
       </c>
       <c r="B292" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
         <v>53</v>
@@ -13505,7 +13505,7 @@
         <v>46204</v>
       </c>
       <c r="B293" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D293" t="s">
         <v>58</v>
@@ -13537,7 +13537,7 @@
         <v>46205</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D294" t="s">
         <v>56</v>
@@ -13569,7 +13569,7 @@
         <v>46205</v>
       </c>
       <c r="B295" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D295" t="s">
         <v>56</v>
@@ -13601,7 +13601,7 @@
         <v>46205</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D296" t="s">
         <v>56</v>
@@ -13633,7 +13633,7 @@
         <v>46205</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D297" t="s">
         <v>56</v>
@@ -13665,7 +13665,7 @@
         <v>46205</v>
       </c>
       <c r="B298" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C298" t="s">
         <v>44</v>
@@ -13700,7 +13700,7 @@
         <v>46205</v>
       </c>
       <c r="B299" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C299" t="s">
         <v>26</v>
@@ -13735,7 +13735,7 @@
         <v>46205</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C300" t="s">
         <v>43</v>
@@ -13770,7 +13770,7 @@
         <v>46205</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C301" t="s">
         <v>18</v>
@@ -13805,7 +13805,7 @@
         <v>46205</v>
       </c>
       <c r="B302" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D302" t="s">
         <v>55</v>
@@ -13837,7 +13837,7 @@
         <v>46205</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C303" t="s">
         <v>53</v>
@@ -13872,7 +13872,7 @@
         <v>46205</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C304" t="s">
         <v>23</v>
@@ -13907,7 +13907,7 @@
         <v>46205</v>
       </c>
       <c r="B305" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D305" t="s">
         <v>55</v>
@@ -13939,7 +13939,7 @@
         <v>46205</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C306" t="s">
         <v>52</v>
@@ -13974,7 +13974,7 @@
         <v>46205</v>
       </c>
       <c r="B307" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C307" t="s">
         <v>29</v>
@@ -14009,7 +14009,7 @@
         <v>46205</v>
       </c>
       <c r="B308" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D308" t="s">
         <v>56</v>
@@ -14041,7 +14041,7 @@
         <v>46205</v>
       </c>
       <c r="B309" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C309" t="s">
         <v>40</v>
@@ -14076,7 +14076,7 @@
         <v>46205</v>
       </c>
       <c r="B310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D310" t="s">
         <v>55</v>
@@ -14108,7 +14108,7 @@
         <v>46205</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C311" t="s">
         <v>40</v>
@@ -14143,7 +14143,7 @@
         <v>46205</v>
       </c>
       <c r="B312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D312" t="s">
         <v>56</v>
@@ -14175,7 +14175,7 @@
         <v>46205</v>
       </c>
       <c r="B313" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C313" t="s">
         <v>40</v>
@@ -14210,7 +14210,7 @@
         <v>46205</v>
       </c>
       <c r="B314" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C314" t="s">
         <v>40</v>
@@ -14245,7 +14245,7 @@
         <v>46205</v>
       </c>
       <c r="B315" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C315" t="s">
         <v>24</v>
@@ -14280,7 +14280,7 @@
         <v>46205</v>
       </c>
       <c r="B316" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C316" t="s">
         <v>48</v>
@@ -14315,7 +14315,7 @@
         <v>46205</v>
       </c>
       <c r="B317" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C317" t="s">
         <v>27</v>
@@ -14350,7 +14350,7 @@
         <v>46205</v>
       </c>
       <c r="B318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C318" t="s">
         <v>30</v>
@@ -14385,7 +14385,7 @@
         <v>46205</v>
       </c>
       <c r="B319" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -14420,7 +14420,7 @@
         <v>46205</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D320" t="s">
         <v>55</v>
@@ -14452,7 +14452,7 @@
         <v>46205</v>
       </c>
       <c r="B321" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D321" t="s">
         <v>56</v>
@@ -14484,7 +14484,7 @@
         <v>46205</v>
       </c>
       <c r="B322" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C322" t="s">
         <v>47</v>
@@ -14519,7 +14519,7 @@
         <v>46205</v>
       </c>
       <c r="B323" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C323" t="s">
         <v>54</v>
@@ -14554,7 +14554,7 @@
         <v>46205</v>
       </c>
       <c r="B324" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C324" t="s">
         <v>51</v>
@@ -14589,7 +14589,7 @@
         <v>46205</v>
       </c>
       <c r="B325" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C325" t="s">
         <v>54</v>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -9167,7 +9167,7 @@
         <v>46203</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D164" t="s">
         <v>56</v>
@@ -9199,7 +9199,7 @@
         <v>46203</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D165" t="s">
         <v>56</v>
@@ -9231,7 +9231,7 @@
         <v>46203</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D166" t="s">
         <v>56</v>
@@ -9263,7 +9263,7 @@
         <v>46203</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D167" t="s">
         <v>56</v>
@@ -9295,7 +9295,7 @@
         <v>46203</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
         <v>32</v>
@@ -9330,7 +9330,7 @@
         <v>46203</v>
       </c>
       <c r="B169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
         <v>29</v>
@@ -9365,7 +9365,7 @@
         <v>46203</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
         <v>26</v>
@@ -9400,7 +9400,7 @@
         <v>46203</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D171" t="s">
         <v>55</v>
@@ -9432,7 +9432,7 @@
         <v>46203</v>
       </c>
       <c r="B172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
         <v>23</v>
@@ -9467,7 +9467,7 @@
         <v>46203</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
         <v>38</v>
@@ -9502,7 +9502,7 @@
         <v>46203</v>
       </c>
       <c r="B174" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
         <v>21</v>
@@ -9537,7 +9537,7 @@
         <v>46203</v>
       </c>
       <c r="B175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D175" t="s">
         <v>56</v>
@@ -9569,7 +9569,7 @@
         <v>46203</v>
       </c>
       <c r="B176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D176" t="s">
         <v>58</v>
@@ -9601,7 +9601,7 @@
         <v>46203</v>
       </c>
       <c r="B177" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D177" t="s">
         <v>58</v>
@@ -9633,7 +9633,7 @@
         <v>46203</v>
       </c>
       <c r="B178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
         <v>46</v>
@@ -9668,7 +9668,7 @@
         <v>46203</v>
       </c>
       <c r="B179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D179" t="s">
         <v>55</v>
@@ -9700,7 +9700,7 @@
         <v>46203</v>
       </c>
       <c r="B180" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D180" t="s">
         <v>58</v>
@@ -9732,7 +9732,7 @@
         <v>46203</v>
       </c>
       <c r="B181" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D181" t="s">
         <v>56</v>
@@ -9764,7 +9764,7 @@
         <v>46203</v>
       </c>
       <c r="B182" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C182" t="s">
         <v>45</v>
@@ -9799,7 +9799,7 @@
         <v>46203</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D183" t="s">
         <v>55</v>
@@ -9831,7 +9831,7 @@
         <v>46203</v>
       </c>
       <c r="B184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D184" t="s">
         <v>55</v>
@@ -9863,7 +9863,7 @@
         <v>46203</v>
       </c>
       <c r="B185" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C185" t="s">
         <v>50</v>
@@ -9898,7 +9898,7 @@
         <v>46203</v>
       </c>
       <c r="B186" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -9930,7 +9930,7 @@
         <v>46203</v>
       </c>
       <c r="B187" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D187" t="s">
         <v>58</v>
@@ -9962,7 +9962,7 @@
         <v>46203</v>
       </c>
       <c r="B188" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C188" t="s">
         <v>51</v>
@@ -9997,7 +9997,7 @@
         <v>46203</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D189" t="s">
         <v>55</v>
@@ -10029,7 +10029,7 @@
         <v>46203</v>
       </c>
       <c r="B190" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D190" t="s">
         <v>61</v>
@@ -10061,7 +10061,7 @@
         <v>46203</v>
       </c>
       <c r="B191" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D191" t="s">
         <v>61</v>
@@ -10093,7 +10093,7 @@
         <v>46203</v>
       </c>
       <c r="B192" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D192" t="s">
         <v>55</v>
@@ -10125,7 +10125,7 @@
         <v>46203</v>
       </c>
       <c r="B193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -10160,7 +10160,7 @@
         <v>46203</v>
       </c>
       <c r="B194" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -10195,7 +10195,7 @@
         <v>46203</v>
       </c>
       <c r="B195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C195" t="s">
         <v>44</v>
@@ -10230,7 +10230,7 @@
         <v>46203</v>
       </c>
       <c r="B196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -10265,7 +10265,7 @@
         <v>46203</v>
       </c>
       <c r="B197" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C197" t="s">
         <v>18</v>
@@ -10300,7 +10300,7 @@
         <v>46203</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C198" t="s">
         <v>32</v>
@@ -10335,7 +10335,7 @@
         <v>46203</v>
       </c>
       <c r="B199" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D199" t="s">
         <v>56</v>
@@ -10367,7 +10367,7 @@
         <v>46203</v>
       </c>
       <c r="B200" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C200" t="s">
         <v>18</v>
@@ -10402,7 +10402,7 @@
         <v>46203</v>
       </c>
       <c r="B201" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C201" t="s">
         <v>50</v>
@@ -10437,7 +10437,7 @@
         <v>46203</v>
       </c>
       <c r="B202" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -10472,7 +10472,7 @@
         <v>46203</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C203" t="s">
         <v>16</v>
@@ -10507,7 +10507,7 @@
         <v>46203</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D204" t="s">
         <v>55</v>
@@ -10539,7 +10539,7 @@
         <v>46203</v>
       </c>
       <c r="B205" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -10574,7 +10574,7 @@
         <v>46203</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -10609,7 +10609,7 @@
         <v>46203</v>
       </c>
       <c r="B207" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D207" t="s">
         <v>55</v>
@@ -10641,7 +10641,7 @@
         <v>46203</v>
       </c>
       <c r="B208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C208" t="s">
         <v>40</v>
@@ -10676,7 +10676,7 @@
         <v>46203</v>
       </c>
       <c r="B209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -10711,7 +10711,7 @@
         <v>46203</v>
       </c>
       <c r="B210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C210" t="s">
         <v>36</v>
@@ -10746,7 +10746,7 @@
         <v>46203</v>
       </c>
       <c r="B211" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D211" t="s">
         <v>56</v>
@@ -10778,7 +10778,7 @@
         <v>46203</v>
       </c>
       <c r="B212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D212" t="s">
         <v>55</v>
@@ -10810,7 +10810,7 @@
         <v>46203</v>
       </c>
       <c r="B213" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D213" t="s">
         <v>61</v>
@@ -10842,7 +10842,7 @@
         <v>46203</v>
       </c>
       <c r="B214" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D214" t="s">
         <v>56</v>
@@ -10874,7 +10874,7 @@
         <v>46203</v>
       </c>
       <c r="B215" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D215" t="s">
         <v>56</v>
@@ -10906,7 +10906,7 @@
         <v>46203</v>
       </c>
       <c r="B216" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D216" t="s">
         <v>57</v>
@@ -10938,7 +10938,7 @@
         <v>46203</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D217" t="s">
         <v>56</v>
@@ -10970,7 +10970,7 @@
         <v>46203</v>
       </c>
       <c r="B218" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D218" t="s">
         <v>55</v>
@@ -11002,7 +11002,7 @@
         <v>46203</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D219" t="s">
         <v>58</v>
@@ -11034,7 +11034,7 @@
         <v>46203</v>
       </c>
       <c r="B220" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -11069,7 +11069,7 @@
         <v>46203</v>
       </c>
       <c r="B221" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D221" t="s">
         <v>63</v>
@@ -11101,7 +11101,7 @@
         <v>46203</v>
       </c>
       <c r="B222" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D222" t="s">
         <v>55</v>
@@ -11133,7 +11133,7 @@
         <v>46203</v>
       </c>
       <c r="B223" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C223" t="s">
         <v>35</v>
@@ -11168,7 +11168,7 @@
         <v>46203</v>
       </c>
       <c r="B224" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D224" t="s">
         <v>55</v>
@@ -11200,7 +11200,7 @@
         <v>46203</v>
       </c>
       <c r="B225" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D225" t="s">
         <v>55</v>
@@ -11232,7 +11232,7 @@
         <v>46203</v>
       </c>
       <c r="B226" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D226" t="s">
         <v>55</v>
@@ -11264,7 +11264,7 @@
         <v>46203</v>
       </c>
       <c r="B227" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C227" t="s">
         <v>30</v>
@@ -11299,7 +11299,7 @@
         <v>46203</v>
       </c>
       <c r="B228" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D228" t="s">
         <v>55</v>
@@ -11331,7 +11331,7 @@
         <v>46203</v>
       </c>
       <c r="B229" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C229" t="s">
         <v>30</v>
@@ -11366,7 +11366,7 @@
         <v>46203</v>
       </c>
       <c r="B230" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C230" t="s">
         <v>38</v>
@@ -11401,7 +11401,7 @@
         <v>46203</v>
       </c>
       <c r="B231" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C231" t="s">
         <v>37</v>
@@ -11436,7 +11436,7 @@
         <v>46203</v>
       </c>
       <c r="B232" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D232" t="s">
         <v>56</v>
@@ -11468,7 +11468,7 @@
         <v>46203</v>
       </c>
       <c r="B233" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C233" t="s">
         <v>24</v>
@@ -11503,7 +11503,7 @@
         <v>46203</v>
       </c>
       <c r="B234" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C234" t="s">
         <v>40</v>
@@ -11538,7 +11538,7 @@
         <v>46203</v>
       </c>
       <c r="B235" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C235" t="s">
         <v>40</v>
@@ -11573,7 +11573,7 @@
         <v>46203</v>
       </c>
       <c r="B236" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C236" t="s">
         <v>27</v>
@@ -11608,7 +11608,7 @@
         <v>46203</v>
       </c>
       <c r="B237" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C237" t="s">
         <v>42</v>
@@ -11643,7 +11643,7 @@
         <v>46203</v>
       </c>
       <c r="B238" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C238" t="s">
         <v>16</v>
@@ -11678,7 +11678,7 @@
         <v>46203</v>
       </c>
       <c r="B239" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C239" t="s">
         <v>40</v>
@@ -11713,7 +11713,7 @@
         <v>46203</v>
       </c>
       <c r="B240" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C240" t="s">
         <v>46</v>
@@ -11748,7 +11748,7 @@
         <v>46203</v>
       </c>
       <c r="B241" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D241" t="s">
         <v>57</v>
@@ -11780,7 +11780,7 @@
         <v>46203</v>
       </c>
       <c r="B242" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C242" t="s">
         <v>49</v>
@@ -11815,7 +11815,7 @@
         <v>46203</v>
       </c>
       <c r="B243" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -11850,7 +11850,7 @@
         <v>46203</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D244" t="s">
         <v>56</v>
@@ -11882,7 +11882,7 @@
         <v>46203</v>
       </c>
       <c r="B245" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D245" t="s">
         <v>56</v>
@@ -11914,7 +11914,7 @@
         <v>46203</v>
       </c>
       <c r="B246" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D246" t="s">
         <v>56</v>
@@ -11946,7 +11946,7 @@
         <v>46203</v>
       </c>
       <c r="B247" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D247" t="s">
         <v>56</v>
@@ -11978,7 +11978,7 @@
         <v>46203</v>
       </c>
       <c r="B248" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D248" t="s">
         <v>56</v>
@@ -12010,7 +12010,7 @@
         <v>46203</v>
       </c>
       <c r="B249" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D249" t="s">
         <v>55</v>
@@ -12042,7 +12042,7 @@
         <v>46203</v>
       </c>
       <c r="B250" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D250" t="s">
         <v>56</v>
@@ -12074,7 +12074,7 @@
         <v>46203</v>
       </c>
       <c r="B251" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D251" t="s">
         <v>56</v>
@@ -12106,7 +12106,7 @@
         <v>46204</v>
       </c>
       <c r="B252" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C252" t="s">
         <v>52</v>
@@ -12141,7 +12141,7 @@
         <v>46204</v>
       </c>
       <c r="B253" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C253" t="s">
         <v>19</v>
@@ -12176,7 +12176,7 @@
         <v>46204</v>
       </c>
       <c r="B254" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -12211,7 +12211,7 @@
         <v>46204</v>
       </c>
       <c r="B255" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C255" t="s">
         <v>19</v>
@@ -12246,7 +12246,7 @@
         <v>46204</v>
       </c>
       <c r="B256" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C256" t="s">
         <v>26</v>
@@ -12281,7 +12281,7 @@
         <v>46204</v>
       </c>
       <c r="B257" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C257" t="s">
         <v>35</v>
@@ -12316,7 +12316,7 @@
         <v>46204</v>
       </c>
       <c r="B258" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C258" t="s">
         <v>48</v>
@@ -12351,7 +12351,7 @@
         <v>46204</v>
       </c>
       <c r="B259" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C259" t="s">
         <v>40</v>
@@ -12386,7 +12386,7 @@
         <v>46204</v>
       </c>
       <c r="B260" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C260" t="s">
         <v>53</v>
@@ -12421,7 +12421,7 @@
         <v>46204</v>
       </c>
       <c r="B261" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D261" t="s">
         <v>58</v>
@@ -12453,7 +12453,7 @@
         <v>46204</v>
       </c>
       <c r="B262" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C262" t="s">
         <v>39</v>
@@ -12488,7 +12488,7 @@
         <v>46204</v>
       </c>
       <c r="B263" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C263" t="s">
         <v>29</v>
@@ -12523,7 +12523,7 @@
         <v>46204</v>
       </c>
       <c r="B264" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D264" t="s">
         <v>58</v>
@@ -12555,7 +12555,7 @@
         <v>46204</v>
       </c>
       <c r="B265" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C265" t="s">
         <v>18</v>
@@ -12590,7 +12590,7 @@
         <v>46204</v>
       </c>
       <c r="B266" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C266" t="s">
         <v>32</v>
@@ -12625,7 +12625,7 @@
         <v>46204</v>
       </c>
       <c r="B267" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C267" t="s">
         <v>16</v>
@@ -12660,7 +12660,7 @@
         <v>46204</v>
       </c>
       <c r="B268" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C268" t="s">
         <v>33</v>
@@ -12695,7 +12695,7 @@
         <v>46204</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D269" t="s">
         <v>55</v>
@@ -12727,7 +12727,7 @@
         <v>46204</v>
       </c>
       <c r="B270" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D270" t="s">
         <v>55</v>
@@ -12759,7 +12759,7 @@
         <v>46204</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D271" t="s">
         <v>55</v>
@@ -12791,7 +12791,7 @@
         <v>46204</v>
       </c>
       <c r="B272" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D272" t="s">
         <v>56</v>
@@ -12823,7 +12823,7 @@
         <v>46204</v>
       </c>
       <c r="B273" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C273" t="s">
         <v>27</v>
@@ -12858,7 +12858,7 @@
         <v>46204</v>
       </c>
       <c r="B274" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D274" t="s">
         <v>56</v>
@@ -12890,7 +12890,7 @@
         <v>46204</v>
       </c>
       <c r="B275" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D275" t="s">
         <v>56</v>
@@ -12922,7 +12922,7 @@
         <v>46204</v>
       </c>
       <c r="B276" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C276" t="s">
         <v>25</v>
@@ -12957,7 +12957,7 @@
         <v>46204</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C277" t="s">
         <v>49</v>
@@ -12992,7 +12992,7 @@
         <v>46204</v>
       </c>
       <c r="B278" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D278" t="s">
         <v>56</v>
@@ -13024,7 +13024,7 @@
         <v>46204</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D279" t="s">
         <v>56</v>
@@ -13056,7 +13056,7 @@
         <v>46204</v>
       </c>
       <c r="B280" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D280" t="s">
         <v>56</v>
@@ -13088,7 +13088,7 @@
         <v>46204</v>
       </c>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C281" t="s">
         <v>40</v>
@@ -13123,7 +13123,7 @@
         <v>46204</v>
       </c>
       <c r="B282" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D282" t="s">
         <v>55</v>
@@ -13155,7 +13155,7 @@
         <v>46204</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C283" t="s">
         <v>38</v>
@@ -13190,7 +13190,7 @@
         <v>46204</v>
       </c>
       <c r="B284" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C284" t="s">
         <v>36</v>
@@ -13225,7 +13225,7 @@
         <v>46204</v>
       </c>
       <c r="B285" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C285" t="s">
         <v>45</v>
@@ -13260,7 +13260,7 @@
         <v>46204</v>
       </c>
       <c r="B286" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C286" t="s">
         <v>40</v>
@@ -13295,7 +13295,7 @@
         <v>46204</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -13330,7 +13330,7 @@
         <v>46204</v>
       </c>
       <c r="B288" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C288" t="s">
         <v>40</v>
@@ -13365,7 +13365,7 @@
         <v>46204</v>
       </c>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C289" t="s">
         <v>29</v>
@@ -13400,7 +13400,7 @@
         <v>46204</v>
       </c>
       <c r="B290" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C290" t="s">
         <v>23</v>
@@ -13435,7 +13435,7 @@
         <v>46204</v>
       </c>
       <c r="B291" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C291" t="s">
         <v>43</v>
@@ -13470,7 +13470,7 @@
         <v>46204</v>
       </c>
       <c r="B292" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C292" t="s">
         <v>53</v>
@@ -13505,7 +13505,7 @@
         <v>46204</v>
       </c>
       <c r="B293" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D293" t="s">
         <v>58</v>
@@ -13537,7 +13537,7 @@
         <v>46205</v>
       </c>
       <c r="B294" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D294" t="s">
         <v>56</v>
@@ -13569,7 +13569,7 @@
         <v>46205</v>
       </c>
       <c r="B295" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D295" t="s">
         <v>56</v>
@@ -13601,7 +13601,7 @@
         <v>46205</v>
       </c>
       <c r="B296" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D296" t="s">
         <v>56</v>
@@ -13633,7 +13633,7 @@
         <v>46205</v>
       </c>
       <c r="B297" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D297" t="s">
         <v>56</v>
@@ -13665,7 +13665,7 @@
         <v>46205</v>
       </c>
       <c r="B298" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C298" t="s">
         <v>44</v>
@@ -13700,7 +13700,7 @@
         <v>46205</v>
       </c>
       <c r="B299" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C299" t="s">
         <v>26</v>
@@ -13735,7 +13735,7 @@
         <v>46205</v>
       </c>
       <c r="B300" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C300" t="s">
         <v>43</v>
@@ -13770,7 +13770,7 @@
         <v>46205</v>
       </c>
       <c r="B301" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
         <v>18</v>
@@ -13805,7 +13805,7 @@
         <v>46205</v>
       </c>
       <c r="B302" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D302" t="s">
         <v>55</v>
@@ -13837,7 +13837,7 @@
         <v>46205</v>
       </c>
       <c r="B303" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
         <v>53</v>
@@ -13872,7 +13872,7 @@
         <v>46205</v>
       </c>
       <c r="B304" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
         <v>23</v>
@@ -13907,7 +13907,7 @@
         <v>46205</v>
       </c>
       <c r="B305" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D305" t="s">
         <v>55</v>
@@ -13939,7 +13939,7 @@
         <v>46205</v>
       </c>
       <c r="B306" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
         <v>52</v>
@@ -13974,7 +13974,7 @@
         <v>46205</v>
       </c>
       <c r="B307" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C307" t="s">
         <v>29</v>
@@ -14009,7 +14009,7 @@
         <v>46205</v>
       </c>
       <c r="B308" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D308" t="s">
         <v>56</v>
@@ -14041,7 +14041,7 @@
         <v>46205</v>
       </c>
       <c r="B309" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C309" t="s">
         <v>40</v>
@@ -14076,7 +14076,7 @@
         <v>46205</v>
       </c>
       <c r="B310" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D310" t="s">
         <v>55</v>
@@ -14108,7 +14108,7 @@
         <v>46205</v>
       </c>
       <c r="B311" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C311" t="s">
         <v>40</v>
@@ -14143,7 +14143,7 @@
         <v>46205</v>
       </c>
       <c r="B312" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D312" t="s">
         <v>56</v>
@@ -14175,7 +14175,7 @@
         <v>46205</v>
       </c>
       <c r="B313" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C313" t="s">
         <v>40</v>
@@ -14210,7 +14210,7 @@
         <v>46205</v>
       </c>
       <c r="B314" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C314" t="s">
         <v>40</v>
@@ -14245,7 +14245,7 @@
         <v>46205</v>
       </c>
       <c r="B315" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C315" t="s">
         <v>24</v>
@@ -14280,7 +14280,7 @@
         <v>46205</v>
       </c>
       <c r="B316" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C316" t="s">
         <v>48</v>
@@ -14315,7 +14315,7 @@
         <v>46205</v>
       </c>
       <c r="B317" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C317" t="s">
         <v>27</v>
@@ -14350,7 +14350,7 @@
         <v>46205</v>
       </c>
       <c r="B318" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C318" t="s">
         <v>30</v>
@@ -14385,7 +14385,7 @@
         <v>46205</v>
       </c>
       <c r="B319" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -14420,7 +14420,7 @@
         <v>46205</v>
       </c>
       <c r="B320" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D320" t="s">
         <v>55</v>
@@ -14452,7 +14452,7 @@
         <v>46205</v>
       </c>
       <c r="B321" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D321" t="s">
         <v>56</v>
@@ -14484,7 +14484,7 @@
         <v>46205</v>
       </c>
       <c r="B322" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C322" t="s">
         <v>47</v>
@@ -14519,7 +14519,7 @@
         <v>46205</v>
       </c>
       <c r="B323" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C323" t="s">
         <v>54</v>
@@ -14554,7 +14554,7 @@
         <v>46205</v>
       </c>
       <c r="B324" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C324" t="s">
         <v>51</v>
@@ -14589,7 +14589,7 @@
         <v>46205</v>
       </c>
       <c r="B325" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C325" t="s">
         <v>54</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="B326" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D326" t="s">
         <v>58</v>
@@ -14656,7 +14656,7 @@
         <v>46206</v>
       </c>
       <c r="B327" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D327" t="s">
         <v>57</v>
@@ -14688,7 +14688,7 @@
         <v>46206</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C328" t="s">
         <v>18</v>
@@ -14723,7 +14723,7 @@
         <v>46206</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C329" t="s">
         <v>37</v>
@@ -14758,7 +14758,7 @@
         <v>46206</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C330" t="s">
         <v>37</v>
@@ -14793,7 +14793,7 @@
         <v>46206</v>
       </c>
       <c r="B331" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C331" t="s">
         <v>37</v>
@@ -14828,7 +14828,7 @@
         <v>46206</v>
       </c>
       <c r="B332" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C332" t="s">
         <v>29</v>
@@ -14863,7 +14863,7 @@
         <v>46206</v>
       </c>
       <c r="B333" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C333" t="s">
         <v>24</v>
@@ -14898,7 +14898,7 @@
         <v>46206</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D334" t="s">
         <v>56</v>
@@ -14930,7 +14930,7 @@
         <v>46206</v>
       </c>
       <c r="B335" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D335" t="s">
         <v>56</v>
@@ -14962,7 +14962,7 @@
         <v>46206</v>
       </c>
       <c r="B336" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D336" t="s">
         <v>56</v>
@@ -14994,7 +14994,7 @@
         <v>46206</v>
       </c>
       <c r="B337" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D337" t="s">
         <v>63</v>
@@ -15026,7 +15026,7 @@
         <v>46206</v>
       </c>
       <c r="B338" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D338" t="s">
         <v>61</v>
@@ -15058,7 +15058,7 @@
         <v>46206</v>
       </c>
       <c r="B339" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D339" t="s">
         <v>56</v>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -12106,7 +12106,7 @@
         <v>46204</v>
       </c>
       <c r="B252" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C252" t="s">
         <v>52</v>
@@ -12141,7 +12141,7 @@
         <v>46204</v>
       </c>
       <c r="B253" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C253" t="s">
         <v>19</v>
@@ -12176,7 +12176,7 @@
         <v>46204</v>
       </c>
       <c r="B254" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C254" t="s">
         <v>18</v>
@@ -12211,7 +12211,7 @@
         <v>46204</v>
       </c>
       <c r="B255" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C255" t="s">
         <v>19</v>
@@ -12246,7 +12246,7 @@
         <v>46204</v>
       </c>
       <c r="B256" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C256" t="s">
         <v>26</v>
@@ -12281,7 +12281,7 @@
         <v>46204</v>
       </c>
       <c r="B257" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C257" t="s">
         <v>35</v>
@@ -12316,7 +12316,7 @@
         <v>46204</v>
       </c>
       <c r="B258" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C258" t="s">
         <v>48</v>
@@ -12351,7 +12351,7 @@
         <v>46204</v>
       </c>
       <c r="B259" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C259" t="s">
         <v>40</v>
@@ -12386,7 +12386,7 @@
         <v>46204</v>
       </c>
       <c r="B260" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C260" t="s">
         <v>53</v>
@@ -12421,7 +12421,7 @@
         <v>46204</v>
       </c>
       <c r="B261" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D261" t="s">
         <v>58</v>
@@ -12453,7 +12453,7 @@
         <v>46204</v>
       </c>
       <c r="B262" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C262" t="s">
         <v>39</v>
@@ -12488,7 +12488,7 @@
         <v>46204</v>
       </c>
       <c r="B263" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C263" t="s">
         <v>29</v>
@@ -12523,7 +12523,7 @@
         <v>46204</v>
       </c>
       <c r="B264" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D264" t="s">
         <v>58</v>
@@ -12555,7 +12555,7 @@
         <v>46204</v>
       </c>
       <c r="B265" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C265" t="s">
         <v>18</v>
@@ -12590,7 +12590,7 @@
         <v>46204</v>
       </c>
       <c r="B266" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C266" t="s">
         <v>32</v>
@@ -12625,7 +12625,7 @@
         <v>46204</v>
       </c>
       <c r="B267" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C267" t="s">
         <v>16</v>
@@ -12660,7 +12660,7 @@
         <v>46204</v>
       </c>
       <c r="B268" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C268" t="s">
         <v>33</v>
@@ -12695,7 +12695,7 @@
         <v>46204</v>
       </c>
       <c r="B269" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D269" t="s">
         <v>55</v>
@@ -12727,7 +12727,7 @@
         <v>46204</v>
       </c>
       <c r="B270" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D270" t="s">
         <v>55</v>
@@ -12759,7 +12759,7 @@
         <v>46204</v>
       </c>
       <c r="B271" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D271" t="s">
         <v>55</v>
@@ -12791,7 +12791,7 @@
         <v>46204</v>
       </c>
       <c r="B272" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D272" t="s">
         <v>56</v>
@@ -12823,7 +12823,7 @@
         <v>46204</v>
       </c>
       <c r="B273" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C273" t="s">
         <v>27</v>
@@ -12858,7 +12858,7 @@
         <v>46204</v>
       </c>
       <c r="B274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D274" t="s">
         <v>56</v>
@@ -12890,7 +12890,7 @@
         <v>46204</v>
       </c>
       <c r="B275" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D275" t="s">
         <v>56</v>
@@ -12922,7 +12922,7 @@
         <v>46204</v>
       </c>
       <c r="B276" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C276" t="s">
         <v>25</v>
@@ -12957,7 +12957,7 @@
         <v>46204</v>
       </c>
       <c r="B277" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C277" t="s">
         <v>49</v>
@@ -12992,7 +12992,7 @@
         <v>46204</v>
       </c>
       <c r="B278" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D278" t="s">
         <v>56</v>
@@ -13024,7 +13024,7 @@
         <v>46204</v>
       </c>
       <c r="B279" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D279" t="s">
         <v>56</v>
@@ -13056,7 +13056,7 @@
         <v>46204</v>
       </c>
       <c r="B280" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D280" t="s">
         <v>56</v>
@@ -13088,7 +13088,7 @@
         <v>46204</v>
       </c>
       <c r="B281" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C281" t="s">
         <v>40</v>
@@ -13123,7 +13123,7 @@
         <v>46204</v>
       </c>
       <c r="B282" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D282" t="s">
         <v>55</v>
@@ -13155,7 +13155,7 @@
         <v>46204</v>
       </c>
       <c r="B283" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C283" t="s">
         <v>38</v>
@@ -13190,7 +13190,7 @@
         <v>46204</v>
       </c>
       <c r="B284" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C284" t="s">
         <v>36</v>
@@ -13225,7 +13225,7 @@
         <v>46204</v>
       </c>
       <c r="B285" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C285" t="s">
         <v>45</v>
@@ -13260,7 +13260,7 @@
         <v>46204</v>
       </c>
       <c r="B286" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C286" t="s">
         <v>40</v>
@@ -13295,7 +13295,7 @@
         <v>46204</v>
       </c>
       <c r="B287" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C287" t="s">
         <v>18</v>
@@ -13330,7 +13330,7 @@
         <v>46204</v>
       </c>
       <c r="B288" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C288" t="s">
         <v>40</v>
@@ -13365,7 +13365,7 @@
         <v>46204</v>
       </c>
       <c r="B289" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C289" t="s">
         <v>29</v>
@@ -13400,7 +13400,7 @@
         <v>46204</v>
       </c>
       <c r="B290" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C290" t="s">
         <v>23</v>
@@ -13435,7 +13435,7 @@
         <v>46204</v>
       </c>
       <c r="B291" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C291" t="s">
         <v>43</v>
@@ -13470,7 +13470,7 @@
         <v>46204</v>
       </c>
       <c r="B292" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C292" t="s">
         <v>53</v>
@@ -13505,7 +13505,7 @@
         <v>46204</v>
       </c>
       <c r="B293" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D293" t="s">
         <v>58</v>
@@ -13537,7 +13537,7 @@
         <v>46205</v>
       </c>
       <c r="B294" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D294" t="s">
         <v>56</v>
@@ -13569,7 +13569,7 @@
         <v>46205</v>
       </c>
       <c r="B295" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D295" t="s">
         <v>56</v>
@@ -13601,7 +13601,7 @@
         <v>46205</v>
       </c>
       <c r="B296" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D296" t="s">
         <v>56</v>
@@ -13633,7 +13633,7 @@
         <v>46205</v>
       </c>
       <c r="B297" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D297" t="s">
         <v>56</v>
@@ -13665,7 +13665,7 @@
         <v>46205</v>
       </c>
       <c r="B298" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C298" t="s">
         <v>44</v>
@@ -13700,7 +13700,7 @@
         <v>46205</v>
       </c>
       <c r="B299" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C299" t="s">
         <v>26</v>
@@ -13735,7 +13735,7 @@
         <v>46205</v>
       </c>
       <c r="B300" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C300" t="s">
         <v>43</v>
@@ -13770,7 +13770,7 @@
         <v>46205</v>
       </c>
       <c r="B301" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C301" t="s">
         <v>18</v>
@@ -13805,7 +13805,7 @@
         <v>46205</v>
       </c>
       <c r="B302" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D302" t="s">
         <v>55</v>
@@ -13837,7 +13837,7 @@
         <v>46205</v>
       </c>
       <c r="B303" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C303" t="s">
         <v>53</v>
@@ -13872,7 +13872,7 @@
         <v>46205</v>
       </c>
       <c r="B304" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C304" t="s">
         <v>23</v>
@@ -13907,7 +13907,7 @@
         <v>46205</v>
       </c>
       <c r="B305" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D305" t="s">
         <v>55</v>
@@ -13939,7 +13939,7 @@
         <v>46205</v>
       </c>
       <c r="B306" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C306" t="s">
         <v>52</v>
@@ -13974,7 +13974,7 @@
         <v>46205</v>
       </c>
       <c r="B307" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C307" t="s">
         <v>29</v>
@@ -14009,7 +14009,7 @@
         <v>46205</v>
       </c>
       <c r="B308" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D308" t="s">
         <v>56</v>
@@ -14041,7 +14041,7 @@
         <v>46205</v>
       </c>
       <c r="B309" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C309" t="s">
         <v>40</v>
@@ -14076,7 +14076,7 @@
         <v>46205</v>
       </c>
       <c r="B310" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D310" t="s">
         <v>55</v>
@@ -14108,7 +14108,7 @@
         <v>46205</v>
       </c>
       <c r="B311" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C311" t="s">
         <v>40</v>
@@ -14143,7 +14143,7 @@
         <v>46205</v>
       </c>
       <c r="B312" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D312" t="s">
         <v>56</v>
@@ -14175,7 +14175,7 @@
         <v>46205</v>
       </c>
       <c r="B313" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C313" t="s">
         <v>40</v>
@@ -14210,7 +14210,7 @@
         <v>46205</v>
       </c>
       <c r="B314" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C314" t="s">
         <v>40</v>
@@ -14245,7 +14245,7 @@
         <v>46205</v>
       </c>
       <c r="B315" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C315" t="s">
         <v>24</v>
@@ -14280,7 +14280,7 @@
         <v>46205</v>
       </c>
       <c r="B316" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C316" t="s">
         <v>48</v>
@@ -14315,7 +14315,7 @@
         <v>46205</v>
       </c>
       <c r="B317" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C317" t="s">
         <v>27</v>
@@ -14350,7 +14350,7 @@
         <v>46205</v>
       </c>
       <c r="B318" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C318" t="s">
         <v>30</v>
@@ -14385,7 +14385,7 @@
         <v>46205</v>
       </c>
       <c r="B319" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C319" t="s">
         <v>18</v>
@@ -14420,7 +14420,7 @@
         <v>46205</v>
       </c>
       <c r="B320" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D320" t="s">
         <v>55</v>
@@ -14452,7 +14452,7 @@
         <v>46205</v>
       </c>
       <c r="B321" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D321" t="s">
         <v>56</v>
@@ -14484,7 +14484,7 @@
         <v>46205</v>
       </c>
       <c r="B322" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C322" t="s">
         <v>47</v>
@@ -14519,7 +14519,7 @@
         <v>46205</v>
       </c>
       <c r="B323" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C323" t="s">
         <v>54</v>
@@ -14554,7 +14554,7 @@
         <v>46205</v>
       </c>
       <c r="B324" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C324" t="s">
         <v>51</v>
@@ -14589,7 +14589,7 @@
         <v>46205</v>
       </c>
       <c r="B325" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C325" t="s">
         <v>54</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="B326" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D326" t="s">
         <v>58</v>
@@ -14656,7 +14656,7 @@
         <v>46206</v>
       </c>
       <c r="B327" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D327" t="s">
         <v>57</v>
@@ -14688,7 +14688,7 @@
         <v>46206</v>
       </c>
       <c r="B328" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C328" t="s">
         <v>18</v>
@@ -14723,7 +14723,7 @@
         <v>46206</v>
       </c>
       <c r="B329" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C329" t="s">
         <v>37</v>
@@ -14758,7 +14758,7 @@
         <v>46206</v>
       </c>
       <c r="B330" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C330" t="s">
         <v>37</v>
@@ -14793,7 +14793,7 @@
         <v>46206</v>
       </c>
       <c r="B331" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C331" t="s">
         <v>37</v>
@@ -14828,7 +14828,7 @@
         <v>46206</v>
       </c>
       <c r="B332" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C332" t="s">
         <v>29</v>
@@ -14863,7 +14863,7 @@
         <v>46206</v>
       </c>
       <c r="B333" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C333" t="s">
         <v>24</v>
@@ -14898,7 +14898,7 @@
         <v>46206</v>
       </c>
       <c r="B334" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D334" t="s">
         <v>56</v>
@@ -14930,7 +14930,7 @@
         <v>46206</v>
       </c>
       <c r="B335" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D335" t="s">
         <v>56</v>
@@ -14962,7 +14962,7 @@
         <v>46206</v>
       </c>
       <c r="B336" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D336" t="s">
         <v>56</v>
@@ -14994,7 +14994,7 @@
         <v>46206</v>
       </c>
       <c r="B337" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D337" t="s">
         <v>63</v>
@@ -15026,7 +15026,7 @@
         <v>46206</v>
       </c>
       <c r="B338" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D338" t="s">
         <v>61</v>
@@ -15058,7 +15058,7 @@
         <v>46206</v>
       </c>
       <c r="B339" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D339" t="s">
         <v>56</v>
@@ -15090,7 +15090,7 @@
         <v>46209</v>
       </c>
       <c r="B340" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C340" t="s">
         <v>40</v>
@@ -15125,7 +15125,7 @@
         <v>46209</v>
       </c>
       <c r="B341" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C341" t="s">
         <v>45</v>
@@ -15160,7 +15160,7 @@
         <v>46209</v>
       </c>
       <c r="B342" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C342" t="s">
         <v>40</v>
@@ -15195,7 +15195,7 @@
         <v>46209</v>
       </c>
       <c r="B343" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C343" t="s">
         <v>40</v>
@@ -15230,7 +15230,7 @@
         <v>46209</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C344" t="s">
         <v>29</v>
@@ -15265,7 +15265,7 @@
         <v>46209</v>
       </c>
       <c r="B345" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C345" t="s">
         <v>19</v>
@@ -15300,7 +15300,7 @@
         <v>46209</v>
       </c>
       <c r="B346" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C346" t="s">
         <v>19</v>
@@ -15335,7 +15335,7 @@
         <v>46209</v>
       </c>
       <c r="B347" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C347" t="s">
         <v>35</v>
@@ -15370,7 +15370,7 @@
         <v>46209</v>
       </c>
       <c r="B348" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C348" t="s">
         <v>40</v>
@@ -15405,7 +15405,7 @@
         <v>46209</v>
       </c>
       <c r="B349" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C349" t="s">
         <v>40</v>
@@ -15440,7 +15440,7 @@
         <v>46209</v>
       </c>
       <c r="B350" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C350" t="s">
         <v>40</v>
@@ -15475,7 +15475,7 @@
         <v>46209</v>
       </c>
       <c r="B351" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C351" t="s">
         <v>19</v>
@@ -15510,7 +15510,7 @@
         <v>46209</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C352" t="s">
         <v>40</v>
@@ -15545,7 +15545,7 @@
         <v>46209</v>
       </c>
       <c r="B353" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C353" t="s">
         <v>40</v>
@@ -15580,7 +15580,7 @@
         <v>46209</v>
       </c>
       <c r="B354" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C354" t="s">
         <v>29</v>
@@ -15615,7 +15615,7 @@
         <v>46209</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C355" t="s">
         <v>41</v>
@@ -15650,7 +15650,7 @@
         <v>46209</v>
       </c>
       <c r="B356" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C356" t="s">
         <v>48</v>
@@ -15685,7 +15685,7 @@
         <v>46209</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C357" t="s">
         <v>40</v>
@@ -15720,7 +15720,7 @@
         <v>46209</v>
       </c>
       <c r="B358" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C358" t="s">
         <v>40</v>
@@ -15755,7 +15755,7 @@
         <v>46209</v>
       </c>
       <c r="B359" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C359" t="s">
         <v>43</v>
@@ -15790,7 +15790,7 @@
         <v>46209</v>
       </c>
       <c r="B360" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C360" t="s">
         <v>32</v>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>BCF</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="144">
   <si>
     <t>data</t>
   </si>
@@ -49,211 +49,328 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
-  </si>
-  <si>
-    <t>BCF</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>TLI</t>
   </si>
   <si>
     <t>RYL</t>
   </si>
   <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>NBG</t>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>Correspondente - Zalaf</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
   </si>
   <si>
     <t>ARC</t>
   </si>
   <si>
+    <t>JQS</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
     <t>GSM</t>
   </si>
   <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>FCG</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>TFR</t>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>Grupo A3</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
   </si>
   <si>
     <t>Grupo B2</t>
   </si>
   <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Whirlpool S.A.</t>
+  </si>
+  <si>
+    <t>Mahle Behr Gerenciamento Térmico Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Americanas S.A.</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participacoes E Companhia Aix De Participacoes</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
   </si>
   <si>
     <t>Embraer S.A.</t>
   </si>
   <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Ouroeste Bioenergia LTDA.</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
     <t>Audiência Inicial - Telepresencial</t>
   </si>
   <si>
+    <t>Sessão de Julgamento TJ - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011835-11.2025.5.15.0084</t>
-  </si>
-  <si>
-    <t>0010484-23.2026.5.03.0174</t>
-  </si>
-  <si>
-    <t>0010064-52.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>0011091-26.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>0010659-07.2026.5.15.0037</t>
-  </si>
-  <si>
-    <t>0010148-68.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>1000584-41.2026.5.02.0363</t>
-  </si>
-  <si>
-    <t>0012537-21.2025.5.15.0095</t>
-  </si>
-  <si>
-    <t>0000438-80.2026.5.05.0121</t>
-  </si>
-  <si>
-    <t>0010626-17.2026.5.15.0037</t>
-  </si>
-  <si>
-    <t>0012372-63.2025.5.15.0130</t>
-  </si>
-  <si>
-    <t>0011566-58.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>1000839-77.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>1000288-07.2026.5.02.0464</t>
-  </si>
-  <si>
-    <t>1000133-67.2026.5.02.0055</t>
-  </si>
-  <si>
-    <t>0011186-18.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Cristiane Paula De Sousa Araujo Carvalho</t>
-  </si>
-  <si>
-    <t>Francinaldo Alves Dos Santos</t>
-  </si>
-  <si>
-    <t>Jessica Nunes Da Silva</t>
-  </si>
-  <si>
-    <t>Luiz Augusto Dias</t>
-  </si>
-  <si>
-    <t>Evandro Martins Ribeiro</t>
-  </si>
-  <si>
-    <t>Erivan Agustinho Furtado</t>
-  </si>
-  <si>
-    <t>Gabriel Da Corte</t>
-  </si>
-  <si>
-    <t>Heleno Dirceu Martins</t>
-  </si>
-  <si>
-    <t>Leandro Dos Santos Lima</t>
-  </si>
-  <si>
-    <t>Jose Ovidio Ferreira De Aquino</t>
-  </si>
-  <si>
-    <t>Marcelo Augusto De Souza Primo</t>
-  </si>
-  <si>
-    <t>Pedro Soares Dos Santos</t>
-  </si>
-  <si>
-    <t>Luiz Carlos Baptista</t>
-  </si>
-  <si>
-    <t>Sarita Ferreira Ventura</t>
-  </si>
-  <si>
-    <t>Luciana De Lima Machado</t>
-  </si>
-  <si>
-    <t>Adilson Maximiano Nogueira</t>
-  </si>
-  <si>
-    <t>08:00:00</t>
-  </si>
-  <si>
-    <t>08:10:00</t>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>1000237-89.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>0010719-78.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010721-48.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010725-85.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010726-70.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>5016566.75.2024.4.04.7201</t>
+  </si>
+  <si>
+    <t>1000618-51.2026.5.02.0319</t>
+  </si>
+  <si>
+    <t>0010643-83.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>0011871-29.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>0011194-92.2025.5.15.0061</t>
+  </si>
+  <si>
+    <t>0011297-43.2026.5.15.0133</t>
+  </si>
+  <si>
+    <t>0010155-46.2026.5.15.0119</t>
+  </si>
+  <si>
+    <t>0011718-25.2024.5.15.0126</t>
+  </si>
+  <si>
+    <t>1000516-14.2026.5.02.0712</t>
+  </si>
+  <si>
+    <t>0011727-56.2025.5.15.0027</t>
+  </si>
+  <si>
+    <t>1000075-55.2023.5.02.0383</t>
+  </si>
+  <si>
+    <t>0011696-36.2025.5.15.0027</t>
+  </si>
+  <si>
+    <t>0000017-35.2026.5.09.0071</t>
+  </si>
+  <si>
+    <t>0011309-54.2026.5.03.0048</t>
+  </si>
+  <si>
+    <t>0011710-87.2025.5.03.0048</t>
+  </si>
+  <si>
+    <t>0011711-72.2025.5.03.0048</t>
+  </si>
+  <si>
+    <t>0011712-57.2025.5.03.0048</t>
+  </si>
+  <si>
+    <t>0010530-11.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>0010879-39.2025.5.03.0048</t>
+  </si>
+  <si>
+    <t>1000149-48.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>0011544-84.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>0011542-17.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>1000464-72.2026.5.02.0015</t>
+  </si>
+  <si>
+    <t>1001737-36.2025.5.02.0431</t>
+  </si>
+  <si>
+    <t>Alex Almeida De Lima</t>
+  </si>
+  <si>
+    <t>Gleydson Freitas Sousa</t>
+  </si>
+  <si>
+    <t>Itamar Jose Da Rocha</t>
+  </si>
+  <si>
+    <t>Tiago De Castro Fonseca</t>
+  </si>
+  <si>
+    <t>Elias Jorge Democh</t>
+  </si>
+  <si>
+    <t>Instituto Nacional Do Seguro Social - Inss</t>
+  </si>
+  <si>
+    <t>Zivanildo Bezerra Barbosa</t>
+  </si>
+  <si>
+    <t>Lucas Vinicius Inamorato</t>
+  </si>
+  <si>
+    <t>Doclesio Custodio Santana</t>
+  </si>
+  <si>
+    <t>Marcio Pereira Santos</t>
+  </si>
+  <si>
+    <t>Claudio Junio Rocha Da Silva</t>
+  </si>
+  <si>
+    <t>Anderson De Santana Franco</t>
+  </si>
+  <si>
+    <t>Mario Jose Da Silva Filho</t>
+  </si>
+  <si>
+    <t>Mauro Francisco Da Silva</t>
+  </si>
+  <si>
+    <t>Dorival De Souza Morais</t>
+  </si>
+  <si>
+    <t>Maria Eslaine Silva Ribeiro Flor</t>
+  </si>
+  <si>
+    <t>Roberto Pereira Da Silva</t>
+  </si>
+  <si>
+    <t>Gilmar Lourenco</t>
+  </si>
+  <si>
+    <t>Kelson Jose De Oliveira Junior</t>
+  </si>
+  <si>
+    <t>Bruno Daniel Da Cruz</t>
+  </si>
+  <si>
+    <t>Adriano Leite Silva</t>
+  </si>
+  <si>
+    <t>Thiago Sebastiao Gervasio De Oliveira</t>
+  </si>
+  <si>
+    <t>Diego Vinicius Stabile David</t>
+  </si>
+  <si>
+    <t>Jose Cicero Barbosa</t>
+  </si>
+  <si>
+    <t>Jonata Tadeu Oliveira Da Costa</t>
+  </si>
+  <si>
+    <t>Giacomo Geroldo Quito</t>
+  </si>
+  <si>
+    <t>Luciano Marco Costa Huerta</t>
+  </si>
+  <si>
+    <t>Leandro De Oliveira Carminatti</t>
+  </si>
+  <si>
+    <t>08:20:00</t>
   </si>
   <si>
     <t>08:30:00</t>
@@ -262,7 +379,13 @@
     <t>08:35:00</t>
   </si>
   <si>
-    <t>09:10:00</t>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>08:45:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
   </si>
   <si>
     <t>09:20:00</t>
@@ -271,25 +394,58 @@
     <t>09:30:00</t>
   </si>
   <si>
-    <t>09:35:00</t>
-  </si>
-  <si>
-    <t>09:50:00</t>
-  </si>
-  <si>
     <t>10:00:00</t>
   </si>
   <si>
-    <t>10:15:00</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>12:20:00</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>10:40:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>12:05:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>13:35:00</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:04:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
   </si>
 </sst>
 </file>
@@ -625,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -665,7 +821,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -674,33 +830,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -709,453 +865,453 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="J12" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -1164,63 +1320,518 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
         <v>25</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>84</v>
+      </c>
+      <c r="I25" t="s">
+        <v>113</v>
+      </c>
+      <c r="J25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
         <v>33</v>
       </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" t="s">
-        <v>77</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" t="s">
+        <v>115</v>
+      </c>
+      <c r="J27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
         <v>33</v>
       </c>
-      <c r="K17" t="s">
-        <v>91</v>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" t="s">
+        <v>115</v>
+      </c>
+      <c r="J28" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" t="s">
+        <v>116</v>
+      </c>
+      <c r="J29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" t="s">
+        <v>117</v>
+      </c>
+      <c r="J30" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>data</t>
   </si>
@@ -52,235 +52,223 @@
     <t>D-1</t>
   </si>
   <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
     <t>MBF</t>
   </si>
   <si>
-    <t>Correspondente - Carlos Florian</t>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>CAL</t>
   </si>
   <si>
     <t>RRU</t>
   </si>
   <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
     <t>ANB</t>
   </si>
   <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>GSF</t>
-  </si>
-  <si>
     <t>JPE</t>
   </si>
   <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
     <t>Grupo E2</t>
   </si>
   <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
     <t>Grupo B1</t>
   </si>
   <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
     <t>Grupo D1</t>
   </si>
   <si>
-    <t>Grupo A3</t>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Robert Bosch Limitada</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Bridgestone do Brasil Indústria e Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
   </si>
   <si>
     <t>Santa Juliana Bioenergia Ltda.</t>
   </si>
   <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A.</t>
+    <t>Bit Services Inovação E Tecnologia Ltda.</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Ouroeste Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Telefônica Brasil S.A</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Mitre Vendas Corretagem De Imóveis Ltda.</t>
-  </si>
-  <si>
-    <t>Bit Services Inovação E Tecnologia Ltda.</t>
-  </si>
-  <si>
-    <t>Telefônica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Whirlpool S.A.</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Semipresencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
   </si>
   <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011127-68.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>1000662-82.2026.5.02.0703</t>
-  </si>
-  <si>
-    <t>0011129-41.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>1000314-07.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>0010478-06.2026.5.15.0037</t>
-  </si>
-  <si>
-    <t>1000586-34.2026.5.02.0032</t>
-  </si>
-  <si>
-    <t>1000645-84.2026.5.02.0464</t>
-  </si>
-  <si>
-    <t>1000858-43.2026.5.02.0609</t>
-  </si>
-  <si>
-    <t>1001499-82.2025.5.02.0086</t>
-  </si>
-  <si>
-    <t>1000894-28.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>1001012-15.2024.5.02.0065</t>
-  </si>
-  <si>
-    <t>1000807-38.2025.5.02.0004</t>
-  </si>
-  <si>
-    <t>1000895-13.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>1001314-38.2023.5.02.0434</t>
-  </si>
-  <si>
-    <t>Elenilson Costa Franca</t>
-  </si>
-  <si>
-    <t>Edilson Stanize</t>
-  </si>
-  <si>
-    <t>Antoniel Silva Dos Santos</t>
-  </si>
-  <si>
-    <t>Evandro Fernandes Augusto</t>
-  </si>
-  <si>
-    <t>Joyce Leticia Gentile Pavao Correia</t>
-  </si>
-  <si>
-    <t>Kleber Faria Dos Santos</t>
-  </si>
-  <si>
-    <t>Gerson Dourado Santos</t>
-  </si>
-  <si>
-    <t>Rodrigo Lopes Da Silva</t>
-  </si>
-  <si>
-    <t>Lidia Teixeira Neves</t>
-  </si>
-  <si>
-    <t>Eduardo Antonio De Souza Braga</t>
-  </si>
-  <si>
-    <t>Andre Fernandes Rodrigues</t>
-  </si>
-  <si>
-    <t>Carla Di Francesco Verdolini</t>
-  </si>
-  <si>
-    <t>Flavio Eduardo Basilio</t>
-  </si>
-  <si>
-    <t>Elenilton Junio De Jesus Silva</t>
-  </si>
-  <si>
-    <t>08:15:00</t>
-  </si>
-  <si>
-    <t>08:20:00</t>
-  </si>
-  <si>
-    <t>09:00:00</t>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011835-11.2025.5.15.0084</t>
+  </si>
+  <si>
+    <t>0011270-80.2026.5.15.0094</t>
+  </si>
+  <si>
+    <t>0000748-68.2026.5.19.0001</t>
+  </si>
+  <si>
+    <t>0010755-23.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010783-88.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010786-43.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010429-51.2025.5.03.0063</t>
+  </si>
+  <si>
+    <t>1001324-86.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>0012273-93.2025.5.15.0130</t>
+  </si>
+  <si>
+    <t>0011280-39.2025.5.03.0080</t>
+  </si>
+  <si>
+    <t>1000537-26.2026.5.02.0603</t>
+  </si>
+  <si>
+    <t>0010871-95.2022.5.03.0168</t>
+  </si>
+  <si>
+    <t>1001751-48.2025.5.02.0066</t>
+  </si>
+  <si>
+    <t>1001754-06.2024.5.02.0432</t>
+  </si>
+  <si>
+    <t>Cristiane Paula De Sousa Araujo Carvalho</t>
+  </si>
+  <si>
+    <t>Clovis Adilson Antonicelli</t>
+  </si>
+  <si>
+    <t>Fernando Santana</t>
+  </si>
+  <si>
+    <t>Marllon De Pinho Da Silva</t>
+  </si>
+  <si>
+    <t>Edley Henrique Silva</t>
+  </si>
+  <si>
+    <t>Milton Vieira De Almeida</t>
+  </si>
+  <si>
+    <t>Kenede Basilio De Araujo</t>
+  </si>
+  <si>
+    <t>Fabiano De Moura Goncalves</t>
+  </si>
+  <si>
+    <t>Francisco Elenilson Alves</t>
+  </si>
+  <si>
+    <t>Adrian Silva De Aquino</t>
+  </si>
+  <si>
+    <t>Domingos Rufino Franco</t>
+  </si>
+  <si>
+    <t>Andrelino Pereira De Mendonca</t>
+  </si>
+  <si>
+    <t>Rosana Lopes De Oliveira Cruz</t>
+  </si>
+  <si>
+    <t>Anderson Rodrigues</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
   </si>
   <si>
     <t>09:30:00</t>
   </si>
   <si>
-    <t>09:50:00</t>
-  </si>
-  <si>
     <t>10:00:00</t>
   </si>
   <si>
     <t>10:10:00</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>13:10:00</t>
-  </si>
-  <si>
-    <t>15:42:00</t>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
   </si>
 </sst>
 </file>
@@ -656,7 +644,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -665,33 +653,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -700,33 +688,33 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -735,33 +723,33 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -770,10 +758,10 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -782,366 +770,366 @@
         <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>VCR</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>VRO</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9FDA973-1726-4978-B32E-61783B1A0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CC9C934-ACFD-4205-90EA-1198CCBE566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A160F25-2670-4677-BD90-34B27A142245}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72218CE6-47E0-40A4-8063-C4D7752BDE5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="200">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,92 +95,557 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010556-64.2023.5.15.0082</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Miguel Jose De Souza</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             177.690,57</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/88415253122?pwd=QzlTNmxwdWpEeGVFZmdwM0lDUFJ4Zz09 ID da reunião: 884 1525 3122 Senha de acesso: 510562</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000973-20.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Sonia Soares Almeida</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             191.275,42</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Luciana França, (11) 96351-8524</t>
+  </si>
+  <si>
+    <t>1001013-02.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>Davi Joao Da Silva</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             629.417,60</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0014731-48.2025.5.15.0077</t>
+  </si>
+  <si>
+    <t>Robert Bosch Limitada</t>
+  </si>
+  <si>
+    <t>Ismael Jose Dos Santos</t>
+  </si>
+  <si>
+    <t>INDAIATUBA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             810.894,79</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1 ID da reunião 882 1575 1954 Senha  150077</t>
+  </si>
+  <si>
+    <t>0011763-13.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Matheus Felipe Januario Domingues</t>
+  </si>
+  <si>
+    <t>R$             356.093,25</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
+  </si>
+  <si>
+    <t>0000846-69.2026.5.05.0251</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Gilson Meireles Dos Santos</t>
+  </si>
+  <si>
+    <t>CONCEIÇÃO DO COITÉ</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>R$               18.131,17</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>JRT</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/segundonucleo4sala2</t>
+  </si>
+  <si>
+    <t>0010954-47.2026.5.15.0133</t>
+  </si>
+  <si>
+    <t>Edivaldo Aparecido De Oliveira</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             262.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 050728</t>
+  </si>
+  <si>
+    <t>0001673-39.2025.5.13.0010</t>
+  </si>
+  <si>
+    <t>Willan Hilario Marcelino</t>
+  </si>
+  <si>
+    <t>GUARABIRA</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$               46.279,00</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>https://trt13-jus-br.zoom.us/my/cejusc13.sala5</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>0010064-52.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Jessica Nunes Da Silva</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             102.270,09</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0010295-44.2026.5.15.0131</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Leite</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>12ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             283.750,20</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83676367506?pwd=VlRlWmFnUGhwdWp3Y2xvaVkxdDFDZz09 ID da reunião: 836 7636 7506 Senha: 24680</t>
+  </si>
+  <si>
+    <t>0000761-97.2026.5.17.0009</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Edilcivane Pereira Ottoni</t>
+  </si>
+  <si>
+    <t>VITÓRIA</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>09ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$                 5.659,29</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Ricardo Baracho Moreira ricardo.baracho@gmail.com (27) 998923622</t>
+  </si>
+  <si>
+    <t>0011575-56.2024.5.15.0087</t>
+  </si>
+  <si>
+    <t>Wesley Felipe Cezar Xavier</t>
+  </si>
+  <si>
+    <t>ORGÃO ESPECIAL</t>
+  </si>
+  <si>
+    <t>2ª Instância</t>
+  </si>
+  <si>
+    <t>R$             150.650,00</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81907928214?pwd=DdJyPKEOQWb3pMKbKp713raBQMIpao.1 ID:  819  0792  8214  Senha: 935266.</t>
+  </si>
+  <si>
+    <t>0010718-92.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>Claudio Richard De Godoy</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88971005711?pwd=FCU0CcOJlu66H4VR8hrXW2o1KrrqXb.1 ID: 889  7100  5711  Senha: 962801</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000010-77.2026.5.09.0092</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Darlan Silva Quintiliano</t>
+  </si>
+  <si>
+    <t>CIANORTE</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$               32.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://trt9-jus-br.zoom.us/j/5580468805?pwd=aXhxc3lyQ2F2K0FTWEVoU3ZOWDhlUT09</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0000431-17.2026.5.10.0811</t>
-  </si>
-  <si>
-    <t>Produtécnica Nordeste Comércio De Insumos Agrícolas Ltda.</t>
-  </si>
-  <si>
-    <t>Jhony Carlos Lucena Cardoso</t>
-  </si>
-  <si>
-    <t>ARAGUAINA</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             125.820,62</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>0010907-03.2025.5.15.0103</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Jeanio Berto Da Costa E Silva</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             149.560,43</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0010466-75.2022.5.15.0087</t>
+  </si>
+  <si>
+    <t>Sidkley Jose Da Silva</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               63.758,95</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/86385704640?pwd=g1Ig2NoEnHBDvn3uZhXt1tmbVhuO14.1</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011112-47.2025.5.03.0012</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Indústria Doceira E Alimentar Ltda.</t>
+  </si>
+  <si>
+    <t>Lucimar Da Silva Costa</t>
+  </si>
+  <si>
+    <t>BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$             162.480,95</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Luiz Henrique Ribeiro Costa (31) 98616-2039 |Preposto - Túlio Moreno Lobo Jardim (31) 99755-9174</t>
+  </si>
+  <si>
+    <t>0010432-81.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Frutal Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Joao Batista Loiola De Sousa</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>R$             401.858,88</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>0010828-57.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Luciano Vicentim Da Cruz</t>
+  </si>
+  <si>
+    <t>R$             274.940,69</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87345253855?pwd=eOmaFv9ph0gYOdbdibavbZapr1i2NE.1 ID:  873  4525  3855  Senha: 223572</t>
+  </si>
+  <si>
+    <t>1002332-26.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>Cesar Luiz Do Amaral</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             231.524,56</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>1000813-89.2020.5.02.0434</t>
+  </si>
+  <si>
+    <t>Alan Alves Sarmento</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>R$             580.213,37</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87687135814?pwd=L21Bd0RobFB3V0I0VVpuMlBDUG5oUT09 ID da reunião: 876 8713 5814 Senha de acesso: 120826</t>
+  </si>
+  <si>
+    <t>0011034-70.2025.5.03.0071</t>
+  </si>
+  <si>
+    <t>Agrocerrado Produtos Agrícolas E Assistência Técnica Ltda.</t>
+  </si>
+  <si>
+    <t>Yure De Andrade Barbosa</t>
+  </si>
+  <si>
+    <t>PATOS DE MINAS</t>
+  </si>
+  <si>
+    <t>R$             339.933,31</t>
   </si>
   <si>
     <t>VRO</t>
   </si>
   <si>
-    <t>link pendente</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001059-81.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Danilo Vieira Dos Santos Andrade Alves</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$             494.873,71</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patosdeminas</t>
+  </si>
+  <si>
+    <t>0010034-31.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Rafael Gustavo Silva</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$             203.419,69</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
+  </si>
+  <si>
+    <t>0010505-52.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Fabio Moreira</t>
+  </si>
+  <si>
+    <t>R$             563.053,70</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83830687320?pwd=aH38p2gWpjsX9F8as5Kbdm0NEYva5j.1 ID:  838  3068  7320  Senha: 344918</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +665,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -279,10 +752,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -305,8 +779,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -638,11 +1116,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B4729B-FAA5-4A97-A1A6-CF400177BBD1}">
-  <dimension ref="A1:R3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13735AE5-06B2-4737-BCA1-0F280F973E76}">
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="130.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,15 +1195,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="84.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104778</v>
+        <v>92215</v>
       </c>
       <c r="B2" s="5">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="C2" s="6">
-        <v>0.4375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -748,39 +1245,39 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="7" t="s">
         <v>31</v>
       </c>
+      <c r="R2" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105181</v>
+        <v>105287</v>
       </c>
       <c r="B3" s="5">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="C3" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.37569444444444444</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>38</v>
@@ -806,11 +1303,1265 @@
       <c r="Q3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="8" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>105371</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>104298</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105365</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>105474</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>105014</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>103125</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>103838</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104044</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105165</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>99370</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>92711</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>103737</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>101919</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>82990</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>103309</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>104995</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>97789</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>103509</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>77958</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.65416666666666667</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>101625</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>99569</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>97460</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/88415253122?pwd=QzlTNmxwdWpEeGVFZmdwM0lDUFJ4Zz09%20ID%20da%20reunião:%20884%201525%203122%20Senha%20de%20acesso:%20510562" xr:uid="{591A07F9-2959-4919-93CB-A3AD9304DD90}"/>
+    <hyperlink ref="R5" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1%20ID%20da%20reunião%20882%201575%201954%20Senha%20%20150077" xr:uid="{067DD09A-0EC6-4278-890B-CF419561F02A}"/>
+    <hyperlink ref="R6" r:id="rId3" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{B2DD1349-1814-4899-9D35-77EB8EBCBC43}"/>
+    <hyperlink ref="R7" r:id="rId4" xr:uid="{C517338F-BF6E-4815-BB46-A88C49F929AC}"/>
+    <hyperlink ref="R8" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%20050728" xr:uid="{59AEE509-077F-461E-9314-87D03BD0B448}"/>
+    <hyperlink ref="R9" r:id="rId6" xr:uid="{648E61A8-9F6E-4E73-8CD0-B4FBD6086661}"/>
+    <hyperlink ref="R11" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/83676367506?pwd=VlRlWmFnUGhwdWp3Y2xvaVkxdDFDZz09%20ID%20da%20reunião:%20836%207636%207506%20Senha:%2024680" xr:uid="{E889D12B-1848-4153-AC54-D6C3647678FE}"/>
+    <hyperlink ref="R12" r:id="rId8" display="mailto:ricardo.baracho@gmail.com" xr:uid="{3A81362D-D5EA-4E7E-BC56-43321FD4C0FE}"/>
+    <hyperlink ref="R13" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/81907928214?pwd=DdJyPKEOQWb3pMKbKp713raBQMIpao.1%20ID:%20%20819%20%200792%20%208214%20%20Senha:%20935266." xr:uid="{14E0A554-F290-43F7-A5B4-91284EF9793E}"/>
+    <hyperlink ref="R14" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/88971005711?pwd=FCU0CcOJlu66H4VR8hrXW2o1KrrqXb.1%20ID:%20889%20%207100%20%205711%20%20Senha:%20962801" xr:uid="{B38FEA93-2EC5-432E-8D77-F6DC75149635}"/>
+    <hyperlink ref="R15" r:id="rId11" xr:uid="{E02D146A-9473-424B-AEE4-80949E395D81}"/>
+    <hyperlink ref="R16" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{301A4E52-2401-49D3-AB83-5006CD159FC4}"/>
+    <hyperlink ref="R17" r:id="rId13" xr:uid="{EA8C0CEC-5A38-4E3C-B488-E87D867BFF7E}"/>
+    <hyperlink ref="R18" r:id="rId14" display="https://trt3-jus-br.zoom.us/my/varabh12" xr:uid="{99E2392B-36B5-4EEA-AE2F-A06B31DD07B3}"/>
+    <hyperlink ref="R19" r:id="rId15" xr:uid="{E70BECCF-3D50-4A17-81D8-494A89B803DD}"/>
+    <hyperlink ref="R20" r:id="rId16" display="https://trt15-jus-br.zoom.us/j/87345253855?pwd=eOmaFv9ph0gYOdbdibavbZapr1i2NE.1%20ID:%20%20873%20%204525%20%203855%20%20Senha:%20223572" xr:uid="{E0F1D676-88B0-4FDF-B3F6-708CA714FCFF}"/>
+    <hyperlink ref="R22" r:id="rId17" display="https://trt2-jus-br.zoom.us/j/87687135814?pwd=L21Bd0RobFB3V0I0VVpuMlBDUG5oUT09%20ID%20da%20reunião:%20876%208713%205814%20Senha%20de%20acesso:%20120826" xr:uid="{9DF4C4D4-34F6-42C0-B7B1-25ED187815ED}"/>
+    <hyperlink ref="R23" r:id="rId18" xr:uid="{61FFECE7-17FA-44C5-97E9-FF073B29FF08}"/>
+    <hyperlink ref="R24" r:id="rId19" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{D2A4FA29-D901-4C8E-ABB0-AA40B517722E}"/>
+    <hyperlink ref="R25" r:id="rId20" display="https://trt15-jus-br.zoom.us/j/83830687320?pwd=aH38p2gWpjsX9F8as5Kbdm0NEYva5j.1%20ID:%20%20838%20%203068%20%207320%20%20Senha:%20344918" xr:uid="{217039DE-0FCC-46C4-B2A3-3167A281CD73}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="117">
   <si>
     <t>data</t>
   </si>
@@ -49,49 +49,322 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
-  </si>
-  <si>
-    <t>VRO</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>TLI</t>
   </si>
   <si>
     <t>GSM</t>
   </si>
   <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
     <t>Grupo E1</t>
   </si>
   <si>
     <t>Grupo B1</t>
   </si>
   <si>
-    <t>Produtécnica Nordeste Comércio De Insumos Agrícolas Ltda.</t>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Robert Bosch Limitada</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Indústria Doceira E Alimentar Ltda.</t>
+  </si>
+  <si>
+    <t>Frutal Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Agrocerrado Produtos Agrícolas E Assistência Técnica Ltda.</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0000431-17.2026.5.10.0811</t>
-  </si>
-  <si>
-    <t>1001059-81.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Jhony Carlos Lucena Cardoso</t>
-  </si>
-  <si>
-    <t>Danilo Vieira Dos Santos Andrade Alves</t>
-  </si>
-  <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>10:50:00</t>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010556-64.2023.5.15.0082</t>
+  </si>
+  <si>
+    <t>1000973-20.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>1001013-02.2026.5.02.0462</t>
+  </si>
+  <si>
+    <t>0014731-48.2025.5.15.0077</t>
+  </si>
+  <si>
+    <t>0011763-13.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>0000846-69.2026.5.05.0251</t>
+  </si>
+  <si>
+    <t>0010954-47.2026.5.15.0133</t>
+  </si>
+  <si>
+    <t>0001673-39.2025.5.13.0010</t>
+  </si>
+  <si>
+    <t>0010064-52.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>0010295-44.2026.5.15.0131</t>
+  </si>
+  <si>
+    <t>0000761-97.2026.5.17.0009</t>
+  </si>
+  <si>
+    <t>0011575-56.2024.5.15.0087</t>
+  </si>
+  <si>
+    <t>0010718-92.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>0000010-77.2026.5.09.0092</t>
+  </si>
+  <si>
+    <t>0010907-03.2025.5.15.0103</t>
+  </si>
+  <si>
+    <t>0010466-75.2022.5.15.0087</t>
+  </si>
+  <si>
+    <t>0011112-47.2025.5.03.0012</t>
+  </si>
+  <si>
+    <t>0010432-81.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>0010828-57.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>1002332-26.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>1000813-89.2020.5.02.0434</t>
+  </si>
+  <si>
+    <t>0011034-70.2025.5.03.0071</t>
+  </si>
+  <si>
+    <t>0010034-31.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>0010505-52.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Miguel Jose De Souza</t>
+  </si>
+  <si>
+    <t>Sonia Soares Almeida</t>
+  </si>
+  <si>
+    <t>Davi Joao Da Silva</t>
+  </si>
+  <si>
+    <t>Ismael Jose Dos Santos</t>
+  </si>
+  <si>
+    <t>Matheus Felipe Januario Domingues</t>
+  </si>
+  <si>
+    <t>Gilson Meireles Dos Santos</t>
+  </si>
+  <si>
+    <t>Edivaldo Aparecido De Oliveira</t>
+  </si>
+  <si>
+    <t>Willan Hilario Marcelino</t>
+  </si>
+  <si>
+    <t>Jessica Nunes Da Silva</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Leite</t>
+  </si>
+  <si>
+    <t>Edilcivane Pereira Ottoni</t>
+  </si>
+  <si>
+    <t>Wesley Felipe Cezar Xavier</t>
+  </si>
+  <si>
+    <t>Claudio Richard De Godoy</t>
+  </si>
+  <si>
+    <t>Darlan Silva Quintiliano</t>
+  </si>
+  <si>
+    <t>Jeanio Berto Da Costa E Silva</t>
+  </si>
+  <si>
+    <t>Sidkley Jose Da Silva</t>
+  </si>
+  <si>
+    <t>Lucimar Da Silva Costa</t>
+  </si>
+  <si>
+    <t>Joao Batista Loiola De Sousa</t>
+  </si>
+  <si>
+    <t>Luciano Vicentim Da Cruz</t>
+  </si>
+  <si>
+    <t>Cesar Luiz Do Amaral</t>
+  </si>
+  <si>
+    <t>Alan Alves Sarmento</t>
+  </si>
+  <si>
+    <t>Yure De Andrade Barbosa</t>
+  </si>
+  <si>
+    <t>Rafael Gustavo Silva</t>
+  </si>
+  <si>
+    <t>Fabio Moreira</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>09:15:00</t>
+  </si>
+  <si>
+    <t>09:45:00</t>
+  </si>
+  <si>
+    <t>10:18:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>15:42:00</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
   </si>
 </sst>
 </file>
@@ -427,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -467,7 +740,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -476,33 +749,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -511,28 +784,798 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" t="s">
+        <v>33</v>
+      </c>
+      <c r="K25" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>MBF</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="137">
   <si>
     <t>data</t>
   </si>
@@ -49,52 +49,64 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>JPL</t>
   </si>
   <si>
     <t>MBF</t>
   </si>
   <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>RYL</t>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>ARC</t>
   </si>
   <si>
     <t>JNE</t>
   </si>
   <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
     <t>FCG</t>
   </si>
   <si>
-    <t>DPR</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
     <t>TLI</t>
   </si>
   <si>
-    <t>GSM</t>
+    <t>Grupo B1</t>
   </si>
   <si>
     <t>Grupo E2</t>
@@ -103,268 +115,316 @@
     <t>Grupo E1</t>
   </si>
   <si>
-    <t>Grupo B1</t>
+    <t>Grupo B2</t>
   </si>
   <si>
     <t>Grupo C</t>
   </si>
   <si>
-    <t>Grupo B3</t>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>A. Raymond Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Candeias - Can</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Robert Bosch Limitada</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Indústria Doceira E Alimentar Ltda.</t>
-  </si>
-  <si>
-    <t>Frutal Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Agrocerrado Produtos Agrícolas E Assistência Técnica Ltda.</t>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
   </si>
   <si>
     <t>Audiência de Conciliação - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Una - Presencial</t>
+    <t>Audiência Inicial - Presencial</t>
   </si>
   <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010556-64.2023.5.15.0082</t>
-  </si>
-  <si>
-    <t>1000973-20.2026.5.02.0462</t>
-  </si>
-  <si>
-    <t>1001013-02.2026.5.02.0462</t>
-  </si>
-  <si>
-    <t>0014731-48.2025.5.15.0077</t>
-  </si>
-  <si>
-    <t>0011763-13.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>0000846-69.2026.5.05.0251</t>
-  </si>
-  <si>
-    <t>0010954-47.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>0001673-39.2025.5.13.0010</t>
-  </si>
-  <si>
-    <t>0010064-52.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>0010295-44.2026.5.15.0131</t>
-  </si>
-  <si>
-    <t>0000761-97.2026.5.17.0009</t>
-  </si>
-  <si>
-    <t>0011575-56.2024.5.15.0087</t>
-  </si>
-  <si>
-    <t>0010718-92.2023.5.15.0071</t>
-  </si>
-  <si>
-    <t>0000010-77.2026.5.09.0092</t>
-  </si>
-  <si>
-    <t>0010907-03.2025.5.15.0103</t>
-  </si>
-  <si>
-    <t>0010466-75.2022.5.15.0087</t>
-  </si>
-  <si>
-    <t>0011112-47.2025.5.03.0012</t>
-  </si>
-  <si>
-    <t>0010432-81.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>0010828-57.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>1002332-26.2025.5.02.0434</t>
-  </si>
-  <si>
-    <t>1000813-89.2020.5.02.0434</t>
-  </si>
-  <si>
-    <t>0011034-70.2025.5.03.0071</t>
-  </si>
-  <si>
-    <t>0010034-31.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>0010505-52.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Miguel Jose De Souza</t>
-  </si>
-  <si>
-    <t>Sonia Soares Almeida</t>
-  </si>
-  <si>
-    <t>Davi Joao Da Silva</t>
-  </si>
-  <si>
-    <t>Ismael Jose Dos Santos</t>
-  </si>
-  <si>
-    <t>Matheus Felipe Januario Domingues</t>
-  </si>
-  <si>
-    <t>Gilson Meireles Dos Santos</t>
-  </si>
-  <si>
-    <t>Edivaldo Aparecido De Oliveira</t>
-  </si>
-  <si>
-    <t>Willan Hilario Marcelino</t>
-  </si>
-  <si>
-    <t>Jessica Nunes Da Silva</t>
-  </si>
-  <si>
-    <t>Marcos Paulo Leite</t>
-  </si>
-  <si>
-    <t>Edilcivane Pereira Ottoni</t>
-  </si>
-  <si>
-    <t>Wesley Felipe Cezar Xavier</t>
-  </si>
-  <si>
-    <t>Claudio Richard De Godoy</t>
-  </si>
-  <si>
-    <t>Darlan Silva Quintiliano</t>
-  </si>
-  <si>
-    <t>Jeanio Berto Da Costa E Silva</t>
-  </si>
-  <si>
-    <t>Sidkley Jose Da Silva</t>
-  </si>
-  <si>
-    <t>Lucimar Da Silva Costa</t>
-  </si>
-  <si>
-    <t>Joao Batista Loiola De Sousa</t>
-  </si>
-  <si>
-    <t>Luciano Vicentim Da Cruz</t>
-  </si>
-  <si>
-    <t>Cesar Luiz Do Amaral</t>
-  </si>
-  <si>
-    <t>Alan Alves Sarmento</t>
-  </si>
-  <si>
-    <t>Yure De Andrade Barbosa</t>
-  </si>
-  <si>
-    <t>Rafael Gustavo Silva</t>
-  </si>
-  <si>
-    <t>Fabio Moreira</t>
-  </si>
-  <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>09:01:00</t>
-  </si>
-  <si>
-    <t>09:15:00</t>
+    <t>Audiência Inicial - Semipresencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>0010127-62.2026.5.15.0092</t>
+  </si>
+  <si>
+    <t>0010503-33.2026.5.15.0097</t>
+  </si>
+  <si>
+    <t>0011078-07.2025.5.03.0066</t>
+  </si>
+  <si>
+    <t>0011006-40.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>0011440-58.2021.5.15.0084</t>
+  </si>
+  <si>
+    <t>0010785-80.2024.5.03.0063</t>
+  </si>
+  <si>
+    <t>0000258-98.2025.5.05.0121</t>
+  </si>
+  <si>
+    <t>1000694-21.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>0000439-62.2026.5.05.0122</t>
+  </si>
+  <si>
+    <t>0000049-56.2026.5.05.0037</t>
+  </si>
+  <si>
+    <t>1000903-95.2026.5.02.0205</t>
+  </si>
+  <si>
+    <t>0010013-06.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>0011603-18.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>1001223-46.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>1001305-68.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>0010199-21.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010190-19.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0010905-03.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>0010469-69.2026.5.15.0061</t>
+  </si>
+  <si>
+    <t>0010127-91.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0011598-50.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>0010198-36.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0011180-49.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>0010194-96.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010150-37.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>1001049-31.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>0011902-83.2023.5.15.0071</t>
+  </si>
+  <si>
+    <t>0012955-39.2025.5.15.0133</t>
+  </si>
+  <si>
+    <t>1000366-37.2025.5.02.0431</t>
+  </si>
+  <si>
+    <t>Weverson Frank Pinto De Carvalho</t>
+  </si>
+  <si>
+    <t>Leiliane Maria Da Rocha Nascimento Teixeira</t>
+  </si>
+  <si>
+    <t>Walleska Souza Menezes</t>
+  </si>
+  <si>
+    <t>Saulo De Tarso Da Silva</t>
+  </si>
+  <si>
+    <t>Maria Valdirene Santos Monteiro</t>
+  </si>
+  <si>
+    <t>Cristiano Felix Da Silva</t>
+  </si>
+  <si>
+    <t>Ryam Kedson Magalhaes Nascimento</t>
+  </si>
+  <si>
+    <t>Rubens Bernardes Da Silva</t>
+  </si>
+  <si>
+    <t>Vagner Bitencourt Dantas</t>
+  </si>
+  <si>
+    <t>Claudio Almeida Barbosa</t>
+  </si>
+  <si>
+    <t>Luciano Pompeo Pasqualini</t>
+  </si>
+  <si>
+    <t>Diego Vinicius Stabile David</t>
+  </si>
+  <si>
+    <t>Anderson Vilela Ribeiro</t>
+  </si>
+  <si>
+    <t>Edson Cavasso</t>
+  </si>
+  <si>
+    <t>Tiago Alves De Lima</t>
+  </si>
+  <si>
+    <t>Marcelo Antonio Lourenco</t>
+  </si>
+  <si>
+    <t>Luiz Marcos Dos Santos</t>
+  </si>
+  <si>
+    <t>Pablo Roberto Da Silva</t>
+  </si>
+  <si>
+    <t>Claudemir Moreira Mendes</t>
+  </si>
+  <si>
+    <t>Luiz Felipe Dos Santos Muniz</t>
+  </si>
+  <si>
+    <t>Osvaldo Ferreira</t>
+  </si>
+  <si>
+    <t>Jose Fidelis Ferreira</t>
+  </si>
+  <si>
+    <t>Viviane Domingues Lopes</t>
+  </si>
+  <si>
+    <t>Emerson Leandro De Jesus</t>
+  </si>
+  <si>
+    <t>Claudio Vinicius Ferreira Leite</t>
+  </si>
+  <si>
+    <t>Rafael Da Silva Sousa</t>
+  </si>
+  <si>
+    <t>Julio Cesar De Castro</t>
+  </si>
+  <si>
+    <t>Marcos Roberto Alves Da Silva</t>
+  </si>
+  <si>
+    <t>Akexsandra Lopes De Abreu</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
   </si>
   <si>
     <t>09:45:00</t>
   </si>
   <si>
-    <t>10:18:00</t>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>10:13:00</t>
   </si>
   <si>
     <t>11:00:00</t>
   </si>
   <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
-    <t>11:40:00</t>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
   </si>
   <si>
     <t>13:30:00</t>
   </si>
   <si>
+    <t>13:35:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
-    <t>15:05:00</t>
-  </si>
-  <si>
-    <t>15:15:00</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>15:40:00</t>
+    <t>15:20:00</t>
   </si>
   <si>
     <t>15:42:00</t>
-  </si>
-  <si>
-    <t>15:50:00</t>
-  </si>
-  <si>
-    <t>16:20:00</t>
-  </si>
-  <si>
-    <t>16:30:00</t>
   </si>
 </sst>
 </file>
@@ -700,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -740,7 +800,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -749,33 +809,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -784,628 +844,628 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K5" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K14" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
         <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" t="s">
         <v>44</v>
       </c>
-      <c r="G17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" t="s">
-        <v>36</v>
-      </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K20" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -1414,68 +1474,68 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K22" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1484,10 +1544,10 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
         <v>48</v>
@@ -1496,86 +1556,261 @@
         <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K23" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K24" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s">
         <v>44</v>
       </c>
-      <c r="G25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" t="s">
-        <v>33</v>
-      </c>
       <c r="K25" t="s">
-        <v>116</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" t="s">
+        <v>81</v>
+      </c>
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s">
+        <v>111</v>
+      </c>
+      <c r="J27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" t="s">
+        <v>112</v>
+      </c>
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" t="s">
+        <v>113</v>
+      </c>
+      <c r="J29" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" t="s">
+        <v>114</v>
+      </c>
+      <c r="J30" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>BSO</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="136">
   <si>
     <t>data</t>
   </si>
@@ -49,367 +49,364 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
-  </si>
-  <si>
-    <t>BSO</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>ARC</t>
   </si>
   <si>
     <t>RYL</t>
   </si>
   <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
     <t>CAL</t>
   </si>
   <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>ARC</t>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>BCF</t>
   </si>
   <si>
     <t>JNE</t>
   </si>
   <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>FCG</t>
-  </si>
-  <si>
-    <t>TLI</t>
+    <t>Grupo E2</t>
   </si>
   <si>
     <t>Grupo B1</t>
   </si>
   <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
   </si>
   <si>
     <t>Grupo B2</t>
   </si>
   <si>
-    <t>Grupo C</t>
+    <t>Viterra Bioenergia S.A.</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>A. Raymond Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Panificadora Cepam Ltda.</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
   </si>
   <si>
     <t>Embraer S.A.</t>
   </si>
   <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A. - Candeias - Can</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
+    <t>Audiência de Conciliação - Semipresencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
   </si>
   <si>
     <t>Audiência Inicial - Telepresencial</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Semipresencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>0010127-62.2026.5.15.0092</t>
-  </si>
-  <si>
-    <t>0010503-33.2026.5.15.0097</t>
-  </si>
-  <si>
-    <t>0011078-07.2025.5.03.0066</t>
-  </si>
-  <si>
-    <t>0011006-40.2023.5.15.0071</t>
-  </si>
-  <si>
-    <t>0011440-58.2021.5.15.0084</t>
-  </si>
-  <si>
-    <t>0010785-80.2024.5.03.0063</t>
-  </si>
-  <si>
-    <t>0000258-98.2025.5.05.0121</t>
-  </si>
-  <si>
-    <t>1000694-21.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>0000439-62.2026.5.05.0122</t>
-  </si>
-  <si>
-    <t>0000049-56.2026.5.05.0037</t>
-  </si>
-  <si>
-    <t>1000903-95.2026.5.02.0205</t>
-  </si>
-  <si>
-    <t>0010013-06.2025.5.15.0013</t>
-  </si>
-  <si>
-    <t>0011603-18.2025.5.15.0013</t>
-  </si>
-  <si>
-    <t>1001223-46.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>1001305-68.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>0010199-21.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>0010190-19.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>0010905-03.2023.5.15.0071</t>
-  </si>
-  <si>
-    <t>0010469-69.2026.5.15.0061</t>
-  </si>
-  <si>
-    <t>0010127-91.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>0011598-50.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>0010198-36.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>0011180-49.2023.5.15.0071</t>
-  </si>
-  <si>
-    <t>0010194-96.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>0010150-37.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>1001049-31.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>0011902-83.2023.5.15.0071</t>
-  </si>
-  <si>
-    <t>0012955-39.2025.5.15.0133</t>
-  </si>
-  <si>
-    <t>1000366-37.2025.5.02.0431</t>
-  </si>
-  <si>
-    <t>Weverson Frank Pinto De Carvalho</t>
-  </si>
-  <si>
-    <t>Leiliane Maria Da Rocha Nascimento Teixeira</t>
-  </si>
-  <si>
-    <t>Walleska Souza Menezes</t>
-  </si>
-  <si>
-    <t>Saulo De Tarso Da Silva</t>
-  </si>
-  <si>
-    <t>Maria Valdirene Santos Monteiro</t>
-  </si>
-  <si>
-    <t>Cristiano Felix Da Silva</t>
-  </si>
-  <si>
-    <t>Ryam Kedson Magalhaes Nascimento</t>
-  </si>
-  <si>
-    <t>Rubens Bernardes Da Silva</t>
-  </si>
-  <si>
-    <t>Vagner Bitencourt Dantas</t>
-  </si>
-  <si>
-    <t>Claudio Almeida Barbosa</t>
-  </si>
-  <si>
-    <t>Luciano Pompeo Pasqualini</t>
-  </si>
-  <si>
-    <t>Diego Vinicius Stabile David</t>
-  </si>
-  <si>
-    <t>Anderson Vilela Ribeiro</t>
-  </si>
-  <si>
-    <t>Edson Cavasso</t>
-  </si>
-  <si>
-    <t>Tiago Alves De Lima</t>
-  </si>
-  <si>
-    <t>Marcelo Antonio Lourenco</t>
-  </si>
-  <si>
-    <t>Luiz Marcos Dos Santos</t>
-  </si>
-  <si>
-    <t>Pablo Roberto Da Silva</t>
-  </si>
-  <si>
-    <t>Claudemir Moreira Mendes</t>
-  </si>
-  <si>
-    <t>Luiz Felipe Dos Santos Muniz</t>
-  </si>
-  <si>
-    <t>Osvaldo Ferreira</t>
-  </si>
-  <si>
-    <t>Jose Fidelis Ferreira</t>
-  </si>
-  <si>
-    <t>Viviane Domingues Lopes</t>
-  </si>
-  <si>
-    <t>Emerson Leandro De Jesus</t>
-  </si>
-  <si>
-    <t>Claudio Vinicius Ferreira Leite</t>
-  </si>
-  <si>
-    <t>Rafael Da Silva Sousa</t>
-  </si>
-  <si>
-    <t>Julio Cesar De Castro</t>
-  </si>
-  <si>
-    <t>Marcos Roberto Alves Da Silva</t>
-  </si>
-  <si>
-    <t>Akexsandra Lopes De Abreu</t>
-  </si>
-  <si>
-    <t>08:33:00</t>
-  </si>
-  <si>
-    <t>08:35:00</t>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010685-63.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>1000527-98.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>1000832-57.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>1000628-78.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>0000827-44.2026.5.08.0101</t>
+  </si>
+  <si>
+    <t>0010704-69.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>1001851-66.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>1002207-61.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>1001238-18.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>1001373-05.2026.5.02.0601</t>
+  </si>
+  <si>
+    <t>0011042-44.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>1001057-08.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>1000383-33.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>1000592-97.2025.5.02.0445</t>
+  </si>
+  <si>
+    <t>0001617-53.2025.5.09.0095</t>
+  </si>
+  <si>
+    <t>0001757-47.2025.5.09.0658</t>
+  </si>
+  <si>
+    <t>1000780-92.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>0010215-72.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0010173-80.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0010480-06.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>0010175-50.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0010530-32.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>1019460-73.2020.8.26.0577</t>
+  </si>
+  <si>
+    <t>0010609-11.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>0010607-41.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>0010417-72.2026.5.15.0029</t>
+  </si>
+  <si>
+    <t>0010300-33.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>0012892-87.2025.5.15.0044</t>
+  </si>
+  <si>
+    <t>0010541-87.2019.5.15.0130</t>
+  </si>
+  <si>
+    <t>Michel Roque Martins Dias</t>
+  </si>
+  <si>
+    <t>Mistoncleso Cruz Da Silva</t>
+  </si>
+  <si>
+    <t>Marli Nogueira Da Silva</t>
+  </si>
+  <si>
+    <t>Adriano Jose Da Silva</t>
+  </si>
+  <si>
+    <t>Rildo Dos Santos Dias</t>
+  </si>
+  <si>
+    <t>Bruno Duque Vanderlei</t>
+  </si>
+  <si>
+    <t>Yago Henrique Almeida Luz</t>
+  </si>
+  <si>
+    <t>Giovani Gustavo Ferreira Da Silva</t>
+  </si>
+  <si>
+    <t>Reinaldo Monteiro</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Arruda Croda</t>
+  </si>
+  <si>
+    <t>Renan De Azevedo Gomes</t>
+  </si>
+  <si>
+    <t>Elizeu Luiz Freire</t>
+  </si>
+  <si>
+    <t>Wesley Thiago Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>Marisilda Henriques</t>
+  </si>
+  <si>
+    <t>Rafael Cordeiro Gripa</t>
+  </si>
+  <si>
+    <t>Arilson Moraes De Almeida</t>
+  </si>
+  <si>
+    <t>Flavio Luiz Cossa</t>
+  </si>
+  <si>
+    <t>Ronan Ramos Gregorio Almeida</t>
+  </si>
+  <si>
+    <t>Vinicius Andre Freitas Diniz</t>
+  </si>
+  <si>
+    <t>Ricardo Mauricio Contel</t>
+  </si>
+  <si>
+    <t>Valdir Pereira Leal</t>
+  </si>
+  <si>
+    <t>Thalia Francisca Ribeiro Da Silva E Silva</t>
+  </si>
+  <si>
+    <t>Daniel Dos Santos Barbosa</t>
+  </si>
+  <si>
+    <t>Tiago Vieira De Sousa</t>
+  </si>
+  <si>
+    <t>Damiao Euflausino Alves</t>
+  </si>
+  <si>
+    <t>Daniel Antonio</t>
+  </si>
+  <si>
+    <t>Matheus Alberto Silva</t>
+  </si>
+  <si>
+    <t>Marcos Lopes Da Silva</t>
+  </si>
+  <si>
+    <t>Gilson Trindade Gama</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
   </si>
   <si>
     <t>09:00:00</t>
   </si>
   <si>
+    <t>09:15:00</t>
+  </si>
+  <si>
     <t>09:20:00</t>
   </si>
   <si>
-    <t>09:30:00</t>
-  </si>
-  <si>
-    <t>09:40:00</t>
-  </si>
-  <si>
-    <t>09:45:00</t>
+    <t>09:50:00</t>
   </si>
   <si>
     <t>10:00:00</t>
   </si>
   <si>
-    <t>10:13:00</t>
-  </si>
-  <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
-    <t>11:10:00</t>
-  </si>
-  <si>
-    <t>11:15:00</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>13:35:00</t>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>13:27:00</t>
+  </si>
+  <si>
+    <t>13:34:00</t>
+  </si>
+  <si>
+    <t>13:42:00</t>
   </si>
   <si>
     <t>14:00:00</t>
   </si>
   <si>
-    <t>14:15:00</t>
+    <t>14:20:00</t>
   </si>
   <si>
     <t>14:30:00</t>
@@ -418,13 +415,13 @@
     <t>14:40:00</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>15:20:00</t>
-  </si>
-  <si>
-    <t>15:42:00</t>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
   </si>
 </sst>
 </file>
@@ -800,7 +797,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -809,33 +806,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -844,33 +841,33 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -879,33 +876,33 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -914,33 +911,33 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -949,25 +946,25 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
         <v>117</v>
@@ -975,209 +972,209 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" t="s">
         <v>122</v>
@@ -1185,34 +1182,34 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s">
         <v>123</v>
@@ -1220,19 +1217,19 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>50</v>
@@ -1241,13 +1238,13 @@
         <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K14" t="s">
         <v>124</v>
@@ -1255,34 +1252,34 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K15" t="s">
         <v>125</v>
@@ -1290,34 +1287,34 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" t="s">
         <v>126</v>
@@ -1325,34 +1322,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K17" t="s">
         <v>127</v>
@@ -1360,34 +1357,34 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K18" t="s">
         <v>128</v>
@@ -1395,69 +1392,69 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
         <v>28</v>
       </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K20" t="s">
         <v>129</v>
@@ -1465,34 +1462,34 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K21" t="s">
         <v>130</v>
@@ -1500,104 +1497,104 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K24" t="s">
         <v>131</v>
@@ -1605,34 +1602,34 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K25" t="s">
         <v>132</v>
@@ -1640,104 +1637,104 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
         <v>134</v>
@@ -1745,72 +1742,72 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J29" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="K29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>AAP</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1948C94B-FE47-4E82-87E9-6CF121AB5BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{488BA91F-948D-437E-B5F4-98A236408E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5E957AC2-4C38-4A88-A791-11AA3C000AF5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA056DD-E450-4C57-B6F0-B71371008E73}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="222">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,37 +95,145 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência de Conciliação - Semipresencial</t>
-  </si>
-  <si>
-    <t>0010685-63.2026.5.15.0050</t>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>0011446-11.2026.5.15.0013</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Luciano Aparecido Pereira</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$                 3.190,34</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1001605-70.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Everton Caldeira Marquesine</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             200.734,15</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>0012525-60.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Reinaldo Aparecido Dos Santos</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             107.093,69</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000008-89.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Everaldo Kovalchuk</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$               39.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/szrfs ID da reunião: 896 7091 7043 Senha: 556658</t>
+  </si>
+  <si>
+    <t>0010718-53.2026.5.15.0050</t>
   </si>
   <si>
     <t>Viterra Bioenergia S.A.</t>
   </si>
   <si>
-    <t>Michel Roque Martins Dias</t>
+    <t>Marco Aurelio Claudio</t>
   </si>
   <si>
     <t>DRACENA</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
     <t>VARA DO TRABALHO</t>
   </si>
   <si>
     <t>Conhecimento</t>
   </si>
   <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             338.733,87</t>
+    <t>R$          1.025.120,00</t>
   </si>
   <si>
     <t>Grupo E2</t>
@@ -137,545 +245,473 @@
     <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
   </si>
   <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000527-98.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Mistoncleso Cruz Da Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$             183.783,60</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1000832-57.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Marli Nogueira Da Silva</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$             173.095,00</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010598-92.2026.5.03.0066</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Da Silva</t>
+  </si>
+  <si>
+    <t>MANHUAÇU</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$               62.608,11</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/varamanhuacu</t>
+  </si>
+  <si>
+    <t>1000510-62.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Cleiton Mendonca De Souza</t>
+  </si>
+  <si>
+    <t>R$             338.128,52</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0010657-67.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda. &amp; Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Fernando Henrique Grecco Dos Santos Garcia</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$             519.531,10</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012012-63.2024.5.15.0066</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Edivane Dos Santos</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PRETO</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               81.480,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/7093890373?pwd=eEJTaWhnbTRwVXJrVTR0R0RyMUhkdz09 Id da reunião: 7093890373 Senha da sala: 345356</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000584-28.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Welington Tavian Baptista</t>
+  </si>
+  <si>
+    <t>R$             939.102,40</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0024058-02.2026.5.24.0022</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Taiane Lima Da Silva</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$               92.200,00</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/my/trt24douvt2sala2</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011078-07.2025.5.03.0066</t>
+  </si>
+  <si>
+    <t>Walleska Souza Menezes</t>
+  </si>
+  <si>
+    <t>VARA DO TRBALHO</t>
+  </si>
+  <si>
+    <t>R$               88.187,38</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011770-60.2025.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Isabela Carolina Bento Belini Vilela</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>06ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             287.798,68</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81390598525?pwd=rdGf0eRPC3KeSMHZlUecdE1edZpE5R.1 ID da reunião: 813 9059 8525 Senha: 127812</t>
+  </si>
+  <si>
+    <t>0012741-24.2025.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Gilberlandio Cascimiro Barbosa</t>
+  </si>
+  <si>
+    <t>R$             236.985,97</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/85763756385?pwd=ZTBCT3ZkZVg1QUVqMFVBNFcxUDdmQT0  ID: 857 6375 6385 e Senha de acesso: 958777</t>
+  </si>
+  <si>
+    <t>0001208-68.2025.5.09.0195</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Cerli Coelho Gomes</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               58.494,52</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/lauqj ID da reunião: 89116526039 Senha de acesso: AdbrJfUkLV</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>1000639-09.2026.5.02.0034</t>
+  </si>
+  <si>
+    <t>Colégio Curumim S/S Ltda</t>
+  </si>
+  <si>
+    <t>Andre Luiz Da Silva Rocumback</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>34ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               48.019,81</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>1002378-21.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Marcilio Alan Ferreira Cavalcanti</t>
+  </si>
+  <si>
+    <t>R$             646.662,33</t>
   </si>
   <si>
     <t>LMI</t>
   </si>
   <si>
-    <t>1000628-78.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>Adriano Jose Da Silva</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          2.518.007,92</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
     <t>BSO</t>
   </si>
   <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000827-44.2026.5.08.0101</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Rildo Dos Santos Dias</t>
-  </si>
-  <si>
-    <t>ABAETETUBA</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             840.804,54</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09 ID: 850  5396  9243 Senha: 1VTAbaete.</t>
-  </si>
-  <si>
-    <t>0010704-69.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Bruno Duque Vanderlei</t>
-  </si>
-  <si>
-    <t>R$             107.564,68</t>
+    <t>1001149-46.2026.5.02.0511</t>
+  </si>
+  <si>
+    <t>Ame Digital Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Daiana Arruda Santos Silva</t>
+  </si>
+  <si>
+    <t>ITAPEVI</t>
+  </si>
+  <si>
+    <t>R$             159.297,56</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Jairo Felipe, (11) 98807-2750</t>
+  </si>
+  <si>
+    <t>0010921-49.2025.5.15.0050</t>
+  </si>
+  <si>
+    <t>Joao Maria Bonifacio Ribeiro</t>
+  </si>
+  <si>
+    <t>Liquidação</t>
+  </si>
+  <si>
+    <t>R$               35.645,00</t>
   </si>
   <si>
     <t>FCG</t>
   </si>
   <si>
-    <t>1001851-66.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>Yago Henrique Almeida Luz</t>
-  </si>
-  <si>
-    <t>R$             107.301,15</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1002207-61.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>Giovani Gustavo Ferreira Da Silva</t>
-  </si>
-  <si>
-    <t>R$             432.485,73</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001238-18.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Reinaldo Monteiro</t>
-  </si>
-  <si>
-    <t>R$             291.960,14</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>1001373-05.2026.5.02.0601</t>
-  </si>
-  <si>
-    <t>Panificadora Cepam Ltda.</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Arruda Croda</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>25ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>ZONA LESTE</t>
-  </si>
-  <si>
-    <t>R$                 8.626,39</t>
-  </si>
-  <si>
-    <t>RYL</t>
+    <t>https://trt15-jus-br.zoom.us/j/86722354209?pwd=V01VL0NmTFZSZEdhcFhjM0tIczd3dz09 ID da reunião: 867 2235 4209 Senha de acesso: 947812</t>
+  </si>
+  <si>
+    <t>1001275-39.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Danilo Oliveira De Lima</t>
+  </si>
+  <si>
+    <t>R$               66.734,63</t>
+  </si>
+  <si>
+    <t>0011437-35.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Paulinia - Pln</t>
+  </si>
+  <si>
+    <t>Jose Maria Pereira</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$               70.308,57</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09 ID da reunião: 83352065501 Senha de acesso: 368465</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Presencial</t>
+  </si>
+  <si>
+    <t>0024683-80.2026.5.24.0072</t>
+  </si>
+  <si>
+    <t>Rio Parana Energia S.A</t>
+  </si>
+  <si>
+    <t>Flavio Rodrigues Valente</t>
+  </si>
+  <si>
+    <t>TRÊS LAGOAS</t>
+  </si>
+  <si>
+    <t>R$             170.573,34</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/2274633182</t>
+  </si>
+  <si>
+    <t>1000607-04.2022.5.02.0435</t>
+  </si>
+  <si>
+    <t>Marcelo Silva Rodrigues</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>R$             336.223,96</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/82477928530?pwd=WENUNkRGZ1NLbUY4VFZLdjdjOXBxUT09 ID da reunião: 824 7792 8530 Senha de acesso: 391604</t>
+  </si>
+  <si>
+    <t>0011841-62.2025.5.15.0134</t>
+  </si>
+  <si>
+    <t>Tiago Viegas Carvalho</t>
+  </si>
+  <si>
+    <t>LEME</t>
+  </si>
+  <si>
+    <t>R$          1.203.488,64</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/8060729658?pwd=NDNlcU8wVzcxZ09qVjFDRFBGT2ljQT09 ID da reunião: 806 072 9658 Senha de acesso: 868717</t>
+  </si>
+  <si>
+    <t>1001826-18.2023.5.02.0435</t>
+  </si>
+  <si>
+    <t>Rodrigo Fernandes Da Silva</t>
+  </si>
+  <si>
+    <t>R$             204.334,53</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/88297719933?pwd=U3VWVjB2RHh0Vm9VMHZ0ZFd1eUk1dz09 ID da reunião: 882 9771 9933 Senha de acesso: 091850</t>
+  </si>
+  <si>
+    <t>1000899-59.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Carlos Alberto De Castro</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$               86.225,68</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/88959116257?pwd=Q09WTmd6SnZibUUrZWxMSFdiRm9tUT09 ID da reunião: 889 5911 6257 Senha de acesso: 136898</t>
+  </si>
+  <si>
+    <t>1001342-80.2021.5.02.0432</t>
+  </si>
+  <si>
+    <t>Natanael Marques Vieira</t>
+  </si>
+  <si>
+    <t>Recurso Parcial de Mérito</t>
+  </si>
+  <si>
+    <t>R$             137.042,10</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/85239557292?pwd=enBMVGxIVlR2bG5uUmk3Sy8yWmR6dz09 ID da reunião: 852 3955 7292 Senha de acesso: 611035</t>
+  </si>
+  <si>
+    <t>1001636-94.2024.5.02.0055</t>
+  </si>
+  <si>
+    <t>Construtora Elias Victor Nigri Ltda.</t>
+  </si>
+  <si>
+    <t>Derivaldo Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>CEJUSC RUY BARBOSA</t>
+  </si>
+  <si>
+    <t>R$             544.507,98</t>
   </si>
   <si>
     <t>CAL</t>
   </si>
   <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0011042-44.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Renan De Azevedo Gomes</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             200.000,00</t>
-  </si>
-  <si>
-    <t>JNE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87100825693?pwd=Ulpt0u9ZPHbqliJGGGKn8D17RPJwW2.1 ID da reunião: 871 0082 5693 Senha: 864984</t>
-  </si>
-  <si>
-    <t>1001057-08.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Elizeu Luiz Freire</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             158.737,00</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>1000383-33.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Wesley Thiago Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>Ação de Consignação em Pagamento</t>
-  </si>
-  <si>
-    <t>R$                 8.821,89</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1000592-97.2025.5.02.0445</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Marisilda Henriques</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>06ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$          2.433.235,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0001617-53.2025.5.09.0095</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Rafael Cordeiro Gripa</t>
-  </si>
-  <si>
-    <t>FOZ DO IGUAÇU</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             326.167,00</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/hpqcg ID da Reunião: 84656312612 Senha: ws3xteM7dN</t>
-  </si>
-  <si>
-    <t>0001757-47.2025.5.09.0658</t>
-  </si>
-  <si>
-    <t>Arilson Moraes De Almeida</t>
-  </si>
-  <si>
-    <t>R$             188.600,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/j7hoq ID da Reunião: 85022178469 Senha: MnoK8bxzgu</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000780-92.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Flavio Luiz Cossa</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>Recursal com Execução Provisória</t>
-  </si>
-  <si>
-    <t>Cumprimento de Sentença</t>
-  </si>
-  <si>
-    <t>R$             565.498,97</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09 ID da reunião: 818 8187 3237 Senha de acesso: 459217</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010215-72.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Ronan Ramos Gregorio Almeida</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             112.417,99</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0010173-80.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Vinicius Andre Freitas Diniz</t>
-  </si>
-  <si>
-    <t>R$             182.474,98</t>
-  </si>
-  <si>
-    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>0010480-06.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Ricardo Mauricio Contel</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>R$             300.000,00</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
-  </si>
-  <si>
-    <t>0010175-50.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Valdir Pereira Leal</t>
-  </si>
-  <si>
-    <t>R$             115.000,00</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>0010530-32.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Thalia Francisca Ribeiro Da Silva E Silva</t>
-  </si>
-  <si>
-    <t>R$               74.592,48</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>1019460-73.2020.8.26.0577</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Daniel Dos Santos Barbosa</t>
-  </si>
-  <si>
-    <t>SAO JOSE DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>08ª VARA CÍVEL</t>
-  </si>
-  <si>
-    <t>Pedido de Benefício - INSS</t>
-  </si>
-  <si>
-    <t>R$               12.540,00</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>0010609-11.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Tiago Vieira De Sousa</t>
-  </si>
-  <si>
-    <t>R$             216.000,00</t>
-  </si>
-  <si>
-    <t>0010607-41.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Damiao Euflausino Alves</t>
-  </si>
-  <si>
-    <t>R$             187.000,00</t>
-  </si>
-  <si>
-    <t>0010417-72.2026.5.15.0029</t>
-  </si>
-  <si>
-    <t>Daniel Antonio</t>
-  </si>
-  <si>
-    <t>JABOTICABAL</t>
-  </si>
-  <si>
-    <t>R$          1.318.000,00</t>
-  </si>
-  <si>
-    <t>https://zoom.us/j/3072626738 ID da reunião: 3072626738 Senha: 159753</t>
-  </si>
-  <si>
-    <t>0010300-33.2026.5.15.0045</t>
-  </si>
-  <si>
-    <t>Matheus Alberto Silva</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$               96.000,00</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>0012892-87.2025.5.15.0044</t>
-  </si>
-  <si>
-    <t>Marcos Lopes Da Silva</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             127.204,51</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09 ID da reunião: 839 0818 7251 e Senha de acesso: 959576</t>
-  </si>
-  <si>
-    <t>0010541-87.2019.5.15.0130</t>
-  </si>
-  <si>
-    <t>Gilson Trindade Gama</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$             326.430,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86385704640?pwd=g1Ig2NoEnHBDvn3uZhXt1tmbVhuO14.1</t>
+    <t>https://trt2-jus-br.zoom.us/j/81872601242?pwd=dmxJTVdoVjBmRGMzSUFKRVoyN0Jndz09</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>R$             544.507,98</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -695,14 +731,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -759,14 +787,16 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -775,18 +805,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -809,12 +840,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1146,29 +1173,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B93C17-7185-46B4-8EC7-C49F3AE7F90C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72B31BF-DC39-4A6F-99E4-E27F8E96566B}">
   <dimension ref="A1:R30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="121" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="111.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,15 +1252,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105072</v>
+        <v>104834</v>
       </c>
       <c r="B2" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C2" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1274,45 +1302,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
+      <c r="R2" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104495</v>
+        <v>102040</v>
       </c>
       <c r="B3" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C3" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1332,43 +1360,43 @@
       <c r="Q3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>103645</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105206</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46232</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="H4" s="7" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1377,54 +1405,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>103745</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46233</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>100523</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46232</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J5" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1433,54 +1461,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="P5" s="7" t="s">
         <v>56</v>
       </c>
       <c r="Q5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="R5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="8" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="6" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105065</v>
+        <v>105148</v>
       </c>
       <c r="B6" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C6" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1489,10 +1517,10 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>66</v>
@@ -1500,40 +1528,40 @@
       <c r="Q6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105105</v>
+        <v>105566</v>
       </c>
       <c r="B7" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C7" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>25</v>
@@ -1545,54 +1573,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>31</v>
+        <v>75</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>102846</v>
+        <v>104499</v>
       </c>
       <c r="B8" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C8" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1601,54 +1629,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>43</v>
+        <v>81</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>103333</v>
+        <v>105115</v>
       </c>
       <c r="B9" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C9" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1657,54 +1685,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>43</v>
+        <v>88</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>105455</v>
+        <v>99079</v>
       </c>
       <c r="B10" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C10" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.42569444444444443</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1713,110 +1741,110 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>43</v>
+        <v>99</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>105327</v>
+        <v>104578</v>
       </c>
       <c r="B11" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C11" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>43</v>
+        <v>105</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>104889</v>
+        <v>104380</v>
       </c>
       <c r="B12" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4375</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1825,54 +1853,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105230</v>
+        <v>105286</v>
       </c>
       <c r="B13" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C13" s="6">
-        <v>0.47222222222222221</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1881,110 +1909,110 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>43</v>
+        <v>75</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>104323</v>
+        <v>103401</v>
       </c>
       <c r="B14" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C14" s="6">
-        <v>0.49305555555555558</v>
+        <v>0.4375</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>43</v>
+        <v>87</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>104171</v>
+        <v>103407</v>
       </c>
       <c r="B15" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C15" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1993,54 +2021,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>43</v>
+        <v>87</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>103594</v>
+        <v>102142</v>
       </c>
       <c r="B16" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C16" s="6">
-        <v>0.56041666666666667</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2049,54 +2077,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>131</v>
+        <v>99</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>103590</v>
+        <v>105113</v>
       </c>
       <c r="B17" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C17" s="6">
-        <v>0.56527777777777777</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2105,110 +2133,110 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>135</v>
+        <v>149</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>104817</v>
+        <v>103621</v>
       </c>
       <c r="B18" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C18" s="6">
-        <v>0.5708333333333333</v>
+        <v>0.47569444444444442</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>143</v>
+        <v>155</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>104360</v>
+        <v>104939</v>
       </c>
       <c r="B19" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C19" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2217,54 +2245,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>152</v>
+        <v>163</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>104030</v>
+        <v>101864</v>
       </c>
       <c r="B20" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C20" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2273,54 +2301,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>156</v>
+        <v>169</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105013</v>
+        <v>105465</v>
       </c>
       <c r="B21" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C21" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2329,54 +2357,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>162</v>
+        <v>81</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>104029</v>
+        <v>102592</v>
       </c>
       <c r="B22" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C22" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.55208333333333337</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2385,54 +2413,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>156</v>
+        <v>75</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>105006</v>
+        <v>104799</v>
       </c>
       <c r="B23" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C23" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.57222222222222219</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2441,110 +2469,110 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>162</v>
+        <v>186</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>93563</v>
+        <v>86787</v>
       </c>
       <c r="B24" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C24" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>174</v>
+        <v>37</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>181</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>192</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>105005</v>
+        <v>103154</v>
       </c>
       <c r="B25" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C25" s="6">
-        <v>0.61111111111111116</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2553,54 +2581,54 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>105009</v>
+        <v>95848</v>
       </c>
       <c r="B26" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C26" s="6">
-        <v>0.61805555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2609,166 +2637,166 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>162</v>
+        <v>81</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>104781</v>
+        <v>105095</v>
       </c>
       <c r="B27" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C27" s="6">
-        <v>0.63194444444444442</v>
+        <v>0.60069444444444442</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>26</v>
+        <v>205</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R27" s="8" t="s">
-        <v>192</v>
+        <v>42</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
-        <v>104065</v>
+        <v>82370</v>
       </c>
       <c r="B28" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C28" s="6">
-        <v>0.63194444444444442</v>
+        <v>0.65625</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>43</v>
+        <v>105</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>103414</v>
+        <v>100423</v>
       </c>
       <c r="B29" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C29" s="6">
-        <v>0.63194444444444442</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>26</v>
@@ -2777,54 +2805,54 @@
         <v>27</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>202</v>
+        <v>218</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
-        <v>96258</v>
+        <v>99594</v>
       </c>
       <c r="B30" s="5">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C30" s="6">
-        <v>0.65625</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>26</v>
@@ -2833,40 +2861,43 @@
         <v>27</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>209</v>
+        <v>218</v>
+      </c>
+      <c r="R30" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{94E2FBC1-C2E7-4B74-9E6B-DA5BAAE3929A}"/>
-    <hyperlink ref="R6" r:id="rId2" display="https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09%20ID:%20850%20%205396%20%209243%20Senha:%201VTAbaete." xr:uid="{7BD1F58B-BB5E-487B-975E-14943DB5FCD3}"/>
-    <hyperlink ref="R7" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{1C870E57-7BAE-4003-9CFB-377D4DBBA871}"/>
-    <hyperlink ref="R12" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/87100825693?pwd=Ulpt0u9ZPHbqliJGGGKn8D17RPJwW2.1%20ID%20da%20reunião:%20871%200082%205693%20Senha:%20864984" xr:uid="{47BC48E8-191E-4A1B-9233-B1B5E2FB51D0}"/>
-    <hyperlink ref="R16" r:id="rId5" xr:uid="{08640A5A-8B6B-4EAC-87F5-86BCDF5D1E0E}"/>
-    <hyperlink ref="R17" r:id="rId6" xr:uid="{EF00F63F-74BE-4BD0-848A-0F4C3BD2D6EC}"/>
-    <hyperlink ref="R18" r:id="rId7" display="https://trt2-jus-br.zoom.us/j/81881873237?pwd=aEs5S29DM2srNHRuRGFVM2ZEYkVUZz09%20ID%20da%20reunião:%20818%208187%203237%20Senha%20de%20acesso:%20459217" xr:uid="{B5F8CDFE-F7E6-429A-9945-B7AD869A5935}"/>
-    <hyperlink ref="R19" r:id="rId8" xr:uid="{37E6A29D-3634-42F7-A2BB-428A9895F54C}"/>
-    <hyperlink ref="R20" r:id="rId9" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{1D375665-4441-4541-A698-63F4F964A26C}"/>
-    <hyperlink ref="R21" r:id="rId10" xr:uid="{82EDF4DE-21BA-4D05-B9F8-4E42FA45026C}"/>
-    <hyperlink ref="R22" r:id="rId11" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{7A149931-A36C-45C1-B336-AB52AC373069}"/>
-    <hyperlink ref="R23" r:id="rId12" xr:uid="{E4D1CF2C-D2EA-42D8-82C4-79508ACFED23}"/>
-    <hyperlink ref="R25" r:id="rId13" xr:uid="{6347FD22-0791-4EEB-80AF-63C5C4D5E585}"/>
-    <hyperlink ref="R26" r:id="rId14" xr:uid="{EAF2C722-A498-4115-A4B0-59F6A4F0100D}"/>
-    <hyperlink ref="R27" r:id="rId15" xr:uid="{DF800CF1-A92F-4AC6-A808-3A316822FA8B}"/>
-    <hyperlink ref="R29" r:id="rId16" display="https://us02web.zoom.us/j/83908187251?pwd=Ty9tcHNFb0pLZk5WQ0l2Y0V3ZHhhdz09%20ID%20da%20reunião:%20839%200818%207251%20e%20Senha%20de%20acesso:%20959576" xr:uid="{EC4398F5-76A5-439E-99D1-62C9A2059FDA}"/>
-    <hyperlink ref="R30" r:id="rId17" xr:uid="{3A595EC5-273C-450A-8DD3-51F1C8129426}"/>
+    <hyperlink ref="R5" r:id="rId1" xr:uid="{674EBA33-DB4C-4F65-9DBF-C83992C187BE}"/>
+    <hyperlink ref="R6" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{51D7CC3B-7D15-40F8-8886-F87945A63542}"/>
+    <hyperlink ref="R7" r:id="rId3" xr:uid="{BBC7DFE6-02AE-451D-9D6D-D70D606E876D}"/>
+    <hyperlink ref="R9" r:id="rId4" xr:uid="{E4B2D7C5-FB0D-4915-ADA2-AB07515DD4DA}"/>
+    <hyperlink ref="R10" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/7093890373?pwd=eEJTaWhnbTRwVXJrVTR0R0RyMUhkdz09%20Id%20da%20reunião:%207093890373%20Senha%20da%20sala:%20345356" xr:uid="{BA81ED6E-6070-4543-987B-2A91129600AE}"/>
+    <hyperlink ref="R12" r:id="rId6" xr:uid="{744E0CB7-63D1-49F3-BD9D-6F1368D0D705}"/>
+    <hyperlink ref="R13" r:id="rId7" xr:uid="{3E247091-0A76-46DD-BA1D-EA7C1ED52468}"/>
+    <hyperlink ref="R14" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/81390598525?pwd=rdGf0eRPC3KeSMHZlUecdE1edZpE5R.1%20ID%20da%20reunião:%20813%209059%208525%20Senha:%20127812" xr:uid="{116199DB-19CB-4BD3-9E9C-64F81FCF17B6}"/>
+    <hyperlink ref="R15" r:id="rId9" display="https://us02web.zoom.us/j/85763756385?pwd=ZTBCT3ZkZVg1QUVqMFVBNFcxUDdmQT0%20%20ID:%20857%206375%206385%20e%20Senha%20de%20acesso:%20958777" xr:uid="{C6692C79-2C91-4182-A7EF-A7EECCCC3633}"/>
+    <hyperlink ref="R16" r:id="rId10" xr:uid="{AB9E8971-11FC-41B1-82DB-23804E4DB5CF}"/>
+    <hyperlink ref="R20" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/86722354209?pwd=V01VL0NmTFZSZEdhcFhjM0tIczd3dz09%20ID%20da%20reunião:%20867%202235%204209%20Senha%20de%20acesso:%20947812" xr:uid="{71DE643D-5A35-4DCA-92EA-A02CC577F5D6}"/>
+    <hyperlink ref="R22" r:id="rId12" display="https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09%20ID%20da%20reunião:%2083352065501%20Senha%20de%20acesso:%20368465" xr:uid="{5C8A79B5-83CE-4DF1-AE4D-1434CA2F9630}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{81D42F8B-DE70-40B5-BC7E-DD0DAD019305}"/>
+    <hyperlink ref="R24" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/82477928530?pwd=WENUNkRGZ1NLbUY4VFZLdjdjOXBxUT09%20ID%20da%20reunião:%20824%207792%208530%20Senha%20de%20acesso:%20391604" xr:uid="{777747EE-C094-4B75-8081-C54A173801A0}"/>
+    <hyperlink ref="R25" r:id="rId15" display="https://us02web.zoom.us/j/8060729658?pwd=NDNlcU8wVzcxZ09qVjFDRFBGT2ljQT09%20ID%20da%20reunião:%20806%20072%209658%20Senha%20de%20acesso:%20868717" xr:uid="{6EC88838-5C81-409F-8423-DF2EB0405174}"/>
+    <hyperlink ref="R26" r:id="rId16" display="https://trt2-jus-br.zoom.us/j/88297719933?pwd=U3VWVjB2RHh0Vm9VMHZ0ZFd1eUk1dz09%20ID%20da%20reunião:%20882%209771%209933%20Senha%20de%20acesso:%20091850" xr:uid="{4C940D36-102D-4184-95F2-EB8CD6BB9E33}"/>
+    <hyperlink ref="R27" r:id="rId17" display="https://trt2-jus-br.zoom.us/j/88959116257?pwd=Q09WTmd6SnZibUUrZWxMSFdiRm9tUT09%20ID%20da%20reunião:%20889%205911%206257%20Senha%20de%20acesso:%20136898" xr:uid="{3AF64A62-9914-4A16-874E-BB858570944E}"/>
+    <hyperlink ref="R28" r:id="rId18" display="https://trt2-jus-br.zoom.us/j/85239557292?pwd=enBMVGxIVlR2bG5uUmk3Sy8yWmR6dz09%20ID%20da%20reunião:%20852%203955%207292%20Senha%20de%20acesso:%20611035" xr:uid="{182D42C1-7F0E-410E-ACC1-2B66CF202943}"/>
+    <hyperlink ref="R29" r:id="rId19" xr:uid="{E437BA56-71D0-4212-8E39-1C8AE4C59A2C}"/>
+    <hyperlink ref="R30" r:id="rId20" xr:uid="{3B93FBF5-C574-4FA2-B257-92DA549A27A8}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="145">
   <si>
     <t>data</t>
   </si>
@@ -49,379 +49,406 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>VSI</t>
   </si>
   <si>
     <t>AAP</t>
   </si>
   <si>
-    <t>Correspondente - Hebert</t>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>JRM</t>
   </si>
   <si>
     <t>LMI</t>
   </si>
   <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>RYL</t>
+    <t>Correspondente - Carlos Florian</t>
   </si>
   <si>
     <t>FCG</t>
   </si>
   <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>JNE</t>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
   </si>
   <si>
     <t>Grupo E2</t>
   </si>
   <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
   </si>
   <si>
     <t>Viterra Bioenergia S.A.</t>
   </si>
   <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Panificadora Cepam Ltda.</t>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda. &amp; Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Semipresencial</t>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Colégio Curumim S/S Ltda</t>
+  </si>
+  <si>
+    <t>Ame Digital Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Paulinia - Pln</t>
+  </si>
+  <si>
+    <t>Rio Parana Energia S.A</t>
+  </si>
+  <si>
+    <t>Construtora Elias Victor Nigri Ltda.</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
     <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
-    <t>Audiência Inicial -  Presencial</t>
+    <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
-    <t>Audiência Inicial -  Telepresencial</t>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
   </si>
   <si>
     <t>Audiência Inicial - Presencial</t>
   </si>
   <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0010685-63.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>1000527-98.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>1000832-57.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>1000628-78.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>0000827-44.2026.5.08.0101</t>
-  </si>
-  <si>
-    <t>0010704-69.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>1001851-66.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>1002207-61.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>1001238-18.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>1001373-05.2026.5.02.0601</t>
-  </si>
-  <si>
-    <t>0011042-44.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>1001057-08.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>1000383-33.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>1000592-97.2025.5.02.0445</t>
-  </si>
-  <si>
-    <t>0001617-53.2025.5.09.0095</t>
-  </si>
-  <si>
-    <t>0001757-47.2025.5.09.0658</t>
-  </si>
-  <si>
-    <t>1000780-92.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>0010215-72.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>0010173-80.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>0010480-06.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>0010175-50.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>0010530-32.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>1019460-73.2020.8.26.0577</t>
-  </si>
-  <si>
-    <t>0010609-11.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>0010607-41.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>0010417-72.2026.5.15.0029</t>
-  </si>
-  <si>
-    <t>0010300-33.2026.5.15.0045</t>
-  </si>
-  <si>
-    <t>0012892-87.2025.5.15.0044</t>
-  </si>
-  <si>
-    <t>0010541-87.2019.5.15.0130</t>
-  </si>
-  <si>
-    <t>Michel Roque Martins Dias</t>
-  </si>
-  <si>
-    <t>Mistoncleso Cruz Da Silva</t>
-  </si>
-  <si>
-    <t>Marli Nogueira Da Silva</t>
-  </si>
-  <si>
-    <t>Adriano Jose Da Silva</t>
-  </si>
-  <si>
-    <t>Rildo Dos Santos Dias</t>
-  </si>
-  <si>
-    <t>Bruno Duque Vanderlei</t>
-  </si>
-  <si>
-    <t>Yago Henrique Almeida Luz</t>
-  </si>
-  <si>
-    <t>Giovani Gustavo Ferreira Da Silva</t>
-  </si>
-  <si>
-    <t>Reinaldo Monteiro</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Arruda Croda</t>
-  </si>
-  <si>
-    <t>Renan De Azevedo Gomes</t>
-  </si>
-  <si>
-    <t>Elizeu Luiz Freire</t>
-  </si>
-  <si>
-    <t>Wesley Thiago Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>Marisilda Henriques</t>
-  </si>
-  <si>
-    <t>Rafael Cordeiro Gripa</t>
-  </si>
-  <si>
-    <t>Arilson Moraes De Almeida</t>
-  </si>
-  <si>
-    <t>Flavio Luiz Cossa</t>
-  </si>
-  <si>
-    <t>Ronan Ramos Gregorio Almeida</t>
-  </si>
-  <si>
-    <t>Vinicius Andre Freitas Diniz</t>
-  </si>
-  <si>
-    <t>Ricardo Mauricio Contel</t>
-  </si>
-  <si>
-    <t>Valdir Pereira Leal</t>
-  </si>
-  <si>
-    <t>Thalia Francisca Ribeiro Da Silva E Silva</t>
-  </si>
-  <si>
-    <t>Daniel Dos Santos Barbosa</t>
-  </si>
-  <si>
-    <t>Tiago Vieira De Sousa</t>
-  </si>
-  <si>
-    <t>Damiao Euflausino Alves</t>
-  </si>
-  <si>
-    <t>Daniel Antonio</t>
-  </si>
-  <si>
-    <t>Matheus Alberto Silva</t>
-  </si>
-  <si>
-    <t>Marcos Lopes Da Silva</t>
-  </si>
-  <si>
-    <t>Gilson Trindade Gama</t>
+    <t>0011446-11.2026.5.15.0013</t>
+  </si>
+  <si>
+    <t>1001605-70.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>0012525-60.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>0000008-89.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>0010718-53.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0010598-92.2026.5.03.0066</t>
+  </si>
+  <si>
+    <t>1000510-62.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>0010657-67.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>0012012-63.2024.5.15.0066</t>
+  </si>
+  <si>
+    <t>1000584-28.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>0024058-02.2026.5.24.0022</t>
+  </si>
+  <si>
+    <t>0011078-07.2025.5.03.0066</t>
+  </si>
+  <si>
+    <t>0011770-60.2025.5.15.0037</t>
+  </si>
+  <si>
+    <t>0012741-24.2025.5.15.0044</t>
+  </si>
+  <si>
+    <t>0001208-68.2025.5.09.0195</t>
+  </si>
+  <si>
+    <t>1000639-09.2026.5.02.0034</t>
+  </si>
+  <si>
+    <t>1002378-21.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>1001149-46.2026.5.02.0511</t>
+  </si>
+  <si>
+    <t>0010921-49.2025.5.15.0050</t>
+  </si>
+  <si>
+    <t>1001275-39.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>0011437-35.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>0024683-80.2026.5.24.0072</t>
+  </si>
+  <si>
+    <t>1000607-04.2022.5.02.0435</t>
+  </si>
+  <si>
+    <t>0011841-62.2025.5.15.0134</t>
+  </si>
+  <si>
+    <t>1001826-18.2023.5.02.0435</t>
+  </si>
+  <si>
+    <t>1000899-59.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>1001342-80.2021.5.02.0432</t>
+  </si>
+  <si>
+    <t>1001636-94.2024.5.02.0055</t>
+  </si>
+  <si>
+    <t>Luciano Aparecido Pereira</t>
+  </si>
+  <si>
+    <t>Everton Caldeira Marquesine</t>
+  </si>
+  <si>
+    <t>Reinaldo Aparecido Dos Santos</t>
+  </si>
+  <si>
+    <t>Everaldo Kovalchuk</t>
+  </si>
+  <si>
+    <t>Marco Aurelio Claudio</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Da Silva</t>
+  </si>
+  <si>
+    <t>Cleiton Mendonca De Souza</t>
+  </si>
+  <si>
+    <t>Fernando Henrique Grecco Dos Santos Garcia</t>
+  </si>
+  <si>
+    <t>Edivane Dos Santos</t>
+  </si>
+  <si>
+    <t>Welington Tavian Baptista</t>
+  </si>
+  <si>
+    <t>Taiane Lima Da Silva</t>
+  </si>
+  <si>
+    <t>Walleska Souza Menezes</t>
+  </si>
+  <si>
+    <t>Isabela Carolina Bento Belini Vilela</t>
+  </si>
+  <si>
+    <t>Gilberlandio Cascimiro Barbosa</t>
+  </si>
+  <si>
+    <t>Cerli Coelho Gomes</t>
+  </si>
+  <si>
+    <t>Andre Luiz Da Silva Rocumback</t>
+  </si>
+  <si>
+    <t>Marcilio Alan Ferreira Cavalcanti</t>
+  </si>
+  <si>
+    <t>Daiana Arruda Santos Silva</t>
+  </si>
+  <si>
+    <t>Joao Maria Bonifacio Ribeiro</t>
+  </si>
+  <si>
+    <t>Danilo Oliveira De Lima</t>
+  </si>
+  <si>
+    <t>Jose Maria Pereira</t>
+  </si>
+  <si>
+    <t>Flavio Rodrigues Valente</t>
+  </si>
+  <si>
+    <t>Marcelo Silva Rodrigues</t>
+  </si>
+  <si>
+    <t>Tiago Viegas Carvalho</t>
+  </si>
+  <si>
+    <t>Rodrigo Fernandes Da Silva</t>
+  </si>
+  <si>
+    <t>Carlos Alberto De Castro</t>
+  </si>
+  <si>
+    <t>Natanael Marques Vieira</t>
+  </si>
+  <si>
+    <t>Derivaldo Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>08:20:00</t>
   </si>
   <si>
     <t>08:30:00</t>
   </si>
   <si>
-    <t>08:50:00</t>
-  </si>
-  <si>
     <t>09:00:00</t>
   </si>
   <si>
-    <t>09:15:00</t>
-  </si>
-  <si>
     <t>09:20:00</t>
   </si>
   <si>
-    <t>09:50:00</t>
+    <t>09:30:00</t>
   </si>
   <si>
     <t>10:00:00</t>
   </si>
   <si>
-    <t>10:10:00</t>
+    <t>10:13:00</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
   </si>
   <si>
     <t>10:30:00</t>
   </si>
   <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
-    <t>11:50:00</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>13:27:00</t>
-  </si>
-  <si>
-    <t>13:34:00</t>
-  </si>
-  <si>
-    <t>13:42:00</t>
+    <t>10:40:00</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>13:15:00</t>
+  </si>
+  <si>
+    <t>13:44:00</t>
+  </si>
+  <si>
+    <t>13:45:00</t>
   </si>
   <si>
     <t>14:00:00</t>
   </si>
   <si>
-    <t>14:20:00</t>
-  </si>
-  <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>14:40:00</t>
-  </si>
-  <si>
-    <t>14:50:00</t>
-  </si>
-  <si>
-    <t>15:10:00</t>
+    <t>14:24:00</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
   </si>
   <si>
     <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
   </si>
 </sst>
 </file>
@@ -797,7 +824,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -806,33 +833,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -841,33 +868,33 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -876,33 +903,33 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -911,33 +938,33 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -946,313 +973,313 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J13" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K13" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -1261,418 +1288,418 @@
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K16" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="J18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K18" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K19" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="K22" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="J23" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="K23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K24" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H26" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K26" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -1681,133 +1708,133 @@
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H27" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K28" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="K29" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="H30" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J30" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDD9EB7-52E2-42D9-8E49-8A48D449AD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B141AB2-1407-4168-AE07-1B4FAA8B790F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E2B891C-2E1B-4231-B07B-EF8302005628}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E2B891C-2E1B-4231-B07B-EF8302005628}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="155">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,18 +95,9 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000058-52.2026.5.02.0435</t>
-  </si>
-  <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Anilton De Sa Silva</t>
-  </si>
-  <si>
     <t>SANTO ANDRÉ</t>
   </si>
   <si>
@@ -125,116 +116,401 @@
     <t>CENTRAL</t>
   </si>
   <si>
-    <t>R$             334.173,52</t>
-  </si>
-  <si>
     <t>Grupo B1</t>
   </si>
   <si>
     <t>JPE</t>
   </si>
   <si>
-    <t>GSM</t>
-  </si>
-  <si>
     <t>Presencial</t>
   </si>
   <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>0000074-09.2026.5.21.0010</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Everton Muller Da Costa Maia</t>
-  </si>
-  <si>
-    <t>NATAL</t>
-  </si>
-  <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>10ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               52.315,43</t>
-  </si>
-  <si>
     <t>Grupo C</t>
   </si>
   <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://trt21-jus-br.zoom.us/my/natal10vt</t>
-  </si>
-  <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
-    <t>1000586-95.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Vagner Aparecido Da Silva</t>
-  </si>
-  <si>
     <t>02ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>R$             196.932,24</t>
-  </si>
-  <si>
     <t>Correspondente - Hebert</t>
   </si>
   <si>
     <t>RFE</t>
   </si>
   <si>
-    <t>1000303-38.2026.5.02.0411</t>
-  </si>
-  <si>
     <t>Cbc - Companhia Brasileira De Cartuchos</t>
   </si>
   <si>
-    <t>Mariane Paulino Dos Santos Alves</t>
-  </si>
-  <si>
     <t>RIBEIRÃO PIRES</t>
   </si>
   <si>
     <t>VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>R$             348.205,41</t>
-  </si>
-  <si>
     <t>Grupo B3</t>
   </si>
   <si>
     <t>LMI</t>
   </si>
   <si>
-    <t>1000859-40.2026.5.02.0411</t>
-  </si>
-  <si>
     <t>Companhia Brasileira De Cartuchos</t>
   </si>
   <si>
-    <t>Elismar Pereira De Jesus Brito</t>
-  </si>
-  <si>
-    <t>R$               50.170,61</t>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0011284-81.2026.5.03.0164</t>
+  </si>
+  <si>
+    <t>Sistenge Construcoes E Comercio Ltda</t>
+  </si>
+  <si>
+    <t>Marionsergio Campos Cabral</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               31.127,22</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/81126952316</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011650-59.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Antonio Carlos Espejo</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             315.485,31</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09   ID DA REUNIÃO: 875 5537 1032 SENHA DE ACESSO: 772981</t>
+  </si>
+  <si>
+    <t>1001261-61.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Potira Brunhera</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               28.968,13</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>1001249-53.2025.5.02.0020</t>
+  </si>
+  <si>
+    <t>Cleivan Oliveira Amorim</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>20ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             254.352,14</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87319779344?pwd=XGh65AWoaNQktqbDH9bXKlU0RqZckb.1 ID da reunião: 873 1977 9344 Senha de acesso: 863962</t>
+  </si>
+  <si>
+    <t>1000659-67.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Jose Roberto Lopes Da Silva</t>
+  </si>
+  <si>
+    <t>R$             280.302,24</t>
+  </si>
+  <si>
+    <t>0000031-87.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Uhe São Simão Energia S.A.</t>
+  </si>
+  <si>
+    <t>Wigor Paulo Saturno Fernandes</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$             204.522,65</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/j/89772670047</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0020030-93.2024.5.04.0029</t>
+  </si>
+  <si>
+    <t>Francisco Boaventura Teixeira Moreira</t>
+  </si>
+  <si>
+    <t>PORTO ALEGRE</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Jaeger</t>
+  </si>
+  <si>
+    <t>https://trt4-jus-br.zoom.us/my/cejusc.revista.sala3 ID da reunião:  286 582 7324</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001341-13.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Nilson Ignacio</t>
+  </si>
+  <si>
+    <t>R$               76.540,57</t>
+  </si>
+  <si>
+    <t>1000939-53.2026.5.02.0039</t>
+  </si>
+  <si>
+    <t>Mitre Realty Empreendimentos E Participacoes Ltda.</t>
+  </si>
+  <si>
+    <t>Aparecida Ferreira Da Silva Mendes</t>
+  </si>
+  <si>
+    <t>39ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             345.284,94</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>1000858-55.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Marco Antonio Ferreira De Moura</t>
+  </si>
+  <si>
+    <t>R$               60.000,00</t>
+  </si>
+  <si>
+    <t>1000815-21.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Maikon Flavio Gomes Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               54.319,65</t>
+  </si>
+  <si>
+    <t>1000864-62.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Silene Antonia Silva De Lima</t>
+  </si>
+  <si>
+    <t>R$               67.618,05</t>
+  </si>
+  <si>
+    <t>0010612-97.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Frutal Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Fernanda De Jesus Martins</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>Ação de Consignação em Pagamento</t>
+  </si>
+  <si>
+    <t>R$                 5.463,72</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>0012826-11.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Rafael Reboucas Dos Santos</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>R$                 4.116,31</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>https://bit.ly/cejusclimeirasala1</t>
+  </si>
+  <si>
+    <t>0024175-55.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Dionaty Sousa Dos Santos</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$               55.756,42</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/88062331360</t>
+  </si>
+  <si>
+    <t>1001486-47.2025.5.02.0001</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Luciene Vicentina Pereira Barros</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$             360.084,51</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81939223002?pwd=VbNbYIp6i5iFsvbFRWAbpt9hdRmaMd.1 ID da reunião: 819 3922 3002 Senha de acesso: 958620</t>
+  </si>
+  <si>
+    <t>0010653-93.2026.5.15.0103</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>Marcelo Aparecido Da Silva</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               99.314,26</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81582489033?pwd=WFBLcGVJNkJMaWQ2Y3JqZ3d6YjIydz09 ID da reunião: 815 824 9033 Senha: 1234</t>
+  </si>
+  <si>
+    <t>1001114-58.2026.5.02.0003</t>
+  </si>
+  <si>
+    <t>T4F Entretenimento S.A.</t>
+  </si>
+  <si>
+    <t>Luiz Carlos Vieira De Jesus</t>
+  </si>
+  <si>
+    <t>R$               25.644,85</t>
+  </si>
+  <si>
+    <t>ANB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +530,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -276,7 +560,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -332,11 +616,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -359,8 +672,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -693,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459E5191-63A4-4A99-A31D-30E5C65929BB}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -715,7 +1047,7 @@
     <col min="18" max="18" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -772,288 +1104,1025 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4">
-        <v>103781</v>
-      </c>
-      <c r="B2" s="5">
-        <v>46234</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="A2" s="8">
+        <v>105542</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46237</v>
+      </c>
+      <c r="C2" s="10">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="L2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="M2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>32</v>
+      <c r="N2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>103864</v>
+        <v>105498</v>
       </c>
       <c r="B3" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C3" s="6">
-        <v>0.375</v>
+        <v>0.3576388888888889</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>104570</v>
+        <v>105456</v>
       </c>
       <c r="B4" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C4" s="6">
-        <v>0.4201388888888889</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="J4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="M4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>104333</v>
+        <v>101846</v>
       </c>
       <c r="B5" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C5" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="M5" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105245</v>
+        <v>104679</v>
       </c>
       <c r="B6" s="5">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C6" s="6">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>103777</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>97099</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105532</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>105224</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>105244</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105210</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C12" s="6">
         <v>0.50347222222222221</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="D12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="7" t="s">
+      <c r="M12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="7" t="s">
+    </row>
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>105288</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105433</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>32</v>
+      <c r="R14" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>99562</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>104492</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>104395</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>105073</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>105595</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46237</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{059A838D-B7D5-4590-915D-C34822A16248}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{76CF7C19-890C-4BFC-B161-BE23385ACD87}"/>
+    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09%20%20%20ID%20DA%20REUNIÃO:%20875%205537%201032%20SENHA%20DE%20ACESSO:%20772981" xr:uid="{C113F32D-984C-4AD8-84D8-4732C3D4F859}"/>
+    <hyperlink ref="R5" r:id="rId3" display="https://trt2-jus-br.zoom.us/j/87319779344?pwd=XGh65AWoaNQktqbDH9bXKlU0RqZckb.1%20ID%20da%20reunião:%20873%201977%209344%20Senha%20de%20acesso:%20863962" xr:uid="{7B009CB1-FD0F-413D-AE50-F30846EBF341}"/>
+    <hyperlink ref="R7" r:id="rId4" xr:uid="{F5F85478-D20B-42D0-ADC0-19E0770A71E9}"/>
+    <hyperlink ref="R8" r:id="rId5" display="https://trt4-jus-br.zoom.us/my/cejusc.revista.sala3 ID da reunião:  286 582 7324" xr:uid="{34A7DEC5-B07C-4753-A27D-D57801DC4C6F}"/>
+    <hyperlink ref="R14" r:id="rId6" xr:uid="{598873CA-A701-4F81-8CB6-BA99895D67A0}"/>
+    <hyperlink ref="R15" r:id="rId7" xr:uid="{111EEB3A-AF07-45FB-B1B7-3653CDEB97B1}"/>
+    <hyperlink ref="R16" r:id="rId8" xr:uid="{35FA42D5-58FB-4F76-A032-4F8C4510EDE0}"/>
+    <hyperlink ref="R17" r:id="rId9" display="https://trt2-jus-br.zoom.us/j/81939223002?pwd=VbNbYIp6i5iFsvbFRWAbpt9hdRmaMd.1%20ID%20da%20reunião:%20819%203922%203002%20Senha%20de%20acesso:%20958620" xr:uid="{D753409F-7EB8-48B7-A0CF-9BD9EF444450}"/>
+    <hyperlink ref="R18" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/81582489033?pwd=WFBLcGVJNkJMaWQ2Y3JqZ3d6YjIydz09%20ID%20da%20reunião:%20815%20824%209033%20Senha:%201234" xr:uid="{C6402A31-C826-4F2D-B6E5-DFC37CB77D80}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
   <si>
     <t>data</t>
   </si>
@@ -49,94 +49,280 @@
     <t>horario</t>
   </si>
   <si>
-    <t>Fatal</t>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>MBF</t>
   </si>
   <si>
     <t>JPE</t>
   </si>
   <si>
-    <t>VSI</t>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>Correspondente - Jaeger</t>
   </si>
   <si>
     <t>Correspondente - Hebert</t>
   </si>
   <si>
-    <t>LMI</t>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
   </si>
   <si>
     <t>Grupo B1</t>
   </si>
   <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
     <t>Grupo C</t>
   </si>
   <si>
-    <t>Grupo B3</t>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Sistenge Construcoes E Comercio Ltda</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Uhe São Simão Energia S.A.</t>
+  </si>
+  <si>
+    <t>Mitre Realty Empreendimentos E Participacoes Ltda.</t>
   </si>
   <si>
     <t>Cbc - Companhia Brasileira De Cartuchos</t>
   </si>
   <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
+    <t>Frutal Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>T4F Entretenimento S.A.</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1000058-52.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>0000074-09.2026.5.21.0010</t>
-  </si>
-  <si>
-    <t>1000586-95.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>1000303-38.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>1000859-40.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Anilton De Sa Silva</t>
-  </si>
-  <si>
-    <t>Everton Muller Da Costa Maia</t>
-  </si>
-  <si>
-    <t>Vagner Aparecido Da Silva</t>
-  </si>
-  <si>
-    <t>Mariane Paulino Dos Santos Alves</t>
-  </si>
-  <si>
-    <t>Elismar Pereira De Jesus Brito</t>
-  </si>
-  <si>
-    <t>08:40:00</t>
+    <t>0011284-81.2026.5.03.0164</t>
+  </si>
+  <si>
+    <t>0011650-59.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>1001261-61.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>1001249-53.2025.5.02.0020</t>
+  </si>
+  <si>
+    <t>1000659-67.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>0000031-87.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>0020030-93.2024.5.04.0029</t>
+  </si>
+  <si>
+    <t>1001341-13.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>1000939-53.2026.5.02.0039</t>
+  </si>
+  <si>
+    <t>1000858-55.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>1000815-21.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>1000864-62.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>0010612-97.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>0012826-11.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>0024175-55.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>1001486-47.2025.5.02.0001</t>
+  </si>
+  <si>
+    <t>0010653-93.2026.5.15.0103</t>
+  </si>
+  <si>
+    <t>1001114-58.2026.5.02.0003</t>
+  </si>
+  <si>
+    <t>Marionsergio Campos Cabral</t>
+  </si>
+  <si>
+    <t>Antonio Carlos Espejo</t>
+  </si>
+  <si>
+    <t>Potira Brunhera</t>
+  </si>
+  <si>
+    <t>Cleivan Oliveira Amorim</t>
+  </si>
+  <si>
+    <t>Jose Roberto Lopes Da Silva</t>
+  </si>
+  <si>
+    <t>Wigor Paulo Saturno Fernandes</t>
+  </si>
+  <si>
+    <t>Francisco Boaventura Teixeira Moreira</t>
+  </si>
+  <si>
+    <t>Nilson Ignacio</t>
+  </si>
+  <si>
+    <t>Aparecida Ferreira Da Silva Mendes</t>
+  </si>
+  <si>
+    <t>Marco Antonio Ferreira De Moura</t>
+  </si>
+  <si>
+    <t>Maikon Flavio Gomes Dos Santos</t>
+  </si>
+  <si>
+    <t>Silene Antonia Silva De Lima</t>
+  </si>
+  <si>
+    <t>Fernanda De Jesus Martins</t>
+  </si>
+  <si>
+    <t>Rafael Reboucas Dos Santos</t>
+  </si>
+  <si>
+    <t>Dionaty Sousa Dos Santos</t>
+  </si>
+  <si>
+    <t>Luciene Vicentina Pereira Barros</t>
+  </si>
+  <si>
+    <t>Marcelo Aparecido Da Silva</t>
+  </si>
+  <si>
+    <t>Luiz Carlos Vieira De Jesus</t>
+  </si>
+  <si>
+    <t>08:10:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
   </si>
   <si>
     <t>09:00:00</t>
   </si>
   <si>
-    <t>10:05:00</t>
-  </si>
-  <si>
-    <t>10:40:00</t>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>09:35:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
   </si>
   <si>
     <t>12:05:00</t>
+  </si>
+  <si>
+    <t>12:20:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
   </si>
 </sst>
 </file>
@@ -472,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -512,7 +698,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -521,33 +707,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -556,33 +742,33 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -591,33 +777,33 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -626,63 +812,518 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>85</v>
+      </c>
+      <c r="J19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="160">
   <si>
     <t>data</t>
   </si>
@@ -52,277 +52,448 @@
     <t>D-1</t>
   </si>
   <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>DPR</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>JQS</t>
+  </si>
+  <si>
     <t>RYL</t>
   </si>
   <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>Correspondente - Jaeger</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>JNE</t>
-  </si>
-  <si>
-    <t>ANB</t>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
   </si>
   <si>
     <t>Grupo E2</t>
   </si>
   <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
     <t>Grupo C</t>
   </si>
   <si>
     <t>Grupo E1</t>
   </si>
   <si>
-    <t>Sistenge Construcoes E Comercio Ltda</t>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Moema</t>
   </si>
   <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Uhe São Simão Energia S.A.</t>
-  </si>
-  <si>
-    <t>Mitre Realty Empreendimentos E Participacoes Ltda.</t>
-  </si>
-  <si>
-    <t>Cbc - Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Frutal Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Dell Computadores Do Brasil Ltda</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Rio Paranapanema Energia S.A.</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Bit Services Inovação E Tecnologia Ltda.</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Salitre Fertilzantes Ltda</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Joanilson Nunes De Oliveira</t>
   </si>
   <si>
     <t>Telefonica Brasil S.A.</t>
   </si>
   <si>
-    <t>Viterra Bioenergia S.A</t>
-  </si>
-  <si>
-    <t>T4F Entretenimento S.A.</t>
+    <t>Eurochem Comercio De Produtos Quimicos Ltda.</t>
+  </si>
+  <si>
+    <t>Direct Express Logística Integrada S.A.</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>International Paper Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
   </si>
   <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TST - Presencial</t>
+  </si>
+  <si>
     <t>Audiência Inicial - Telepresencial</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
   </si>
   <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>0011284-81.2026.5.03.0164</t>
-  </si>
-  <si>
-    <t>0011650-59.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>1001261-61.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>1001249-53.2025.5.02.0020</t>
-  </si>
-  <si>
-    <t>1000659-67.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>0000031-87.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>0020030-93.2024.5.04.0029</t>
-  </si>
-  <si>
-    <t>1001341-13.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>1000939-53.2026.5.02.0039</t>
-  </si>
-  <si>
-    <t>1000858-55.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>1000815-21.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>1000864-62.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>0010612-97.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>0012826-11.2024.5.15.0152</t>
-  </si>
-  <si>
-    <t>0024175-55.2026.5.24.0066</t>
-  </si>
-  <si>
-    <t>1001486-47.2025.5.02.0001</t>
-  </si>
-  <si>
-    <t>0010653-93.2026.5.15.0103</t>
-  </si>
-  <si>
-    <t>1001114-58.2026.5.02.0003</t>
-  </si>
-  <si>
-    <t>Marionsergio Campos Cabral</t>
-  </si>
-  <si>
-    <t>Antonio Carlos Espejo</t>
-  </si>
-  <si>
-    <t>Potira Brunhera</t>
-  </si>
-  <si>
-    <t>Cleivan Oliveira Amorim</t>
-  </si>
-  <si>
-    <t>Jose Roberto Lopes Da Silva</t>
-  </si>
-  <si>
-    <t>Wigor Paulo Saturno Fernandes</t>
-  </si>
-  <si>
-    <t>Francisco Boaventura Teixeira Moreira</t>
-  </si>
-  <si>
-    <t>Nilson Ignacio</t>
-  </si>
-  <si>
-    <t>Aparecida Ferreira Da Silva Mendes</t>
-  </si>
-  <si>
-    <t>Marco Antonio Ferreira De Moura</t>
-  </si>
-  <si>
-    <t>Maikon Flavio Gomes Dos Santos</t>
-  </si>
-  <si>
-    <t>Silene Antonia Silva De Lima</t>
-  </si>
-  <si>
-    <t>Fernanda De Jesus Martins</t>
-  </si>
-  <si>
-    <t>Rafael Reboucas Dos Santos</t>
-  </si>
-  <si>
-    <t>Dionaty Sousa Dos Santos</t>
-  </si>
-  <si>
-    <t>Luciene Vicentina Pereira Barros</t>
-  </si>
-  <si>
-    <t>Marcelo Aparecido Da Silva</t>
-  </si>
-  <si>
-    <t>Luiz Carlos Vieira De Jesus</t>
-  </si>
-  <si>
-    <t>08:10:00</t>
-  </si>
-  <si>
-    <t>08:35:00</t>
+    <t>0012545-86.2025.5.15.0001</t>
+  </si>
+  <si>
+    <t>1001866-53.2025.5.02.0039</t>
+  </si>
+  <si>
+    <t>0010484-64.2026.5.03.0031</t>
+  </si>
+  <si>
+    <t>0011099-48.2016.5.15.0103</t>
+  </si>
+  <si>
+    <t>0000167-80.2026.5.09.0567</t>
+  </si>
+  <si>
+    <t>0010782-28.2024.5.03.0063</t>
+  </si>
+  <si>
+    <t>1000297-47.2026.5.02.0050</t>
+  </si>
+  <si>
+    <t>0011509-40.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>0010703-78.2026.5.03.0063</t>
+  </si>
+  <si>
+    <t>0000355-16.2025.5.05.0019</t>
+  </si>
+  <si>
+    <t>0010751-83.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>1000773-09.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>0012465-43.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>0011744-39.2023.5.15.0132</t>
+  </si>
+  <si>
+    <t>1002067-85.2025.5.02.0058</t>
+  </si>
+  <si>
+    <t>1000911-89.2026.5.02.0361</t>
+  </si>
+  <si>
+    <t>0001705-27.2025.5.09.0084</t>
+  </si>
+  <si>
+    <t>0010290-14.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>1000623-26.2026.5.02.0464</t>
+  </si>
+  <si>
+    <t>1000152-53.2023.5.02.0613</t>
+  </si>
+  <si>
+    <t>0010226-04.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>0001578-56.2025.5.09.0095</t>
+  </si>
+  <si>
+    <t>0011022-49.2025.5.15.0030</t>
+  </si>
+  <si>
+    <t>1001126-80.2017.5.02.0361</t>
+  </si>
+  <si>
+    <t>0010416-24.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0107600-10.2009.5.15.0071</t>
+  </si>
+  <si>
+    <t>0010376-28.2024.5.15.0045</t>
+  </si>
+  <si>
+    <t>1000407-97.2022.5.02.0434</t>
+  </si>
+  <si>
+    <t>0010054-22.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>0012301-55.2025.5.15.0132</t>
+  </si>
+  <si>
+    <t>0010344-23.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Marcos De Faria Paes</t>
+  </si>
+  <si>
+    <t>Cleber Donizeti Da Trindade</t>
+  </si>
+  <si>
+    <t>Kaio Rodrigo Goncalves Da Cruz</t>
+  </si>
+  <si>
+    <t>Luiz Antonio Goncalves</t>
+  </si>
+  <si>
+    <t>Claudemir Mendonca</t>
+  </si>
+  <si>
+    <t>Carlos Fernando Santos Silva</t>
+  </si>
+  <si>
+    <t>Marcelo Bertossi Barbosa</t>
+  </si>
+  <si>
+    <t>Moises De Aguiar Caires</t>
+  </si>
+  <si>
+    <t>Robert Da Silva Vilela</t>
+  </si>
+  <si>
+    <t>Denilson Dos Santos</t>
+  </si>
+  <si>
+    <t>Wellinthon Dos Reis Garajau</t>
+  </si>
+  <si>
+    <t>Jonathan Wanus Batista Santos</t>
+  </si>
+  <si>
+    <t>Horlando Cicero Da Silva</t>
+  </si>
+  <si>
+    <t>Lucas Moreira Fabricio</t>
+  </si>
+  <si>
+    <t>Rafael Vinicius Campioto</t>
+  </si>
+  <si>
+    <t>Jose Leite De Sousa</t>
+  </si>
+  <si>
+    <t>Pedro Lopes Barboza</t>
+  </si>
+  <si>
+    <t>Joao Marcos Pereira De Souza</t>
+  </si>
+  <si>
+    <t>Darcisio Campos Da Cruz</t>
+  </si>
+  <si>
+    <t>Edson De Lima Solla</t>
+  </si>
+  <si>
+    <t>Wesley Fernando Araujo</t>
+  </si>
+  <si>
+    <t>Allan Ferreira Silva</t>
+  </si>
+  <si>
+    <t>Sara Beatriz Correa De Andrade</t>
+  </si>
+  <si>
+    <t>Thiago Rodrigues Da Silva</t>
+  </si>
+  <si>
+    <t>Luis Antonio Pedro</t>
+  </si>
+  <si>
+    <t>Ministério Público Do Trabalho</t>
+  </si>
+  <si>
+    <t>Anderson Rodrigo Da Costa</t>
+  </si>
+  <si>
+    <t>Cleiton Goncalves Ferreira</t>
+  </si>
+  <si>
+    <t>Edson Aparecido Arf</t>
+  </si>
+  <si>
+    <t>Anderson Izidoro Dos Santos</t>
+  </si>
+  <si>
+    <t>Reginaldo Rodrigues Da Silva</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
   </si>
   <si>
     <t>09:00:00</t>
   </si>
   <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
     <t>09:30:00</t>
   </si>
   <si>
-    <t>09:35:00</t>
+    <t>09:31:00</t>
   </si>
   <si>
     <t>10:00:00</t>
   </si>
   <si>
-    <t>10:45:00</t>
+    <t>10:05:00</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>10:40:00</t>
   </si>
   <si>
     <t>11:00:00</t>
   </si>
   <si>
-    <t>11:35:00</t>
-  </si>
-  <si>
-    <t>12:05:00</t>
-  </si>
-  <si>
-    <t>12:20:00</t>
-  </si>
-  <si>
-    <t>13:55:00</t>
-  </si>
-  <si>
-    <t>14:16:00</t>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>13:44:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>14:22:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
   </si>
   <si>
     <t>14:45:00</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>15:05:00</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
+    <t>14:50:00</t>
   </si>
 </sst>
 </file>
@@ -658,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -698,7 +869,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -707,33 +878,33 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -742,33 +913,33 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -777,33 +948,33 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -812,33 +983,33 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -847,33 +1018,33 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -882,33 +1053,33 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -917,33 +1088,33 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -952,33 +1123,33 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -987,343 +1158,833 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K13" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="J14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K16" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="J17" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="K17" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K18" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" t="s">
+        <v>120</v>
+      </c>
+      <c r="J20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" t="s">
+        <v>121</v>
+      </c>
+      <c r="J21" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s">
         <v>67</v>
       </c>
-      <c r="I19" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="G24" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" t="s">
+        <v>125</v>
+      </c>
+      <c r="J25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" t="s">
+        <v>126</v>
+      </c>
+      <c r="J26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" t="s">
+        <v>127</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" t="s">
+        <v>128</v>
+      </c>
+      <c r="J28" t="s">
+        <v>57</v>
+      </c>
+      <c r="K28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" t="s">
+        <v>129</v>
+      </c>
+      <c r="J29" t="s">
+        <v>51</v>
+      </c>
+      <c r="K29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" t="s">
+        <v>99</v>
+      </c>
+      <c r="I30" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" t="s">
+        <v>100</v>
+      </c>
+      <c r="I31" t="s">
+        <v>131</v>
+      </c>
+      <c r="J31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" t="s">
+        <v>132</v>
+      </c>
+      <c r="J32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" t="s">
         <v>102</v>
+      </c>
+      <c r="I33" t="s">
+        <v>133</v>
+      </c>
+      <c r="J33" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -49,7 +49,7 @@
     <t>horario</t>
   </si>
   <si>
-    <t>D-1</t>
+    <t>Fatal</t>
   </si>
   <si>
     <t>LMI</t>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5287349A-8B24-40D2-AE46-E2D24C546495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE373951-5D8F-43B0-AEF3-5C3AC9BCCB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{07A9244C-00B7-4833-97D7-4C2981ADAB32}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{225BCCB4-A3DE-452D-8192-B4F51D0812AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="196">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,73 +95,543 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0001040-75.2026.5.08.0125</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Daniel Costa Cardoso</t>
+  </si>
+  <si>
+    <t>BELÉM</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               48.686,40</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt8-jus-br.zoom.us/j/82503841073?pwd=YXYyUXBQV3FTSGdKckZTTDJhZFRIQT09 ID da reunião: 825 0384 1073 Senha: 6KHd1p3p</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0017135-90.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Leonardo Dos Santos</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$          1.392.263,61</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0010813-25.2026.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Igor Jacintho</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>R$             167.795,50</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1001760-73.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Jonathan Henrique Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             491.829,02</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000972-70.2026.5.02.0321</t>
+  </si>
+  <si>
+    <t>Mahle Behr Gerenciamento Térmico Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Celso Virissimo Da Silva</t>
+  </si>
+  <si>
+    <t>GUARULHOS</t>
+  </si>
+  <si>
+    <t>11ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             230.284,04</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Ana Caroline, (11) 96079-1682 | Preposto - Thayna Rodrigues Rangel, CPF 427.201.568-09, RG 381215611, (11) 95196-8671</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Semipresencial</t>
+  </si>
+  <si>
+    <t>0010804-24.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Ivan Martins Dos Santos</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             405.082,60</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0000412-85.2025.5.05.0002</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Alexsandro Barbosa Santos</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               44.015,25</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/sl2vtssa</t>
+  </si>
+  <si>
+    <t>0010751-43.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Ederson Aparecido Da Silva Santos</t>
+  </si>
+  <si>
+    <t>R$             765.446,14</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>1001767-62.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>Anderson Luiz De Andrade</t>
+  </si>
+  <si>
+    <t>R$             216.000,00</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0021380-65.2025.5.04.0261</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Andressa Busnello Dos Santos</t>
-  </si>
-  <si>
-    <t>MONTENEGRO</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               31.194,00</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>https://trt4-jus-br.zoom.us/my/varamontenegrojt</t>
-  </si>
-  <si>
-    <t>Perícia de Engenharia</t>
-  </si>
-  <si>
-    <t>0013072-83.2025.5.15.0083</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Ronaldo Costa Da Silva</t>
+    <t>0000357-82.2026.5.09.0069</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Darlan Silva Quintiliano</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$             533.600,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/u6g7p ID da Reunião: 88243064176 Senha: ZztF8Rq70A</t>
+  </si>
+  <si>
+    <t>1002246-18.2025.5.02.0511</t>
+  </si>
+  <si>
+    <t>Ame Digital Brasil Instituição De Pagamento</t>
+  </si>
+  <si>
+    <t>Bruna Silva De Santana</t>
+  </si>
+  <si>
+    <t>ITAPEVI</t>
+  </si>
+  <si>
+    <t>R$             128.654,00</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>JQS</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Jairo Felipe, (11) 98807-2750</t>
+  </si>
+  <si>
+    <t>0000016-66.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Niuto Jose Osorio Junior</t>
+  </si>
+  <si>
+    <t>R$               28.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/tdj3d ID da Reunião: 89966449108 Senha: Z1CJO3LQG9</t>
+  </si>
+  <si>
+    <t>0000353-27.2026.5.09.0657</t>
+  </si>
+  <si>
+    <t>Jean Gilbert Dos Santos</t>
+  </si>
+  <si>
+    <t>COLOMBO</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             384.000,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/jvlyh ID da Reunião: 84705145674 Senha: wE1P9GjYo4</t>
+  </si>
+  <si>
+    <t>0011077-31.2024.5.03.0042</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Edivan Lima Do Nascimento</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>2ª Instância</t>
+  </si>
+  <si>
+    <t>R$               84.605,25</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/sala3cejusc2</t>
+  </si>
+  <si>
+    <t>1000703-86.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Davi Amaral Maximiniano</t>
+  </si>
+  <si>
+    <t>R$             102.932,21</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>1002005-87.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Eder Soares De Lima</t>
+  </si>
+  <si>
+    <t>R$          1.586.216,55</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010576-15.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A</t>
+  </si>
+  <si>
+    <t>Tulio Santos Da Silva</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             114.481,88</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
+  </si>
+  <si>
+    <t>0010579-67.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Rodrigo Protazio Viana</t>
+  </si>
+  <si>
+    <t>R$             113.201,22</t>
+  </si>
+  <si>
+    <t>1000702-06.2018.5.02.0716</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Elisangela Maria De Sena Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>CEJUSC SUL</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>Zona Sul</t>
+  </si>
+  <si>
+    <t>R$               12.569,66</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81968799845</t>
+  </si>
+  <si>
+    <t>1001350-25.2026.5.02.0386</t>
+  </si>
+  <si>
+    <t>Bit Services Inovação E Tecnologia Ltda</t>
+  </si>
+  <si>
+    <t>Fernanda De Carvalho Coelho</t>
+  </si>
+  <si>
+    <t>OSASCO</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.364.776,32</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/82126268844?pwd=bqahALjgyeuINDEiQ397dgVizovUGI.1 ID da reunião: 821 2626 8844 Senha de acesso: 226365</t>
+  </si>
+  <si>
+    <t>0011490-19.2025.5.15.0125</t>
+  </si>
+  <si>
+    <t>Ronaldo Pires Da Silva</t>
+  </si>
+  <si>
+    <t>SERTÃOZINHO</t>
+  </si>
+  <si>
+    <t>R$             150.750,59</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial | Advogada - Sílvia Selli </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>sissaselli@yahoo.com.br</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (16)9922-77526 | Preposto - Luana Francielle Ribeiro Ferreira Alves </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>luanalfralves.010@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (16)9941-31213</t>
+    </r>
+  </si>
+  <si>
+    <t>0010438-06.2021.5.15.0132</t>
+  </si>
+  <si>
+    <t>Yaborã Indústria Aeronáutica S.A.</t>
+  </si>
+  <si>
+    <t>Jose Wellington Gomes De Oliveira</t>
   </si>
   <si>
     <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               93.500,00</t>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             219.965,99</t>
   </si>
   <si>
     <t>Grupo B2</t>
@@ -170,434 +640,38 @@
     <t>VCR</t>
   </si>
   <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010412-48.2026.5.03.0073</t>
-  </si>
-  <si>
-    <t>Hrz Energia</t>
-  </si>
-  <si>
-    <t>Alexandre Nery Ferreira</t>
-  </si>
-  <si>
-    <t>PASSOS</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             644.064,82</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt2.passos</t>
-  </si>
-  <si>
-    <t>0010795-05.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Lineker Moraes De Santana</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$             339.906,28</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>FCG</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0010796-87.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Nilton Pereira De Souza Filho</t>
-  </si>
-  <si>
-    <t>R$             367.977,55</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0012673-77.2025.5.15.0140</t>
-  </si>
-  <si>
-    <t>Grammer Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Rosilania Alves De Araujo</t>
-  </si>
-  <si>
-    <t>ATIBAIA</t>
-  </si>
-  <si>
-    <t>R$             128.794,35</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Semipresencial</t>
-  </si>
-  <si>
-    <t>1000743-68.2026.5.02.0044</t>
-  </si>
-  <si>
-    <t>Mccann Erickson Publicidade Ltda</t>
-  </si>
-  <si>
-    <t>Claudia Maria Giesbrecht</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>44ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             575.263,54</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>0010789-55.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Alessandre Rodrigues De Oliveira</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             773.639,23</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>0010366-37.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Ivan Dias Nascimento</t>
-  </si>
-  <si>
-    <t>ITURAMA</t>
-  </si>
-  <si>
-    <t>R$             117.887,66</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.iturama</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010118-66.2025.5.15.0050</t>
-  </si>
-  <si>
-    <t>Claudemir José Da Silva</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>Liquidação</t>
-  </si>
-  <si>
-    <t>R$               40.000,00</t>
-  </si>
-  <si>
-    <t>JNE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86722354209?pwd=V01VL0NmTFZSZEdhcFhjM0tIczd3dz09</t>
-  </si>
-  <si>
-    <t>0000068-43.2026.5.09.0072</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Elieonai Jesse De Oliveira</t>
-  </si>
-  <si>
-    <t>PATO BRANCO</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               18.000,00</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/7mcvk ID da Reunião: 82782550827 Senha: K6vUlKTDKO</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0000287-87.2026.5.10.0861</t>
-  </si>
-  <si>
-    <t>Pedro Afonso Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Gerson Freitas Da Silva</t>
-  </si>
-  <si>
-    <t>GUARAÍ</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>R$               65.405,99</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Shysnnen Sousa Milhomem shysnnensousamilhomem@gmail.com (63) 984122082</t>
-  </si>
-  <si>
-    <t>1002069-97.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Adriana Ferreira Silveira</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             150.000,00</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>1000578-41.2026.5.02.0005</t>
-  </si>
-  <si>
-    <t>Ocp Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Leandra Conceicao Dos Santos</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               51.876,14</t>
-  </si>
-  <si>
-    <t>Grupo A2</t>
-  </si>
-  <si>
-    <t>NBG</t>
-  </si>
-  <si>
-    <t>0011126-86.2026.5.15.0133</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Delmario Soares Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             304.000,00</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09 ID da reunião: 897 7008 2465 Senha de acesso: 908050</t>
-  </si>
-  <si>
-    <t>1000486-47.2026.5.02.0463</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Douglas Ferreira De Gouveia</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>R$             320.000,00</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>Audiência de Encerramento de Instrução</t>
-  </si>
-  <si>
-    <t>0024822-84.2025.5.24.0066</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Sueli Benites Do Amaral</t>
-  </si>
-  <si>
-    <t>PONTA PORÃ</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$               25.114,85</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/j/89699921902</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1001290-45.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Olivia Maria Dos Santos</t>
-  </si>
-  <si>
-    <t>02ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$          1.363.180,14</t>
-  </si>
-  <si>
-    <t>0011492-36.2023.5.15.0132</t>
-  </si>
-  <si>
-    <t>Andreia Aparecida De Moraes Almeida</t>
-  </si>
-  <si>
-    <t>R$             133.000,00</t>
-  </si>
-  <si>
-    <t>0010966-22.2023.5.15.0083</t>
-  </si>
-  <si>
-    <t>Almir Paulo Vitor</t>
-  </si>
-  <si>
-    <t>R$               86.961,75</t>
-  </si>
-  <si>
-    <t>1000166-27.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Marcos Vinicius Leal De Brito</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$             199.790,75</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/87954974516?pwd=Z422AaVXFvqhK2Xil7daQHrTdaRtRa.1 ID da reunião: 879 5497 4516 Senha de acesso: 428377</t>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>1000632-60.2026.5.02.0052</t>
+  </si>
+  <si>
+    <t>Telefônica Brasil S.A</t>
+  </si>
+  <si>
+    <t>Marcia Silva Cesar</t>
+  </si>
+  <si>
+    <t>52ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          2.015.620,67</t>
+  </si>
+  <si>
+    <t>Grupo A3</t>
+  </si>
+  <si>
+    <t>PBS</t>
+  </si>
+  <si>
+    <t>SOF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,6 +689,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF467886"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -706,7 +786,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -731,7 +811,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1068,8 +1148,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF4431B-44E5-4BD5-9264-DF29CBBD9482}">
-  <dimension ref="A1:R22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B455ACF-2A1A-4113-9223-A9FEF04A11FE}">
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -1077,21 +1157,21 @@
     <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="127.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="135.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1147,15 +1227,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>103358</v>
+        <v>105496</v>
       </c>
       <c r="B2" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1203,15 +1283,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>103131</v>
+        <v>103475</v>
       </c>
       <c r="B3" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.35069444444444442</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>32</v>
@@ -1253,42 +1333,42 @@
         <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>105528</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105368</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>25</v>
@@ -1300,51 +1380,51 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>102213</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>105571</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1356,54 +1436,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="R5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="R5" s="8" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="6" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105572</v>
+        <v>105000</v>
       </c>
       <c r="B6" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C6" s="6">
         <v>0.375</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1412,54 +1492,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>102873</v>
+        <v>105316</v>
       </c>
       <c r="B7" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C7" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.375</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1468,51 +1548,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>104973</v>
+        <v>102334</v>
       </c>
       <c r="B8" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C8" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1524,54 +1604,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="R8" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105197</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>105277</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1580,51 +1660,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>104277</v>
+        <v>103097</v>
       </c>
       <c r="B10" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C10" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>97</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1636,54 +1716,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104375</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="P10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R10" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>100628</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="J11" s="7" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1692,51 +1772,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="O11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="P11" s="7" t="s">
+      <c r="Q11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Q11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="R11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>102764</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>103850</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1748,51 +1828,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="O12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>118</v>
-      </c>
     </row>
-    <row r="13" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105459</v>
+        <v>103726</v>
       </c>
       <c r="B13" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C13" s="6">
         <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1804,51 +1884,51 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>103175</v>
+        <v>104517</v>
       </c>
       <c r="B14" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C14" s="6">
-        <v>0.48958333333333331</v>
+        <v>0.44305555555555554</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1860,54 +1940,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>99078</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="K15" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
-        <v>105486</v>
-      </c>
-      <c r="B15" s="5">
-        <v>46239</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1916,51 +1996,51 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>105325</v>
+        <v>104801</v>
       </c>
       <c r="B16" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C16" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>25</v>
@@ -1972,51 +2052,51 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>104610</v>
+        <v>103122</v>
       </c>
       <c r="B17" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C17" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>25</v>
@@ -2028,51 +2108,51 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>104336</v>
+        <v>104917</v>
       </c>
       <c r="B18" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C18" s="6">
-        <v>0.55902777777777779</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>25</v>
@@ -2084,54 +2164,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>101710</v>
+        <v>104919</v>
       </c>
       <c r="B19" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C19" s="6">
-        <v>0.5625</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2140,110 +2220,110 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>95512</v>
+        <v>66382</v>
       </c>
       <c r="B20" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C20" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.57222222222222219</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>77</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>94453</v>
+        <v>105656</v>
       </c>
       <c r="B21" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C21" s="6">
-        <v>0.625</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2252,91 +2332,205 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>99829</v>
+        <v>102043</v>
       </c>
       <c r="B22" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C22" s="6">
-        <v>0.68055555555555558</v>
+        <v>0.59722222222222221</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>93799</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="G23" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="O22" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q22" s="7" t="s">
+      <c r="H23" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="R22" s="8" t="s">
+      <c r="I23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>183</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104777</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{423263F2-5C5E-4E9C-8578-E2BDAF39B10A}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{95956DBF-FE8C-4B6F-B825-100348991273}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{C81DE944-F27D-47D2-9FD5-830E8657BA42}"/>
-    <hyperlink ref="R6" r:id="rId4" xr:uid="{DB672D63-DFE3-462B-96E0-44AD8315AA9F}"/>
-    <hyperlink ref="R9" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{0B866530-C511-49F8-B9A1-D1770E5AC47C}"/>
-    <hyperlink ref="R10" r:id="rId6" xr:uid="{C456B911-777A-4192-BDDA-FA2DD9574F5E}"/>
-    <hyperlink ref="R11" r:id="rId7" xr:uid="{22DAA534-3D50-448D-91A7-5FB4EEBFA1CF}"/>
-    <hyperlink ref="R12" r:id="rId8" xr:uid="{C5EFF703-43FB-49C3-BFF5-97097F9187CF}"/>
-    <hyperlink ref="R13" r:id="rId9" display="mailto:shysnnensousamilhomem@gmail.com" xr:uid="{5D90B44E-E374-43B6-B9D3-4D46B0CD53DA}"/>
-    <hyperlink ref="R16" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09%20ID%20da%20reunião:%20897%207008%202465%20Senha%20de%20acesso:%20908050" xr:uid="{7E418810-828A-42B3-8E27-2867892DB0E5}"/>
-    <hyperlink ref="R18" r:id="rId11" xr:uid="{E789E70B-E93F-4359-8E6F-44967F5EB62E}"/>
-    <hyperlink ref="R22" r:id="rId12" display="https://trt2-jus-br.zoom.us/j/87954974516?pwd=Z422AaVXFvqhK2Xil7daQHrTdaRtRa.1%20ID%20da%20reunião:%20879%205497%204516%20Senha%20de%20acesso:%20428377" xr:uid="{5C589CA9-A329-4E7D-B596-55A46C899E51}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://trt8-jus-br.zoom.us/j/82503841073?pwd=YXYyUXBQV3FTSGdKckZTTDJhZFRIQT09" xr:uid="{F78C397C-A5F3-4A13-96D7-FF35731DDDC3}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{138D7397-B99D-47D9-884F-43900E9A4BB3}"/>
+    <hyperlink ref="R4" r:id="rId3" xr:uid="{E37FB1BE-BA85-42A1-9E98-3B2F7422DFDF}"/>
+    <hyperlink ref="R7" r:id="rId4" xr:uid="{4AF92C36-680E-4F0C-B13B-02D77A87E482}"/>
+    <hyperlink ref="R8" r:id="rId5" xr:uid="{E53FBBC9-9825-48E7-9AA1-3EF2F772DB29}"/>
+    <hyperlink ref="R9" r:id="rId6" xr:uid="{02D2A9B5-3254-4B9C-AA34-9784694003BA}"/>
+    <hyperlink ref="R11" r:id="rId7" xr:uid="{48E63EA1-C687-4126-9A66-1712A14FE0BD}"/>
+    <hyperlink ref="R13" r:id="rId8" xr:uid="{05115D02-15B6-4D6F-BB70-5BFCAD5EF345}"/>
+    <hyperlink ref="R14" r:id="rId9" xr:uid="{9BFC168A-6C6B-4EC4-A392-B7DD9801B886}"/>
+    <hyperlink ref="R15" r:id="rId10" xr:uid="{DA59A652-BD04-4799-9933-0916D991E692}"/>
+    <hyperlink ref="R18" r:id="rId11" xr:uid="{65D393F3-FF11-4712-83C0-B1BAAA2B39F8}"/>
+    <hyperlink ref="R19" r:id="rId12" xr:uid="{9CB8FEBF-F55E-42AA-B955-A13C12082505}"/>
+    <hyperlink ref="R20" r:id="rId13" xr:uid="{6584D44C-5E09-4696-BD15-8AE047B67C5C}"/>
+    <hyperlink ref="R21" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/82126268844?pwd=bqahALjgyeuINDEiQ397dgVizovUGI.1%20ID%20da%20reunião:%20821%202626%208844%20Senha%20de%20acesso:%20226365" xr:uid="{2FEECF4A-0ED2-400B-9DD8-8AB10D435BF2}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB90DA08-74CA-4237-AA12-6AF6B1CC556C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05DDE9D-E5F1-4496-AD32-0CE32A04B1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5887CEB3-535E-43A1-8951-4C0AB082E04F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECACBBAE-0407-4536-883E-0345D98247B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,25 +95,25 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000593-90.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Jurandir Pereira Da Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010610-42.2026.5.03.0152</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Everton De Menezes Santos</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
   </si>
   <si>
     <t>Instrução</t>
@@ -125,110 +125,26 @@
     <t>CENTRAL</t>
   </si>
   <si>
-    <t>R$             893.529,55</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1000759-22.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Samuel Sousa Salgado</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             271.985,81</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>Audiência de Encerramento de Instrução</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>Itumbiara Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Isadora Moscardini Roschel</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>22ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.198.073,17</t>
+    <t>R$               83.122,87</t>
   </si>
   <si>
     <t>Grupo E2</t>
   </si>
   <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Dispensado o comparecimento das partes</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000916-95.2026.5.10.0009</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Industria Doceira E Alimentar Ltda</t>
-  </si>
-  <si>
-    <t>Jose Carlos Dos Santos Ramos</t>
-  </si>
-  <si>
-    <t>BRASÍLIA</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>09ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             630.017,05</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://trt10-jus-br.zoom.us/j/2748578818</t>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt3uberaba</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +164,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -327,10 +251,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,8 +278,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -686,30 +615,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C3838E7-10E4-4CBA-967B-D9FFCBE8CB54}">
-  <dimension ref="A1:R5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8489D535-48A6-45C0-9211-4EB3308F96FB}">
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="35.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,15 +694,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104579</v>
+        <v>105324</v>
       </c>
       <c r="B2" s="5">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C2" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -817,181 +746,13 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>104772</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46241</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.4513888888888889</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>102861</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46241</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>105612</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46241</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.66111111111111109</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R5" r:id="rId1" xr:uid="{6BAA673C-60B3-4830-B9B2-BFA693A810EA}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{E47E0F5C-03E4-4A63-A1AC-7B1AC9FF3CEE}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05DDE9D-E5F1-4496-AD32-0CE32A04B1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{695807F2-5749-4209-91D4-BA627D32AF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECACBBAE-0407-4536-883E-0345D98247B8}"/>
+    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{6DC7A003-6E25-4122-922C-6AFFD9D0FBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="278">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,49 +95,784 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000044-43.2026.5.09.0095</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Gabriel Labiak</t>
+  </si>
+  <si>
+    <t>FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               13.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/gcggc ID da Reunião: 85323079278 Senha: YdtW4vgwZV</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010708-49.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Gustavo Martins Montandon</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               70.920,29</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0010915-61.2026.5.15.0097</t>
+  </si>
+  <si>
+    <t>A. Raymond Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Wesley Klaesner</t>
+  </si>
+  <si>
+    <t>JUNDIAÍ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             102.250,39</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85290954703?pwd=ZldYYzczVnhUbm1VN3BPVzAvRmY5QT09 ID da reunião: 852 9095 4703 Senha de acesso: 517309</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1000889-75.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuhos</t>
+  </si>
+  <si>
+    <t>Anderson Fernando Da Silva</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               83.648,82</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1000908-81.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Cbc - Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Rodrigo Da Silva Alves</t>
+  </si>
+  <si>
+    <t>R$             313.477,00</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000564-28.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Vanderson Soares Leal</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             108.013,23</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000076-20.2026.5.09.0072</t>
+  </si>
+  <si>
+    <t>Dheividi Antonio Bottega</t>
+  </si>
+  <si>
+    <t>PATO BRANCO</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               52.742,16</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/dlay4 ID da Reunião: 87503709525 Senha: vdjx1W7evI</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001127-22.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Evandro Felisberto</t>
+  </si>
+  <si>
+    <t>R$             103.670,17</t>
+  </si>
+  <si>
+    <t>0000093-56.2026.5.09.0072</t>
+  </si>
+  <si>
+    <t>Valmir Facin</t>
+  </si>
+  <si>
+    <t>R$               89.687,20</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/g461u ID da Reunião: 86092009599 Senha: d41aSQbv0s</t>
+  </si>
+  <si>
+    <t>1001176-72.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Marcos Cesar Santos Nascimento</t>
+  </si>
+  <si>
+    <t>R$             458.348,52</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>0010477-85.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Lucas Dos Santos Araujo</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>R$             290.180,77</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>JNE</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>1001399-16.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Massao Carvalho Hara</t>
+  </si>
+  <si>
+    <t>R$             357.804,58</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>0012424-76.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Cicera De Barros Gois</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$             195.234,22</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09 ID da reunião: 873 7536 5338 Senha de acesso: 203482</t>
+  </si>
+  <si>
+    <t>1001244-39.2026.5.02.0491</t>
+  </si>
+  <si>
+    <t>Gesse De Oliveira Marciano</t>
+  </si>
+  <si>
+    <t>SUZANO</t>
+  </si>
+  <si>
+    <t>R$               51.604,12</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial | Preposto - Fabiana da Silva Souza fsouza.correspondenciajuridica@gmail.com (11)9612-58642</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012500-03.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Leandro Juriati De Alencar</t>
+  </si>
+  <si>
+    <t>R$             384.860,81</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>1000724-56.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Wilson Aparecido Sant Ana</t>
+  </si>
+  <si>
+    <t>R$               79.500,00</t>
+  </si>
+  <si>
+    <t>0011405-31.2025.5.15.0061</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>David Rodrigues</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             215.406,50</t>
+  </si>
+  <si>
+    <t>Correspondente - Carla</t>
+  </si>
+  <si>
+    <t>FCG</t>
+  </si>
+  <si>
+    <t>0000131-68.2026.5.09.0072</t>
+  </si>
+  <si>
+    <t>Adriano Ferreira Nize</t>
+  </si>
+  <si>
+    <t>R$               30.866,14</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/r7lru ID da reunião: 89205457621 Senha de acesso: JrPTNLbAKI</t>
+  </si>
+  <si>
+    <t>0012494-93.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Luiz Fernando Candido</t>
+  </si>
+  <si>
+    <t>R$             175.134,71</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000573-04.2024.5.12.0013</t>
+  </si>
+  <si>
+    <t>Uhe São Simão Energia S.A.</t>
+  </si>
+  <si>
+    <t>Deidison Nogueira Chaves</t>
+  </si>
+  <si>
+    <t>CAÇADOR</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             154.282,68</t>
+  </si>
+  <si>
+    <t>https://trt12-jus-br.zoom.us/j/84661896705?pwd=L1paSzMvcTdBYmVQekpvTTN4UFYxZz09</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000117-84.2026.5.09.0072</t>
+  </si>
+  <si>
+    <t>Ederson Bortolamedi</t>
+  </si>
+  <si>
+    <t>R$               70.980,20</t>
+  </si>
+  <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>0010610-42.2026.5.03.0152</t>
+    <t>1001448-64.2026.5.02.0271</t>
+  </si>
+  <si>
+    <t>Itw Chemical Products Ltda</t>
+  </si>
+  <si>
+    <t>Claudevania Alves Da Silva</t>
+  </si>
+  <si>
+    <t>EMBU DAS ARTES</t>
+  </si>
+  <si>
+    <t>R$               74.855,56</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87042849408?pwd=MWKY5WPzbL9Y8YG7Eapl4HZvxXWsuu.1 ID da reunião: 870 4284 9408 Senha de acesso: 596170</t>
+  </si>
+  <si>
+    <t>0000143-82.2026.5.09.0072</t>
+  </si>
+  <si>
+    <t>Clovis Bueno Necke</t>
+  </si>
+  <si>
+    <t>R$               66.664,34</t>
+  </si>
+  <si>
+    <t>0013480-97.2025.5.15.0140</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Paulo Henrique De Oliveira Capitao</t>
+  </si>
+  <si>
+    <t>ATIBAIA</t>
+  </si>
+  <si>
+    <t>R$               39.337,26</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87915621902?pwd=rxRFrbhsQyciIjUesIVP4IDsww7bNo.1 ID: 87915621902 Senha: 726007</t>
+  </si>
+  <si>
+    <t>1000067-74.2026.5.02.0027</t>
+  </si>
+  <si>
+    <t>Bit Services Inovação E Tecnologia Ltda</t>
+  </si>
+  <si>
+    <t>Anderson Da Silva Maciel</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>27ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             902.193,80</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>0014381-60.2025.5.15.0077</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Ezequiel Borges Diniz</t>
+  </si>
+  <si>
+    <t>INDAIATUBA</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               42.673,82</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1 ID da reunião 882 1575 1954 Senha 150077</t>
+  </si>
+  <si>
+    <t>1000742-84.2026.5.02.0464</t>
+  </si>
+  <si>
+    <t>Gerson Dourado Santos</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             171.969,67</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>1000540-73.2026.5.02.0055</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Rodrigo De Souza Carvalho</t>
+  </si>
+  <si>
+    <t>55ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             187.199,20</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001140-87.2021.5.02.0017</t>
+  </si>
+  <si>
+    <t>Ivanyra Maura De Medeiros Correia</t>
+  </si>
+  <si>
+    <t>Zurich Minas Brasil Seguros S.A.</t>
+  </si>
+  <si>
+    <t>16ª TURMA</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$          1.025.574,44</t>
+  </si>
+  <si>
+    <t>Grupo A2</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>1001132-84.2025.5.02.0045</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Priscila Oliveira Yashiro</t>
+  </si>
+  <si>
+    <t>R$          1.093.287,00</t>
+  </si>
+  <si>
+    <t>1000278-27.2026.5.02.0087</t>
+  </si>
+  <si>
+    <t>Paulo Sergio De Souza</t>
+  </si>
+  <si>
+    <t>87ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               92.201,00</t>
+  </si>
+  <si>
+    <t>0011319-78.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Simone Camargo</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$             188.376,72</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>0000012-13.2026.5.09.0071</t>
+  </si>
+  <si>
+    <t>Marcos Paulo Rufino Sampaio</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>R$               46.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/xnrmx ID da reunião: 86081852357 Senha de acesso: ieM9kAEuoc</t>
+  </si>
+  <si>
+    <t>0000020-87.2026.5.09.0071</t>
+  </si>
+  <si>
+    <t>R$             238.600,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/e97nv ID da reunião: 82868807069 Senha de acesso: SW0CI1kIpC</t>
+  </si>
+  <si>
+    <t>0010114-50.2025.5.15.0140</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Ana Lucia Pereira Alves</t>
+  </si>
+  <si>
+    <t>R$               95.708,68</t>
+  </si>
+  <si>
+    <t>0010009-67.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Ediney Rogerio Alkmin</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$             156.594,02</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>0000353-48.2026.5.09.0068</t>
+  </si>
+  <si>
+    <t>Valdinei Candido Da Silva</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>R$             358.600,00</t>
+  </si>
+  <si>
+    <t>Correspondente</t>
+  </si>
+  <si>
+    <t>0010519-30.2026.5.03.0029</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Joao Victor Marques De Oliveira</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>R$               45.726,15</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem</t>
+  </si>
+  <si>
+    <t>0000012-22.2026.5.09.0068</t>
+  </si>
+  <si>
+    <t>R$               58.000,00</t>
+  </si>
+  <si>
+    <t>1000419-28.2019.5.02.0431</t>
+  </si>
+  <si>
+    <t>Jose Marcos Labadessa</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               50.984,07</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/85239557292?pwd=enBMVGxIVlR2bG5uUmk3Sy8yWmR6dz09 ID da reunião: 852 3955 7292 Senha de acesso: 611035</t>
+  </si>
+  <si>
+    <t>0010061-24.2024.5.03.0048</t>
   </si>
   <si>
     <t>Santa Juliana Bioenergia Ltda.</t>
   </si>
   <si>
-    <t>Everton De Menezes Santos</t>
-  </si>
-  <si>
-    <t>UBERABA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               83.122,87</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>JNE</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt3uberaba</t>
+    <t>Katia Aparecida Hinham</t>
+  </si>
+  <si>
+    <t>ARAXÁ</t>
+  </si>
+  <si>
+    <t>R$             743.196,04</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
   </si>
 </sst>
 </file>
@@ -615,30 +1350,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8489D535-48A6-45C0-9211-4EB3308F96FB}">
-  <dimension ref="A1:R2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE838D4-D970-474D-B21E-BCAB060EBE48}">
+  <dimension ref="A1:R42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,15 +1429,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105324</v>
+        <v>103769</v>
       </c>
       <c r="B2" s="5">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34375</v>
+        <v>0.35069444444444442</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -750,9 +1485,2268 @@
         <v>32</v>
       </c>
     </row>
+    <row r="3" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>105331</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>104698</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>105299</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105458</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>104526</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>103879</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105258</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>103926</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>105334</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105326</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>105616</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>99427</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>105415</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>99864</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>104771</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>103627</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>104045</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>99860</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>97984</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>104018</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>105097</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104066</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>103804</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>103845</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>103255</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>105003</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>104661</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>80980</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>104092</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>104326</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>101302</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>103751</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>103733</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>99791</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>99660</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="R37" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>104373</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>104559</v>
+      </c>
+      <c r="B39" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.63958333333333328</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>103730</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>66582</v>
+      </c>
+      <c r="B41" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>97004</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46246</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="O42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P42" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{E47E0F5C-03E4-4A63-A1AC-7B1AC9FF3CEE}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{BBF47088-3F17-42C3-AA5B-43F090BC0C61}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{E812C3D3-9547-46E6-B6E3-4ACB8D0F1CAF}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/85290954703?pwd=ZldYYzczVnhUbm1VN3BPVzAvRmY5QT09%20ID%20da%20reunião:%20852%209095%204703%20Senha%20de%20acesso:%20517309" xr:uid="{7ECD4C40-2A01-4DFB-A0D7-0A58CFD9A73C}"/>
+    <hyperlink ref="R8" r:id="rId4" display="https://url.trt9.jus.br/dlay4" xr:uid="{097E40AF-203B-4DC6-BA5B-E86CF234C5A8}"/>
+    <hyperlink ref="R10" r:id="rId5" xr:uid="{22A3B19A-B37E-408D-8A79-26BD7D466DB7}"/>
+    <hyperlink ref="R12" r:id="rId6" xr:uid="{CCD5148B-9C54-4021-9C61-BD3F2B0653B4}"/>
+    <hyperlink ref="R14" r:id="rId7" display="https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09%20ID%20da%20reunião:%20873%207536%205338%20Senha%20de%20acesso:%20203482" xr:uid="{7D3F6C56-0488-45FB-8684-F10BB31BA91D}"/>
+    <hyperlink ref="R15" r:id="rId8" display="mailto:fsouza.correspondenciajuridica@gmail.com" xr:uid="{7524DC30-991C-4443-90AE-1E4634B49B49}"/>
+    <hyperlink ref="R19" r:id="rId9" xr:uid="{DCB53F66-886F-4C1D-B538-EE52A5E95F4E}"/>
+    <hyperlink ref="R21" r:id="rId10" xr:uid="{311DE6E7-2084-4FB6-9BC5-976DE538A922}"/>
+    <hyperlink ref="R22" r:id="rId11" xr:uid="{0FDABE2A-92A9-43E0-A37A-C3D9D959A0DB}"/>
+    <hyperlink ref="R23" r:id="rId12" display="https://trt2-jus-br.zoom.us/j/87042849408?pwd=MWKY5WPzbL9Y8YG7Eapl4HZvxXWsuu.1%20ID%20da%20reunião:%20870%204284%209408%20Senha%20de%20acesso:%20596170" xr:uid="{DADD4023-044E-47B4-9B7F-71C8B7BAA202}"/>
+    <hyperlink ref="R24" r:id="rId13" xr:uid="{A684A5BC-9594-4766-8310-FEB0AB8CA0C7}"/>
+    <hyperlink ref="R25" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/87915621902?pwd=rxRFrbhsQyciIjUesIVP4IDsww7bNo.1%20ID:%2087915621902%20Senha:%20726007" xr:uid="{F6F996F8-FF1B-49D4-88D5-59ED840D8157}"/>
+    <hyperlink ref="R27" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1%20ID%20da%20reunião%20882%201575%201954%20Senha%20150077" xr:uid="{CCA79AF8-3AEA-43A1-B3DD-B5FB31BAB416}"/>
+    <hyperlink ref="R34" r:id="rId16" xr:uid="{A7C6B1D1-4A13-4056-81B8-3BDD59562862}"/>
+    <hyperlink ref="R35" r:id="rId17" xr:uid="{24C57B20-78F2-4EB6-A476-EC60D3AE1DAB}"/>
+    <hyperlink ref="R39" r:id="rId18" xr:uid="{B87AAAB3-7477-41ED-99D4-2512B2FF068E}"/>
+    <hyperlink ref="R41" r:id="rId19" display="https://trt2-jus-br.zoom.us/j/85239557292?pwd=enBMVGxIVlR2bG5uUmk3Sy8yWmR6dz09%20ID%20da%20reunião:%20852%203955%207292%20Senha%20de%20acesso:%20611035" xr:uid="{B918E695-63E1-4AD2-AE97-EBD1FE7A80DD}"/>
+    <hyperlink ref="R42" r:id="rId20" xr:uid="{05658072-DD60-43CA-8172-7020106E5B4A}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{118F98CF-9F96-4836-96F3-38225CB15CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C92D722-EB8E-4C8E-9FD3-1ADB62797771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C419C5D1-0D51-4A22-9EF9-68A772DDFDBF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{827517D9-4175-4433-AFC0-C5B9D3204545}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="268">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -98,520 +98,751 @@
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0024894-71.2025.5.24.0066</t>
+    <t>0000407-11.2026.5.09.0069</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Rafael Butori Da Silva</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             398.100,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/oqtux ID da Reunião: 89475386843 Senha: vMXmvyZFhQ</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010608-26.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Denilson Silva Bonfim</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             182.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09 ID DA REUNIÃO: 899 3988 0446 SENHA:  608226</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011655-15.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Joao Paulo De Oliveira Borges</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>Ação Revisional</t>
+  </si>
+  <si>
+    <t>R$                 1.000,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010809-09.2026.5.03.0041</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Renato Soares Da Silva</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$               36.889,64</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/88449648691 ID da reunião: 884 4964 8691 Senha de acesso: 0041</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000257-55.2026.5.09.0093</t>
+  </si>
+  <si>
+    <t>Marcelo Favaro Cunha Nishyama</t>
+  </si>
+  <si>
+    <t>CORNÉLIO PROCÓPIO</t>
+  </si>
+  <si>
+    <t>R$             335.000,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/ubsbs ID da reunião: 87911901337 Senha de acesso: 0dguJ0ryKr</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010069-19.2025.5.03.0063</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Wedson Da Silva</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$               60.946,56</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1itba</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010534-24.2020.5.15.0013</t>
+  </si>
+  <si>
+    <t>Lauro Batista De Siqueira</t>
+  </si>
+  <si>
+    <t>04ª TURMA</t>
+  </si>
+  <si>
+    <t>R$               88.083,92</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87813703141?pwd=StmQzxzeHcTb0VEfPuO14t0BBfbEsm.1 ID da reunião: 878 1370 3141 Senha: 592669</t>
+  </si>
+  <si>
+    <t>0012496-63.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Emily Aline De Oliveira</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$               48.339,13</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09 ID da reunião: 873 7536 5338 Senha de acesso: 203482</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0012648-75.2025.5.15.0007</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Fabio Roberto Carvalho Ferreira</t>
+  </si>
+  <si>
+    <t>AMERICANA</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             595.082,69</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/86483603580?pwd=bm1zQld2eFdic1JQQ2pMdWg5ZjhQUT09 ID da reunião: 864 8360 3580 Senha: 070707</t>
+  </si>
+  <si>
+    <t>0010500-39.2025.5.15.0089</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Alan Dias Almeida</t>
+  </si>
+  <si>
+    <t>BAURU</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               64.910,61</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/my/salaprincipal2vtbauru?pwd=TGIvVEZVbGNUOXNSYm40SXFrVlpBQT09</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010542-09.2025.5.15.0083</t>
+  </si>
+  <si>
+    <t>Fernando Jose Haas</t>
+  </si>
+  <si>
+    <t>R$             176.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Camila</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>0011443-56.2026.5.15.0013</t>
+  </si>
+  <si>
+    <t>Clecio Renato Dos Santos De Andrade</t>
+  </si>
+  <si>
+    <t>R$                 3.559,72</t>
+  </si>
+  <si>
+    <t>0010044-97.2024.5.15.0130</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Tonyelzio Frances Feitosa Lima</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             175.217,38</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1 ID da reunião: 870 3865 6391 Senha: 771785</t>
+  </si>
+  <si>
+    <t>1000968-88.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Vinicius Correia Dos Santos</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             134.964,33</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>1001230-15.2026.5.02.0084</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Raphael Fernandes De Castro</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>84ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             674.018,47</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0010901-88.2024.5.15.0019</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Edivaldo Ribeiro Costa</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             797.678,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Carla</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>0010882-58.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Marcos Roberto Teixeira Flores</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$               37.967,57</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0000463-74.2026.5.14.0111</t>
+  </si>
+  <si>
+    <t>Syngenta Digital Ltda</t>
+  </si>
+  <si>
+    <t>Lucas Rafael Chiquito De Souza</t>
+  </si>
+  <si>
+    <t>PIMENTA BUENO</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>R$             235.287,92</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>https://trt14-jus-br.zoom.us/j/82618890933?pwd=fjl4saUL32oiFfej0JXbzWkPLUEvVa.1 ID da reunião: 826 1889 0933 Senha: 140240</t>
+  </si>
+  <si>
+    <t>1000635-87.2026.5.02.0028</t>
+  </si>
+  <si>
+    <t>Bit Services Inovação E Tecnologia Ltda.</t>
+  </si>
+  <si>
+    <t>Bruno Casa Nova Mariano</t>
+  </si>
+  <si>
+    <t>28ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.428.844,18</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>JQS</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81345987692?pwd=VzFEVDJseUNwWUxQaHFYRTlrRjdXUT09 ID da reunião: 813 4598 7692 Senha de acesso: 663288</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1000956-71.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Bruno Farabotti Clemente</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               85.454,67</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001647-34.2025.5.02.0041</t>
+  </si>
+  <si>
+    <t>Alessandra Roberta Lucia Gabeloni De Carvalho</t>
+  </si>
+  <si>
+    <t>R$               81.751,24</t>
+  </si>
+  <si>
+    <t>1002221-85.2024.5.02.0431</t>
+  </si>
+  <si>
+    <t>Rodrigo Grecco De Freitas Franco</t>
+  </si>
+  <si>
+    <t>09ª TURMA</t>
+  </si>
+  <si>
+    <t>R$               60.000,00</t>
+  </si>
+  <si>
+    <t>1000152-53.2023.5.02.0613</t>
+  </si>
+  <si>
+    <t>Edson De Lima Solla</t>
+  </si>
+  <si>
+    <t>ZONA LESTE</t>
+  </si>
+  <si>
+    <t>R$               58.320,39</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>0010336-60.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Robson Vinicius Clavico Da Silva</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$               40.614,74</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>1001873-24.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>Cliford Jean Baptiste</t>
+  </si>
+  <si>
+    <t>11ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             226.807,85</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>0011151-62.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Rafael Henrique Fernandes Afonso</t>
+  </si>
+  <si>
+    <t>R$               38.433,00</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
+  </si>
+  <si>
+    <t>1002293-38.2025.5.02.0431</t>
+  </si>
+  <si>
+    <t>Paulo Cesar Sparapani</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>R$             143.577,46</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81886655332?pwd=ANovV8FZBJKHJra3ybU2cVjJ0AgvHW.1 ID da reunião: 818 8665 5332 Senha de acesso: 813179</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010859-77.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Marcio De Moraes</t>
+  </si>
+  <si>
+    <t>R$             450.425,56</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>0020456-64.2023.5.04.0733</t>
+  </si>
+  <si>
+    <t>Luis Augusto Do Carmo</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ DO SUL</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>R$          1.023.904,45</t>
+  </si>
+  <si>
+    <t>https://trt4-jus-br.zoom.us/my/turma03</t>
+  </si>
+  <si>
+    <t>0000015-81.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Carlos Henrique De Andrade Rocha</t>
+  </si>
+  <si>
+    <t>R$               62.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/3jy7c ID da Reunião: 88086506714 Senha: QFav9LoTol</t>
+  </si>
+  <si>
+    <t>0020262-52.2025.5.04.0003</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Daniel Oliveira Da Silva</t>
+  </si>
+  <si>
+    <t>PORTO ALEGRE</t>
+  </si>
+  <si>
+    <t>R$             447.130,45</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>Correspondente - Jaeger</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>0025591-33.2025.5.24.0021</t>
   </si>
   <si>
     <t>Moema Bioenergia S.A. - Monteverde</t>
   </si>
   <si>
-    <t>Wellington Nazareth Da Silva</t>
-  </si>
-  <si>
-    <t>PONTA PORÃ</t>
+    <t>Nerivaldo Paiva Santos</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
   </si>
   <si>
     <t>MS</t>
   </si>
   <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             726.147,56</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/j/82166071438</t>
-  </si>
-  <si>
-    <t>0000480-69.2026.5.08.0114</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Hugo Fabiano Pereira Porto</t>
-  </si>
-  <si>
-    <t>PARAUAPEBAS</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          6.244.218,36</t>
+    <t>R$             218.910,14</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
   </si>
   <si>
     <t>ARC</t>
   </si>
   <si>
-    <t>https://trt8-jus-br.zoom.us/j/83916347992?pwd=dDN3TGZJRUluQmNDQUcvOWhNRlM0Zz09 ID da reunião: 839 1634 7992 Senha de Acesso: Q9EuZ6sq</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0000261-32.2026.5.10.0007</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Industria Doceria E Alimentar Ltda</t>
-  </si>
-  <si>
-    <t>Katia De Souza Malheiros</t>
-  </si>
-  <si>
-    <t>BRASÍLIA</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>07ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             283.091,87</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Larissa de Carvalho Costa (61) 98137-5115 | Preposto - Emanuel Vinicius Alves Pereira (61) 98215-3051</t>
-  </si>
-  <si>
-    <t>0000241-54.2026.5.12.0017</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Vismar Thomazi Junior</t>
-  </si>
-  <si>
-    <t>MAFRA</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>R$               42.968,96</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>https://trt12-jus-br.zoom.us/j/85925876294?pwd=ur06OyWDjIqWmgea6xMgHIUbbPkC27.1 ID da reunião: 859 2587 6294 Senha: 268259</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Presencial</t>
-  </si>
-  <si>
-    <t>0010307-24.2026.5.15.0013</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Douglas De Almeida</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>R$             218.000,00</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>1001217-47.2021.5.02.0001</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Danielle Araujo De Sa</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>CEJUSC TST</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$          2.127.237,00</t>
-  </si>
-  <si>
-    <t>Grupo A3</t>
-  </si>
-  <si>
-    <t>PBS</t>
-  </si>
-  <si>
-    <t>SOF</t>
-  </si>
-  <si>
-    <t>bit.ly/Cejusc2026</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001433-03.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Wagner Goncalves Rosario</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$          1.064.563,78</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0012095-88.2025.5.15.0084</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Gislene De Abreu Pereira</t>
+    <t>Presencial | Advogada - Kelly Cristine Vieira de Souza kellycvsa@hotmail.com 67999609707</t>
+  </si>
+  <si>
+    <t>0000477-87.2026.5.07.0035</t>
+  </si>
+  <si>
+    <t>Joao Vitor Barbosa Da Silva</t>
+  </si>
+  <si>
+    <t>ARACATI</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>R$                 5.817,92</t>
+  </si>
+  <si>
+    <t>https://trt7-jus-br.zoom.us/j/81867554890?pwd=Q0hoOGxaajVCSS9WakV3VnFQZHlWQT0</t>
+  </si>
+  <si>
+    <t>1002200-66.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>Renato Eli Minarini Souza</t>
   </si>
   <si>
     <t>04ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>R$               30.021,85</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Juliana Falarara Saez julianasaez@gmail.com (12)9970-08631</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0016544-53.2026.5.16.0011</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Ruan Carlos Teixeira Gomes</t>
-  </si>
-  <si>
-    <t>BALSAS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             253.073,03</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81494992654?pwd=USK67SZiJxCJyz0JF8BOTyafLlaitb.1</t>
-  </si>
-  <si>
-    <t>0011158-27.2026.5.15.0025</t>
-  </si>
-  <si>
-    <t>Julio Cesar Vieira</t>
-  </si>
-  <si>
-    <t>BOTUCATU</t>
-  </si>
-  <si>
-    <t>R$             102.668,64</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87539096808?pwd=ZG9OblpFcVRDVnFiNUdrZEdkazkzQT09</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0011271-24.2026.5.15.0043</t>
-  </si>
-  <si>
-    <t>Marcelo Cesar Dos Santos</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.169.645,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1 ID da reunião: 838 7184 7087 Senha: TRT15</t>
-  </si>
-  <si>
-    <t>0011238-08.2026.5.15.0084</t>
-  </si>
-  <si>
-    <t>Leonardo Rodolfo De Carvalho</t>
-  </si>
-  <si>
-    <t>R$             277.509,87</t>
-  </si>
-  <si>
-    <t>0010589-87.2026.5.15.0037</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Bruna Goncalves Silvio</t>
-  </si>
-  <si>
-    <t>FERNANDÓPOLIS</t>
-  </si>
-  <si>
-    <t>R$               13.796,09</t>
-  </si>
-  <si>
-    <t>NLO</t>
-  </si>
-  <si>
-    <t>JNE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09 ID da reunião: 897 7008 2465 Senha de acesso: 908050</t>
-  </si>
-  <si>
-    <t>1000404-80.2024.5.02.0432</t>
-  </si>
-  <si>
-    <t>Rodrigo Ramiro Da Silva</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>R$             104.005,19</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/89948204968?pwd=yyk35cWYYCBUq9BWwsyYbda4EqkZvp.1 ID da reunião: 899 4820 4968 Senha de acesso: 202123</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Telepresencial</t>
-  </si>
-  <si>
-    <t>1001794-73.2025.5.02.0069</t>
-  </si>
-  <si>
-    <t>Sueli Aparecida Dourado</t>
-  </si>
-  <si>
-    <t>12ª TURMA</t>
-  </si>
-  <si>
-    <t>R$          2.139.761,00</t>
-  </si>
-  <si>
-    <t>Não sustentaremos</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0010756-65.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>Marcio Cleyberg De Sousa Silva</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             138.432,71</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
-  </si>
-  <si>
-    <t>0011187-20.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>Zildevalda De Souza Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             889.400,20</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 050728</t>
-  </si>
-  <si>
-    <t>0010825-69.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Jeronimo Da Silva Junior</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>R$               18.773,02</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1002089-82.2025.5.02.0434</t>
-  </si>
-  <si>
-    <t>Andre Ranolfi Alves</t>
-  </si>
-  <si>
-    <t>R$             218.958,20</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0010827-38.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Rafael Querubim Medici Amorim</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             331.734,05</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>https://bit.ly/cejusclimeirasala1</t>
-  </si>
-  <si>
-    <t>0011323-34.2024.5.15.0061</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Larine Aparecida Pereira Custodio</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$             309.178,65</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>bit.ly/cejusc2grau</t>
+    <t>R$             407.184,07</t>
+  </si>
+  <si>
+    <t>0010319-09.2026.5.03.0066</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Felipe Pimentel De Oliveira</t>
+  </si>
+  <si>
+    <t>MANHUAÇU</t>
+  </si>
+  <si>
+    <t>R$               64.433,60</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/varamanhuacu</t>
   </si>
 </sst>
 </file>
@@ -1089,30 +1320,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4179163A-25FD-44F3-8101-A7337B18057D}">
-  <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB358652-6F55-4BBF-991A-C45A8B2F5C20}">
+  <dimension ref="A1:R36"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="124.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,12 +1383,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>103799</v>
+        <v>104442</v>
       </c>
       <c r="B2" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C2" s="6">
         <v>0.35416666666666669</v>
@@ -1224,39 +1439,39 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104773</v>
+        <v>104970</v>
       </c>
       <c r="B3" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C3" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1265,104 +1480,104 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>104319</v>
+        <v>102126</v>
       </c>
       <c r="B4" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C4" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>104344</v>
+        <v>105618</v>
       </c>
       <c r="B5" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C5" s="6">
-        <v>0.43055555555555558</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>24</v>
@@ -1377,51 +1592,51 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>104304</v>
+        <v>104512</v>
       </c>
       <c r="B6" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C6" s="6">
-        <v>0.43402777777777779</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>25</v>
@@ -1433,110 +1648,110 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>95808</v>
+        <v>99778</v>
       </c>
       <c r="B7" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C7" s="6">
-        <v>0.44583333333333336</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105632</v>
+        <v>93812</v>
       </c>
       <c r="B8" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C8" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1545,51 +1760,51 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>103144</v>
+        <v>99861</v>
       </c>
       <c r="B9" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C9" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>25</v>
@@ -1601,54 +1816,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>104928</v>
+        <v>103570</v>
       </c>
       <c r="B10" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C10" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.40625</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1657,39 +1872,39 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>107</v>
       </c>
       <c r="Q10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="R10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>100301</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>104980</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46251</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.46527777777777779</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>111</v>
@@ -1698,10 +1913,10 @@
         <v>112</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>25</v>
@@ -1713,54 +1928,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>105440</v>
+        <v>100391</v>
       </c>
       <c r="B12" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4826388888888889</v>
+        <v>0.4201388888888889</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1769,51 +1984,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="Q12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="P12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>104837</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Q12" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="R12" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>105307</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46251</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="H13" s="7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1825,54 +2040,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>97080</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>105366</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46251</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="I14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1884,51 +2099,51 @@
         <v>132</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>97452</v>
+        <v>105045</v>
       </c>
       <c r="B15" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C15" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.44097222222222221</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1937,54 +2152,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>104177</v>
+        <v>105661</v>
       </c>
       <c r="B16" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C16" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1993,54 +2208,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="R16" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>101300</v>
+        <v>100730</v>
       </c>
       <c r="B17" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C17" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>151</v>
+        <v>24</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2049,54 +2264,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105242</v>
+        <v>105770</v>
       </c>
       <c r="B18" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C18" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2105,51 +2320,51 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>105345</v>
+        <v>105754</v>
       </c>
       <c r="B19" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C19" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>25</v>
@@ -2161,51 +2376,51 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>103174</v>
+        <v>104766</v>
       </c>
       <c r="B20" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C20" s="6">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
@@ -2217,54 +2432,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>59</v>
+        <v>177</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>101325</v>
+        <v>105037</v>
       </c>
       <c r="B21" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C21" s="6">
-        <v>0.62569444444444444</v>
+        <v>0.51736111111111116</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2273,54 +2488,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>100731</v>
+        <v>104077</v>
       </c>
       <c r="B22" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C22" s="6">
-        <v>0.62847222222222221</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2329,36 +2544,829 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R22" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>99645</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>190</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>101209</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>104450</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>102844</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>98160</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>103494</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>97826</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>101136</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>103725</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>100232</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>102185</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.63194444444444442</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>105472</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>103299</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="R35" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>104720</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46252</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{887B62A6-FD0C-4BB3-806E-C9AD0234BB17}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt8-jus-br.zoom.us/j/83916347992?pwd=dDN3TGZJRUluQmNDQUcvOWhNRlM0Zz09%20ID%20da%20reunião:%20839%201634%207992%20Senha%20de%20Acesso:%20Q9EuZ6sq" xr:uid="{A69536C2-7D7C-489F-8D92-E0690E4BF5B5}"/>
-    <hyperlink ref="R5" r:id="rId3" display="https://trt12-jus-br.zoom.us/j/85925876294?pwd=ur06OyWDjIqWmgea6xMgHIUbbPkC27.1%20ID%20da%20reunião:%20859%202587%206294%20Senha:%20268259" xr:uid="{03B5252C-C223-40DD-A86B-167D186EE6E2}"/>
-    <hyperlink ref="R9" r:id="rId4" display="mailto:julianasaez@gmail.com" xr:uid="{6A57F515-8A2D-4007-AE71-E4267EE8E12F}"/>
-    <hyperlink ref="R10" r:id="rId5" xr:uid="{F36D6169-124C-485B-AF6C-A5AEDFA52E99}"/>
-    <hyperlink ref="R11" r:id="rId6" xr:uid="{31C060E4-3208-426F-940B-191D9E62CBDA}"/>
-    <hyperlink ref="R12" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1%20ID%20da%20reunião:%20838%207184%207087%20Senha:%20TRT15" xr:uid="{B4DFABAE-C6FC-4DB5-A944-C1BC1556387D}"/>
-    <hyperlink ref="R14" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09%20ID%20da%20reunião:%20897%207008%202465%20Senha%20de%20acesso:%20908050" xr:uid="{2040FC28-BCA9-4B67-9EE6-D29D3DC21D8A}"/>
-    <hyperlink ref="R15" r:id="rId9" display="https://trt2-jus-br.zoom.us/j/89948204968?pwd=yyk35cWYYCBUq9BWwsyYbda4EqkZvp.1%20ID%20da%20reunião:%20899%204820%204968%20Senha%20de%20acesso:%20202123" xr:uid="{30E07435-A4B7-4E4F-8F0C-E10CD7A02237}"/>
-    <hyperlink ref="R17" r:id="rId10" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{6AD5BD76-BB39-4B83-9819-89C6DD91A204}"/>
-    <hyperlink ref="R18" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%20050728" xr:uid="{BB239B18-D5AB-4E4F-81A1-D44D119B7492}"/>
-    <hyperlink ref="R19" r:id="rId12" xr:uid="{7BF74185-6309-4825-852F-90B7842637DA}"/>
-    <hyperlink ref="R21" r:id="rId13" xr:uid="{EB6BC3CF-85DB-40AE-AD0A-CA4C6343830F}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{4A4AC88E-43F6-46DC-9044-7720C362971B}"/>
+    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09%20ID%20DA%20REUNIÃO:%20899%203988%200446%20SENHA:%20%20608226" xr:uid="{475DCCC6-5CDB-4CE3-ACBF-13649C5CCB15}"/>
+    <hyperlink ref="R4" r:id="rId3" xr:uid="{46773B6D-B1F6-48CF-BFB7-C51B74C57B70}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{5128EDB7-3130-459F-AB05-908CB6DF928D}"/>
+    <hyperlink ref="R6" r:id="rId5" xr:uid="{902C2858-4F9E-49B6-B5EA-250E1740B353}"/>
+    <hyperlink ref="R7" r:id="rId6" xr:uid="{748EEF30-ABA0-420E-86FF-67613DED89A4}"/>
+    <hyperlink ref="R8" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/87813703141?pwd=StmQzxzeHcTb0VEfPuO14t0BBfbEsm.1%20ID%20da%20reunião:%20878%201370%203141%20Senha:%20592669" xr:uid="{E1B8947F-7C76-49D6-975A-86C5DA16997C}"/>
+    <hyperlink ref="R9" r:id="rId8" display="https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09%20ID%20da%20reunião:%20873%207536%205338%20Senha%20de%20acesso:%20203482" xr:uid="{639F2DB6-6617-4AB2-9AFF-A911D16B5F1D}"/>
+    <hyperlink ref="R10" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/86483603580?pwd=bm1zQld2eFdic1JQQ2pMdWg5ZjhQUT09%20ID%20da%20reunião:%20864%208360%203580%20Senha:%20070707" xr:uid="{1B72B8F2-6F7F-4581-B6E5-CCDCB94BA896}"/>
+    <hyperlink ref="R11" r:id="rId10" xr:uid="{DABE8546-D328-46E7-A8A2-8A5B1899A49D}"/>
+    <hyperlink ref="R14" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1%20ID%20da%20reunião:%20870%203865%206391%20Senha:%20771785" xr:uid="{1C83783C-FBDA-41D3-BEED-E0FBD76F9053}"/>
+    <hyperlink ref="R18" r:id="rId12" xr:uid="{7C6EB58B-30D6-4543-8A60-28E2398ECB86}"/>
+    <hyperlink ref="R19" r:id="rId13" display="https://trt14-jus-br.zoom.us/j/82618890933?pwd=fjl4saUL32oiFfej0JXbzWkPLUEvVa.1%20ID%20da%20reunião:%20826%201889%200933%20Senha:%20140240" xr:uid="{CCF47ADE-97DD-4AE6-8117-B3986FD89D6E}"/>
+    <hyperlink ref="R20" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/81345987692?pwd=VzFEVDJseUNwWUxQaHFYRTlrRjdXUT09%20ID%20da%20reunião:%20813%204598%207692%20Senha%20de%20acesso:%20663288" xr:uid="{525084FE-D55F-4B2D-B536-DD99C2A106DF}"/>
+    <hyperlink ref="R25" r:id="rId15" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{7ECDF771-F11B-46EC-BB5A-42EAC5647A12}"/>
+    <hyperlink ref="R27" r:id="rId16" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%20532%20639%201733%20Senha%20de%20acesso:%20959215" xr:uid="{68C526E3-BD32-467A-9476-B365F8D3F8A8}"/>
+    <hyperlink ref="R28" r:id="rId17" display="https://trt2-jus-br.zoom.us/j/81886655332?pwd=ANovV8FZBJKHJra3ybU2cVjJ0AgvHW.1%20ID%20da%20reunião:%20818%208665%205332%20Senha%20de%20acesso:%20813179" xr:uid="{9EEE2C27-56C9-4D3B-8B74-D0E076EDA8C4}"/>
+    <hyperlink ref="R30" r:id="rId18" xr:uid="{F3D9AA88-5E6F-4D92-99B6-50C926B93076}"/>
+    <hyperlink ref="R31" r:id="rId19" xr:uid="{824DFD90-6C39-4F4F-86A4-7D101AA01646}"/>
+    <hyperlink ref="R33" r:id="rId20" display="mailto:kellycvsa@hotmail.com" xr:uid="{8C06B2AA-8645-42DD-9677-20C3FAEB161B}"/>
+    <hyperlink ref="R34" r:id="rId21" xr:uid="{F78ABBA4-9D95-4149-8B97-D4AF9858523F}"/>
+    <hyperlink ref="R36" r:id="rId22" xr:uid="{8764E2B9-EE8F-4857-990D-ADF47498C139}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C92D722-EB8E-4C8E-9FD3-1ADB62797771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F940ABCA-5FE4-42C5-BD57-B3C9A4DBA479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{827517D9-4175-4433-AFC0-C5B9D3204545}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B9FAA55-AB92-455D-AB64-0CE2BEE64997}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="255">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,761 +95,722 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010374-60.2025.5.15.0130</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Paloma Vianna De Andrade</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>11ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               79.669,83</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Isis Zuri, (19) 99287-5454</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000571-25.2026.5.05.0121</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Rodrigo Andrade Paes</t>
+  </si>
+  <si>
+    <t>CANDEIAS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               13.009,50</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt5-jus-br.zoom.us/my/sl1vtca</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1001416-92.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Adriano Lopes De Lima</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          2.463.695,63</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011566-58.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Pedro Soares Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             276.000,00</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0000407-11.2026.5.09.0069</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Rafael Butori Da Silva</t>
-  </si>
-  <si>
-    <t>CASCAVEL</t>
-  </si>
-  <si>
-    <t>PR</t>
+    <t>0011841-62.2025.5.15.0134</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Tiago Viegas Carvalho</t>
+  </si>
+  <si>
+    <t>LEME</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$          1.203.488,64</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/8060729658?</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010708-42.2026.5.15.0136</t>
+  </si>
+  <si>
+    <t>Valagro Brazil Manufacturing Industria E Comércio De Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Andre Gustavo Fernandes Da Silva</t>
+  </si>
+  <si>
+    <t>PIRASSUNUNGA</t>
+  </si>
+  <si>
+    <t>R$               54.010,00</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/2133746772?pwd=ZkJNaUxTODBrZXlqUitqQzdKSWhwdz09 ID da Reunião: 2133746772 Senha: 396868</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010313-37.2015.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Natalino Antonio Da Silva</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>3ª Instância</t>
+  </si>
+  <si>
+    <t>R$             456.285,50</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>bit.ly/Cejusc2026</t>
+  </si>
+  <si>
+    <t>0010861-42.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Silvana Aparecida Da Silva</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               24.796,46</t>
+  </si>
+  <si>
+    <t>NLO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0012530-38.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Luan Henrique Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>R$             113.637,10</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>0010885-70.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Valter Antonio Da Cunha</t>
+  </si>
+  <si>
+    <t>R$             120.629,30</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>0011714-72.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Marcos Rogerio De Paula Julio</t>
+  </si>
+  <si>
+    <t>CAÇAPAVA</t>
+  </si>
+  <si>
+    <t>R$               26.294,72</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88067116578?pwd=SGEwS2NQOUhSODlDK2krT2I5UmRvUT09 ID da reunião: 880 6711 6578 Senha: 223832</t>
+  </si>
+  <si>
+    <t>0011372-60.2015.5.15.0071</t>
+  </si>
+  <si>
+    <t>Marcos Roberto Teixeira</t>
+  </si>
+  <si>
+    <t>R$             177.520,50</t>
+  </si>
+  <si>
+    <t>0010883-03.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Joao Carlos Lucas Silva Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               26.157,44</t>
+  </si>
+  <si>
+    <t>0010865-79.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Francisco Mandu</t>
+  </si>
+  <si>
+    <t>R$          1.015.003,47</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001457-19.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Gabriel Rocha De Queiroz</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             140.162,55</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0000469-73.2026.5.10.0861</t>
+  </si>
+  <si>
+    <t>Pedro Afonso Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Marizete Rodrigues Torres</t>
+  </si>
+  <si>
+    <t>GUARAÍ</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>Ação de Consignação em Pagamento</t>
+  </si>
+  <si>
+    <t>R$                 6.001,59</t>
+  </si>
+  <si>
+    <t>NBB</t>
+  </si>
+  <si>
+    <t>https://trt10-jus-br.zoom.us/j/6334644559</t>
+  </si>
+  <si>
+    <t>0011927-13.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>Wickbold &amp; Nosso Pão Indústrias Alimentícias Ltda</t>
+  </si>
+  <si>
+    <t>Fagner Jose Ferreira Da Silva</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$             185.426,66</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (19) 99949-8727</t>
+  </si>
+  <si>
+    <t>0010409-81.2017.5.15.0071</t>
+  </si>
+  <si>
+    <t>Paulo Afonso De Carvalho Barbosa Junior</t>
+  </si>
+  <si>
+    <t>R$             171.669,54</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0000698-43.2026.5.22.0006</t>
+  </si>
+  <si>
+    <t>Sandro Rafael Da Silva</t>
+  </si>
+  <si>
+    <t>TERESINA</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>06ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               75.934,98</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>0011422-23.2014.5.15.0071</t>
+  </si>
+  <si>
+    <t>Cicero Elias Silva</t>
+  </si>
+  <si>
+    <t>R$             238.163,98</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000946-93.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Cbc- Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Wagner Martins Do Nascimento</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               39.544,15</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>1001404-06.2025.5.02.0263</t>
+  </si>
+  <si>
+    <t>Msa Do Brasil Equipamentos E Instrumentos De Segurança Ltda.</t>
+  </si>
+  <si>
+    <t>Maria Aparecida Bispo Da Silva</t>
+  </si>
+  <si>
+    <t>DIADEMA</t>
+  </si>
+  <si>
+    <t>R$               24.779,14</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>1001628-26.2022.5.02.0011</t>
+  </si>
+  <si>
+    <t>Ame Digital Brasil Instituição De Pagamento</t>
+  </si>
+  <si>
+    <t>Valdicionei Santana Santos</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             237.397,83</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>JQS</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001733-96.2025.5.02.0431</t>
+  </si>
+  <si>
+    <t>Carlos Jose Licio Junior</t>
+  </si>
+  <si>
+    <t>16ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             107.180,92</t>
+  </si>
+  <si>
+    <t>0010645-23.2026.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Cleverson Luan Vitorio Modesto Seixas</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>R$               37.977,69</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09 ID da reunião: 897 7008 2465 Senha de acesso: 908050</t>
+  </si>
+  <si>
+    <t>0012078-76.2024.5.15.0152</t>
+  </si>
+  <si>
+    <t>Edmilson Henrique De Sousa</t>
+  </si>
+  <si>
+    <t>R$               46.573,10</t>
+  </si>
+  <si>
+    <t>0010761-24.2025.5.15.0050</t>
+  </si>
+  <si>
+    <t>Ademir Lemes Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             408.240,44</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>0010338-30.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Luciano Da Silva Santos</t>
+  </si>
+  <si>
+    <t>R$             252.500,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0011314-84.2026.5.15.0002</t>
+  </si>
+  <si>
+    <t>A. Raymond Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Waldianne Do Amaral Borges</t>
+  </si>
+  <si>
+    <t>JUNDIAÍ</t>
   </si>
   <si>
     <t>01ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             398.100,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/oqtux ID da Reunião: 89475386843 Senha: vMXmvyZFhQ</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010608-26.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Denilson Silva Bonfim</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
+    <t>R$               46.300,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84650100355?pwd=BroxU7aJY35Y65x7JsIkbLF1EeFvHT.1 ID da reunião: 846 5010 0355 Senha: 1234</t>
+  </si>
+  <si>
+    <t>0010199-64.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Anderson Lopes Gomes</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             420.000,00</t>
+  </si>
+  <si>
+    <t>KBM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1 ID da reunião: 852 6787 6480  Senha: TRT15</t>
+  </si>
+  <si>
+    <t>0010261-21.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Guilherme Eduardo Machado Correa</t>
+  </si>
+  <si>
+    <t>R$             165.000,00</t>
+  </si>
+  <si>
+    <t>0016544-53.2026.5.16.0011</t>
+  </si>
+  <si>
+    <t>Ruan Carlos Teixeira Gomes</t>
+  </si>
+  <si>
+    <t>BALSAS</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>R$             253.073,03</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81494992654?pwd=USK67SZiJxCJyz0JF8BOTyafLlaitb.1 ID da reunião: 814 9499 2654 Senha: 315858</t>
+  </si>
+  <si>
+    <t>1000682-86.2026.5.02.0052</t>
+  </si>
+  <si>
+    <t>L. Sant'Angelo Pinturas Ltda.</t>
+  </si>
+  <si>
+    <t>Marcio Jose Santos Da Silva</t>
+  </si>
+  <si>
+    <t>52ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             191.421,43</t>
+  </si>
+  <si>
+    <t>0012008-54.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Paulo Magalhaes Junior</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
     <t>Inicial</t>
   </si>
   <si>
-    <t>R$             182.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09 ID DA REUNIÃO: 899 3988 0446 SENHA:  608226</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011655-15.2025.5.15.0045</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Joao Paulo De Oliveira Borges</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal TRT</t>
-  </si>
-  <si>
-    <t>Ação Revisional</t>
-  </si>
-  <si>
-    <t>R$                 1.000,00</t>
+    <t>R$               93.500,00</t>
   </si>
   <si>
     <t>Grupo B2</t>
   </si>
   <si>
-    <t>ANB</t>
-  </si>
-  <si>
     <t>BCF</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010809-09.2026.5.03.0041</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Renato Soares Da Silva</t>
-  </si>
-  <si>
-    <t>UBERABA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$               36.889,64</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/88449648691 ID da reunião: 884 4964 8691 Senha de acesso: 0041</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000257-55.2026.5.09.0093</t>
-  </si>
-  <si>
-    <t>Marcelo Favaro Cunha Nishyama</t>
-  </si>
-  <si>
-    <t>CORNÉLIO PROCÓPIO</t>
-  </si>
-  <si>
-    <t>R$             335.000,00</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/ubsbs ID da reunião: 87911901337 Senha de acesso: 0dguJ0ryKr</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010069-19.2025.5.03.0063</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Wedson Da Silva</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$               60.946,56</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt1itba</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010534-24.2020.5.15.0013</t>
-  </si>
-  <si>
-    <t>Lauro Batista De Siqueira</t>
-  </si>
-  <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>R$               88.083,92</t>
-  </si>
-  <si>
     <t>VCR</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/87813703141?pwd=StmQzxzeHcTb0VEfPuO14t0BBfbEsm.1 ID da reunião: 878 1370 3141 Senha: 592669</t>
-  </si>
-  <si>
-    <t>0012496-63.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Emily Aline De Oliveira</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>R$               48.339,13</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09 ID da reunião: 873 7536 5338 Senha de acesso: 203482</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0012648-75.2025.5.15.0007</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Fabio Roberto Carvalho Ferreira</t>
-  </si>
-  <si>
-    <t>AMERICANA</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             595.082,69</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/86483603580?pwd=bm1zQld2eFdic1JQQ2pMdWg5ZjhQUT09 ID da reunião: 864 8360 3580 Senha: 070707</t>
-  </si>
-  <si>
-    <t>0010500-39.2025.5.15.0089</t>
-  </si>
-  <si>
-    <t>Dell Computadores Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Alan Dias Almeida</t>
-  </si>
-  <si>
-    <t>BAURU</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               64.910,61</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/my/salaprincipal2vtbauru?pwd=TGIvVEZVbGNUOXNSYm40SXFrVlpBQT09</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010542-09.2025.5.15.0083</t>
-  </si>
-  <si>
-    <t>Fernando Jose Haas</t>
-  </si>
-  <si>
-    <t>R$             176.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Camila</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0011443-56.2026.5.15.0013</t>
-  </si>
-  <si>
-    <t>Clecio Renato Dos Santos De Andrade</t>
-  </si>
-  <si>
-    <t>R$                 3.559,72</t>
-  </si>
-  <si>
-    <t>0010044-97.2024.5.15.0130</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Tonyelzio Frances Feitosa Lima</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             175.217,38</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1 ID da reunião: 870 3865 6391 Senha: 771785</t>
-  </si>
-  <si>
-    <t>1000968-88.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Vinicius Correia Dos Santos</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             134.964,33</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>1001230-15.2026.5.02.0084</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Raphael Fernandes De Castro</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>84ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             674.018,47</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0010901-88.2024.5.15.0019</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Edivaldo Ribeiro Costa</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$             797.678,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Carla</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>0010882-58.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Marcos Roberto Teixeira Flores</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$               37.967,57</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0000463-74.2026.5.14.0111</t>
-  </si>
-  <si>
-    <t>Syngenta Digital Ltda</t>
-  </si>
-  <si>
-    <t>Lucas Rafael Chiquito De Souza</t>
-  </si>
-  <si>
-    <t>PIMENTA BUENO</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t>R$             235.287,92</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>https://trt14-jus-br.zoom.us/j/82618890933?pwd=fjl4saUL32oiFfej0JXbzWkPLUEvVa.1 ID da reunião: 826 1889 0933 Senha: 140240</t>
-  </si>
-  <si>
-    <t>1000635-87.2026.5.02.0028</t>
-  </si>
-  <si>
-    <t>Bit Services Inovação E Tecnologia Ltda.</t>
-  </si>
-  <si>
-    <t>Bruno Casa Nova Mariano</t>
-  </si>
-  <si>
-    <t>28ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.428.844,18</t>
-  </si>
-  <si>
-    <t>Grupo D1</t>
-  </si>
-  <si>
-    <t>JQS</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81345987692?pwd=VzFEVDJseUNwWUxQaHFYRTlrRjdXUT09 ID da reunião: 813 4598 7692 Senha de acesso: 663288</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1000956-71.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Bruno Farabotti Clemente</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               85.454,67</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1001647-34.2025.5.02.0041</t>
-  </si>
-  <si>
-    <t>Alessandra Roberta Lucia Gabeloni De Carvalho</t>
-  </si>
-  <si>
-    <t>R$               81.751,24</t>
-  </si>
-  <si>
-    <t>1002221-85.2024.5.02.0431</t>
-  </si>
-  <si>
-    <t>Rodrigo Grecco De Freitas Franco</t>
-  </si>
-  <si>
-    <t>09ª TURMA</t>
-  </si>
-  <si>
-    <t>R$               60.000,00</t>
-  </si>
-  <si>
-    <t>1000152-53.2023.5.02.0613</t>
-  </si>
-  <si>
-    <t>Edson De Lima Solla</t>
-  </si>
-  <si>
-    <t>ZONA LESTE</t>
-  </si>
-  <si>
-    <t>R$               58.320,39</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>0010336-60.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Robson Vinicius Clavico Da Silva</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$               40.614,74</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>1001873-24.2025.5.02.0434</t>
-  </si>
-  <si>
-    <t>Cliford Jean Baptiste</t>
-  </si>
-  <si>
-    <t>11ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             226.807,85</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0011151-62.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Rafael Henrique Fernandes Afonso</t>
-  </si>
-  <si>
-    <t>R$               38.433,00</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
-  </si>
-  <si>
-    <t>1002293-38.2025.5.02.0431</t>
-  </si>
-  <si>
-    <t>Paulo Cesar Sparapani</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>R$             143.577,46</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81886655332?pwd=ANovV8FZBJKHJra3ybU2cVjJ0AgvHW.1 ID da reunião: 818 8665 5332 Senha de acesso: 813179</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010859-77.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Marcio De Moraes</t>
-  </si>
-  <si>
-    <t>R$             450.425,56</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>0020456-64.2023.5.04.0733</t>
-  </si>
-  <si>
-    <t>Luis Augusto Do Carmo</t>
-  </si>
-  <si>
-    <t>SANTA CRUZ DO SUL</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>R$          1.023.904,45</t>
-  </si>
-  <si>
-    <t>https://trt4-jus-br.zoom.us/my/turma03</t>
-  </si>
-  <si>
-    <t>0000015-81.2026.5.09.0195</t>
-  </si>
-  <si>
-    <t>Carlos Henrique De Andrade Rocha</t>
-  </si>
-  <si>
-    <t>R$               62.000,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/3jy7c ID da Reunião: 88086506714 Senha: QFav9LoTol</t>
-  </si>
-  <si>
-    <t>0020262-52.2025.5.04.0003</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Daniel Oliveira Da Silva</t>
-  </si>
-  <si>
-    <t>PORTO ALEGRE</t>
-  </si>
-  <si>
-    <t>R$             447.130,45</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>Correspondente - Jaeger</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>0025591-33.2025.5.24.0021</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Nerivaldo Paiva Santos</t>
-  </si>
-  <si>
-    <t>DOURADOS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$             218.910,14</t>
+    <t>0000067-13.2026.5.17.0015</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Eduardo De Souza</t>
+  </si>
+  <si>
+    <t>VITÓRIA</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>15ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               30.919,43</t>
   </si>
   <si>
     <t>Correspondente - doc9</t>
   </si>
   <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Kelly Cristine Vieira de Souza kellycvsa@hotmail.com 67999609707</t>
-  </si>
-  <si>
-    <t>0000477-87.2026.5.07.0035</t>
-  </si>
-  <si>
-    <t>Joao Vitor Barbosa Da Silva</t>
-  </si>
-  <si>
-    <t>ARACATI</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>R$                 5.817,92</t>
-  </si>
-  <si>
-    <t>https://trt7-jus-br.zoom.us/j/81867554890?pwd=Q0hoOGxaajVCSS9WakV3VnFQZHlWQT0</t>
-  </si>
-  <si>
-    <t>1002200-66.2025.5.02.0434</t>
-  </si>
-  <si>
-    <t>Renato Eli Minarini Souza</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             407.184,07</t>
-  </si>
-  <si>
-    <t>0010319-09.2026.5.03.0066</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A.</t>
-  </si>
-  <si>
-    <t>Felipe Pimentel De Oliveira</t>
-  </si>
-  <si>
-    <t>MANHUAÇU</t>
-  </si>
-  <si>
-    <t>R$               64.433,60</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/varamanhuacu</t>
+    <t>Presencial | Advogada - Grazielle Gusmão Tavares Dias grazielleadvocacia@gmail.com 27997516239</t>
+  </si>
+  <si>
+    <t>1001276-58.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Nivaldo Morande Barbosa</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Recursal com Execução Provisória</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$               50.417,08</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/89630041613?pwd=QkJkdDQ5dFdEV2ZVMzg1ZGN0b3RXQT09 ID da reunião: 896 3004 1613 Senha de acesso: 683711</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,14 +830,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -933,14 +886,16 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -949,18 +904,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -983,12 +939,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1320,14 +1272,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB358652-6F55-4BBF-991A-C45A8B2F5C20}">
-  <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="28" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A986E37E-F3E3-4FD5-B5B2-D2476C8D0B9B}">
+  <dimension ref="A1:R37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1383,15 +1332,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104442</v>
+        <v>100159</v>
       </c>
       <c r="B2" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C2" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1433,45 +1382,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R2" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104970</v>
+        <v>105270</v>
       </c>
       <c r="B3" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C3" s="6">
         <v>0.36458333333333331</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1491,16 +1440,16 @@
       <c r="Q3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>102126</v>
+        <v>101900</v>
       </c>
       <c r="B4" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C4" s="6">
         <v>0.375</v>
@@ -1512,75 +1461,75 @@
         <v>46</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="O4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>105160</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="F5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="I5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>105618</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.38541666666666669</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1592,54 +1541,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>103154</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>104512</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1648,110 +1597,110 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>104985</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R6" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>99778</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>63326</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.40347222222222223</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>93812</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1760,54 +1709,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105442</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P8" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R8" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>99861</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1816,54 +1765,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>99877</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="R9" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>103570</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.40625</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1872,54 +1821,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>100301</v>
+        <v>105547</v>
       </c>
       <c r="B11" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C11" s="6">
         <v>0.41666666666666669</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1928,54 +1877,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>100391</v>
+        <v>103637</v>
       </c>
       <c r="B12" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4201388888888889</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1984,54 +1933,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>104837</v>
+        <v>71646</v>
       </c>
       <c r="B13" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C13" s="6">
-        <v>0.43402777777777779</v>
+        <v>0.42430555555555555</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -2040,54 +1989,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="Q13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105484</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="R13" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>97080</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="G14" s="7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -2096,54 +2045,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105045</v>
+        <v>105448</v>
       </c>
       <c r="B15" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C15" s="6">
-        <v>0.44097222222222221</v>
+        <v>0.4375</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -2152,51 +2101,51 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="R15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>105651</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>105661</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46252</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="F16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="H16" s="7" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>25</v>
@@ -2208,107 +2157,107 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>100730</v>
+        <v>105574</v>
       </c>
       <c r="B17" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C17" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105770</v>
+        <v>98855</v>
       </c>
       <c r="B18" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C18" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>25</v>
@@ -2320,54 +2269,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>105754</v>
+        <v>72545</v>
       </c>
       <c r="B19" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C19" s="6">
-        <v>0.48958333333333331</v>
+        <v>0.44513888888888886</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2376,54 +2325,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>104766</v>
+        <v>104894</v>
       </c>
       <c r="B20" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C20" s="6">
-        <v>0.5</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2432,54 +2381,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105037</v>
+        <v>71737</v>
       </c>
       <c r="B21" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C21" s="6">
-        <v>0.51736111111111116</v>
+        <v>0.46597222222222223</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2488,54 +2437,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>104077</v>
+        <v>105423</v>
       </c>
       <c r="B22" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C22" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2544,54 +2493,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>99645</v>
+        <v>103406</v>
       </c>
       <c r="B23" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C23" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2600,110 +2549,110 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>101209</v>
+        <v>89578</v>
       </c>
       <c r="B24" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C24" s="6">
         <v>0.54166666666666663</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>196</v>
+        <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>104450</v>
+        <v>102194</v>
       </c>
       <c r="B25" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C25" s="6">
-        <v>0.5625</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>201</v>
+        <v>48</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>38</v>
+        <v>183</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2712,54 +2661,54 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>102844</v>
+        <v>105377</v>
       </c>
       <c r="B26" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C26" s="6">
         <v>0.5625</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="G26" s="7" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2768,51 +2717,51 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
-        <v>98160</v>
+        <v>98797</v>
       </c>
       <c r="B27" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C27" s="6">
         <v>0.56944444444444442</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>25</v>
@@ -2824,54 +2773,54 @@
         <v>27</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>213</v>
+        <v>30</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="R27" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
-        <v>103494</v>
+        <v>101585</v>
       </c>
       <c r="B28" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C28" s="6">
-        <v>0.56944444444444442</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>217</v>
+        <v>39</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>26</v>
@@ -2880,51 +2829,51 @@
         <v>27</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
-        <v>97826</v>
+        <v>104460</v>
       </c>
       <c r="B29" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C29" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>25</v>
@@ -2936,54 +2885,54 @@
         <v>27</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="R29" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
-        <v>101136</v>
+        <v>105050</v>
       </c>
       <c r="B30" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C30" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>228</v>
+        <v>23</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>50</v>
+        <v>206</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>26</v>
@@ -2992,54 +2941,54 @@
         <v>27</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="R30" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
-        <v>103725</v>
+        <v>104048</v>
       </c>
       <c r="B31" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C31" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>22</v>
+        <v>211</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>26</v>
@@ -3048,51 +2997,51 @@
         <v>27</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="R31" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
-        <v>100232</v>
+        <v>104264</v>
       </c>
       <c r="B32" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C32" s="6">
         <v>0.625</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>228</v>
+        <v>23</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>183</v>
+        <v>39</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>25</v>
@@ -3104,54 +3053,54 @@
         <v>27</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="R32" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
-        <v>102185</v>
+        <v>104928</v>
       </c>
       <c r="B33" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C33" s="6">
-        <v>0.63194444444444442</v>
+        <v>0.625</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>26</v>
@@ -3160,54 +3109,54 @@
         <v>27</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>249</v>
+        <v>69</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="R33" s="8" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="R33" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
-        <v>105472</v>
+        <v>104841</v>
       </c>
       <c r="B34" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C34" s="6">
         <v>0.63888888888888884</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>255</v>
+        <v>23</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>26</v>
@@ -3216,54 +3165,54 @@
         <v>27</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R34" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
-        <v>103299</v>
+        <v>102074</v>
       </c>
       <c r="B35" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C35" s="6">
-        <v>0.65277777777777779</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>260</v>
+        <v>57</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>25</v>
+        <v>234</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>26</v>
@@ -3272,51 +3221,51 @@
         <v>27</v>
       </c>
       <c r="N35" s="7" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>135</v>
+        <v>237</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
-        <v>104720</v>
+        <v>103945</v>
       </c>
       <c r="B36" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C36" s="6">
-        <v>0.65625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>25</v>
@@ -3328,45 +3277,98 @@
         <v>27</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="O36" s="7" t="s">
         <v>41</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>267</v>
+        <v>197</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>101635</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{4A4AC88E-43F6-46DC-9044-7720C362971B}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/89939880446?pwd=ZHhwbjhhMUk2aGtDbmUwRTdELzhZUT09%20ID%20DA%20REUNIÃO:%20899%203988%200446%20SENHA:%20%20608226" xr:uid="{475DCCC6-5CDB-4CE3-ACBF-13649C5CCB15}"/>
-    <hyperlink ref="R4" r:id="rId3" xr:uid="{46773B6D-B1F6-48CF-BFB7-C51B74C57B70}"/>
-    <hyperlink ref="R5" r:id="rId4" xr:uid="{5128EDB7-3130-459F-AB05-908CB6DF928D}"/>
-    <hyperlink ref="R6" r:id="rId5" xr:uid="{902C2858-4F9E-49B6-B5EA-250E1740B353}"/>
-    <hyperlink ref="R7" r:id="rId6" xr:uid="{748EEF30-ABA0-420E-86FF-67613DED89A4}"/>
-    <hyperlink ref="R8" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/87813703141?pwd=StmQzxzeHcTb0VEfPuO14t0BBfbEsm.1%20ID%20da%20reunião:%20878%201370%203141%20Senha:%20592669" xr:uid="{E1B8947F-7C76-49D6-975A-86C5DA16997C}"/>
-    <hyperlink ref="R9" r:id="rId8" display="https://us02web.zoom.us/j/87375365338?pwd=MkRVVDdySnNNZjJMVXB1N2JITEtGUT09%20ID%20da%20reunião:%20873%207536%205338%20Senha%20de%20acesso:%20203482" xr:uid="{639F2DB6-6617-4AB2-9AFF-A911D16B5F1D}"/>
-    <hyperlink ref="R10" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/86483603580?pwd=bm1zQld2eFdic1JQQ2pMdWg5ZjhQUT09%20ID%20da%20reunião:%20864%208360%203580%20Senha:%20070707" xr:uid="{1B72B8F2-6F7F-4581-B6E5-CCDCB94BA896}"/>
-    <hyperlink ref="R11" r:id="rId10" xr:uid="{DABE8546-D328-46E7-A8A2-8A5B1899A49D}"/>
-    <hyperlink ref="R14" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/87038656391?pwd=IrcPB0kBZsAy2afYHrEkMIRmge213e.1%20ID%20da%20reunião:%20870%203865%206391%20Senha:%20771785" xr:uid="{1C83783C-FBDA-41D3-BEED-E0FBD76F9053}"/>
-    <hyperlink ref="R18" r:id="rId12" xr:uid="{7C6EB58B-30D6-4543-8A60-28E2398ECB86}"/>
-    <hyperlink ref="R19" r:id="rId13" display="https://trt14-jus-br.zoom.us/j/82618890933?pwd=fjl4saUL32oiFfej0JXbzWkPLUEvVa.1%20ID%20da%20reunião:%20826%201889%200933%20Senha:%20140240" xr:uid="{CCF47ADE-97DD-4AE6-8117-B3986FD89D6E}"/>
-    <hyperlink ref="R20" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/81345987692?pwd=VzFEVDJseUNwWUxQaHFYRTlrRjdXUT09%20ID%20da%20reunião:%20813%204598%207692%20Senha%20de%20acesso:%20663288" xr:uid="{525084FE-D55F-4B2D-B536-DD99C2A106DF}"/>
-    <hyperlink ref="R25" r:id="rId15" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{7ECDF771-F11B-46EC-BB5A-42EAC5647A12}"/>
-    <hyperlink ref="R27" r:id="rId16" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%20532%20639%201733%20Senha%20de%20acesso:%20959215" xr:uid="{68C526E3-BD32-467A-9476-B365F8D3F8A8}"/>
-    <hyperlink ref="R28" r:id="rId17" display="https://trt2-jus-br.zoom.us/j/81886655332?pwd=ANovV8FZBJKHJra3ybU2cVjJ0AgvHW.1%20ID%20da%20reunião:%20818%208665%205332%20Senha%20de%20acesso:%20813179" xr:uid="{9EEE2C27-56C9-4D3B-8B74-D0E076EDA8C4}"/>
-    <hyperlink ref="R30" r:id="rId18" xr:uid="{F3D9AA88-5E6F-4D92-99B6-50C926B93076}"/>
-    <hyperlink ref="R31" r:id="rId19" xr:uid="{824DFD90-6C39-4F4F-86A4-7D101AA01646}"/>
-    <hyperlink ref="R33" r:id="rId20" display="mailto:kellycvsa@hotmail.com" xr:uid="{8C06B2AA-8645-42DD-9677-20C3FAEB161B}"/>
-    <hyperlink ref="R34" r:id="rId21" xr:uid="{F78ABBA4-9D95-4149-8B97-D4AF9858523F}"/>
-    <hyperlink ref="R36" r:id="rId22" xr:uid="{8764E2B9-EE8F-4857-990D-ADF47498C139}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{D9477CB6-E1E8-4C21-A267-790A3CDCA72C}"/>
+    <hyperlink ref="R5" r:id="rId2" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{93C90E10-EB95-42BC-A131-6605AEB5FF39}"/>
+    <hyperlink ref="R6" r:id="rId3" display="https://us02web.zoom.us/j/8060729658?pwd=NDNlcU8wVzcxZ09qVjFDRFBGT2ljQT09" xr:uid="{132F217E-7D9F-4EB9-82EF-03CA378E0B1C}"/>
+    <hyperlink ref="R7" r:id="rId4" display="https://us02web.zoom.us/j/2133746772?pwd=ZkJNaUxTODBrZXlqUitqQzdKSWhwdz09%20ID%20da%20Reunião:%202133746772%20Senha:%20396868" xr:uid="{B169268D-01D0-406D-BC6C-A17408C98339}"/>
+    <hyperlink ref="R9" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{A74A63E8-3DB3-4319-BFE5-E31097A03E57}"/>
+    <hyperlink ref="R11" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{F1C7E0CA-2EDA-422F-B69C-AFCAF91522C1}"/>
+    <hyperlink ref="R12" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/88067116578?pwd=SGEwS2NQOUhSODlDK2krT2I5UmRvUT09%20ID%20da%20reunião:%20880%206711%206578%20Senha:%20223832" xr:uid="{C8C56E77-BBF5-4655-A2F6-1A551C5FD903}"/>
+    <hyperlink ref="R14" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{F8EA440E-4BC4-48CC-8C41-B322F1506958}"/>
+    <hyperlink ref="R15" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{7BB5AB3B-089D-4D35-9287-D7FBD7EE9E09}"/>
+    <hyperlink ref="R17" r:id="rId10" xr:uid="{715FFFED-D931-4DA7-ACAA-2B097AA8B42A}"/>
+    <hyperlink ref="R26" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/89770082465?pwd=K09aQWhUOW5ESytiRUdCOUFSa2E4dz09%20ID%20da%20reunião:%20897%207008%202465%20Senha%20de%20acesso:%20908050" xr:uid="{44291D10-63C7-4269-8712-D3F372584017}"/>
+    <hyperlink ref="R28" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{A9741DB7-1A4D-4113-A79D-D47BB8AF505E}"/>
+    <hyperlink ref="R29" r:id="rId13" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{1B90A186-6F54-4AF2-B8FD-AD6481385E70}"/>
+    <hyperlink ref="R30" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/84650100355?pwd=BroxU7aJY35Y65x7JsIkbLF1EeFvHT.1%20ID%20da%20reunião:%20846%205010%200355%20Senha:%201234" xr:uid="{9BDF1969-39DE-4817-A482-CAA287E18D50}"/>
+    <hyperlink ref="R31" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1%20ID%20da%20reunião:%20852%206787%206480%20%20Senha:%20TRT15" xr:uid="{F02C72A3-DE51-49B5-A6ED-4EDDFFECB56A}"/>
+    <hyperlink ref="R32" r:id="rId16" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{36E62800-4CD2-42C6-8E07-AEA601FC88D5}"/>
+    <hyperlink ref="R33" r:id="rId17" display="https://us02web.zoom.us/j/81494992654?pwd=USK67SZiJxCJyz0JF8BOTyafLlaitb.1%20ID%20da%20reunião:%20814%209499%202654%20Senha:%20315858" xr:uid="{95E267EC-D10D-4608-8B97-4C6C898AB0E9}"/>
+    <hyperlink ref="R36" r:id="rId18" display="mailto:grazielleadvocacia@gmail.com" xr:uid="{BD4EFBDB-5DDB-4BB0-B499-253C0EC0A892}"/>
+    <hyperlink ref="R37" r:id="rId19" display="https://trt2-jus-br.zoom.us/j/89630041613?pwd=QkJkdDQ5dFdEV2ZVMzg1ZGN0b3RXQT09%20ID%20da%20reunião:%20896%203004%201613%20Senha%20de%20acesso:%20683711" xr:uid="{D4FE2913-739F-4318-819B-F1B0038F2D1D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7293C3AB-EAF7-402B-A014-CA1059AB195E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E258CBB-6F42-4177-A246-1D94F6CAF5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65BBCE65-2529-4BE0-B818-D767658108DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4934E6B1-2F0E-496B-9B2E-DAF3D74207C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="182">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Foro</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor da Causa </t>
+    <t>Valor da Causa</t>
   </si>
   <si>
     <t>Equipe responsável</t>
@@ -95,142 +95,496 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000664-53.2026.5.23.0002</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Domingos Dos Santos Fujii</t>
+  </si>
+  <si>
+    <t>CUIABÁ</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             425.307,82</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/8472007323?pwd=RjBlQU1kdWJySjVQRWVhVlZTd2VuUT09</t>
+  </si>
+  <si>
+    <t>0010665-14.2026.5.15.0037</t>
+  </si>
+  <si>
+    <t>Ouroeste Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Jair Carlos Viviani</t>
+  </si>
+  <si>
+    <t>FERNANDÓPOLIS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             310.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09  ID DA REUNIÃO: 875 5537 1032 SENHA DE ACESSO: 772981</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Presencial</t>
   </si>
   <si>
-    <t>1000641-37.2026.5.02.0435</t>
+    <t>0011973-04.2024.5.15.0022</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Viviane Aparecida Dias De Andrade</t>
+  </si>
+  <si>
+    <t>MOGI MIRIM</t>
+  </si>
+  <si>
+    <t>R$               53.077,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0013049-44.2025.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Odair Roque Goncalves Da Costa</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             714.330,31</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>0000903-53.2026.5.19.0007</t>
+  </si>
+  <si>
+    <t>Sistenge Construcoes E Comercio Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Aldo Alves Da Silva</t>
+  </si>
+  <si>
+    <t>MACEIÓ</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>07ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               12.548,78</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Raianny Yulle Rousan de Lucena Alexandre adv.raiannyyulle@gmail.com 82 9 99597231</t>
+  </si>
+  <si>
+    <t>0010769-58.2026.5.03.0063</t>
+  </si>
+  <si>
+    <t>Uhe São Simão Energia S.A.</t>
+  </si>
+  <si>
+    <t>Rodrigo Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$             241.221,05</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/85042016732</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000191-51.2026.5.09.0004</t>
+  </si>
+  <si>
+    <t>Ferrero Do Brasil Direto Ferrero Rocher</t>
+  </si>
+  <si>
+    <t>Liliana Carolina De Araujo Nieves</t>
+  </si>
+  <si>
+    <t>CURITIBA</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               67.014,01</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/qkpyb ID da Reunião: 87012853638 Senha: SB8Y2l7YZl</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0001856-42.2025.5.09.0003</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Sergio Heins</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             296.414,50</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/d4q6b ID da Reunião: 84102546803 Senha: ZV4FzHdDhT</t>
+  </si>
+  <si>
+    <t>0010320-24.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>Jhony Jose Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>R$             121.048,40</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>1000902-11.2026.5.02.0432</t>
   </si>
   <si>
     <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
   </si>
   <si>
-    <t>Gilson Fernando Da Silva</t>
+    <t>Paulo Aru Pinheiro De Melo</t>
   </si>
   <si>
     <t>SANTO ANDRÉ</t>
   </si>
   <si>
-    <t>SP</t>
+    <t>R$             507.775,60</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>0101030-85.2024.5.01.0066</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Alexandre Bernardino Da Silva</t>
+  </si>
+  <si>
+    <t>RIO DE JANEIRO</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>66ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             155.452,28</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>https://trt1-jus-br.zoom.us/j/87372480598</t>
+  </si>
+  <si>
+    <t>0010378-43.2024.5.03.0041</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Osvaldo Marcelino Gomes</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>R$               64.072,23</t>
+  </si>
+  <si>
+    <t>  https://trt3-jus-br.zoom.us/j/82356057731 ID da reunião:82356057731</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Semipresencial</t>
+  </si>
+  <si>
+    <t>0024875-66.2026.5.24.0022</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Ezequiel De Paula Mendes</t>
+  </si>
+  <si>
+    <t>DOURADOS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$             683.586,00</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/my/trt24douvt2sala1</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Presencial</t>
+  </si>
+  <si>
+    <t>1016886-07.2025.5.02.0000</t>
+  </si>
+  <si>
+    <t>Lojas Americanas S.A.</t>
+  </si>
+  <si>
+    <t>Sindicato Dos Empregados No Comercio De Osasco E Regiao</t>
+  </si>
+  <si>
+    <t>OSASCO</t>
+  </si>
+  <si>
+    <t>CEJUSC</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>Reclamação Pré-processual</t>
+  </si>
+  <si>
+    <t>R$               32.000,00</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010536-34.2023.5.15.0095</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Welber Da Soledade Cruz</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$             118.377,60</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>bit.ly/cejusc2grau</t>
+  </si>
+  <si>
+    <t>0011429-40.2025.5.15.0132</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Edson Almeida Souza</t>
   </si>
   <si>
     <t>05ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$             106.098,92 </t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
+    <t>R$             260.040,01</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Jociene de Jesus Oliveira Jocieneadv@gmail.com 12988871868</t>
+  </si>
+  <si>
+    <t>0010137-18.2025.5.03.0176</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Divino Dos Santos Filho</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               49.755,19</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/89176162090</t>
+  </si>
+  <si>
+    <t>0010552-21.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Rafael Cristian Batista</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             169.430,26</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
+  </si>
+  <si>
+    <t>1000003-52.2022.5.02.0432</t>
+  </si>
+  <si>
+    <t>Fabiano Lopes</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>R$             125.200,00</t>
   </si>
   <si>
     <t>JPE</t>
   </si>
   <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1000944-26.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Cbc - Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Fernando Jose Mariano</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$             260.532,93 </t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>1000945-11.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Alexandre Augusto Da Silva Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$             294.787,17 </t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1002347-49.2024.5.02.0201</t>
-  </si>
-  <si>
-    <t>Ipe Realty Ltda</t>
-  </si>
-  <si>
-    <t>Priscilla Sayuri Higa Rivellino</t>
-  </si>
-  <si>
-    <t>BARUERI</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$          1.485.730,40 </t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012658-41.2025.5.15.0130</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Pedro Chiconini</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>11ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R$          1.246.000,00 </t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1 ID da reunião: 852 6787 6480 Senha: TRT15</t>
+    <t>https://trt2-jus-br.zoom.us/j/89437519049?pwd=eVN6UGhFUDRkM1ljUEMzMTIrYnMxUT09 ID da reunião: 894 3751 9049 Senha de acesso: 493641</t>
   </si>
 </sst>
 </file>
@@ -297,13 +651,13 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -311,35 +665,35 @@
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -348,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -359,23 +713,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -711,11 +1062,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360F270F-15CD-4B13-B364-742B210A9F5B}">
-  <dimension ref="A1:R6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7203D894-FB8D-4A66-A6D3-980B5841DA88}">
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -767,293 +1121,1090 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>104644</v>
-      </c>
-      <c r="B2" s="6">
-        <v>46255</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D2" s="8" t="s">
+    <row r="2" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>105525</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>105399</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
+      <c r="F3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>105420</v>
-      </c>
-      <c r="B3" s="6">
-        <v>46255</v>
-      </c>
-      <c r="C3" s="7">
+    <row r="4" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>99485</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.36180555555555555</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>103760</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105617</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C6" s="6">
         <v>0.3888888888888889</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="D6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>105850</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.39652777777777776</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>104055</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>103595</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>104217</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="J10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104988</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>101276</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>97701</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="R13" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105053</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>103159</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>91722</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.62708333333333333</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>101867</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.63194444444444442</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>32</v>
+      <c r="R17" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>105421</v>
-      </c>
-      <c r="B4" s="6">
-        <v>46255</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="8" t="s">
+    <row r="18" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>100017</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>32</v>
+      <c r="N18" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>99374</v>
-      </c>
-      <c r="B5" s="6">
-        <v>46255</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="8" t="s">
+    <row r="19" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>100795</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="P19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>82097</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46258</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.68333333333333335</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>104230</v>
-      </c>
-      <c r="B6" s="6">
-        <v>46255</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>63</v>
+      <c r="N20" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R6" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/85267876480?pwd=tETOC8GDaqZZdf9WNGOaW98aPE2MQx.1%20ID%20da%20reunião:%20852%206787%206480%20Senha:%20TRT15" xr:uid="{0E7CDA17-7884-4AD3-B700-38B0B04DF0CB}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{4CB767CF-A375-4216-9B63-E8BF38AFC011}"/>
+    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09%20%20ID%20DA%20REUNIÃO:%20875%205537%201032%20SENHA%20DE%20ACESSO:%20772981" xr:uid="{B684BA9B-611F-4E8E-B17C-C4C83206471E}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{B674480C-46C4-4854-92B8-14F8D1E057F5}"/>
+    <hyperlink ref="R6" r:id="rId4" display="mailto:adv.raiannyyulle@gmail.com" xr:uid="{FA89402D-249C-4FDB-8FF7-E1A873C04CA8}"/>
+    <hyperlink ref="R7" r:id="rId5" xr:uid="{FAB8E623-25E0-447A-9101-03635C1303F2}"/>
+    <hyperlink ref="R8" r:id="rId6" display="https://url.trt9.jus.br/qkpyb" xr:uid="{9A071592-4278-4777-A73C-98F76C0930A4}"/>
+    <hyperlink ref="R9" r:id="rId7" xr:uid="{C2EFF221-9C79-4093-A6B6-F9149E624849}"/>
+    <hyperlink ref="R12" r:id="rId8" xr:uid="{2311E317-D067-486B-A600-B0D80785FB19}"/>
+    <hyperlink ref="R13" r:id="rId9" display="https://trt3-jus-br.zoom.us/j/82356057731" xr:uid="{64CF60B8-A430-4B55-BB7E-5DD0AB54521D}"/>
+    <hyperlink ref="R14" r:id="rId10" xr:uid="{BB9AA4C6-F5BA-49D5-A147-DA08BDD24704}"/>
+    <hyperlink ref="R17" r:id="rId11" display="mailto:Jocieneadv@gmail.com" xr:uid="{77B3E250-CE1A-4CA0-B27F-58A4E4E265BE}"/>
+    <hyperlink ref="R18" r:id="rId12" xr:uid="{283741D4-7409-497C-8C1E-EC21E0DBA104}"/>
+    <hyperlink ref="R19" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{801F2E95-4CEF-4C8A-A46D-8F390E43754F}"/>
+    <hyperlink ref="R20" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/89437519049?pwd=eVN6UGhFUDRkM1ljUEMzMTIrYnMxUT09%20ID%20da%20reunião:%20894%203751%209049%20Senha%20de%20acesso:%20493641" xr:uid="{2152A80F-AB64-460B-B39F-E9E5B9AB687C}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E258CBB-6F42-4177-A246-1D94F6CAF5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17777405-75B0-4CB2-B768-BCD85A360759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4934E6B1-2F0E-496B-9B2E-DAF3D74207C3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{726E2D3D-FA46-4F68-98CF-88C636972229}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="205">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -98,493 +98,562 @@
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0000664-53.2026.5.23.0002</t>
+    <t>0011932-54.2025.5.15.0102</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Michael Klayvert Eliziario Dos Santos</t>
+  </si>
+  <si>
+    <t>TAUBATÉ</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               26.122,65</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81695106516?pwd=bTd4VU1OTWpNOU9Pcmh6YWFnOTVsZz09 ID da reunião: 816 9510 6516 Senha de acesso: 530013</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0013316-28.2025.5.15.0013</t>
+  </si>
+  <si>
+    <t>Embraer S.A</t>
+  </si>
+  <si>
+    <t>Edvaldo Rodrigues De Miranda</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$               92.084,54</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>0011524-30.2026.5.03.0048</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Cicero Luiz Dos Santos</t>
+  </si>
+  <si>
+    <t>ARAXÁ</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             430.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>NLO</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0012147-91.2025.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Antonio Borges Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             103.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Juliana Souza, (17) 99682-9421</t>
+  </si>
+  <si>
+    <t>0012457-97.2025.5.15.0017</t>
+  </si>
+  <si>
+    <t>Fabio Junio Marques</t>
+  </si>
+  <si>
+    <t>R$             186.000,00</t>
+  </si>
+  <si>
+    <t>1001029-11.2025.5.02.0261</t>
+  </si>
+  <si>
+    <t>Msa Do Brasil Equipamentos E Instrumentos De Segurança Ltda.</t>
+  </si>
+  <si>
+    <t>Cleunice Divino De Oliveira</t>
+  </si>
+  <si>
+    <t>DIADEMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             182.146,40</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0010094-06.2026.5.15.0017</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo Da Silva</t>
+  </si>
+  <si>
+    <t>R$             335.000,00</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0024861-81.2025.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>Rodrigo Domingos Da Silva</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$             125.258,41</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/89440353042</t>
+  </si>
+  <si>
+    <t>0012027-17.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Israel Alvernaz</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$             808.083,80</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011346-96.2014.5.15.0071</t>
+  </si>
+  <si>
+    <t>Odirley Oliveira Dos Santos</t>
+  </si>
+  <si>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>3ª Instância</t>
+  </si>
+  <si>
+    <t>R$               30.000,00</t>
+  </si>
+  <si>
+    <t>bit.ly/Cejusc2026</t>
+  </si>
+  <si>
+    <t>0011709-34.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Reginaldo Rodrigo Francisco</t>
+  </si>
+  <si>
+    <t>R$             442.019,00</t>
+  </si>
+  <si>
+    <t>0010087-13.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Roberto Da Fonseca Julio</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             171.538,44</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09 ID da reunião: 818 6908 4210 Senha de acesso: 306523</t>
+  </si>
+  <si>
+    <t>0010417-19.2024.5.03.0048</t>
+  </si>
+  <si>
+    <t>Celio Junior Da Silva</t>
+  </si>
+  <si>
+    <t>R$               69.911,27</t>
+  </si>
+  <si>
+    <t>0011360-26.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Paulinia - Pln</t>
+  </si>
+  <si>
+    <t>Welington Cesar Bento Cabral</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             230.595,89</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0011791-60.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Celio Barbosa De Sousa</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               25.043,76</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
+  </si>
+  <si>
+    <t>0010198-36.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Fidelis Ferreira</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$             147.866,42</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011136-75.2022.5.15.0132</t>
   </si>
   <si>
     <t>Embraer S.A.</t>
   </si>
   <si>
-    <t>Domingos Dos Santos Fujii</t>
-  </si>
-  <si>
-    <t>CUIABÁ</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             425.307,82</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/8472007323?pwd=RjBlQU1kdWJySjVQRWVhVlZTd2VuUT09</t>
-  </si>
-  <si>
-    <t>0010665-14.2026.5.15.0037</t>
+    <t>Mario Guilherme Ribeiro</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             250.000,00</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83377008514?pwd=VmFp6LzK2QCjdCZjdRHLVKSglYOLmi.1 ID da reunião: 833 7700 8514 Senha: 092842</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>0011348-33.2026.5.15.0140</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda</t>
+  </si>
+  <si>
+    <t>Michele Vitoria Eufrasio</t>
+  </si>
+  <si>
+    <t>ATIBAIA</t>
+  </si>
+  <si>
+    <t>R$               43.608,54</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>0010897-20.2026.5.03.0147</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S/A</t>
+  </si>
+  <si>
+    <t>Jonathan Matheus Souza Borges</t>
+  </si>
+  <si>
+    <t>TRÊS CORAÇÕES</t>
+  </si>
+  <si>
+    <t>R$               48.096,00</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Matheus Pimenta Barros matheuspb26@live.com (35) 999092279</t>
+  </si>
+  <si>
+    <t>0010476-36.2026.5.15.0037</t>
   </si>
   <si>
     <t>Ouroeste Bioenergia Ltda.</t>
   </si>
   <si>
-    <t>Jair Carlos Viviani</t>
+    <t>Elisiario Marques De Souza</t>
   </si>
   <si>
     <t>FERNANDÓPOLIS</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             310.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09  ID DA REUNIÃO: 875 5537 1032 SENHA DE ACESSO: 772981</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011973-04.2024.5.15.0022</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Viviane Aparecida Dias De Andrade</t>
-  </si>
-  <si>
-    <t>MOGI MIRIM</t>
-  </si>
-  <si>
-    <t>R$               53.077,00</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0013049-44.2025.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Odair Roque Goncalves Da Costa</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             714.330,31</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0000903-53.2026.5.19.0007</t>
-  </si>
-  <si>
-    <t>Sistenge Construcoes E Comercio Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Aldo Alves Da Silva</t>
-  </si>
-  <si>
-    <t>MACEIÓ</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>07ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               12.548,78</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Raianny Yulle Rousan de Lucena Alexandre adv.raiannyyulle@gmail.com 82 9 99597231</t>
-  </si>
-  <si>
-    <t>0010769-58.2026.5.03.0063</t>
-  </si>
-  <si>
-    <t>Uhe São Simão Energia S.A.</t>
-  </si>
-  <si>
-    <t>Rodrigo Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>R$             241.221,05</t>
+    <t>R$          1.093.572,33</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 050728</t>
+  </si>
+  <si>
+    <t>0011623-31.2025.5.15.0038</t>
+  </si>
+  <si>
+    <t>Grammer Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Wagner Maciel De Matos</t>
+  </si>
+  <si>
+    <t>R$               33.333,84</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89066503696?pwd=OFVsanFhMUg1aUFuaGR3WC8vTWpQZz09 ID da reunião: 890 6650 3696 Senha de acesso: 053083</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0000018-26.2026.5.09.0069</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Vanderlei Teixeira Menezes</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>R$               27.000,00</t>
   </si>
   <si>
     <t>Grupo C</t>
   </si>
   <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/85042016732</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000191-51.2026.5.09.0004</t>
-  </si>
-  <si>
-    <t>Ferrero Do Brasil Direto Ferrero Rocher</t>
-  </si>
-  <si>
-    <t>Liliana Carolina De Araujo Nieves</t>
-  </si>
-  <si>
-    <t>CURITIBA</t>
-  </si>
-  <si>
-    <t>PR</t>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/hjwrx ID da reunião: 89549820908 Senha de acesso: Hhtcw0SRcL</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010588-30.2026.5.15.0061</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Myller Gomes Santos</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$               49.966,45</t>
+  </si>
+  <si>
+    <t>NBB</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
+  </si>
+  <si>
+    <t>1001152-38.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Rafael Bergamin Cardoso</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
   </si>
   <si>
     <t>04ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>R$               67.014,01</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/qkpyb ID da Reunião: 87012853638 Senha: SB8Y2l7YZl</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0001856-42.2025.5.09.0003</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Sergio Heins</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             296.414,50</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/d4q6b ID da Reunião: 84102546803 Senha: ZV4FzHdDhT</t>
-  </si>
-  <si>
-    <t>0010320-24.2026.5.15.0045</t>
-  </si>
-  <si>
-    <t>Jhony Jose Dos Santos Silva</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$             121.048,40</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>1000902-11.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Paulo Aru Pinheiro De Melo</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             507.775,60</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
+    <t>R$             181.143,51</t>
   </si>
   <si>
     <t>GSM</t>
   </si>
   <si>
-    <t>0101030-85.2024.5.01.0066</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Alexandre Bernardino Da Silva</t>
-  </si>
-  <si>
-    <t>RIO DE JANEIRO</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>66ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             155.452,28</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>https://trt1-jus-br.zoom.us/j/87372480598</t>
-  </si>
-  <si>
-    <t>0010378-43.2024.5.03.0041</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Osvaldo Marcelino Gomes</t>
-  </si>
-  <si>
-    <t>UBERABA</t>
-  </si>
-  <si>
-    <t>R$               64.072,23</t>
-  </si>
-  <si>
-    <t>  https://trt3-jus-br.zoom.us/j/82356057731 ID da reunião:82356057731</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Semipresencial</t>
-  </si>
-  <si>
-    <t>0024875-66.2026.5.24.0022</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Ezequiel De Paula Mendes</t>
-  </si>
-  <si>
-    <t>DOURADOS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$             683.586,00</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/my/trt24douvt2sala1</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Presencial</t>
-  </si>
-  <si>
-    <t>1016886-07.2025.5.02.0000</t>
-  </si>
-  <si>
-    <t>Lojas Americanas S.A.</t>
-  </si>
-  <si>
-    <t>Sindicato Dos Empregados No Comercio De Osasco E Regiao</t>
-  </si>
-  <si>
-    <t>OSASCO</t>
-  </si>
-  <si>
-    <t>CEJUSC</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>Reclamação Pré-processual</t>
-  </si>
-  <si>
-    <t>R$               32.000,00</t>
-  </si>
-  <si>
-    <t>Grupo D1</t>
-  </si>
-  <si>
-    <t>BBO</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010536-34.2023.5.15.0095</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Welber Da Soledade Cruz</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$             118.377,60</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>bit.ly/cejusc2grau</t>
-  </si>
-  <si>
-    <t>0011429-40.2025.5.15.0132</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Edson Almeida Souza</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             260.040,01</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Jociene de Jesus Oliveira Jocieneadv@gmail.com 12988871868</t>
-  </si>
-  <si>
-    <t>0010137-18.2025.5.03.0176</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Divino Dos Santos Filho</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$               49.755,19</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/89176162090</t>
-  </si>
-  <si>
-    <t>0010552-21.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>Rafael Cristian Batista</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             169.430,26</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
-  </si>
-  <si>
-    <t>1000003-52.2022.5.02.0432</t>
-  </si>
-  <si>
-    <t>Fabiano Lopes</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>R$             125.200,00</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/89437519049?pwd=eVN6UGhFUDRkM1ljUEMzMTIrYnMxUT09 ID da reunião: 894 3751 9049 Senha de acesso: 493641</t>
+    <t>0010194-96.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Emerson Leandro De Jesus</t>
+  </si>
+  <si>
+    <t>R$             203.177,51</t>
+  </si>
+  <si>
+    <t>0010453-51.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Joao Antonio Alves Bessa</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$             127.002,96</t>
+  </si>
+  <si>
+    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>0011943-65.2014.5.15.0071</t>
+  </si>
+  <si>
+    <t>Rodrigo Jose De Souza</t>
   </si>
 </sst>
 </file>
@@ -1062,14 +1131,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7203D894-FB8D-4A66-A6D3-980B5841DA88}">
-  <dimension ref="A1:R20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BE90FD-E7DB-4FE6-984B-8D8F7D278770}">
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="130.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1125,15 +1210,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105525</v>
+        <v>104040</v>
       </c>
       <c r="B2" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34027777777777779</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1175,45 +1260,45 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105399</v>
+        <v>103642</v>
       </c>
       <c r="B3" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C3" s="6">
-        <v>0.3576388888888889</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1222,54 +1307,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>99485</v>
+        <v>105622</v>
       </c>
       <c r="B4" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C4" s="6">
-        <v>0.36180555555555555</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1278,51 +1363,51 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>103760</v>
+        <v>102788</v>
       </c>
       <c r="B5" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C5" s="6">
-        <v>0.38194444444444442</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>25</v>
@@ -1334,51 +1419,51 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>103162</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105617</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46258</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="G6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="I6" s="7" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>25</v>
@@ -1393,51 +1478,51 @@
         <v>68</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>103410</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R6" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>105850</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46258</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.39652777777777776</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="I7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1446,51 +1531,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>104284</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>104055</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46258</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1502,42 +1587,42 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>103595</v>
+        <v>104199</v>
       </c>
       <c r="B9" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C9" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>84</v>
@@ -1546,10 +1631,10 @@
         <v>85</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1558,51 +1643,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>104217</v>
+        <v>99053</v>
       </c>
       <c r="B10" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C10" s="6">
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1614,54 +1699,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104988</v>
+        <v>63324</v>
       </c>
       <c r="B11" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C11" s="6">
-        <v>0.44097222222222221</v>
+        <v>0.4375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1670,51 +1755,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>101276</v>
+        <v>98770</v>
       </c>
       <c r="B12" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4513888888888889</v>
+        <v>0.4375</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1726,51 +1811,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>97701</v>
+        <v>103855</v>
       </c>
       <c r="B13" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C13" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1782,51 +1867,51 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105053</v>
+        <v>97319</v>
       </c>
       <c r="B14" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C14" s="6">
-        <v>0.5625</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1838,110 +1923,110 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>103159</v>
+        <v>102612</v>
       </c>
       <c r="B15" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C15" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>91722</v>
+        <v>102973</v>
       </c>
       <c r="B16" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C16" s="6">
-        <v>0.62708333333333333</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1950,51 +2035,51 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="O16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>104349</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>101867</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46258</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.63194444444444442</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="J17" s="7" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>25</v>
@@ -2006,54 +2091,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>100017</v>
+        <v>93868</v>
       </c>
       <c r="B18" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C18" s="6">
-        <v>0.65625</v>
+        <v>0.5625</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2062,54 +2147,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>100795</v>
+        <v>105015</v>
       </c>
       <c r="B19" s="5">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C19" s="6">
-        <v>0.65972222222222221</v>
+        <v>0.57291666666666663</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="F19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="I19" s="7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2118,54 +2203,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="O19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>105809</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>82097</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46258</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.68333333333333335</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="J20" s="7" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2174,37 +2259,487 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>105243</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>102015</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>103724</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="P23" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="P20" s="7" t="s">
+      <c r="Q23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="R23" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="R20" s="8" t="s">
+    </row>
+    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>104929</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>181</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>105360</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>104646</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>104567</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R27" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>71633</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.68958333333333333</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="R28" s="8" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{4CB767CF-A375-4216-9B63-E8BF38AFC011}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/87555371032?pwd=ckVSVmpnMHBpcnhHQUZzd0VtT0JBUT09%20%20ID%20DA%20REUNIÃO:%20875%205537%201032%20SENHA%20DE%20ACESSO:%20772981" xr:uid="{B684BA9B-611F-4E8E-B17C-C4C83206471E}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{B674480C-46C4-4854-92B8-14F8D1E057F5}"/>
-    <hyperlink ref="R6" r:id="rId4" display="mailto:adv.raiannyyulle@gmail.com" xr:uid="{FA89402D-249C-4FDB-8FF7-E1A873C04CA8}"/>
-    <hyperlink ref="R7" r:id="rId5" xr:uid="{FAB8E623-25E0-447A-9101-03635C1303F2}"/>
-    <hyperlink ref="R8" r:id="rId6" display="https://url.trt9.jus.br/qkpyb" xr:uid="{9A071592-4278-4777-A73C-98F76C0930A4}"/>
-    <hyperlink ref="R9" r:id="rId7" xr:uid="{C2EFF221-9C79-4093-A6B6-F9149E624849}"/>
-    <hyperlink ref="R12" r:id="rId8" xr:uid="{2311E317-D067-486B-A600-B0D80785FB19}"/>
-    <hyperlink ref="R13" r:id="rId9" display="https://trt3-jus-br.zoom.us/j/82356057731" xr:uid="{64CF60B8-A430-4B55-BB7E-5DD0AB54521D}"/>
-    <hyperlink ref="R14" r:id="rId10" xr:uid="{BB9AA4C6-F5BA-49D5-A147-DA08BDD24704}"/>
-    <hyperlink ref="R17" r:id="rId11" display="mailto:Jocieneadv@gmail.com" xr:uid="{77B3E250-CE1A-4CA0-B27F-58A4E4E265BE}"/>
-    <hyperlink ref="R18" r:id="rId12" xr:uid="{283741D4-7409-497C-8C1E-EC21E0DBA104}"/>
-    <hyperlink ref="R19" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{801F2E95-4CEF-4C8A-A46D-8F390E43754F}"/>
-    <hyperlink ref="R20" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/89437519049?pwd=eVN6UGhFUDRkM1ljUEMzMTIrYnMxUT09%20ID%20da%20reunião:%20894%203751%209049%20Senha%20de%20acesso:%20493641" xr:uid="{2152A80F-AB64-460B-B39F-E9E5B9AB687C}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81695106516?pwd=bTd4VU1OTWpNOU9Pcmh6YWFnOTVsZz09%20ID%20da%20reunião:%20816%209510%206516%20Senha%20de%20acesso:%20530013" xr:uid="{B24ECCFD-2277-43AD-AA38-B61CF2140CA6}"/>
+    <hyperlink ref="R4" r:id="rId2" xr:uid="{F05DB665-4527-4505-B230-74A27FC2F1B0}"/>
+    <hyperlink ref="R9" r:id="rId3" xr:uid="{D8BD7E66-24EF-4372-A4A3-705815A441BB}"/>
+    <hyperlink ref="R13" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{A00502EB-C750-4A2E-ACC8-085CCF615C14}"/>
+    <hyperlink ref="R14" r:id="rId5" xr:uid="{3D86CFB6-77C7-4876-BB54-CA9540044E95}"/>
+    <hyperlink ref="R15" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{29E6F9FD-9BC4-4147-BAED-D1CDD862FEDF}"/>
+    <hyperlink ref="R16" r:id="rId7" xr:uid="{19ED79D9-DCDE-41CD-B6CB-24A7749C2F2D}"/>
+    <hyperlink ref="R17" r:id="rId8" xr:uid="{89B674CB-7531-43D4-9948-11BEB1EFDE56}"/>
+    <hyperlink ref="R18" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/83377008514?pwd=VmFp6LzK2QCjdCZjdRHLVKSglYOLmi.1%20ID%20da%20reunião:%20833%207700%208514%20Senha:%20092842" xr:uid="{48BD82D6-CAF2-486A-83CB-74ED1322BB64}"/>
+    <hyperlink ref="R20" r:id="rId10" display="mailto:matheuspb26@live.com" xr:uid="{A84A2C72-FD01-4ECA-9CF2-B3C4D15E9154}"/>
+    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%20050728" xr:uid="{9747B427-64D2-4824-B98A-EFCA8971D629}"/>
+    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/89066503696?pwd=OFVsanFhMUg1aUFuaGR3WC8vTWpQZz09%20ID%20da%20reunião:%20890%206650%203696%20Senha%20de%20acesso:%20053083" xr:uid="{070448C7-CE12-4AB8-945E-552232919BEF}"/>
+    <hyperlink ref="R23" r:id="rId13" xr:uid="{0786286F-7377-4FA7-9CBA-5721ABDD4B04}"/>
+    <hyperlink ref="R24" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{0A2A4DC4-1EA4-48E3-AF0B-347E1C8C052D}"/>
+    <hyperlink ref="R26" r:id="rId15" xr:uid="{A5E90415-D446-43EF-A219-C14EE4CE128F}"/>
+    <hyperlink ref="R27" r:id="rId16" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{057A12BE-96DB-4856-9722-D5BE7FF6A0C4}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17777405-75B0-4CB2-B768-BCD85A360759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F57424A0-C247-464F-988B-B0D8FF84694D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{726E2D3D-FA46-4F68-98CF-88C636972229}"/>
+    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{0DC0B007-B3CF-437F-9E6D-B2303E3D8587}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="190">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,565 +95,520 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000537-91.2025.5.02.0043</t>
+  </si>
+  <si>
+    <t>Mccann Erickson Publicidade Ltda</t>
+  </si>
+  <si>
+    <t>Sabrina Alves Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>43ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             219.665,96</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>NBG</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/83528814744?pwd=bXtkzQFolwYadCbIpf0Q3ZvYw7Uc2e.1 ID da reunião: 835 2881 4744 Senha de acesso: 099184</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010548-43.2026.5.15.0095</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Jorge Augusto Ferreira Da Silva</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>08ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             110.930,75</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83331967214?pwd=SFNmQUIvT0tRaHlDaVYrN3l5bzJVQT09</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0011932-54.2025.5.15.0102</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Michael Klayvert Eliziario Dos Santos</t>
-  </si>
-  <si>
-    <t>TAUBATÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
+    <t>0017461-96.2026.5.16.0003</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Gilberto Do Espirito Santo Martins</t>
+  </si>
+  <si>
+    <t>SÃO LUIS</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             174.558,82</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/86803464313?pwd=dIvtienMBrIv5kAUh9dUca02AGfmoX.1</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001226-96.2026.5.02.0465</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Jose Luiz Patricio De Oliveira Batista</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             223.000,00</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010680-62.2017.5.03.0156</t>
+  </si>
+  <si>
+    <t>Frutal Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Sind. Dos Arrumadores E Trab. Na Movimentacao De Maercadorias Em Geral De Frutal</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$               50.000,00</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>1000980-03.2026.5.02.0465</t>
+  </si>
+  <si>
+    <t>Claudio Oliveira Monte</t>
+  </si>
+  <si>
+    <t>R$             298.844,55</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011190-75.2025.5.15.0119</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Marcio Jose Chagas Bastos Pereira</t>
+  </si>
+  <si>
+    <t>CAÇAPAVA</t>
+  </si>
+  <si>
+    <t>R$             282.283,49</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>0010702-08.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Ronaldo Bertonhi</t>
+  </si>
+  <si>
+    <t>R$             100.000,00</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>0012532-08.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Jociel Guedes Paiva</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$             146.696,95</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>0010765-27.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A</t>
+  </si>
+  <si>
+    <t>Marcos Da Silva Correa</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$             362.733,41</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010062-14.2026.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Jander De Morais</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
     <t>02ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               26.122,65</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81695106516?pwd=bTd4VU1OTWpNOU9Pcmh6YWFnOTVsZz09 ID da reunião: 816 9510 6516 Senha de acesso: 530013</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0013316-28.2025.5.15.0013</t>
-  </si>
-  <si>
-    <t>Embraer S.A</t>
-  </si>
-  <si>
-    <t>Edvaldo Rodrigues De Miranda</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
+    <t>R$             435.701,18</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>0010034-02.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Acacio Eduardo Cardoso</t>
+  </si>
+  <si>
+    <t>R$             611.072,50</t>
+  </si>
+  <si>
+    <t>0010704-69.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Bruno Duque Vanderlei</t>
+  </si>
+  <si>
+    <t>R$             107.564,68</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010778-26.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Regiani Felipe Adami</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               65.723,45</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (19) 99949-8727</t>
+  </si>
+  <si>
+    <t>0010022-85.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Rafael Cardoso Goncalves</t>
+  </si>
+  <si>
+    <t>R$               41.434,50</t>
+  </si>
+  <si>
+    <t>0010768-85.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Usina Frutal Acucar E Alcool Ltda.</t>
+  </si>
+  <si>
+    <t>Luiz Adriano Da Silva</t>
+  </si>
+  <si>
+    <t>R$                 1.621,00</t>
+  </si>
+  <si>
+    <t>0012435-28.2024.5.15.0129</t>
+  </si>
+  <si>
+    <t>Romulo Natal Franca</t>
+  </si>
+  <si>
+    <t>10ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             272.813,25</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Juliana da Silva, (19) 98743-4081</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010841-91.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Juliano Roberto Ferreira</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$          1.218.035,77</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0010286-40.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Caio Henrique Martins Da Paz</t>
+  </si>
+  <si>
+    <t>R$             226.457,91</t>
+  </si>
+  <si>
+    <t>1000899-59.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Carlos Alberto De Castro</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t>R$               86.225,68</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/89599035768?pwd=SkVKNzE1Nk1oVVlFdW5FekwyWStvUT09 ID da reunião: 895 9903 5768 Senha de acesso: 974594</t>
+  </si>
+  <si>
+    <t>0010362-10.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Lidiane De Andrade Domingos Valentim</t>
+  </si>
+  <si>
+    <t>R$             423.277,50</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>1001987-60.2025.5.02.0434</t>
+  </si>
+  <si>
+    <t>Jefferson Inacio</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             687.096,48</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Tiago Dias Santos</t>
+  </si>
+  <si>
+    <t>0011100-65.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Alexsandra Da Silva</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$             161.000,00</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>0011219-09.2026.5.15.0017</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Fabio Leonardo Pascoal</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
   </si>
   <si>
     <t>01ª VARA DO TRABALHO</t>
   </si>
   <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               92.084,54</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>0011524-30.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Cicero Luiz Dos Santos</t>
-  </si>
-  <si>
-    <t>ARAXÁ</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             430.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>NLO</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0012147-91.2025.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Antonio Borges Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             103.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Juliana Souza, (17) 99682-9421</t>
-  </si>
-  <si>
-    <t>0012457-97.2025.5.15.0017</t>
-  </si>
-  <si>
-    <t>Fabio Junio Marques</t>
-  </si>
-  <si>
-    <t>R$             186.000,00</t>
-  </si>
-  <si>
-    <t>1001029-11.2025.5.02.0261</t>
-  </si>
-  <si>
-    <t>Msa Do Brasil Equipamentos E Instrumentos De Segurança Ltda.</t>
-  </si>
-  <si>
-    <t>Cleunice Divino De Oliveira</t>
-  </si>
-  <si>
-    <t>DIADEMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             182.146,40</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>0010094-06.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Carlos Eduardo Da Silva</t>
-  </si>
-  <si>
-    <t>R$             335.000,00</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0024861-81.2025.5.24.0066</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Monteverde</t>
-  </si>
-  <si>
-    <t>Rodrigo Domingos Da Silva</t>
-  </si>
-  <si>
-    <t>PONTA PORÃ</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>R$             125.258,41</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt24-jus-br.zoom.us/j/89440353042</t>
-  </si>
-  <si>
-    <t>0012027-17.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Israel Alvernaz</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>R$             808.083,80</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011346-96.2014.5.15.0071</t>
-  </si>
-  <si>
-    <t>Odirley Oliveira Dos Santos</t>
-  </si>
-  <si>
-    <t>CEJUSC TST</t>
-  </si>
-  <si>
-    <t>3ª Instância</t>
-  </si>
-  <si>
-    <t>R$               30.000,00</t>
-  </si>
-  <si>
-    <t>bit.ly/Cejusc2026</t>
-  </si>
-  <si>
-    <t>0011709-34.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Reginaldo Rodrigo Francisco</t>
-  </si>
-  <si>
-    <t>R$             442.019,00</t>
-  </si>
-  <si>
-    <t>0010087-13.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Roberto Da Fonseca Julio</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             171.538,44</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09 ID da reunião: 818 6908 4210 Senha de acesso: 306523</t>
-  </si>
-  <si>
-    <t>0010417-19.2024.5.03.0048</t>
-  </si>
-  <si>
-    <t>Celio Junior Da Silva</t>
-  </si>
-  <si>
-    <t>R$               69.911,27</t>
-  </si>
-  <si>
-    <t>0011360-26.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S.A. - Paulinia - Pln</t>
-  </si>
-  <si>
-    <t>Welington Cesar Bento Cabral</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             230.595,89</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0011791-60.2025.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Celio Barbosa De Sousa</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$               25.043,76</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
-  </si>
-  <si>
-    <t>0010198-36.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Fidelis Ferreira</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$             147.866,42</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0011136-75.2022.5.15.0132</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Mario Guilherme Ribeiro</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             250.000,00</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83377008514?pwd=VmFp6LzK2QCjdCZjdRHLVKSglYOLmi.1 ID da reunião: 833 7700 8514 Senha: 092842</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0011348-33.2026.5.15.0140</t>
-  </si>
-  <si>
-    <t>Grammer Do Brasil Ltda</t>
-  </si>
-  <si>
-    <t>Michele Vitoria Eufrasio</t>
-  </si>
-  <si>
-    <t>ATIBAIA</t>
-  </si>
-  <si>
-    <t>R$               43.608,54</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>0010897-20.2026.5.03.0147</t>
-  </si>
-  <si>
-    <t>Fertilizantes Heringer S/A</t>
-  </si>
-  <si>
-    <t>Jonathan Matheus Souza Borges</t>
-  </si>
-  <si>
-    <t>TRÊS CORAÇÕES</t>
-  </si>
-  <si>
-    <t>R$               48.096,00</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Matheus Pimenta Barros matheuspb26@live.com (35) 999092279</t>
-  </si>
-  <si>
-    <t>0010476-36.2026.5.15.0037</t>
-  </si>
-  <si>
-    <t>Ouroeste Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Elisiario Marques De Souza</t>
-  </si>
-  <si>
-    <t>FERNANDÓPOLIS</t>
-  </si>
-  <si>
-    <t>R$          1.093.572,33</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1 ID da reunião: 885 4267 2682 Senha de acesso: 050728</t>
-  </si>
-  <si>
-    <t>0011623-31.2025.5.15.0038</t>
-  </si>
-  <si>
-    <t>Grammer Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Wagner Maciel De Matos</t>
-  </si>
-  <si>
-    <t>R$               33.333,84</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89066503696?pwd=OFVsanFhMUg1aUFuaGR3WC8vTWpQZz09 ID da reunião: 890 6650 3696 Senha de acesso: 053083</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0000018-26.2026.5.09.0069</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Vanderlei Teixeira Menezes</t>
-  </si>
-  <si>
-    <t>CASCAVEL</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>R$               27.000,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/hjwrx ID da reunião: 89549820908 Senha de acesso: Hhtcw0SRcL</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010588-30.2026.5.15.0061</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Myller Gomes Santos</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$               49.966,45</t>
-  </si>
-  <si>
-    <t>NBB</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
-  </si>
-  <si>
-    <t>1001152-38.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Rafael Bergamin Cardoso</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             181.143,51</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0010194-96.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Emerson Leandro De Jesus</t>
-  </si>
-  <si>
-    <t>R$             203.177,51</t>
-  </si>
-  <si>
-    <t>0010453-51.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Joao Antonio Alves Bessa</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$             127.002,96</t>
-  </si>
-  <si>
-    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>0011943-65.2014.5.15.0071</t>
-  </si>
-  <si>
-    <t>Rodrigo Jose De Souza</t>
+    <t>R$             563.244,91</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89099322953?pwd=TDFoQ1FqaENlUit2YXptSTJwa2lnZz</t>
   </si>
 </sst>
 </file>
@@ -1131,30 +1086,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BE90FD-E7DB-4FE6-984B-8D8F7D278770}">
-  <dimension ref="A1:R28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6535074-504F-4915-8C8E-DB4E349166CE}">
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="67.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="130.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="126.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,15 +1165,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104040</v>
+        <v>100480</v>
       </c>
       <c r="B2" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.37152777777777779</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1266,15 +1221,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>103642</v>
+        <v>104493</v>
       </c>
       <c r="B3" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C3" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1298,7 +1253,7 @@
         <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1307,33 +1262,33 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>105169</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105622</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>45</v>
@@ -1372,45 +1327,45 @@
         <v>54</v>
       </c>
       <c r="Q4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>105688</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>102788</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1419,54 +1374,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>103162</v>
+        <v>85885</v>
       </c>
       <c r="B6" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C6" s="6">
-        <v>0.36805555555555558</v>
+        <v>0.375</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1475,54 +1430,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O6" s="7" t="s">
         <v>53</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>103410</v>
+        <v>105370</v>
       </c>
       <c r="B7" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C7" s="6">
-        <v>0.375</v>
+        <v>0.38541666666666669</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1531,51 +1486,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>104284</v>
+        <v>102832</v>
       </c>
       <c r="B8" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C8" s="6">
-        <v>0.38194444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1587,54 +1542,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O8" s="7" t="s">
         <v>53</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>104199</v>
+        <v>105621</v>
       </c>
       <c r="B9" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C9" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.40625</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1643,51 +1598,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>53</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>99053</v>
+        <v>99893</v>
       </c>
       <c r="B10" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C10" s="6">
         <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1696,57 +1651,57 @@
         <v>26</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>63324</v>
+        <v>105222</v>
       </c>
       <c r="B11" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C11" s="6">
-        <v>0.4375</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1755,51 +1710,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>98770</v>
+        <v>104722</v>
       </c>
       <c r="B12" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4375</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1811,51 +1766,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="O12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>99913</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>103855</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>25</v>
@@ -1864,57 +1819,57 @@
         <v>26</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>97319</v>
+        <v>105105</v>
       </c>
       <c r="B14" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C14" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1923,54 +1878,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>53</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>102612</v>
+        <v>101322</v>
       </c>
       <c r="B15" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C15" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1979,107 +1934,107 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>102973</v>
+        <v>99895</v>
       </c>
       <c r="B16" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C16" s="6">
-        <v>0.47916666666666669</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>104349</v>
+        <v>105779</v>
       </c>
       <c r="B17" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C17" s="6">
-        <v>0.5625</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>25</v>
@@ -2091,42 +2046,42 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>53</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>93868</v>
+        <v>101373</v>
       </c>
       <c r="B18" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C18" s="6">
-        <v>0.5625</v>
+        <v>0.49652777777777779</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>37</v>
@@ -2135,10 +2090,10 @@
         <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2147,54 +2102,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>105015</v>
+        <v>105649</v>
       </c>
       <c r="B19" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C19" s="6">
-        <v>0.57291666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2203,51 +2158,51 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>105809</v>
+        <v>104685</v>
       </c>
       <c r="B20" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C20" s="6">
-        <v>0.57638888888888884</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
@@ -2265,104 +2220,104 @@
         <v>53</v>
       </c>
       <c r="P20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>105095</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="R20" s="8" t="s">
+      <c r="F21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4">
-        <v>105243</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>162</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="Q21" s="7" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>102015</v>
+        <v>100335</v>
       </c>
       <c r="B22" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C22" s="6">
-        <v>0.59375</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>167</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2374,48 +2329,48 @@
         <v>168</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="P22" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q22" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="Q22" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="R22" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>103039</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>103724</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="F23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="H23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>25</v>
@@ -2427,54 +2382,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>180</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>104929</v>
+        <v>100847</v>
       </c>
       <c r="B24" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C24" s="6">
-        <v>0.60069444444444442</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2483,51 +2438,51 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>105360</v>
+        <v>100787</v>
       </c>
       <c r="B25" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C25" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>25</v>
@@ -2539,51 +2494,51 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>104646</v>
+        <v>105042</v>
       </c>
       <c r="B26" s="5">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C26" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>25</v>
@@ -2595,152 +2550,37 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>104567</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.625</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="R27" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
-        <v>71633</v>
-      </c>
-      <c r="B28" s="5">
-        <v>46259</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.68958333333333333</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://us02web.zoom.us/j/81695106516?pwd=bTd4VU1OTWpNOU9Pcmh6YWFnOTVsZz09%20ID%20da%20reunião:%20816%209510%206516%20Senha%20de%20acesso:%20530013" xr:uid="{B24ECCFD-2277-43AD-AA38-B61CF2140CA6}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{F05DB665-4527-4505-B230-74A27FC2F1B0}"/>
-    <hyperlink ref="R9" r:id="rId3" xr:uid="{D8BD7E66-24EF-4372-A4A3-705815A441BB}"/>
-    <hyperlink ref="R13" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{A00502EB-C750-4A2E-ACC8-085CCF615C14}"/>
-    <hyperlink ref="R14" r:id="rId5" xr:uid="{3D86CFB6-77C7-4876-BB54-CA9540044E95}"/>
-    <hyperlink ref="R15" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{29E6F9FD-9BC4-4147-BAED-D1CDD862FEDF}"/>
-    <hyperlink ref="R16" r:id="rId7" xr:uid="{19ED79D9-DCDE-41CD-B6CB-24A7749C2F2D}"/>
-    <hyperlink ref="R17" r:id="rId8" xr:uid="{89B674CB-7531-43D4-9948-11BEB1EFDE56}"/>
-    <hyperlink ref="R18" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/83377008514?pwd=VmFp6LzK2QCjdCZjdRHLVKSglYOLmi.1%20ID%20da%20reunião:%20833%207700%208514%20Senha:%20092842" xr:uid="{48BD82D6-CAF2-486A-83CB-74ED1322BB64}"/>
-    <hyperlink ref="R20" r:id="rId10" display="mailto:matheuspb26@live.com" xr:uid="{A84A2C72-FD01-4ECA-9CF2-B3C4D15E9154}"/>
-    <hyperlink ref="R21" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/88542672682?pwd=7pQ4QRhZmRG9RAQAWKowymbwNawa7t.1%20ID%20da%20reunião:%20885%204267%202682%20Senha%20de%20acesso:%20050728" xr:uid="{9747B427-64D2-4824-B98A-EFCA8971D629}"/>
-    <hyperlink ref="R22" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/89066503696?pwd=OFVsanFhMUg1aUFuaGR3WC8vTWpQZz09%20ID%20da%20reunião:%20890%206650%203696%20Senha%20de%20acesso:%20053083" xr:uid="{070448C7-CE12-4AB8-945E-552232919BEF}"/>
-    <hyperlink ref="R23" r:id="rId13" xr:uid="{0786286F-7377-4FA7-9CBA-5721ABDD4B04}"/>
-    <hyperlink ref="R24" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{0A2A4DC4-1EA4-48E3-AF0B-347E1C8C052D}"/>
-    <hyperlink ref="R26" r:id="rId15" xr:uid="{A5E90415-D446-43EF-A219-C14EE4CE128F}"/>
-    <hyperlink ref="R27" r:id="rId16" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{057A12BE-96DB-4856-9722-D5BE7FF6A0C4}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/83528814744?pwd=bXtkzQFolwYadCbIpf0Q3ZvYw7Uc2e.1%20ID%20da%20reunião:%20835%202881%204744%20Senha%20de%20acesso:%20099184" xr:uid="{78E641D5-EE7B-421B-9F72-9A6E5FC7C7A1}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{0A4E51CB-246C-4896-B6C7-C695C5D2FB3A}"/>
+    <hyperlink ref="R4" r:id="rId3" xr:uid="{389D516D-0DA7-4B6D-AB20-BD3EE86A7994}"/>
+    <hyperlink ref="R6" r:id="rId4" xr:uid="{3C188A79-8E55-4114-B8C5-AEDC86305ACC}"/>
+    <hyperlink ref="R9" r:id="rId5" xr:uid="{EACC0A6E-6711-4747-BEFA-3FC97EB5BB72}"/>
+    <hyperlink ref="R11" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{075D3E85-B906-4730-838F-681AE8301A94}"/>
+    <hyperlink ref="R14" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{9C320D4F-5529-444C-AE16-1E420F3F96C7}"/>
+    <hyperlink ref="R17" r:id="rId8" xr:uid="{9CCDDC77-5C06-49D5-9DDA-F89E3BE201D0}"/>
+    <hyperlink ref="R19" r:id="rId9" xr:uid="{13D1C0F5-7729-4112-A5AA-162D194CA681}"/>
+    <hyperlink ref="R20" r:id="rId10" xr:uid="{31EBDEAC-975F-429E-8F10-86AC17616228}"/>
+    <hyperlink ref="R21" r:id="rId11" display="https://trt2-jus-br.zoom.us/j/89599035768?pwd=SkVKNzE1Nk1oVVlFdW5FekwyWStvUT09%20ID%20da%20reunião:%20895%209903%205768%20Senha%20de%20acesso:%20974594" xr:uid="{A0553A76-829D-4430-88FE-9A109D784029}"/>
+    <hyperlink ref="R26" r:id="rId12" xr:uid="{D7F09F58-AEEA-441D-BAD2-08FB1242B71D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F57424A0-C247-464F-988B-B0D8FF84694D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD56DE3B-4493-4D02-95DF-44D77EE5EB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{0DC0B007-B3CF-437F-9E6D-B2303E3D8587}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F83BFE05-AF33-4DB2-B167-EF9CDE76396B}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="180">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,142 +95,334 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000422-56.2026.5.09.0658</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Leandro Nassar</t>
+  </si>
+  <si>
+    <t>FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             395.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/47hf4 ID da Reunião: 82187253702 Senha: f6o1hS63pW</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000437-25.2026.5.09.0658</t>
+  </si>
+  <si>
+    <t>Vilson Nandi</t>
+  </si>
+  <si>
+    <t>R$               96.000,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/3ct1k ID da Reunião: 81059501113 Senha: G6iGPmA6XQ</t>
+  </si>
+  <si>
+    <t>0000507-87.2026.5.09.0643</t>
+  </si>
+  <si>
+    <t>Celso Alves</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             154.240,00</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/byms7 id: 81469473153 senha: O1ZZggw4p7</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Presencial</t>
+  </si>
+  <si>
+    <t>0010123-25.2021.5.15.0084</t>
+  </si>
+  <si>
+    <t>Eleb Equipamentos Ltda.</t>
+  </si>
+  <si>
+    <t>Gilberto Alves Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>4ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$             112.400,80</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Semipresencial</t>
+  </si>
+  <si>
+    <t>1001146-03.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Mailson Ferreira Balbino</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               65.006,00</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81264440862?pwd=fO1DbCbSfbmcUakkvweGCngdmimhP9.1 ID da reunião: 812 6444 0862 Senha de acesso: 028055</t>
+  </si>
+  <si>
     <t>Audiência Una - Telepresencial</t>
   </si>
   <si>
-    <t>1000537-91.2025.5.02.0043</t>
-  </si>
-  <si>
-    <t>Mccann Erickson Publicidade Ltda</t>
-  </si>
-  <si>
-    <t>Sabrina Alves Dos Santos</t>
+    <t>0010499-41.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Fernando Carvalho Silva</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               79.565,02</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09 ID da reunião: 821 8299 1000 Senha de acesso: 060642</t>
+  </si>
+  <si>
+    <t>0010725-02.2026.5.15.0032</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Felipe Luis Barbosa</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>R$             102.417,63</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>1000971-09.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Cbc - Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Matheus Avila Ruis</t>
+  </si>
+  <si>
+    <t>R$             148.411,67</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/85009685110?pwd=Ah1Tp4Y85y3TcszzhnGcAvN0FrOuF6.1 ID da reunião: 850 0968 5110w Senha de acesso: 345889</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010089-80.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Jose Augusto Souza Santos Junior</t>
+  </si>
+  <si>
+    <t>R$               90.000,00</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09 ID da reunião: 818 6908 4210 Senha de acesso: 306523</t>
+  </si>
+  <si>
+    <t>0010097-57.2026.5.15.0082</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda. &amp; Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Aparecido Dos Santos Oliveira</t>
+  </si>
+  <si>
+    <t>R$               98.000,00</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>0010297-82.2025.5.03.0066</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A. - Manhuacu - Mcu</t>
+  </si>
+  <si>
+    <t>Astrogildo Benedito Junior</t>
+  </si>
+  <si>
+    <t>MANHUAÇU</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>R$               81.100,86</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/varamanhuacu</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1002135-25.2025.5.02.0029</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Viviane Aparecida Juzo</t>
   </si>
   <si>
     <t>SÃO PAULO</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>43ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             219.665,96</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>NBG</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/83528814744?pwd=bXtkzQFolwYadCbIpf0Q3ZvYw7Uc2e.1 ID da reunião: 835 2881 4744 Senha de acesso: 099184</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010548-43.2026.5.15.0095</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Jorge Augusto Ferreira Da Silva</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>08ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             110.930,75</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83331967214?pwd=SFNmQUIvT0tRaHlDaVYrN3l5bzJVQT09</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0017461-96.2026.5.16.0003</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Gilberto Do Espirito Santo Martins</t>
-  </si>
-  <si>
-    <t>SÃO LUIS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
+    <t>29ª VARA DO TRABALHO</t>
   </si>
   <si>
     <t>Conhecimento</t>
   </si>
   <si>
-    <t>R$             174.558,82</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/86803464313?pwd=dIvtienMBrIv5kAUh9dUca02AGfmoX.1</t>
+    <t>R$          3.623.037,67</t>
+  </si>
+  <si>
+    <t>TFR</t>
   </si>
   <si>
     <t>Audiência Una - Presencial</t>
   </si>
   <si>
-    <t>1001226-96.2026.5.02.0465</t>
+    <t>1001201-86.2026.5.02.0464</t>
   </si>
   <si>
     <t>Mahle Metal Leve S.A.</t>
   </si>
   <si>
-    <t>Jose Luiz Patricio De Oliveira Batista</t>
+    <t>Theilor Bernardo Da Silva</t>
   </si>
   <si>
     <t>SÃO BERNARDO DO CAMPO</t>
   </si>
   <si>
-    <t>05ª VARA DO TRABALHO</t>
+    <t>04ª VARA DO TRABALHO</t>
   </si>
   <si>
     <t>Inicial</t>
   </si>
   <si>
-    <t>R$             223.000,00</t>
+    <t>R$             316.306,11</t>
   </si>
   <si>
     <t>Grupo E1</t>
@@ -239,202 +431,145 @@
     <t>VRO</t>
   </si>
   <si>
-    <t>Presencial</t>
+    <t>PSI</t>
   </si>
   <si>
     <t>Audiência de Conciliação - Telepresencial</t>
   </si>
   <si>
-    <t>0010680-62.2017.5.03.0156</t>
-  </si>
-  <si>
-    <t>Frutal Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Sind. Dos Arrumadores E Trab. Na Movimentacao De Maercadorias Em Geral De Frutal</t>
-  </si>
-  <si>
-    <t>FRUTAL</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$               50.000,00</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
-  </si>
-  <si>
-    <t>1000980-03.2026.5.02.0465</t>
-  </si>
-  <si>
-    <t>Claudio Oliveira Monte</t>
-  </si>
-  <si>
-    <t>R$             298.844,55</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011190-75.2025.5.15.0119</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Marcio Jose Chagas Bastos Pereira</t>
-  </si>
-  <si>
-    <t>CAÇAPAVA</t>
-  </si>
-  <si>
-    <t>R$             282.283,49</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>0010702-08.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Ronaldo Bertonhi</t>
-  </si>
-  <si>
-    <t>R$             100.000,00</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>0012532-08.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Jociel Guedes Paiva</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>R$             146.696,95</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>0010765-27.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A</t>
-  </si>
-  <si>
-    <t>Marcos Da Silva Correa</t>
-  </si>
-  <si>
-    <t>DRACENA</t>
-  </si>
-  <si>
-    <t>R$             362.733,41</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
-  </si>
-  <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0010062-14.2026.5.15.0045</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Jander De Morais</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             435.701,18</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>0010034-02.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Acacio Eduardo Cardoso</t>
-  </si>
-  <si>
-    <t>R$             611.072,50</t>
-  </si>
-  <si>
-    <t>0010704-69.2026.5.15.0050</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Bruno Duque Vanderlei</t>
-  </si>
-  <si>
-    <t>R$             107.564,68</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010778-26.2025.5.15.0126</t>
+    <t>0010556-18.2026.5.03.0042</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Josenildo Da Silva Santos</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>R$               84.294,72</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/89450925044 ID da reunião: 894 5092 5044</t>
+  </si>
+  <si>
+    <t>0010304-41.2023.5.15.0121</t>
+  </si>
+  <si>
+    <t>Americanas S.A.</t>
+  </si>
+  <si>
+    <t>Flavia Cavalcante Patricio</t>
+  </si>
+  <si>
+    <t>SÃO SEBASTIÃO</t>
+  </si>
+  <si>
+    <t>R$             293.430,53</t>
+  </si>
+  <si>
+    <t>Grupo D1</t>
+  </si>
+  <si>
+    <t>JQS</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83921225378?pwd=YhypVdE7UmYb8yS9ShDzir1DtTYXqh.1 ID da reunião: 839 2122 5378 Senha: 520497</t>
+  </si>
+  <si>
+    <t>1001267-95.2022.5.02.0435</t>
+  </si>
+  <si>
+    <t>Jeferson Fernandes De Carvalho</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>CEJUSC ABC</t>
+  </si>
+  <si>
+    <t>R$               96.803,06</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/88959116257?pwd=Q09WTmd6SnZibUUrZWxMSFdiRm9tUT09 ID da reunião: 889 5911 6257 Senha de acesso: 136898</t>
+  </si>
+  <si>
+    <t>0010871-95.2022.5.03.0168</t>
+  </si>
+  <si>
+    <t>Andrelino Pereira De Mendonca</t>
+  </si>
+  <si>
+    <t>R$             114.300,00</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/89017526223</t>
+  </si>
+  <si>
+    <t>0024037-88.2026.5.24.0066</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Monteverde</t>
+  </si>
+  <si>
+    <t>David Serafim Rocha</t>
+  </si>
+  <si>
+    <t>PONTA PORÃ</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>R$             232.999,00</t>
+  </si>
+  <si>
+    <t>https://trt24-jus-br.zoom.us/j/85172612476</t>
+  </si>
+  <si>
+    <t>0011942-45.2025.5.15.0152</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Anderson De Souza Vaz</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>R$               20.051,60</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Victor Sousa da Rocha vs.rocha@hotmail.com (19) 997799266</t>
+  </si>
+  <si>
+    <t>0011247-92.2025.5.15.0087</t>
   </si>
   <si>
     <t>Syngenta Proteção De Cultivos Ltda.</t>
   </si>
   <si>
-    <t>Regiani Felipe Adami</t>
+    <t>Ironildo Rocha Santos</t>
   </si>
   <si>
     <t>PAULÍNIA</t>
   </si>
   <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>R$               65.723,45</t>
+    <t>R$               86.728,77</t>
   </si>
   <si>
     <t>Correspondente - Carlos Florian</t>
@@ -444,171 +579,6 @@
   </si>
   <si>
     <t>Presencial | Advogada - Dra. Eliane Mendes, (19) 99949-8727</t>
-  </si>
-  <si>
-    <t>0010022-85.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Rafael Cardoso Goncalves</t>
-  </si>
-  <si>
-    <t>R$               41.434,50</t>
-  </si>
-  <si>
-    <t>0010768-85.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Usina Frutal Acucar E Alcool Ltda.</t>
-  </si>
-  <si>
-    <t>Luiz Adriano Da Silva</t>
-  </si>
-  <si>
-    <t>R$                 1.621,00</t>
-  </si>
-  <si>
-    <t>0012435-28.2024.5.15.0129</t>
-  </si>
-  <si>
-    <t>Romulo Natal Franca</t>
-  </si>
-  <si>
-    <t>10ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             272.813,25</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Juliana da Silva, (19) 98743-4081</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010841-91.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Juliano Roberto Ferreira</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$          1.218.035,77</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0010286-40.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Caio Henrique Martins Da Paz</t>
-  </si>
-  <si>
-    <t>R$             226.457,91</t>
-  </si>
-  <si>
-    <t>1000899-59.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Carlos Alberto De Castro</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>CEJUSC ABC</t>
-  </si>
-  <si>
-    <t>Cumprimento de Sentença</t>
-  </si>
-  <si>
-    <t>R$               86.225,68</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/89599035768?pwd=SkVKNzE1Nk1oVVlFdW5FekwyWStvUT09 ID da reunião: 895 9903 5768 Senha de acesso: 974594</t>
-  </si>
-  <si>
-    <t>0010362-10.2025.5.15.0045</t>
-  </si>
-  <si>
-    <t>Lidiane De Andrade Domingos Valentim</t>
-  </si>
-  <si>
-    <t>R$             423.277,50</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>1001987-60.2025.5.02.0434</t>
-  </si>
-  <si>
-    <t>Jefferson Inacio</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             687.096,48</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Tiago Dias Santos</t>
-  </si>
-  <si>
-    <t>0011100-65.2025.5.15.0152</t>
-  </si>
-  <si>
-    <t>Dell Computadores Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Alexsandra Da Silva</t>
-  </si>
-  <si>
-    <t>HORTOLÂNDIA</t>
-  </si>
-  <si>
-    <t>R$             161.000,00</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>0011219-09.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Fabio Leonardo Pascoal</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             563.244,91</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89099322953?pwd=TDFoQ1FqaENlUit2YXptSTJwa2lnZz</t>
   </si>
 </sst>
 </file>
@@ -1086,30 +1056,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6535074-504F-4915-8C8E-DB4E349166CE}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5CB49A-61F7-4436-94CE-DD092AE08D36}">
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="67.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="126.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="121.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,15 +1135,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>100480</v>
+        <v>104513</v>
       </c>
       <c r="B2" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C2" s="6">
-        <v>0.37152777777777779</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1215,42 +1185,42 @@
         <v>30</v>
       </c>
       <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>104544</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
-        <v>104493</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>25</v>
@@ -1262,54 +1232,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105169</v>
+        <v>105518</v>
       </c>
       <c r="B4" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C4" s="6">
         <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1318,54 +1288,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105688</v>
+        <v>93751</v>
       </c>
       <c r="B5" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C5" s="6">
-        <v>0.375</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1374,54 +1344,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>85885</v>
+        <v>105736</v>
       </c>
       <c r="B6" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C6" s="6">
-        <v>0.375</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1430,54 +1400,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105370</v>
+        <v>104303</v>
       </c>
       <c r="B7" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C7" s="6">
-        <v>0.38541666666666669</v>
+        <v>0.40625</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1486,51 +1456,51 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>102832</v>
+        <v>105265</v>
       </c>
       <c r="B8" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C8" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>25</v>
@@ -1542,54 +1512,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105453</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>105621</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.40625</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="H9" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1598,51 +1568,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>103900</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>99893</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>93</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>25</v>
@@ -1651,57 +1621,57 @@
         <v>26</v>
       </c>
       <c r="M10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P10" s="7" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>103880</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="R10" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>105222</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1710,51 +1680,51 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>102447</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="O11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P11" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Q11" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="R11" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>104722</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J12" s="7" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>25</v>
@@ -1766,110 +1736,110 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>104266</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="Q12" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="I13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>99913</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="O13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="Q13" s="7" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105105</v>
+        <v>105667</v>
       </c>
       <c r="B14" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C14" s="6">
-        <v>0.4375</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1878,54 +1848,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>101322</v>
+        <v>105007</v>
       </c>
       <c r="B15" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C15" s="6">
-        <v>0.4375</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1934,110 +1904,110 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>99895</v>
+        <v>91306</v>
       </c>
       <c r="B16" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C16" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105779</v>
+        <v>96585</v>
       </c>
       <c r="B17" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C17" s="6">
-        <v>0.44791666666666669</v>
+        <v>0.60069444444444442</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2046,51 +2016,51 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>101373</v>
+        <v>89689</v>
       </c>
       <c r="B18" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C18" s="6">
-        <v>0.49652777777777779</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>25</v>
@@ -2102,51 +2072,51 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="O18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>104293</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
-        <v>105649</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>25</v>
@@ -2158,51 +2128,51 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>104685</v>
+        <v>101868</v>
       </c>
       <c r="B20" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C20" s="6">
-        <v>0.59027777777777779</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>25</v>
@@ -2214,373 +2184,96 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="R20" s="8" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105095</v>
+        <v>101930</v>
       </c>
       <c r="B21" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C21" s="6">
-        <v>0.62847222222222221</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>100335</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>103039</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
-        <v>100847</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>100787</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>105042</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46260</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://trt2-jus-br.zoom.us/j/83528814744?pwd=bXtkzQFolwYadCbIpf0Q3ZvYw7Uc2e.1%20ID%20da%20reunião:%20835%202881%204744%20Senha%20de%20acesso:%20099184" xr:uid="{78E641D5-EE7B-421B-9F72-9A6E5FC7C7A1}"/>
-    <hyperlink ref="R3" r:id="rId2" xr:uid="{0A4E51CB-246C-4896-B6C7-C695C5D2FB3A}"/>
-    <hyperlink ref="R4" r:id="rId3" xr:uid="{389D516D-0DA7-4B6D-AB20-BD3EE86A7994}"/>
-    <hyperlink ref="R6" r:id="rId4" xr:uid="{3C188A79-8E55-4114-B8C5-AEDC86305ACC}"/>
-    <hyperlink ref="R9" r:id="rId5" xr:uid="{EACC0A6E-6711-4747-BEFA-3FC97EB5BB72}"/>
-    <hyperlink ref="R11" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{075D3E85-B906-4730-838F-681AE8301A94}"/>
-    <hyperlink ref="R14" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{9C320D4F-5529-444C-AE16-1E420F3F96C7}"/>
-    <hyperlink ref="R17" r:id="rId8" xr:uid="{9CCDDC77-5C06-49D5-9DDA-F89E3BE201D0}"/>
-    <hyperlink ref="R19" r:id="rId9" xr:uid="{13D1C0F5-7729-4112-A5AA-162D194CA681}"/>
-    <hyperlink ref="R20" r:id="rId10" xr:uid="{31EBDEAC-975F-429E-8F10-86AC17616228}"/>
-    <hyperlink ref="R21" r:id="rId11" display="https://trt2-jus-br.zoom.us/j/89599035768?pwd=SkVKNzE1Nk1oVVlFdW5FekwyWStvUT09%20ID%20da%20reunião:%20895%209903%205768%20Senha%20de%20acesso:%20974594" xr:uid="{A0553A76-829D-4430-88FE-9A109D784029}"/>
-    <hyperlink ref="R26" r:id="rId12" xr:uid="{D7F09F58-AEEA-441D-BAD2-08FB1242B71D}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{C767B6F7-B9B6-42A1-94EA-363EEE02DB43}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{657105BB-209B-4662-9E1A-1E21C9CFCF67}"/>
+    <hyperlink ref="R4" r:id="rId3" xr:uid="{E2FF5602-F83D-4D36-A856-5B977B2C106E}"/>
+    <hyperlink ref="R6" r:id="rId4" display="https://trt2-jus-br.zoom.us/j/81264440862?pwd=fO1DbCbSfbmcUakkvweGCngdmimhP9.1%20ID%20da%20reunião:%20812%206444%200862%20Senha%20de%20acesso:%20028055" xr:uid="{86A89871-70E3-4EBD-B7A2-96932FE31AA1}"/>
+    <hyperlink ref="R7" r:id="rId5" display="https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09%20ID%20da%20reunião:%20821%208299%201000%20Senha%20de%20acesso:%20060642" xr:uid="{A1CE2ED2-EFC6-4C1D-BF3B-A466965CCA0D}"/>
+    <hyperlink ref="R8" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{5A570A1E-53C3-4869-A094-92FEE3ED0443}"/>
+    <hyperlink ref="R9" r:id="rId7" display="https://trt2-jus-br.zoom.us/j/85009685110?pwd=Ah1Tp4Y85y3TcszzhnGcAvN0FrOuF6.1%20ID%20da%20reunião:%20850%200968%205110w%20Senha%20de%20acesso:%20345889" xr:uid="{1B93FD83-0BCA-4A4B-B5D8-5555A173C4E1}"/>
+    <hyperlink ref="R10" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{ABA2A479-67C5-4D85-8BBD-103B668266E9}"/>
+    <hyperlink ref="R11" r:id="rId9" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{D560530E-A72F-4BF1-99AB-2A1768240D3B}"/>
+    <hyperlink ref="R12" r:id="rId10" xr:uid="{ACD4E080-F192-45DC-8483-512BF768BFB4}"/>
+    <hyperlink ref="R15" r:id="rId11" xr:uid="{6D35CE3C-C1FB-49BB-9153-14806E2B951E}"/>
+    <hyperlink ref="R16" r:id="rId12" display="https://trt15-jus-br.zoom.us/j/83921225378?pwd=YhypVdE7UmYb8yS9ShDzir1DtTYXqh.1%20ID%20da%20reunião:%20839%202122%205378%20Senha:%20520497" xr:uid="{FFD4D435-9118-4D64-82D6-6B13F22D9310}"/>
+    <hyperlink ref="R17" r:id="rId13" display="https://trt2-jus-br.zoom.us/j/88959116257?pwd=Q09WTmd6SnZibUUrZWxMSFdiRm9tUT09%20ID%20da%20reunião:%20889%205911%206257%20Senha%20de%20acesso:%20136898" xr:uid="{1B968B48-168E-4AED-B20F-EB1C264FC151}"/>
+    <hyperlink ref="R18" r:id="rId14" xr:uid="{D1FF1ED4-0C91-4BA0-AE5B-C185147FA70E}"/>
+    <hyperlink ref="R19" r:id="rId15" xr:uid="{2FEB939D-E90B-4F3A-8728-E70538DC27C2}"/>
+    <hyperlink ref="R20" r:id="rId16" display="mailto:vs.rocha@hotmail.com" xr:uid="{E27BE3CC-0A25-4D1F-8225-97C5C5FA001F}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peixotoecuryadv-my.sharepoint.com/personal/blu_peixotoecury_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83F675F7-239A-4454-8121-5D9A8386F7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDC202D-505B-4DB3-9CC0-97F21ADC752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{882225A2-E4F3-4ADF-913D-09EB867047ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1CC5714-94CC-4D0C-AD10-3598BE313F79}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="195">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,337 +95,535 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010940-21.2025.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Edvanio Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               72.310,02</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0012114-81.2024.5.15.0132</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Ronnie Anderson Benedito</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>04ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal TRT</t>
+  </si>
+  <si>
+    <t>R$             671.139,88</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/82717131621?pwd=pODkGMMik6OAPMNpdT855vizOcYdKQ.1 iD da reunião: 827 1713 1621 Senha: 761332</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1000658-10.2026.5.02.0262</t>
+  </si>
+  <si>
+    <t>Msa Do Brasil Equip E Instrumentos De Seguranca Ltda.</t>
+  </si>
+  <si>
+    <t>Sara Francisca Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>14ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$               42.898,20</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/87449545935?pwd=wCgGe2V8ntb7v8A97BI4itvBX6i0Ya.1 ID da reunião: 874 4954 5935 Senha de acesso: 047941</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1000978-35.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Lucas Figueiredo Saturnino</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             863.640,00</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1001287-79.2026.5.02.0004</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Marcia Valeria Brandao De Mello Cucco Pereira</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.958.789,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/83934068085?pwd=vsilyvu3m7bMldNPplkinUYQRGR2Xz.1 ID da reunião: 839 3406 8085 Senha de acesso: 359721</t>
+  </si>
+  <si>
+    <t>0010417-48.2026.5.03.0048</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Samuel Henrique Saturnino</t>
+  </si>
+  <si>
+    <t>ITURAMA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             556.517,03</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.iturama</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011252-18.2025.5.15.0022</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Jailton Aparecido De Souza Senne</t>
+  </si>
+  <si>
+    <t>MOGI MIRIM</t>
+  </si>
+  <si>
+    <t>R$             212.312,95</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>0011298-88.2025.5.15.0092</t>
+  </si>
+  <si>
+    <t>Waldemar Da Silva Filho</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             210.000,00</t>
+  </si>
+  <si>
+    <t>Correspondente - Daniela Prandi</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0000949-91.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participacoes S.A.</t>
-  </si>
-  <si>
-    <t>Cosmo Alves Da Silva</t>
-  </si>
-  <si>
-    <t>QUIRINÓPOLIS</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$                       38.688,52</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
+    <t>0000309-08.2026.5.09.0657</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Jean Gilbert Dos Santos</t>
+  </si>
+  <si>
+    <t>COLOMBO</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               73.000,00</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/xx0w9 ID da reunião: 82127329940 Senha de acesso: W0FBQYvT0q</t>
+  </si>
+  <si>
+    <t>0011763-13.2026.5.15.0044</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Matheus Felipe Januario Domingues</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>R$             356.093,25</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
+  </si>
+  <si>
+    <t>0010974-59.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Ronilson Rodrigues De Souza</t>
+  </si>
+  <si>
+    <t>R$             135.668,67</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09 ID da reunião: 833 5206 5501 Senha de acesso: 368465</t>
+  </si>
+  <si>
+    <t>0010719-78.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Gleydson Freitas Sousa</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             117.254,25</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0010708-49.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Gustavo Martins Montandon</t>
+  </si>
+  <si>
+    <t>R$               70.920,29</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1000249-72.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Eraldo Joao Pimentel</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$             137.570,07</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>1001385-17.2023.5.02.0086</t>
+  </si>
+  <si>
+    <t>Rodrigo Da Silva Pareschi</t>
+  </si>
+  <si>
+    <t>10ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             240.242,94</t>
   </si>
   <si>
     <t>RCF</t>
   </si>
   <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
-  </si>
-  <si>
-    <t>0000943-84.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Jose Carlos Do Nascimento</t>
-  </si>
-  <si>
-    <t>R$                       40.220,45</t>
+    <t>Presencial | https://trt2-jus-br.zoom.us/j/89651014670?pwd=FW0AFzyGa5XXc5LOiaXNalueDYjcGW.1 ID da reunião: 896 5101 4670 Senha de acesso: 729254</t>
+  </si>
+  <si>
+    <t>0011639-51.2026.5.03.0048</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda</t>
+  </si>
+  <si>
+    <t>Julio Cesar Mulina</t>
+  </si>
+  <si>
+    <t>ARAXÁ</t>
+  </si>
+  <si>
+    <t>R$             144.023,89</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001792-72.2025.5.02.0435</t>
+  </si>
+  <si>
+    <t>Ricardo Aparecido De Lima</t>
+  </si>
+  <si>
+    <t>11ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             242.576,46</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0010227-28.2025.5.15.0132</t>
+  </si>
+  <si>
+    <t>Alexandre Leite Da Silva</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             253.000,00</t>
+  </si>
+  <si>
+    <t>0010641-40.2026.5.15.0019</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Ricardo Francisco De Almeida</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             227.571,64</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09 ID da reunião: 839 0807 6312 Senha de acesso: 248026</t>
+  </si>
+  <si>
+    <t>0010218-66.2025.5.15.0132</t>
+  </si>
+  <si>
+    <t>R$             140.841,42</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>0010555-69.2026.5.15.0019</t>
+  </si>
+  <si>
+    <t>Marcos Lima Moreira</t>
+  </si>
+  <si>
+    <t>R$             187.618,69</t>
+  </si>
+  <si>
+    <t>0001510-51.2025.5.12.0054</t>
+  </si>
+  <si>
+    <t>Pilkington Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Leonardo Jose Vivas Castillejo</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               42.832,25</t>
+  </si>
+  <si>
+    <t>https://trt12-jus-br.zoom.us/j/86949386199</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010813-79.2026.5.15.0019</t>
+  </si>
+  <si>
+    <t>Valdeir David De Souza</t>
+  </si>
+  <si>
+    <t>R$             144.381,80</t>
+  </si>
+  <si>
+    <t>0012756-50.2025.5.15.0025</t>
+  </si>
+  <si>
+    <t>Silmara Campos De Oliveira</t>
+  </si>
+  <si>
+    <t>BOTUCATU</t>
+  </si>
+  <si>
+    <t>R$             222.776,26</t>
   </si>
   <si>
     <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
-    <t>1001266-74.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Douglas Bernardo Santos</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                     128.884,72</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010455-22.2026.5.15.0082</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Doralice Da Silva Ferreira</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                     650.000,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09 ID da reunião: 818 6908 4210 Senha de acesso: 306523</t>
-  </si>
-  <si>
-    <t>0010095-88.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Tiago Firmino Dos Santos</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                     238.000,00</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/81715388288?pwd=UFAwUGVFQkN1bGNXcStQUEovR2VZUT09</t>
-  </si>
-  <si>
-    <t>0010810-37.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Itapagipe Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Miguel Oliveira Braz</t>
-  </si>
-  <si>
-    <t>FRUTAL</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>Ação de Consignação em Pagamento</t>
-  </si>
-  <si>
-    <t>R$                       10.795,94</t>
-  </si>
-  <si>
-    <t> MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010592-67.2026.5.15.0061</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Tiago Gomes Dos Santos</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                     232.079,12</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1001761-88.2025.5.02.0035</t>
-  </si>
-  <si>
-    <t>Willian Marcelino</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>35ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$                     573.120,80</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>0012042-69.2025.5.15.0032</t>
-  </si>
-  <si>
-    <t>Itw Ppf Brasil Adesivos Ltda.</t>
-  </si>
-  <si>
-    <t>Jose Victor Da Silva Pereira</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>R$                       13.880,81</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89978823106?pwd=TlFNRkViSE1yUjJyWjUvY2hSd2lVUT09 ID da reunião: 899 7882 3106 Senha: 112233</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010690-03.2026.5.15.0045</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Carlos Ulisses De Almeida</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$                     111.462,89</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81965031150?pwd=OG5KcVh3WVFncjA5SWhDTDRrb3E2QT09 ID: 819 6503 1150 Senha: 351446 - Preposto: Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000469-73.2026.5.10.0861</t>
-  </si>
-  <si>
-    <t>Pedro Afonso Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Marizete Rodrigues Torres</t>
-  </si>
-  <si>
-    <t>GUARAÍ</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>Conciliação</t>
-  </si>
-  <si>
-    <t>R$                         6.001,59</t>
-  </si>
-  <si>
-    <t>https://trt10-jus-br.zoom.us/j/6334644559</t>
-  </si>
-  <si>
-    <t>1001034-62.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Guilherme Arenghi</t>
-  </si>
-  <si>
-    <t>R$                       31.203,97</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001188-78.2026.5.02.0467</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Rita De Cassia Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>07ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$                       39.364,65</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>TLI</t>
+    <t>0010992-15.2026.5.15.0083</t>
+  </si>
+  <si>
+    <t>Fabiano Benedito Ribeiro</t>
+  </si>
+  <si>
+    <t>R$             157.090,00</t>
+  </si>
+  <si>
+    <t>VCR</t>
   </si>
 </sst>
 </file>
@@ -903,11 +1101,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20669F14-8D00-4D50-8AA2-3B7681DDCFEF}">
-  <dimension ref="A1:R14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{196F33B3-08C0-41F4-8779-9AF243AC5467}">
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="130" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,15 +1180,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105814</v>
+        <v>101561</v>
       </c>
       <c r="B2" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C2" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1019,39 +1236,39 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105813</v>
+        <v>99373</v>
       </c>
       <c r="B3" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C3" s="6">
-        <v>0.375</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1060,54 +1277,54 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105500</v>
+        <v>105315</v>
       </c>
       <c r="B4" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C4" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1116,54 +1333,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>104283</v>
+        <v>105046</v>
       </c>
       <c r="B5" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C5" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1172,54 +1389,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="P5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105811</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>104054</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46265</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.40972222222222221</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1228,110 +1445,110 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>105877</v>
+        <v>104382</v>
       </c>
       <c r="B7" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C7" s="6">
-        <v>0.54513888888888884</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>104931</v>
+        <v>101611</v>
       </c>
       <c r="B8" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C8" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.43194444444444446</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="K8" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1340,54 +1557,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="R8" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>101555</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>103266</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46265</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1396,54 +1613,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>103794</v>
+        <v>104422</v>
       </c>
       <c r="B10" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C10" s="6">
-        <v>0.55555555555555558</v>
+        <v>0.45277777777777778</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1452,54 +1669,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>104623</v>
+        <v>105365</v>
       </c>
       <c r="B11" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C11" s="6">
-        <v>0.5625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1508,110 +1725,110 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>105574</v>
+        <v>105375</v>
       </c>
       <c r="B12" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C12" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105186</v>
+        <v>105389</v>
       </c>
       <c r="B13" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C13" s="6">
-        <v>0.61111111111111116</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1620,54 +1837,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105634</v>
+        <v>105331</v>
       </c>
       <c r="B14" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C14" s="6">
-        <v>0.68055555555555558</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>120</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>122</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="J14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1676,32 +1893,711 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="Q14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R14" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>47</v>
+    </row>
+    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>104242</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>101265</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>105778</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>102783</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.5625</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>99942</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>105069</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>99870</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>105173</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>102767</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>105441</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.60555555555555551</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>105847</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>104977</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46266</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{C9190C39-CA9A-4ABB-9C1C-AD98FA321DD5}"/>
-    <hyperlink ref="R3" r:id="rId2" xr:uid="{4F6A4EEF-8A6F-4ABE-94F7-BF81531B5040}"/>
-    <hyperlink ref="R5" r:id="rId3" display="https://trt15-jus-br.zoom.us/j/81869084210?pwd=V0EwalRCY0V5ZFhUY0lCMEU1QVBJQT09%20ID%20da%20reunião:%20818%206908%204210%20Senha%20de%20acesso:%20306523" xr:uid="{D27B1D90-2F74-4FD0-816F-6D7266A3F711}"/>
-    <hyperlink ref="R6" r:id="rId4" xr:uid="{834CC90E-942F-4E41-9C64-E740868A639C}"/>
-    <hyperlink ref="R7" r:id="rId5" xr:uid="{7796BE1C-FE79-41A2-9DD3-0810F9DFE1D0}"/>
-    <hyperlink ref="R8" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{BB1C6E94-B4E6-47A8-BD57-424D8A4B9F57}"/>
-    <hyperlink ref="R10" r:id="rId7" display="https://trt15-jus-br.zoom.us/j/89978823106?pwd=TlFNRkViSE1yUjJyWjUvY2hSd2lVUT09%20ID%20da%20reunião:%20899%207882%203106%20Senha:%20112233" xr:uid="{F48BAFCE-0E97-4ADD-B998-EAF7F5138387}"/>
-    <hyperlink ref="R11" r:id="rId8" display="https://us02web.zoom.us/j/81965031150?pwd=OG5KcVh3WVFncjA5SWhDTDRrb3E2QT09%20ID:%20819%206503%201150%20Senha:%20351446%20-%20Preposto:%20Correspondente%20-%20Hebert" xr:uid="{341F6CF5-2499-4125-85AA-86BCB476064D}"/>
-    <hyperlink ref="R12" r:id="rId9" xr:uid="{EF469F9B-93A4-4F57-A5BB-A01CB60FCF84}"/>
+    <hyperlink ref="R2" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{8D689261-A6BE-494D-9C3C-A54ACE6B562B}"/>
+    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/82717131621?pwd=pODkGMMik6OAPMNpdT855vizOcYdKQ.1%20iD%20da%20reunião:%20827%201713%201621%20Senha:%20761332" xr:uid="{70B921AB-E3D1-4594-9320-9F10D6B32A82}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://trt2-jus-br.zoom.us/j/87449545935?pwd=wCgGe2V8ntb7v8A97BI4itvBX6i0Ya.1%20ID%20da%20reunião:%20874%204954%205935%20Senha%20de%20acesso:%20047941" xr:uid="{730BBD45-D7BD-4EC9-8257-F4BA3663EBFA}"/>
+    <hyperlink ref="R6" r:id="rId4" display="https://trt2-jus-br.zoom.us/j/83934068085?pwd=vsilyvu3m7bMldNPplkinUYQRGR2Xz.1%20ID%20da%20reunião:%20839%203406%208085%20Senha%20de%20acesso:%20359721" xr:uid="{C2EC9EAD-6678-4EF6-90BE-AEFBE0085A0D}"/>
+    <hyperlink ref="R7" r:id="rId5" xr:uid="{43731B18-E42F-46D2-8A68-CF18DB233278}"/>
+    <hyperlink ref="R10" r:id="rId6" xr:uid="{F12C266A-23D0-4642-8C4C-28A921164996}"/>
+    <hyperlink ref="R11" r:id="rId7" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{C4E791E1-5919-48B1-9A63-6CF826D68207}"/>
+    <hyperlink ref="R12" r:id="rId8" display="https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09%20ID%20da%20reunião:%20833%205206%205501%20Senha%20de%20acesso:%20368465" xr:uid="{12460121-9F59-4D5B-A10A-07D590EC3A5E}"/>
+    <hyperlink ref="R13" r:id="rId9" xr:uid="{4DD08ADD-D135-4263-979E-6D8C2089F4FE}"/>
+    <hyperlink ref="R14" r:id="rId10" xr:uid="{CD24E493-B451-4B64-A644-902CDE18A4EB}"/>
+    <hyperlink ref="R16" r:id="rId11" display="https://trt2-jus-br.zoom.us/j/89651014670?pwd=FW0AFzyGa5XXc5LOiaXNalueDYjcGW.1" xr:uid="{2C9F0EDD-D834-4CB9-8061-0E56DF462839}"/>
+    <hyperlink ref="R17" r:id="rId12" xr:uid="{F3FB26E2-B13C-4E77-9C9F-08B878B92941}"/>
+    <hyperlink ref="R20" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{6FD5EE01-87B2-4E0E-815B-1933C9C47DA8}"/>
+    <hyperlink ref="R22" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{6BD86EEA-E27E-4433-9555-67EB5F2DEC2B}"/>
+    <hyperlink ref="R23" r:id="rId15" xr:uid="{7879208E-C822-4031-AE76-6F815C47568B}"/>
+    <hyperlink ref="R24" r:id="rId16" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{AD29B6A5-5445-43F1-80DD-59DA7ECE936C}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peixotoecuryadv-my.sharepoint.com/personal/blu_peixotoecury_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDC202D-505B-4DB3-9CC0-97F21ADC752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D90EC3-1F8C-4661-99C7-443C7A87E8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1CC5714-94CC-4D0C-AD10-3598BE313F79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4A46497-76E1-4CB4-87CA-D8B4BC75C853}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="188">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,542 +95,521 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>0011041-26.2026.5.03.0104</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Ariel Da Silva Amorim</t>
+  </si>
+  <si>
+    <t>UBERLÂNDIA</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             102.839,56</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Gabriela Viana, (34) 99135-5994 | Preposta - Sanyla Araujo Gomes, CPF 113.901.946-55, (34) 99155-5119</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0000740-70.2026.5.09.0195</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Julio Cezar Zanella Porto</t>
+  </si>
+  <si>
+    <t>CASCAVEL</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$             549.600,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>link pendente</t>
+  </si>
+  <si>
+    <t>1001128-79.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Ana Cristina Suzana De Souza Araujo</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             140.645,39</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>1001760-73.2025.5.02.0433</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Jonathan Henrique Da Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             491.829,02</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011547-30.2026.5.03.0030</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Wemerson Henrique Dos Santos</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
+  </si>
+  <si>
+    <t>R$               32.440,05</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/j/4023578726</t>
+  </si>
+  <si>
     <t>Audiência Instrução - Telepresencial</t>
   </si>
   <si>
-    <t>0010940-21.2025.5.15.0126</t>
+    <t>0000014-06.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>Douglas Rodrigo Dos Santos</t>
+  </si>
+  <si>
+    <t>R$             567.600,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/smdbp ID da Reunião: 87520843356 Senha: NYGaKNnDl3</t>
+  </si>
+  <si>
+    <t>1001155-34.2025.5.02.0464</t>
+  </si>
+  <si>
+    <t>Sandra De Almeida Salvador</t>
+  </si>
+  <si>
+    <t>SÃO BERNARDO DO CAMPO</t>
+  </si>
+  <si>
+    <t>R$               91.657,11</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Presencial | Advogado - Dr. Sergio Luis, (11) 95551-2594 | Preposta - Valdenice Maria Pereira (11) 98073-5101</t>
+  </si>
+  <si>
+    <t>0011002-27.2026.5.15.0126</t>
   </si>
   <si>
     <t>Syngenta Proteção De Cultivos Ltda.</t>
   </si>
   <si>
-    <t>Edvanio Dos Santos Silva</t>
+    <t>Joao Leandro Da Conceicao Filho</t>
   </si>
   <si>
     <t>PAULÍNIA</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$               72.310,02</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>R$               55.155,49</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09 ID da reunião: 833 5206 5501 Senha de acesso: 368465</t>
+  </si>
+  <si>
+    <t>0010638-32.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes</t>
+  </si>
+  <si>
+    <t>Gilmar Martins</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$             200.328,74</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>0010639-17.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda</t>
+  </si>
+  <si>
+    <t>Maria Terezinha Bom</t>
+  </si>
+  <si>
+    <t>R$             300.002,77</t>
+  </si>
+  <si>
+    <t>0010640-02.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Orlando Santana De Souza</t>
+  </si>
+  <si>
+    <t>1001489-30.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Leonardo Da Silva</t>
+  </si>
+  <si>
+    <t>R$             317.496,66</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>0010641-84.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Eronalto Jose De Sousa</t>
+  </si>
+  <si>
+    <t>R$             230.228,47</t>
+  </si>
+  <si>
+    <t>0010642-69.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Leonardo Mendes De Freitas</t>
+  </si>
+  <si>
+    <t>0010934-83.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Guariroba Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Osvaldo Aparecido Correia Sales</t>
+  </si>
+  <si>
+    <t>VOTUPORANGA</t>
+  </si>
+  <si>
+    <t>R$          2.843.098,39</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
+  </si>
+  <si>
+    <t>0010936-53.2026.5.15.0027</t>
+  </si>
+  <si>
+    <t>Luciana De Oliveira Souza</t>
+  </si>
+  <si>
+    <t>R$               70.542,88</t>
+  </si>
+  <si>
+    <t>Audiência Una- Telepresencial</t>
+  </si>
+  <si>
+    <t>0011041-24.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Ezildo Tobias Idelfonso</t>
+  </si>
+  <si>
+    <t>R$                 7.101,74</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0011637-76.2024.5.15.0126</t>
+  </si>
+  <si>
+    <t>Gabriel Marques De Lima</t>
+  </si>
+  <si>
+    <t>CEJUSC 2º GRAU</t>
+  </si>
+  <si>
+    <t>2ª Instância</t>
+  </si>
+  <si>
+    <t>R$             216.022,11</t>
   </si>
   <si>
     <t>JRM</t>
   </si>
   <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09 ID da reunião: 997 370 0634 Senha: 592209</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0012114-81.2024.5.15.0132</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Ronnie Anderson Benedito</t>
+    <t>bit.ly/cejusc2grau</t>
+  </si>
+  <si>
+    <t>0011055-80.2025.5.15.0081</t>
+  </si>
+  <si>
+    <t>Ana Claudia Garcia</t>
+  </si>
+  <si>
+    <t>MATÃO</t>
+  </si>
+  <si>
+    <t>R$               84.809,98</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>1001311-78.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Flavio Jose Antunes De Sousa</t>
+  </si>
+  <si>
+    <t>R$             190.753,38</t>
+  </si>
+  <si>
+    <t>0011027-94.2025.5.15.0087</t>
+  </si>
+  <si>
+    <t>Deivson Nunes Chaves</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               29.332,49</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (19) 99949-8727</t>
+  </si>
+  <si>
+    <t>0011795-54.2024.5.15.0087</t>
+  </si>
+  <si>
+    <t>Jose Ailson Aquino Conceicao</t>
+  </si>
+  <si>
+    <t>R$               44.661,74</t>
+  </si>
+  <si>
+    <t>0011108-44.2021.5.15.0132</t>
+  </si>
+  <si>
+    <t>Yaborã Indústria Aeronáutica S.A.</t>
+  </si>
+  <si>
+    <t>Claudio Roberto Martins</t>
   </si>
   <si>
     <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal TRT</t>
-  </si>
-  <si>
-    <t>R$             671.139,88</t>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$               98.413,55</t>
   </si>
   <si>
     <t>Grupo B2</t>
   </si>
   <si>
-    <t>GSM</t>
-  </si>
-  <si>
     <t>BCF</t>
   </si>
   <si>
-    <t>https://trt15-jus-br.zoom.us/j/82717131621?pwd=pODkGMMik6OAPMNpdT855vizOcYdKQ.1 iD da reunião: 827 1713 1621 Senha: 761332</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>1000658-10.2026.5.02.0262</t>
-  </si>
-  <si>
-    <t>Msa Do Brasil Equip E Instrumentos De Seguranca Ltda.</t>
-  </si>
-  <si>
-    <t>Sara Francisca Dos Santos</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>14ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$               42.898,20</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/87449545935?pwd=wCgGe2V8ntb7v8A97BI4itvBX6i0Ya.1 ID da reunião: 874 4954 5935 Senha de acesso: 047941</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1000978-35.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Lucas Figueiredo Saturnino</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             863.640,00</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>1001287-79.2026.5.02.0004</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Marcia Valeria Brandao De Mello Cucco Pereira</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.958.789,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/83934068085?pwd=vsilyvu3m7bMldNPplkinUYQRGR2Xz.1 ID da reunião: 839 3406 8085 Senha de acesso: 359721</t>
-  </si>
-  <si>
-    <t>0010417-48.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Samuel Henrique Saturnino</t>
-  </si>
-  <si>
-    <t>ITURAMA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             556.517,03</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.iturama</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0011252-18.2025.5.15.0022</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Jailton Aparecido De Souza Senne</t>
-  </si>
-  <si>
-    <t>MOGI MIRIM</t>
-  </si>
-  <si>
-    <t>R$             212.312,95</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>0011298-88.2025.5.15.0092</t>
-  </si>
-  <si>
-    <t>Waldemar Da Silva Filho</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             210.000,00</t>
-  </si>
-  <si>
-    <t>Correspondente - Daniela Prandi</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000309-08.2026.5.09.0657</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Jean Gilbert Dos Santos</t>
-  </si>
-  <si>
-    <t>COLOMBO</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               73.000,00</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/xx0w9 ID da reunião: 82127329940 Senha de acesso: W0FBQYvT0q</t>
-  </si>
-  <si>
-    <t>0011763-13.2026.5.15.0044</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Matheus Felipe Januario Domingues</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>R$             356.093,25</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09 ID DA REUNIÃO: 817 5724 3738 SENHA: 954332</t>
-  </si>
-  <si>
-    <t>0010974-59.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Ronilson Rodrigues De Souza</t>
-  </si>
-  <si>
-    <t>R$             135.668,67</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09 ID da reunião: 833 5206 5501 Senha de acesso: 368465</t>
-  </si>
-  <si>
-    <t>0010719-78.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Gleydson Freitas Sousa</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             117.254,25</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0010708-49.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Gustavo Martins Montandon</t>
-  </si>
-  <si>
-    <t>R$               70.920,29</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1000249-72.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Eraldo Joao Pimentel</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>R$             137.570,07</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>1001385-17.2023.5.02.0086</t>
-  </si>
-  <si>
-    <t>Rodrigo Da Silva Pareschi</t>
-  </si>
-  <si>
-    <t>10ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             240.242,94</t>
-  </si>
-  <si>
-    <t>RCF</t>
-  </si>
-  <si>
-    <t>Presencial | https://trt2-jus-br.zoom.us/j/89651014670?pwd=FW0AFzyGa5XXc5LOiaXNalueDYjcGW.1 ID da reunião: 896 5101 4670 Senha de acesso: 729254</t>
-  </si>
-  <si>
-    <t>0011639-51.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda</t>
-  </si>
-  <si>
-    <t>Julio Cesar Mulina</t>
-  </si>
-  <si>
-    <t>ARAXÁ</t>
-  </si>
-  <si>
-    <t>R$             144.023,89</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1001792-72.2025.5.02.0435</t>
-  </si>
-  <si>
-    <t>Ricardo Aparecido De Lima</t>
-  </si>
-  <si>
-    <t>11ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             242.576,46</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0010227-28.2025.5.15.0132</t>
-  </si>
-  <si>
-    <t>Alexandre Leite Da Silva</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             253.000,00</t>
-  </si>
-  <si>
-    <t>0010641-40.2026.5.15.0019</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Ricardo Francisco De Almeida</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$             227.571,64</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09 ID da reunião: 839 0807 6312 Senha de acesso: 248026</t>
-  </si>
-  <si>
-    <t>0010218-66.2025.5.15.0132</t>
-  </si>
-  <si>
-    <t>R$             140.841,42</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>0010555-69.2026.5.15.0019</t>
-  </si>
-  <si>
-    <t>Marcos Lima Moreira</t>
-  </si>
-  <si>
-    <t>R$             187.618,69</t>
-  </si>
-  <si>
-    <t>0001510-51.2025.5.12.0054</t>
-  </si>
-  <si>
-    <t>Pilkington Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Leonardo Jose Vivas Castillejo</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               42.832,25</t>
-  </si>
-  <si>
-    <t>https://trt12-jus-br.zoom.us/j/86949386199</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010813-79.2026.5.15.0019</t>
-  </si>
-  <si>
-    <t>Valdeir David De Souza</t>
-  </si>
-  <si>
-    <t>R$             144.381,80</t>
-  </si>
-  <si>
-    <t>0012756-50.2025.5.15.0025</t>
-  </si>
-  <si>
-    <t>Silmara Campos De Oliveira</t>
-  </si>
-  <si>
-    <t>BOTUCATU</t>
-  </si>
-  <si>
-    <t>R$             222.776,26</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>0010992-15.2026.5.15.0083</t>
-  </si>
-  <si>
-    <t>Fabiano Benedito Ribeiro</t>
-  </si>
-  <si>
-    <t>R$             157.090,00</t>
-  </si>
-  <si>
     <t>VCR</t>
+  </si>
+  <si>
+    <t>1000239-56.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Valdeci Barbosa Goncalves</t>
+  </si>
+  <si>
+    <t>R$          1.157.821,02</t>
+  </si>
+  <si>
+    <t>0010496-08.2025.5.15.0087</t>
+  </si>
+  <si>
+    <t>Wellington Sousa Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               78.161,59</t>
+  </si>
+  <si>
+    <t>0001328-93.2026.5.18.0141</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Joarez Rodrigues Da Silva</t>
+  </si>
+  <si>
+    <t>CATALÃO</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$               67.077,08</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.tarde</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>1002610-57.2025.5.02.0521</t>
+  </si>
+  <si>
+    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
+  </si>
+  <si>
+    <t>Moises Mantoani De Amorim</t>
+  </si>
+  <si>
+    <t>ARUJÁ</t>
+  </si>
+  <si>
+    <t>R$             215.958,87</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81381532305?pwd=Zprq03uth1fKfxUiDb1GGLAiRaUFP1.1 ID da reunião: 813 8153 2305 Senha de acesso: vtaruja01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,14 +629,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -737,11 +708,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,12 +734,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1101,17 +1067,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{196F33B3-08C0-41F4-8779-9AF243AC5467}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4768B6-04E8-4042-90AB-3B525CA52E07}">
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -1121,10 +1087,10 @@
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="130" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="99.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1180,15 +1146,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>101561</v>
+        <v>105282</v>
       </c>
       <c r="B2" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C2" s="6">
-        <v>0.3888888888888889</v>
+        <v>0.33680555555555558</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1232,19 +1198,19 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>99373</v>
+        <v>105021</v>
       </c>
       <c r="B3" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C3" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1262,13 +1228,13 @@
         <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>26</v>
@@ -1277,33 +1243,33 @@
         <v>27</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R3" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105315</v>
+        <v>105693</v>
       </c>
       <c r="B4" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C4" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>46</v>
@@ -1318,13 +1284,13 @@
         <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1344,19 +1310,19 @@
       <c r="Q4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105046</v>
+        <v>102213</v>
       </c>
       <c r="B5" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C5" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.375</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>56</v>
@@ -1374,13 +1340,13 @@
         <v>60</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1389,54 +1355,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105811</v>
+        <v>105844</v>
       </c>
       <c r="B6" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C6" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.39930555555555558</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1445,54 +1411,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>104382</v>
+        <v>103718</v>
       </c>
       <c r="B7" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C7" s="6">
-        <v>0.4236111111111111</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1501,54 +1467,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>101777</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R7" s="8" t="s">
+      <c r="F8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
-        <v>101611</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="I8" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1557,54 +1523,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105427</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>101555</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1613,54 +1579,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>105190</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="Q9" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>104422</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45277777777777778</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1669,54 +1635,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>105192</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>105365</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1725,54 +1691,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>105375</v>
+        <v>105189</v>
       </c>
       <c r="B12" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C12" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1781,54 +1747,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105389</v>
+        <v>105702</v>
       </c>
       <c r="B13" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C13" s="6">
-        <v>0.46527777777777779</v>
+        <v>0.51736111111111116</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1837,54 +1803,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105331</v>
+        <v>105188</v>
       </c>
       <c r="B14" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C14" s="6">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1893,54 +1859,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>104242</v>
+        <v>105193</v>
       </c>
       <c r="B15" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C15" s="6">
-        <v>0.49305555555555558</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1949,27 +1915,27 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>101265</v>
+        <v>105522</v>
       </c>
       <c r="B16" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C16" s="6">
         <v>0.54166666666666663</v>
@@ -1978,25 +1944,25 @@
         <v>33</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2005,54 +1971,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105778</v>
+        <v>105516</v>
       </c>
       <c r="B17" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C17" s="6">
-        <v>0.5625</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2061,54 +2027,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>102783</v>
+        <v>105473</v>
       </c>
       <c r="B18" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C18" s="6">
-        <v>0.5625</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2117,54 +2083,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>99942</v>
+        <v>99369</v>
       </c>
       <c r="B19" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C19" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.56527777777777777</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2173,54 +2139,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R19" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>105069</v>
+        <v>101708</v>
       </c>
       <c r="B20" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C20" s="6">
-        <v>0.60069444444444442</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2229,54 +2195,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>99870</v>
+        <v>105553</v>
       </c>
       <c r="B21" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C21" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.56944444444444442</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2285,54 +2251,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>105173</v>
+        <v>101660</v>
       </c>
       <c r="B22" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C22" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.63194444444444442</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2341,54 +2307,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>102767</v>
+        <v>99530</v>
       </c>
       <c r="B23" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C23" s="6">
-        <v>0.60416666666666663</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2397,54 +2363,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>105441</v>
+        <v>93668</v>
       </c>
       <c r="B24" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C24" s="6">
-        <v>0.60555555555555551</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2453,54 +2419,54 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="R24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>104038</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>105847</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46266</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.625</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="F25" s="7" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2509,54 +2475,54 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="R25" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>104977</v>
+        <v>100398</v>
       </c>
       <c r="B26" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C26" s="6">
         <v>0.65277777777777779</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>26</v>
@@ -2565,39 +2531,148 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>194</v>
+        <v>30</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>64</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>105613</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>103473</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" display="https://trt15-jus-br.zoom.us/j/9973700634?pwd=dENDekhCNjFLekRnSExiTzhmK1VLdz09%20ID%20da%20reunião:%20997%20370%200634%20Senha:%20592209" xr:uid="{8D689261-A6BE-494D-9C3C-A54ACE6B562B}"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://trt15-jus-br.zoom.us/j/82717131621?pwd=pODkGMMik6OAPMNpdT855vizOcYdKQ.1%20iD%20da%20reunião:%20827%201713%201621%20Senha:%20761332" xr:uid="{70B921AB-E3D1-4594-9320-9F10D6B32A82}"/>
-    <hyperlink ref="R4" r:id="rId3" display="https://trt2-jus-br.zoom.us/j/87449545935?pwd=wCgGe2V8ntb7v8A97BI4itvBX6i0Ya.1%20ID%20da%20reunião:%20874%204954%205935%20Senha%20de%20acesso:%20047941" xr:uid="{730BBD45-D7BD-4EC9-8257-F4BA3663EBFA}"/>
-    <hyperlink ref="R6" r:id="rId4" display="https://trt2-jus-br.zoom.us/j/83934068085?pwd=vsilyvu3m7bMldNPplkinUYQRGR2Xz.1%20ID%20da%20reunião:%20839%203406%208085%20Senha%20de%20acesso:%20359721" xr:uid="{C2EC9EAD-6678-4EF6-90BE-AEFBE0085A0D}"/>
-    <hyperlink ref="R7" r:id="rId5" xr:uid="{43731B18-E42F-46D2-8A68-CF18DB233278}"/>
-    <hyperlink ref="R10" r:id="rId6" xr:uid="{F12C266A-23D0-4642-8C4C-28A921164996}"/>
-    <hyperlink ref="R11" r:id="rId7" display="https://us02web.zoom.us/j/81757243738?pwd=UXAvdEpveHlrNU05M2ZsZnRrYy9Vdz09%20ID%20DA%20REUNIÃO:%20817%205724%203738%20SENHA:%20954332" xr:uid="{C4E791E1-5919-48B1-9A63-6CF826D68207}"/>
-    <hyperlink ref="R12" r:id="rId8" display="https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09%20ID%20da%20reunião:%20833%205206%205501%20Senha%20de%20acesso:%20368465" xr:uid="{12460121-9F59-4D5B-A10A-07D590EC3A5E}"/>
-    <hyperlink ref="R13" r:id="rId9" xr:uid="{4DD08ADD-D135-4263-979E-6D8C2089F4FE}"/>
-    <hyperlink ref="R14" r:id="rId10" xr:uid="{CD24E493-B451-4B64-A644-902CDE18A4EB}"/>
-    <hyperlink ref="R16" r:id="rId11" display="https://trt2-jus-br.zoom.us/j/89651014670?pwd=FW0AFzyGa5XXc5LOiaXNalueDYjcGW.1" xr:uid="{2C9F0EDD-D834-4CB9-8061-0E56DF462839}"/>
-    <hyperlink ref="R17" r:id="rId12" xr:uid="{F3FB26E2-B13C-4E77-9C9F-08B878B92941}"/>
-    <hyperlink ref="R20" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{6FD5EE01-87B2-4E0E-815B-1933C9C47DA8}"/>
-    <hyperlink ref="R22" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{6BD86EEA-E27E-4433-9555-67EB5F2DEC2B}"/>
-    <hyperlink ref="R23" r:id="rId15" xr:uid="{7879208E-C822-4031-AE76-6F815C47568B}"/>
-    <hyperlink ref="R24" r:id="rId16" display="https://trt15-jus-br.zoom.us/j/83908076312?pwd=VnVGRnpYWFZmZjFwN3k4eVpnYTNSZz09%20ID%20da%20reunião:%20839%200807%206312%20Senha%20de%20acesso:%20248026" xr:uid="{AD29B6A5-5445-43F1-80DD-59DA7ECE936C}"/>
+    <hyperlink ref="R6" r:id="rId1" xr:uid="{2C853BDA-615E-4AF9-ACFB-14664F3B8F6E}"/>
+    <hyperlink ref="R7" r:id="rId2" xr:uid="{35D62E18-A5DC-4199-AF6A-D429C9E98465}"/>
+    <hyperlink ref="R9" r:id="rId3" display="https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09%20ID%20da%20reunião:%20833%205206%205501%20Senha%20de%20acesso:%20368465" xr:uid="{DDAF2BDB-8CB9-4E45-971B-D005E4F56D75}"/>
+    <hyperlink ref="R10" r:id="rId4" xr:uid="{89835212-E73D-4C84-8CA6-9C779E354519}"/>
+    <hyperlink ref="R11" r:id="rId5" xr:uid="{F9B8EB36-6A15-45C6-94C8-A3D8943A2AB6}"/>
+    <hyperlink ref="R12" r:id="rId6" xr:uid="{5C7653E8-326C-48B9-B4D6-FA6077A4CF9A}"/>
+    <hyperlink ref="R14" r:id="rId7" xr:uid="{75DFD632-0AFA-4435-853C-A5FB9A5F80CE}"/>
+    <hyperlink ref="R15" r:id="rId8" xr:uid="{C957D60E-A457-4699-95B5-6198E743A2AC}"/>
+    <hyperlink ref="R16" r:id="rId9" xr:uid="{63C7FDDE-9DE6-490A-A92E-82121660D02E}"/>
+    <hyperlink ref="R17" r:id="rId10" xr:uid="{9443BDDC-0B87-441F-83C1-A45648560DD4}"/>
+    <hyperlink ref="R18" r:id="rId11" xr:uid="{9DFE4066-A762-4DE3-84B1-B2A66D5A3894}"/>
+    <hyperlink ref="R27" r:id="rId12" xr:uid="{807B206A-78B9-4CD8-8578-3E926F3947AD}"/>
+    <hyperlink ref="R28" r:id="rId13" display="https://trt2-jus-br.zoom.us/j/81381532305?pwd=Zprq03uth1fKfxUiDb1GGLAiRaUFP1.1%20ID%20da%20reunião:%20813%208153%202305%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{745C84A2-CD29-4354-980F-734B539DBE6F}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://peixotoecuryadv-my.sharepoint.com/personal/blu_peixotoecury_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D90EC3-1F8C-4661-99C7-443C7A87E8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51FD206F-829D-45CE-BD4B-500F835F5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4A46497-76E1-4CB4-87CA-D8B4BC75C853}"/>
+    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{061FD02A-F0B4-4626-B0D0-B4793BA7C286}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,61 +95,508 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Perícia Técnica</t>
+  </si>
+  <si>
+    <t>0010443-02.2026.5.15.0084</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Marcos Vinicius Da Silva Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             164.005,36</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>Iremos acompanhar</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0001645-75.2026.5.18.0211</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Maria Aparecida Pereira Da Silva</t>
+  </si>
+  <si>
+    <t>FORMOSA</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>R$               31.498,82</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/CEJUSCdigital.manha2 ID da reunião: 903 468 6962</t>
+  </si>
+  <si>
+    <t>0000959-38.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A.</t>
+  </si>
+  <si>
+    <t>Reginaldo Pereira Santos</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
+  </si>
+  <si>
+    <t>R$               29.450,02</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
+  </si>
+  <si>
+    <t>0000958-53.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A</t>
+  </si>
+  <si>
+    <t>Jose Cicero Da Silva</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               45.609,10</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>0000748-68.2026.5.19.0001</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda</t>
+  </si>
+  <si>
+    <t>Fernando Santana</t>
+  </si>
+  <si>
+    <t>MACEIÓ</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               37.300,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Raianny Yulle Rousan de Lucena Alexandre 82 9 99597231 adv.raiannyyulle@gmail.com</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010243-05.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Leandro Teixeira Soares</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>R$             162.021,59</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0000957-68.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Celma Aparecida Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               28.175,65</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000521-09.2026.5.07.0035</t>
+  </si>
+  <si>
+    <t>Simone Da Silva Mariano</t>
+  </si>
+  <si>
+    <t>ARACATI</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>R$               45.126,27</t>
+  </si>
+  <si>
+    <t>JRM</t>
+  </si>
+  <si>
+    <t>https://trt7-jus-br.zoom.us/j/81867554890?pwd=Q0hoOGxaajVCSS9WakV3VnFQZHlWQT0</t>
+  </si>
+  <si>
+    <t>1000248-24.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Murilo De Oliveira Correa</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             146.644,35</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0012906-54.2025.5.15.0082</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Morais Da Silva</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             210.000,00</t>
+  </si>
+  <si>
+    <t>https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09 ID da reunião: 821 8299 1000 Senha de acesso: 060642</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010625-61.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Espolio De Maria Claudete Teixeira Bergamii</t>
+  </si>
+  <si>
+    <t>R$               38.640,00</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Semipresencial</t>
+  </si>
+  <si>
+    <t>0012322-39.2023.5.15.0152</t>
+  </si>
+  <si>
+    <t>Dell Computadores Do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Vanessa Dos Santos Macedo</t>
+  </si>
+  <si>
+    <t>HORTOLÂNDIA</t>
+  </si>
+  <si>
+    <t>04ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             316.889,10</t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>ALF</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84629297969?pwd=r3nz47WDFpnMMSOdEQbkHHb6s2qCwW.1</t>
+  </si>
+  <si>
+    <t>Audiência Una - Semipresencial</t>
+  </si>
+  <si>
+    <t>1001055-73.2026.5.02.0002</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Cibele Martins Julio</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>R$          1.359.264,00</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>0011713-71.2024.5.15.0071</t>
+  </si>
+  <si>
+    <t>Claudemir Sergio Da Silva</t>
+  </si>
+  <si>
+    <t>R$               29.383,89</t>
+  </si>
+  <si>
+    <t>1000856-13.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Evandro Xavier De Arruda</t>
+  </si>
+  <si>
+    <t>SÃO CAETANO DO SUL</t>
+  </si>
+  <si>
+    <t>R$          3.267.980,00</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/83090135690?pwd=RmliNUV3VDFGS2htNk84dnFFc1c1dz09 ID da reunião: 830 9013 5690 Senha de acesso: 419796</t>
+  </si>
+  <si>
+    <t>1000827-69.2026.5.02.0432</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo Salgado</t>
+  </si>
+  <si>
+    <t>R$             322.306,74</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0012829-61.2025.5.15.0109</t>
+  </si>
+  <si>
+    <t>Umberto Aparecido Lima</t>
+  </si>
+  <si>
+    <t>SOROCABA</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$             856.425,61</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/82942004538?pwd=ZG1mUWNiUEdXN3JmWTFqcW9YdlBkQT09 ID da reunião: 829 4200 4538 Senha de acesso: 786979</t>
+  </si>
+  <si>
+    <t>0010664-73.2026.5.15.0087</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Antonio Francisco De Sousa</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>R$             147.855,33</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
+  </si>
+  <si>
     <t>Audiência Inicial -  Presencial</t>
   </si>
   <si>
-    <t>0011041-26.2026.5.03.0104</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Ariel Da Silva Amorim</t>
-  </si>
-  <si>
-    <t>UBERLÂNDIA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             102.839,56</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Gabriela Viana, (34) 99135-5994 | Preposta - Sanyla Araujo Gomes, CPF 113.901.946-55, (34) 99155-5119</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0000740-70.2026.5.09.0195</t>
+    <t>1001532-58.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Kennety Luiz Santos Silva</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             220.000,00</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1002002-35.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Anderson Lima Teles</t>
+  </si>
+  <si>
+    <t>03ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             166.182,19</t>
+  </si>
+  <si>
+    <t>0012187-87.2024.5.15.0056</t>
+  </si>
+  <si>
+    <t>Rio Paraná Energia S.A.</t>
+  </si>
+  <si>
+    <t>Alessandro Dos Santos Rodrigues</t>
+  </si>
+  <si>
+    <t>ANDRADINA</t>
+  </si>
+  <si>
+    <t>R$               80.000,00</t>
+  </si>
+  <si>
+    <t>0020454-84.2025.5.04.0261</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Maria Geovana Da Silva Zweibrucker</t>
+  </si>
+  <si>
+    <t>MONTENEGRO</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>01ª TURMA</t>
+  </si>
+  <si>
+    <t>R$             132.825,00</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>https://trt4-jus-br.zoom.us/j/8649257802?_x_zm_rtaid=eF1kvF5oTjO_AFaCI6_ZRw.1788530250450.93a0d0a5d29493b7247ae72b3f96b690&amp;_x_zm_rhtaid=657#success</t>
+  </si>
+  <si>
+    <t>0000049-63.2026.5.09.0128</t>
   </si>
   <si>
     <t>Companhia Act De Participações E Companhia Aix De Participações</t>
   </si>
   <si>
-    <t>Julio Cezar Zanella Porto</t>
+    <t>Edison Luiz Souza</t>
   </si>
   <si>
     <t>CASCAVEL</t>
@@ -158,451 +605,43 @@
     <t>PR</t>
   </si>
   <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$             549.600,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>TFR</t>
+    <t>R$               61.000,00</t>
   </si>
   <si>
     <t>VSI</t>
   </si>
   <si>
-    <t>link pendente</t>
-  </si>
-  <si>
-    <t>1001128-79.2026.5.02.0411</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Ana Cristina Suzana De Souza Araujo</t>
-  </si>
-  <si>
-    <t>RIBEIRÃO PIRES</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             140.645,39</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>1001760-73.2025.5.02.0433</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Jonathan Henrique Da Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             491.829,02</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011547-30.2026.5.03.0030</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Wemerson Henrique Dos Santos</t>
-  </si>
-  <si>
-    <t>CONTAGEM</t>
-  </si>
-  <si>
-    <t>R$               32.440,05</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/j/4023578726</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000014-06.2026.5.09.0128</t>
-  </si>
-  <si>
-    <t>Douglas Rodrigo Dos Santos</t>
-  </si>
-  <si>
-    <t>R$             567.600,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/smdbp ID da Reunião: 87520843356 Senha: NYGaKNnDl3</t>
-  </si>
-  <si>
-    <t>1001155-34.2025.5.02.0464</t>
-  </si>
-  <si>
-    <t>Sandra De Almeida Salvador</t>
-  </si>
-  <si>
-    <t>SÃO BERNARDO DO CAMPO</t>
-  </si>
-  <si>
-    <t>R$               91.657,11</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>Presencial | Advogado - Dr. Sergio Luis, (11) 95551-2594 | Preposta - Valdenice Maria Pereira (11) 98073-5101</t>
-  </si>
-  <si>
-    <t>0011002-27.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Joao Leandro Da Conceicao Filho</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$               55.155,49</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09 ID da reunião: 833 5206 5501 Senha de acesso: 368465</t>
-  </si>
-  <si>
-    <t>0010638-32.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes</t>
-  </si>
-  <si>
-    <t>Gilmar Martins</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$             200.328,74</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>0010639-17.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda</t>
-  </si>
-  <si>
-    <t>Maria Terezinha Bom</t>
-  </si>
-  <si>
-    <t>R$             300.002,77</t>
-  </si>
-  <si>
-    <t>0010640-02.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Orlando Santana De Souza</t>
-  </si>
-  <si>
-    <t>1001489-30.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Leonardo Da Silva</t>
-  </si>
-  <si>
-    <t>R$             317.496,66</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>0010641-84.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Eronalto Jose De Sousa</t>
-  </si>
-  <si>
-    <t>R$             230.228,47</t>
-  </si>
-  <si>
-    <t>0010642-69.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Leonardo Mendes De Freitas</t>
-  </si>
-  <si>
-    <t>0010934-83.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Guariroba Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Osvaldo Aparecido Correia Sales</t>
-  </si>
-  <si>
-    <t>VOTUPORANGA</t>
-  </si>
-  <si>
-    <t>R$          2.843.098,39</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82212757993?pwd=aSt4Q29rc0JRMnFXSTU0UzdCVVZyQT09</t>
-  </si>
-  <si>
-    <t>0010936-53.2026.5.15.0027</t>
-  </si>
-  <si>
-    <t>Luciana De Oliveira Souza</t>
-  </si>
-  <si>
-    <t>R$               70.542,88</t>
-  </si>
-  <si>
-    <t>Audiência Una- Telepresencial</t>
-  </si>
-  <si>
-    <t>0011041-24.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Ezildo Tobias Idelfonso</t>
-  </si>
-  <si>
-    <t>R$                 7.101,74</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0011637-76.2024.5.15.0126</t>
-  </si>
-  <si>
-    <t>Gabriel Marques De Lima</t>
-  </si>
-  <si>
-    <t>CEJUSC 2º GRAU</t>
-  </si>
-  <si>
-    <t>2ª Instância</t>
-  </si>
-  <si>
-    <t>R$             216.022,11</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>bit.ly/cejusc2grau</t>
-  </si>
-  <si>
-    <t>0011055-80.2025.5.15.0081</t>
-  </si>
-  <si>
-    <t>Ana Claudia Garcia</t>
-  </si>
-  <si>
-    <t>MATÃO</t>
-  </si>
-  <si>
-    <t>R$               84.809,98</t>
-  </si>
-  <si>
-    <t>TLI</t>
-  </si>
-  <si>
-    <t>1001311-78.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Flavio Jose Antunes De Sousa</t>
-  </si>
-  <si>
-    <t>R$             190.753,38</t>
-  </si>
-  <si>
-    <t>0011027-94.2025.5.15.0087</t>
-  </si>
-  <si>
-    <t>Deivson Nunes Chaves</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               29.332,49</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Eliane Mendes, (19) 99949-8727</t>
-  </si>
-  <si>
-    <t>0011795-54.2024.5.15.0087</t>
-  </si>
-  <si>
-    <t>Jose Ailson Aquino Conceicao</t>
-  </si>
-  <si>
-    <t>R$               44.661,74</t>
-  </si>
-  <si>
-    <t>0011108-44.2021.5.15.0132</t>
-  </si>
-  <si>
-    <t>Yaborã Indústria Aeronáutica S.A.</t>
-  </si>
-  <si>
-    <t>Claudio Roberto Martins</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$               98.413,55</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>BCF</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>1000239-56.2026.5.02.0434</t>
-  </si>
-  <si>
-    <t>Valdeci Barbosa Goncalves</t>
-  </si>
-  <si>
-    <t>R$          1.157.821,02</t>
-  </si>
-  <si>
-    <t>0010496-08.2025.5.15.0087</t>
-  </si>
-  <si>
-    <t>Wellington Sousa Dos Santos</t>
-  </si>
-  <si>
-    <t>R$               78.161,59</t>
-  </si>
-  <si>
-    <t>0001328-93.2026.5.18.0141</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Joarez Rodrigues Da Silva</t>
-  </si>
-  <si>
-    <t>CATALÃO</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>R$               67.077,08</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.tarde</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>1002610-57.2025.5.02.0521</t>
-  </si>
-  <si>
-    <t>Mahle Thermal And Fluid Systems Brazil Ltda.</t>
-  </si>
-  <si>
-    <t>Moises Mantoani De Amorim</t>
-  </si>
-  <si>
-    <t>ARUJÁ</t>
-  </si>
-  <si>
-    <t>R$             215.958,87</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/81381532305?pwd=Zprq03uth1fKfxUiDb1GGLAiRaUFP1.1 ID da reunião: 813 8153 2305 Senha de acesso: vtaruja01</t>
+    <t>https://url.trt9.jus.br/q9tfx ID da Reunião: 84067414281 Senha: fFgDgs9z6o</t>
+  </si>
+  <si>
+    <t>0010648-03.2026.5.15.0061</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Clebson Goncalves Da Silva</t>
+  </si>
+  <si>
+    <t>ARAÇATUBA</t>
+  </si>
+  <si>
+    <t>R$             195.038,09</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
+  </si>
+  <si>
+    <t>0000183-90.2026.5.09.0128</t>
+  </si>
+  <si>
+    <t>R$             205.600,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/hd5v1 ID da Reunião: 85709636455 Senha: fSqjWJtU8U</t>
   </si>
 </sst>
 </file>
@@ -1067,30 +1106,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4768B6-04E8-4042-90AB-3B525CA52E07}">
-  <dimension ref="A1:R28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C8FC89-9124-4A34-811C-1893FACB0BF4}">
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="99.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="124.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,15 +1185,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105282</v>
+        <v>104439</v>
       </c>
       <c r="B2" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C2" s="6">
-        <v>0.33680555555555558</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -1202,12 +1241,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105021</v>
+        <v>105629</v>
       </c>
       <c r="B3" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C3" s="6">
         <v>0.34722222222222221</v>
@@ -1258,18 +1297,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>105693</v>
+        <v>105826</v>
       </c>
       <c r="B4" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C4" s="6">
-        <v>0.375</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>46</v>
@@ -1284,13 +1323,13 @@
         <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1299,54 +1338,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>105825</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>102213</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="H5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1355,54 +1394,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>105361</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105844</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.39930555555555558</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="K6" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1411,54 +1450,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>97246</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>103718</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1467,54 +1506,54 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O7" s="7" t="s">
         <v>42</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="R7" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>101777</v>
+        <v>105824</v>
       </c>
       <c r="B8" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C8" s="6">
-        <v>0.40972222222222221</v>
+        <v>0.375</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>81</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
@@ -1523,54 +1562,54 @@
         <v>27</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>105573</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="F9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>105427</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>39</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1579,54 +1618,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>104022</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>105190</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1635,54 +1674,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="R10" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>103396</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>105192</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1691,54 +1730,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>105189</v>
+        <v>100360</v>
       </c>
       <c r="B12" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C12" s="6">
-        <v>0.5</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1747,54 +1786,54 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105702</v>
+        <v>96917</v>
       </c>
       <c r="B13" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C13" s="6">
-        <v>0.51736111111111116</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
@@ -1803,54 +1842,54 @@
         <v>27</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105188</v>
+        <v>105625</v>
       </c>
       <c r="B14" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C14" s="6">
-        <v>0.52083333333333337</v>
+        <v>0.40625</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1859,54 +1898,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>105193</v>
+        <v>98644</v>
       </c>
       <c r="B15" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C15" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1915,54 +1954,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="Q15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>104944</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46273</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>105522</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1971,54 +2010,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105516</v>
+        <v>104895</v>
       </c>
       <c r="B17" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C17" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.4201388888888889</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2027,54 +2066,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>105473</v>
+        <v>103165</v>
       </c>
       <c r="B18" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C18" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2083,54 +2122,54 @@
         <v>27</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>31</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>99369</v>
+        <v>104863</v>
       </c>
       <c r="B19" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C19" s="6">
-        <v>0.56527777777777777</v>
+        <v>0.44097222222222221</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2139,54 +2178,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>101708</v>
+        <v>105742</v>
       </c>
       <c r="B20" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C20" s="6">
-        <v>0.56597222222222221</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2195,54 +2234,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>105553</v>
+        <v>103123</v>
       </c>
       <c r="B21" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C21" s="6">
-        <v>0.56944444444444442</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2251,54 +2290,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>101660</v>
+        <v>99402</v>
       </c>
       <c r="B22" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C22" s="6">
-        <v>0.63194444444444442</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2307,54 +2346,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>99530</v>
+        <v>100489</v>
       </c>
       <c r="B23" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C23" s="6">
-        <v>0.63888888888888884</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2363,54 +2402,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>29</v>
+        <v>180</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>93668</v>
+        <v>103768</v>
       </c>
       <c r="B24" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C24" s="6">
-        <v>0.64583333333333337</v>
+        <v>0.59722222222222221</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2419,54 +2458,54 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>104038</v>
+        <v>105049</v>
       </c>
       <c r="B25" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C25" s="6">
-        <v>0.65277777777777779</v>
+        <v>0.60763888888888884</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>26</v>
@@ -2475,51 +2514,51 @@
         <v>27</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>64</v>
+        <v>196</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>112</v>
+        <v>196</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>100398</v>
+        <v>104017</v>
       </c>
       <c r="B26" s="5">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="C26" s="6">
-        <v>0.65277777777777779</v>
+        <v>0.625</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>25</v>
@@ -2531,148 +2570,39 @@
         <v>27</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>105613</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
-        <v>103473</v>
-      </c>
-      <c r="B28" s="5">
-        <v>46268</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="R28" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R6" r:id="rId1" xr:uid="{2C853BDA-615E-4AF9-ACFB-14664F3B8F6E}"/>
-    <hyperlink ref="R7" r:id="rId2" xr:uid="{35D62E18-A5DC-4199-AF6A-D429C9E98465}"/>
-    <hyperlink ref="R9" r:id="rId3" display="https://us02web.zoom.us/j/83352065501?pwd=Lzc2WUJGSVpVWmJyZjB3Y0NvUmJPZz09%20ID%20da%20reunião:%20833%205206%205501%20Senha%20de%20acesso:%20368465" xr:uid="{DDAF2BDB-8CB9-4E45-971B-D005E4F56D75}"/>
-    <hyperlink ref="R10" r:id="rId4" xr:uid="{89835212-E73D-4C84-8CA6-9C779E354519}"/>
-    <hyperlink ref="R11" r:id="rId5" xr:uid="{F9B8EB36-6A15-45C6-94C8-A3D8943A2AB6}"/>
-    <hyperlink ref="R12" r:id="rId6" xr:uid="{5C7653E8-326C-48B9-B4D6-FA6077A4CF9A}"/>
-    <hyperlink ref="R14" r:id="rId7" xr:uid="{75DFD632-0AFA-4435-853C-A5FB9A5F80CE}"/>
-    <hyperlink ref="R15" r:id="rId8" xr:uid="{C957D60E-A457-4699-95B5-6198E743A2AC}"/>
-    <hyperlink ref="R16" r:id="rId9" xr:uid="{63C7FDDE-9DE6-490A-A92E-82121660D02E}"/>
-    <hyperlink ref="R17" r:id="rId10" xr:uid="{9443BDDC-0B87-441F-83C1-A45648560DD4}"/>
-    <hyperlink ref="R18" r:id="rId11" xr:uid="{9DFE4066-A762-4DE3-84B1-B2A66D5A3894}"/>
-    <hyperlink ref="R27" r:id="rId12" xr:uid="{807B206A-78B9-4CD8-8578-3E926F3947AD}"/>
-    <hyperlink ref="R28" r:id="rId13" display="https://trt2-jus-br.zoom.us/j/81381532305?pwd=Zprq03uth1fKfxUiDb1GGLAiRaUFP1.1%20ID%20da%20reunião:%20813%208153%202305%20Senha%20de%20acesso:%20vtaruja01" xr:uid="{745C84A2-CD29-4354-980F-734B539DBE6F}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{1EEF21AB-BF38-4741-88DD-27B0EF125B50}"/>
+    <hyperlink ref="R4" r:id="rId2" xr:uid="{EAEAD525-5E3E-4CF2-9063-1B4C01CC9987}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{A7D3837C-1E3E-480A-AB55-1D1891B25CEC}"/>
+    <hyperlink ref="R6" r:id="rId4" display="mailto:adv.raiannyyulle@gmail.com" xr:uid="{FD869AFF-1FC9-4189-B6A1-7D0183F22B4A}"/>
+    <hyperlink ref="R8" r:id="rId5" xr:uid="{7F4E5B37-90E2-440E-A6D2-DDC8658416CA}"/>
+    <hyperlink ref="R9" r:id="rId6" xr:uid="{0EED135A-3C97-4BCA-8F81-9CF7BF4D216E}"/>
+    <hyperlink ref="R11" r:id="rId7" display="https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09%20ID%20da%20reunião:%20821%208299%201000%20Senha%20de%20acesso:%20060642" xr:uid="{37D9F4DF-066D-4B36-952C-08D4CE8A6156}"/>
+    <hyperlink ref="R12" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%20532%20639%201733%20Senha%20de%20acesso:%20959215" xr:uid="{C29D4946-403E-4CB2-ABBB-07D7045102A3}"/>
+    <hyperlink ref="R13" r:id="rId9" xr:uid="{2D66DC5E-C290-4B60-AA6A-59F093E27EAF}"/>
+    <hyperlink ref="R16" r:id="rId10" display="https://trt2-jus-br.zoom.us/j/83090135690?pwd=RmliNUV3VDFGS2htNk84dnFFc1c1dz09%20ID%20da%20reunião:%20830%209013%205690%20Senha%20de%20acesso:%20419796" xr:uid="{02CA44D8-29FD-41B9-B4B0-E36899E4C724}"/>
+    <hyperlink ref="R18" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/82942004538?pwd=ZG1mUWNiUEdXN3JmWTFqcW9YdlBkQT09%20ID%20da%20reunião:%20829%204200%204538%20Senha%20de%20acesso:%20786979" xr:uid="{2B73D235-E877-4A0E-A261-95DD7AFABFE6}"/>
+    <hyperlink ref="R22" r:id="rId12" xr:uid="{796663F5-FF2E-43F9-91C6-EB02E2F02934}"/>
+    <hyperlink ref="R23" r:id="rId13" location="success" display="https://trt4-jus-br.zoom.us/j/8649257802?_x_zm_rtaid=eF1kvF5oTjO_AFaCI6_ZRw.1788530250450.93a0d0a5d29493b7247ae72b3f96b690&amp;_x_zm_rhtaid=657 - success" xr:uid="{37FDA05B-0CA4-4749-9DA0-C4F9C4BC8C07}"/>
+    <hyperlink ref="R24" r:id="rId14" display="https://url.trt9.jus.br/q9tfx" xr:uid="{EAED98A0-63CD-4C18-8D39-46F28597A444}"/>
+    <hyperlink ref="R25" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{81F9DD1D-39AC-4921-AFBE-8D0BFF672AE6}"/>
+    <hyperlink ref="R26" r:id="rId16" xr:uid="{221E967E-29AC-4982-BFBE-03778FD68537}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51FD206F-829D-45CE-BD4B-500F835F5A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EA4526F-0969-47D3-B89C-286529931865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2610" windowWidth="20730" windowHeight="11040" xr2:uid="{061FD02A-F0B4-4626-B0D0-B4793BA7C286}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A568F592-88FD-4335-8AF9-30E12F039940}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="182">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,37 +95,427 @@
     <t>Link/Observações</t>
   </si>
   <si>
-    <t>Perícia Técnica</t>
-  </si>
-  <si>
-    <t>0010443-02.2026.5.15.0084</t>
+    <t>Audiência Inicial -  Telepresencial</t>
+  </si>
+  <si>
+    <t>0011748-65.2026.5.03.0048</t>
+  </si>
+  <si>
+    <t>Santa Juliana Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Antonio Carlos Pereira Dos Santos</t>
+  </si>
+  <si>
+    <t>ARAXÁ</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$             143.152,18</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>BBO</t>
+  </si>
+  <si>
+    <t>LWP</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0010471-74.2026.5.15.0017</t>
+  </si>
+  <si>
+    <t>Moema Bioenergia S.A. - Moema</t>
+  </si>
+  <si>
+    <t>Wivison Alves Melo</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DO RIO PRETO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$             317.975,40</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Kelly Cristina Perez kelly.perez@terra.com.br (17) 99111-4699</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0000014-47.2026.5.09.0664</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Rafael Igor Bordini</t>
+  </si>
+  <si>
+    <t>LONDRINA</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$               58.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1 ID da reunião: 873 5191 4639 Senha: 997272</t>
+  </si>
+  <si>
+    <t>0010966-59.2026.5.03.0080</t>
+  </si>
+  <si>
+    <t>Salitre Fertilizantes Ltda.</t>
+  </si>
+  <si>
+    <t>Raniel Luis Martins</t>
+  </si>
+  <si>
+    <t>PATROCÍNIO</t>
+  </si>
+  <si>
+    <t>R$               71.405,55</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001538-77.2026.5.02.0431</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Gilson Siqueira Silva</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             437.883,24</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>0000018-84.2026.5.09.0664</t>
+  </si>
+  <si>
+    <t>R$             538.600,00</t>
+  </si>
+  <si>
+    <t>0010056-60.2025.5.15.0071</t>
+  </si>
+  <si>
+    <t>Mahle Metal Leve S.A.</t>
+  </si>
+  <si>
+    <t>Reginaldo Jose De Souza</t>
+  </si>
+  <si>
+    <t>MOGI GUAÇU</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>R$             360.271,60</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - Ana</t>
+  </si>
+  <si>
+    <t>PSI</t>
+  </si>
+  <si>
+    <t>1000145-14.2026.5.02.0433</t>
+  </si>
+  <si>
+    <t>Rogerio Aparecido Gava</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$          1.138.821,89</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010028-86.2026.5.15.0094</t>
+  </si>
+  <si>
+    <t>Wesley Monteiro Franca Da Silva</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>07ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             187.934,79</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>Audiência Inicial -  Presencial</t>
+  </si>
+  <si>
+    <t>1001539-50.2026.5.02.0435</t>
+  </si>
+  <si>
+    <t>Maciano Almeida Soares</t>
+  </si>
+  <si>
+    <t>R$             361.934,80</t>
+  </si>
+  <si>
+    <t>Correspondente - Hebert</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>Audiência Una - Telepresencial</t>
+  </si>
+  <si>
+    <t>1001377-21.2026.5.02.0608</t>
+  </si>
+  <si>
+    <t>Cepam Panificadora E Restaurante Ltda</t>
+  </si>
+  <si>
+    <t>Maria Valdirene Lima Da Silva</t>
+  </si>
+  <si>
+    <t>SÃO PAULO - ZONA LESTE</t>
+  </si>
+  <si>
+    <t>08ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>ZONA LESTE</t>
+  </si>
+  <si>
+    <t>R$             102.760,38</t>
+  </si>
+  <si>
+    <t>0001073-40.2026.5.08.0101</t>
+  </si>
+  <si>
+    <t>Fertilizantes Tocantins S.A</t>
+  </si>
+  <si>
+    <t>Bruno Wallyson Da Silva Azevedo</t>
+  </si>
+  <si>
+    <t>ABAETETUBA</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>R$             155.483,58</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09 ID da Reunião: 850 5396 9243 Senha: 1VTAbaete</t>
+  </si>
+  <si>
+    <t>1000910-22.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Felipe Da Silva Evangelista</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             183.690,60</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0211600-32.2007.5.15.0071</t>
+  </si>
+  <si>
+    <t>Tereza Fernandes</t>
+  </si>
+  <si>
+    <t>CEJUSC TST</t>
+  </si>
+  <si>
+    <t>3ª Instância</t>
+  </si>
+  <si>
+    <t>R$               18.360,12</t>
+  </si>
+  <si>
+    <t>bit.ly/Cejusc2026</t>
+  </si>
+  <si>
+    <t>0000956-83.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A.</t>
+  </si>
+  <si>
+    <t>Sinval Palhares da Silva</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>R$               45.609,10</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
+  </si>
+  <si>
+    <t>0000991-43.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Messias Vitor Dos Santos</t>
+  </si>
+  <si>
+    <t>0010316-75.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Itapagipe Bioenergia Ltda.</t>
+  </si>
+  <si>
+    <t>Rogerio Nunes Bernardino</t>
+  </si>
+  <si>
+    <t>FRUTAL</t>
+  </si>
+  <si>
+    <t>R$             214.662,00</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>MBF</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
+  </si>
+  <si>
+    <t>0010328-89.2026.5.03.0156</t>
+  </si>
+  <si>
+    <t>Valdomiro Carvalho De Souza</t>
+  </si>
+  <si>
+    <t>R$             161.186,00</t>
+  </si>
+  <si>
+    <t>0010394-11.2026.5.15.0132</t>
   </si>
   <si>
     <t>Embraer S.A.</t>
   </si>
   <si>
-    <t>Marcos Vinicius Da Silva Santos</t>
+    <t>Gilson Brito Soares</t>
   </si>
   <si>
     <t>SÃO JOSÉ DOS CAMPOS</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>04ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             164.005,36</t>
+    <t>R$             150.000,00</t>
   </si>
   <si>
     <t>Grupo B2</t>
@@ -137,518 +527,71 @@
     <t>ANB</t>
   </si>
   <si>
-    <t>Iremos acompanhar</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Telepresencial</t>
-  </si>
-  <si>
-    <t>0001645-75.2026.5.18.0211</t>
-  </si>
-  <si>
-    <t>Syngenta Seeds Ltda.</t>
-  </si>
-  <si>
-    <t>Maria Aparecida Pereira Da Silva</t>
-  </si>
-  <si>
-    <t>FORMOSA</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>VARA DO TRABALHO</t>
+    <t>0011493-69.2022.5.15.0095</t>
+  </si>
+  <si>
+    <t>Jose Roberto Francisco</t>
+  </si>
+  <si>
+    <t>CEJUSC CAMPINAS</t>
+  </si>
+  <si>
+    <t>Execução</t>
+  </si>
+  <si>
+    <t>R$             157.477,74</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
+  </si>
+  <si>
+    <t>0011032-62.2026.5.15.0126</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Francisco Almeida Lima</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
   </si>
   <si>
     <t>1ª Instância</t>
   </si>
   <si>
-    <t>R$               31.498,82</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
+    <t>R$               32.183,40</t>
+  </si>
+  <si>
+    <t>VRO</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
+  </si>
+  <si>
+    <t>0011233-12.2026.5.15.0043</t>
+  </si>
+  <si>
+    <t>Jose Fabio Silva Dos Santos</t>
+  </si>
+  <si>
+    <t>R$               80.917,00</t>
   </si>
   <si>
     <t>JPL</t>
   </si>
   <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/CEJUSCdigital.manha2 ID da reunião: 903 468 6962</t>
-  </si>
-  <si>
-    <t>0000959-38.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participacoes S.A.</t>
-  </si>
-  <si>
-    <t>Reginaldo Pereira Santos</t>
-  </si>
-  <si>
-    <t>QUIRINÓPOLIS</t>
-  </si>
-  <si>
-    <t>R$               29.450,02</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
-  </si>
-  <si>
-    <t>0000958-53.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participacoes S.A</t>
-  </si>
-  <si>
-    <t>Jose Cicero Da Silva</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>R$               45.609,10</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>0000748-68.2026.5.19.0001</t>
-  </si>
-  <si>
-    <t>Sistenge Construções E Comércio Ltda</t>
-  </si>
-  <si>
-    <t>Fernando Santana</t>
-  </si>
-  <si>
-    <t>MACEIÓ</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               37.300,00</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Raianny Yulle Rousan de Lucena Alexandre 82 9 99597231 adv.raiannyyulle@gmail.com</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010243-05.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Leandro Teixeira Soares</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
-  </si>
-  <si>
-    <t>R$             162.021,59</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>0000957-68.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Celma Aparecida Dos Santos</t>
-  </si>
-  <si>
-    <t>R$               28.175,65</t>
-  </si>
-  <si>
-    <t>Audiência Inicial - Telepresencial</t>
-  </si>
-  <si>
-    <t>0000521-09.2026.5.07.0035</t>
-  </si>
-  <si>
-    <t>Simone Da Silva Mariano</t>
-  </si>
-  <si>
-    <t>ARACATI</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>R$               45.126,27</t>
-  </si>
-  <si>
-    <t>JRM</t>
-  </si>
-  <si>
-    <t>https://trt7-jus-br.zoom.us/j/81867554890?pwd=Q0hoOGxaajVCSS9WakV3VnFQZHlWQT0</t>
-  </si>
-  <si>
-    <t>1000248-24.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Murilo De Oliveira Correa</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             146.644,35</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0012906-54.2025.5.15.0082</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Morais Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             210.000,00</t>
-  </si>
-  <si>
-    <t>https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09 ID da reunião: 821 8299 1000 Senha de acesso: 060642</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010625-61.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Espolio De Maria Claudete Teixeira Bergamii</t>
-  </si>
-  <si>
-    <t>R$               38.640,00</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09 ID da reunião: 532 639 1733 Senha de acesso: 959215</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Semipresencial</t>
-  </si>
-  <si>
-    <t>0012322-39.2023.5.15.0152</t>
-  </si>
-  <si>
-    <t>Dell Computadores Do Brasil Ltda.</t>
-  </si>
-  <si>
-    <t>Vanessa Dos Santos Macedo</t>
-  </si>
-  <si>
-    <t>HORTOLÂNDIA</t>
-  </si>
-  <si>
-    <t>04ª TURMA</t>
-  </si>
-  <si>
-    <t>Recursal</t>
-  </si>
-  <si>
-    <t>R$             316.889,10</t>
-  </si>
-  <si>
-    <t>AAP</t>
-  </si>
-  <si>
-    <t>ALF</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/84629297969?pwd=r3nz47WDFpnMMSOdEQbkHHb6s2qCwW.1</t>
-  </si>
-  <si>
-    <t>Audiência Una - Semipresencial</t>
-  </si>
-  <si>
-    <t>1001055-73.2026.5.02.0002</t>
-  </si>
-  <si>
-    <t>Telefonica Brasil S.A.</t>
-  </si>
-  <si>
-    <t>Cibele Martins Julio</t>
-  </si>
-  <si>
-    <t>SÃO PAULO</t>
-  </si>
-  <si>
-    <t>R$          1.359.264,00</t>
-  </si>
-  <si>
-    <t>TFR</t>
-  </si>
-  <si>
-    <t>0011713-71.2024.5.15.0071</t>
-  </si>
-  <si>
-    <t>Claudemir Sergio Da Silva</t>
-  </si>
-  <si>
-    <t>R$               29.383,89</t>
-  </si>
-  <si>
-    <t>1000856-13.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Evandro Xavier De Arruda</t>
-  </si>
-  <si>
-    <t>SÃO CAETANO DO SUL</t>
-  </si>
-  <si>
-    <t>R$          3.267.980,00</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>https://trt2-jus-br.zoom.us/j/83090135690?pwd=RmliNUV3VDFGS2htNk84dnFFc1c1dz09 ID da reunião: 830 9013 5690 Senha de acesso: 419796</t>
-  </si>
-  <si>
-    <t>1000827-69.2026.5.02.0432</t>
-  </si>
-  <si>
-    <t>Carlos Eduardo Salgado</t>
-  </si>
-  <si>
-    <t>R$             322.306,74</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>0012829-61.2025.5.15.0109</t>
-  </si>
-  <si>
-    <t>Umberto Aparecido Lima</t>
-  </si>
-  <si>
-    <t>SOROCABA</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>R$             856.425,61</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/82942004538?pwd=ZG1mUWNiUEdXN3JmWTFqcW9YdlBkQT09 ID da reunião: 829 4200 4538 Senha de acesso: 786979</t>
-  </si>
-  <si>
-    <t>0010664-73.2026.5.15.0087</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Antonio Francisco De Sousa</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>R$             147.855,33</t>
-  </si>
-  <si>
-    <t>Correspondente - Carlos Florian</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001532-58.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Kennety Luiz Santos Silva</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             220.000,00</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>Sessão de Julgamento TRT - Presencial</t>
-  </si>
-  <si>
-    <t>1002002-35.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Anderson Lima Teles</t>
-  </si>
-  <si>
-    <t>03ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             166.182,19</t>
-  </si>
-  <si>
-    <t>0012187-87.2024.5.15.0056</t>
-  </si>
-  <si>
-    <t>Rio Paraná Energia S.A.</t>
-  </si>
-  <si>
-    <t>Alessandro Dos Santos Rodrigues</t>
-  </si>
-  <si>
-    <t>ANDRADINA</t>
-  </si>
-  <si>
-    <t>R$               80.000,00</t>
-  </si>
-  <si>
-    <t>0020454-84.2025.5.04.0261</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Maria Geovana Da Silva Zweibrucker</t>
-  </si>
-  <si>
-    <t>MONTENEGRO</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>01ª TURMA</t>
-  </si>
-  <si>
-    <t>R$             132.825,00</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>https://trt4-jus-br.zoom.us/j/8649257802?_x_zm_rtaid=eF1kvF5oTjO_AFaCI6_ZRw.1788530250450.93a0d0a5d29493b7247ae72b3f96b690&amp;_x_zm_rhtaid=657#success</t>
-  </si>
-  <si>
-    <t>0000049-63.2026.5.09.0128</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Edison Luiz Souza</t>
-  </si>
-  <si>
-    <t>CASCAVEL</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>R$               61.000,00</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/q9tfx ID da Reunião: 84067414281 Senha: fFgDgs9z6o</t>
-  </si>
-  <si>
-    <t>0010648-03.2026.5.15.0061</t>
-  </si>
-  <si>
-    <t>Viterra Bioenergia S.A.</t>
-  </si>
-  <si>
-    <t>Clebson Goncalves Da Silva</t>
-  </si>
-  <si>
-    <t>ARAÇATUBA</t>
-  </si>
-  <si>
-    <t>R$             195.038,09</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09 ID da reunião: 859 6885 4254 Senha de Acesso: 1234</t>
-  </si>
-  <si>
-    <t>0000183-90.2026.5.09.0128</t>
-  </si>
-  <si>
-    <t>R$             205.600,00</t>
-  </si>
-  <si>
-    <t>https://url.trt9.jus.br/hd5v1 ID da Reunião: 85709636455 Senha: fSqjWJtU8U</t>
+    <t>https://trt15-jus-br.zoom.us/j/7789578906?pwd=RlVpOTVlK1Y5Sm96WDlrNmczYklHQT09 Id: 778 957 8906 Senha: 101200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,6 +611,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -747,10 +698,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,8 +725,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1106,30 +1062,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C8FC89-9124-4A34-811C-1893FACB0BF4}">
-  <dimension ref="A1:R26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFCE559-4AF4-4D62-8FC3-404FC081B65D}">
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="124.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="117" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,12 +1140,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>104439</v>
+        <v>105859</v>
       </c>
       <c r="B2" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C2" s="6">
         <v>0.33333333333333331</v>
@@ -1237,19 +1192,19 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>105629</v>
+        <v>104285</v>
       </c>
       <c r="B3" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3" s="6">
-        <v>0.34722222222222221</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1285,30 +1240,30 @@
         <v>41</v>
       </c>
       <c r="O3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>103754</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>105826</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.34722222222222221</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>46</v>
@@ -1323,13 +1278,13 @@
         <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>26</v>
@@ -1338,54 +1293,54 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105825</v>
+        <v>105905</v>
       </c>
       <c r="B5" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C5" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.37152777777777779</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>26</v>
@@ -1394,54 +1349,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>105361</v>
+        <v>105740</v>
       </c>
       <c r="B6" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C6" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1450,54 +1405,54 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="R6" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="R6" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>97246</v>
+        <v>103738</v>
       </c>
       <c r="B7" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C7" s="6">
-        <v>0.375</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>26</v>
@@ -1506,107 +1461,107 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>79</v>
+        <v>54</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>105824</v>
+        <v>99917</v>
       </c>
       <c r="B8" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C8" s="6">
-        <v>0.375</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>38</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="N8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>53</v>
+      <c r="R8" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>105573</v>
+        <v>103916</v>
       </c>
       <c r="B9" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C9" s="6">
-        <v>0.375</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>40</v>
@@ -1618,54 +1573,54 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>103752</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="P9" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="R9" s="7" t="s">
+      <c r="F10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>104022</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="I10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="K10" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>26</v>
@@ -1674,54 +1629,54 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>105796</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>103396</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>26</v>
@@ -1730,54 +1685,54 @@
         <v>27</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="O11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>105735</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="P11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>100360</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1786,107 +1741,107 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>96917</v>
+        <v>105406</v>
       </c>
       <c r="B13" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C13" s="6">
-        <v>0.39583333333333331</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>123</v>
+        <v>43</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>105625</v>
+        <v>105386</v>
       </c>
       <c r="B14" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C14" s="6">
-        <v>0.40625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>25</v>
@@ -1898,54 +1853,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>79</v>
+        <v>119</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>98644</v>
+        <v>101259</v>
       </c>
       <c r="B15" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C15" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1954,54 +1909,54 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="P15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>72686</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.46597222222222223</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="Q15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
-        <v>104944</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -2010,54 +1965,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>105822</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="O16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>104895</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.4201388888888889</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="J17" s="7" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2066,54 +2021,54 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>105933</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>103165</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.4236111111111111</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="H18" s="7" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>26</v>
@@ -2121,52 +2076,52 @@
       <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N18" s="7" t="s">
-        <v>148</v>
+      <c r="N18" s="7">
+        <v>45609.1</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>149</v>
+        <v>139</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>104863</v>
+        <v>104775</v>
       </c>
       <c r="B19" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C19" s="6">
-        <v>0.44097222222222221</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>40</v>
@@ -2178,54 +2133,54 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>156</v>
+        <v>149</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>105742</v>
+        <v>104776</v>
       </c>
       <c r="B20" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C20" s="6">
-        <v>0.46527777777777779</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>26</v>
@@ -2234,54 +2189,54 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>79</v>
+        <v>149</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>103123</v>
+        <v>104370</v>
       </c>
       <c r="B21" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C21" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.61458333333333337</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>26</v>
@@ -2290,54 +2245,54 @@
         <v>27</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>79</v>
+        <v>161</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>99402</v>
+        <v>96644</v>
       </c>
       <c r="B22" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C22" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2346,54 +2301,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>105462</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46274</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="R22" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>100489</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2402,54 +2357,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>103768</v>
+        <v>105275</v>
       </c>
       <c r="B24" s="5">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C24" s="6">
-        <v>0.59722222222222221</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2458,152 +2413,39 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4">
-        <v>105049</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.60763888888888884</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>104017</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46273</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.625</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="R26" s="7" t="s">
-        <v>200</v>
+        <v>175</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R3" r:id="rId1" xr:uid="{1EEF21AB-BF38-4741-88DD-27B0EF125B50}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{EAEAD525-5E3E-4CF2-9063-1B4C01CC9987}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{A7D3837C-1E3E-480A-AB55-1D1891B25CEC}"/>
-    <hyperlink ref="R6" r:id="rId4" display="mailto:adv.raiannyyulle@gmail.com" xr:uid="{FD869AFF-1FC9-4189-B6A1-7D0183F22B4A}"/>
-    <hyperlink ref="R8" r:id="rId5" xr:uid="{7F4E5B37-90E2-440E-A6D2-DDC8658416CA}"/>
-    <hyperlink ref="R9" r:id="rId6" xr:uid="{0EED135A-3C97-4BCA-8F81-9CF7BF4D216E}"/>
-    <hyperlink ref="R11" r:id="rId7" display="https://us02web.zoom.us/j/82182991000?pwd=enFRZ2M3ZWVUNHR5UkNMc2k2SzN5QT09%20ID%20da%20reunião:%20821%208299%201000%20Senha%20de%20acesso:%20060642" xr:uid="{37D9F4DF-066D-4B36-952C-08D4CE8A6156}"/>
-    <hyperlink ref="R12" r:id="rId8" display="https://trt15-jus-br.zoom.us/j/5326391733?pwd=Qjc4RFBXWjZNbVd1bG5wNldjR3dWZz09%20ID%20da%20reunião:%20532%20639%201733%20Senha%20de%20acesso:%20959215" xr:uid="{C29D4946-403E-4CB2-ABBB-07D7045102A3}"/>
-    <hyperlink ref="R13" r:id="rId9" xr:uid="{2D66DC5E-C290-4B60-AA6A-59F093E27EAF}"/>
-    <hyperlink ref="R16" r:id="rId10" display="https://trt2-jus-br.zoom.us/j/83090135690?pwd=RmliNUV3VDFGS2htNk84dnFFc1c1dz09%20ID%20da%20reunião:%20830%209013%205690%20Senha%20de%20acesso:%20419796" xr:uid="{02CA44D8-29FD-41B9-B4B0-E36899E4C724}"/>
-    <hyperlink ref="R18" r:id="rId11" display="https://trt15-jus-br.zoom.us/j/82942004538?pwd=ZG1mUWNiUEdXN3JmWTFqcW9YdlBkQT09%20ID%20da%20reunião:%20829%204200%204538%20Senha%20de%20acesso:%20786979" xr:uid="{2B73D235-E877-4A0E-A261-95DD7AFABFE6}"/>
-    <hyperlink ref="R22" r:id="rId12" xr:uid="{796663F5-FF2E-43F9-91C6-EB02E2F02934}"/>
-    <hyperlink ref="R23" r:id="rId13" location="success" display="https://trt4-jus-br.zoom.us/j/8649257802?_x_zm_rtaid=eF1kvF5oTjO_AFaCI6_ZRw.1788530250450.93a0d0a5d29493b7247ae72b3f96b690&amp;_x_zm_rhtaid=657 - success" xr:uid="{37FDA05B-0CA4-4749-9DA0-C4F9C4BC8C07}"/>
-    <hyperlink ref="R24" r:id="rId14" display="https://url.trt9.jus.br/q9tfx" xr:uid="{EAED98A0-63CD-4C18-8D39-46F28597A444}"/>
-    <hyperlink ref="R25" r:id="rId15" display="https://trt15-jus-br.zoom.us/j/85968854254?pwd=UkYxemkvazd5bU94Y2MrQWRZTFVJdz09%20ID%20da%20reunião:%20859%206885%204254%20Senha%20de%20Acesso:%201234" xr:uid="{81F9DD1D-39AC-4921-AFBE-8D0BFF672AE6}"/>
-    <hyperlink ref="R26" r:id="rId16" xr:uid="{221E967E-29AC-4982-BFBE-03778FD68537}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{9BB30BC5-44AD-4A42-8883-0E049C6B8289}"/>
+    <hyperlink ref="R3" r:id="rId2" display="mailto:kelly.perez@terra.com.br" xr:uid="{6E3FAE6C-A432-4ED8-8338-53E338307DF2}"/>
+    <hyperlink ref="R4" r:id="rId3" display="https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1%20ID%20da%20reunião:%20873%205191%204639%20Senha:%20997272" xr:uid="{B6BADF55-607E-4995-AEB5-6F853156AF5B}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{D303B6F2-66EF-4512-BB2F-90049E36973E}"/>
+    <hyperlink ref="R7" r:id="rId5" display="https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1%20ID%20da%20reunião:%20873%205191%204639%20Senha:%20997272" xr:uid="{E33D51CF-6773-4935-9E19-2F62DBEB9BF0}"/>
+    <hyperlink ref="R10" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{B4D172A7-8AA3-4922-83ED-9FFB73E4A370}"/>
+    <hyperlink ref="R14" r:id="rId7" display="https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09%20ID%20da%20Reunião:%20850%205396%209243%20Senha:%201VTAbaete" xr:uid="{349DE195-AFB1-4605-9345-FBACD79E5170}"/>
+    <hyperlink ref="R17" r:id="rId8" xr:uid="{7041F983-C504-4D21-867D-B47791B4D477}"/>
+    <hyperlink ref="R18" r:id="rId9" xr:uid="{AAC53428-E28A-4C85-89F0-82631DD506CB}"/>
+    <hyperlink ref="R19" r:id="rId10" xr:uid="{02C4FCBB-9D54-4350-A00B-607CBE6BEBD2}"/>
+    <hyperlink ref="R20" r:id="rId11" xr:uid="{2FDDEC29-9C26-4510-BCF3-81AA329977A1}"/>
+    <hyperlink ref="R22" r:id="rId12" xr:uid="{093B09E2-7A05-49ED-8B04-DBBD2E06822A}"/>
+    <hyperlink ref="R23" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{3A2FF20F-758A-488C-9BE0-4A5D8A94CF1D}"/>
+    <hyperlink ref="R24" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/7789578906?pwd=RlVpOTVlK1Y5Sm96WDlrNmczYklHQT09%20Id:%20778%20957%208906%20Senha:%20101200" xr:uid="{E740943B-E45B-442E-BCFF-28964FA3F17C}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId15"/>
 </worksheet>
 </file>
--- a/Pauta_de_Audiencias.xlsx
+++ b/Pauta_de_Audiencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EA4526F-0969-47D3-B89C-286529931865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D76B860-D602-44BF-A3B4-07E5ACC7A3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A568F592-88FD-4335-8AF9-30E12F039940}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFD1EC26-1664-43BA-94B0-9598598C706A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="194">
   <si>
     <t>Código P&amp;C</t>
   </si>
@@ -95,496 +95,561 @@
     <t>Link/Observações</t>
   </si>
   <si>
+    <t>Audiência Instrução - Presencial</t>
+  </si>
+  <si>
+    <t>0011274-93.2025.5.15.0081</t>
+  </si>
+  <si>
+    <t>Syngenta Seeds Ltda.</t>
+  </si>
+  <si>
+    <t>Agata Fernanda Da Silva Rocha</t>
+  </si>
+  <si>
+    <t>MATÃO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>1ª Instância</t>
+  </si>
+  <si>
+    <t>Reclamação Trabalhista</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>R$               61.602,49</t>
+  </si>
+  <si>
+    <t>Grupo E1</t>
+  </si>
+  <si>
+    <t>Correspondente - doc9</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Presencial | Advogada - Gabriella Fernanda Vizicati (16) 993811319 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>gabriellavizicati.adv@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | Preposto - Ketelyn Caroline Maria da Silva Ferreira(16) 997725288 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF467886"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ketelynmaria7@gmail.com</t>
+    </r>
+  </si>
+  <si>
     <t>Audiência Inicial -  Telepresencial</t>
   </si>
   <si>
-    <t>0011748-65.2026.5.03.0048</t>
-  </si>
-  <si>
-    <t>Santa Juliana Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Antonio Carlos Pereira Dos Santos</t>
-  </si>
-  <si>
-    <t>ARAXÁ</t>
+    <t>0000473-65.2026.5.09.0303</t>
+  </si>
+  <si>
+    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
+  </si>
+  <si>
+    <t>Gabriel Goncalves De Jesus</t>
+  </si>
+  <si>
+    <t>FOZ DO IGUAÇU</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>03ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t>R$               44.000,00</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>VSI</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/k9rj6 ID da reunião: 81873598553 Senha de acesso: 3vxqUEfxil</t>
+  </si>
+  <si>
+    <t>0000854-73.2026.5.09.0303</t>
+  </si>
+  <si>
+    <t>R$             371.600,00</t>
+  </si>
+  <si>
+    <t>https://url.trt9.jus.br/v45lh ID da reunião: 83746953609 Senha de acesso: fmLDmfFrpD</t>
+  </si>
+  <si>
+    <t>0010054-90.2026.5.15.0092</t>
+  </si>
+  <si>
+    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Silvio Cesar De Oliveira</t>
+  </si>
+  <si>
+    <t>CAMPINAS</t>
+  </si>
+  <si>
+    <t>05ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             584.709,77</t>
+  </si>
+  <si>
+    <t>Grupo B1</t>
+  </si>
+  <si>
+    <t>BSO</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/84146096644?pwd=STloZzBJSTFaMW5PeXZRYlIrRGlIdz09</t>
+  </si>
+  <si>
+    <t>0012129-83.2025.5.15.0045</t>
+  </si>
+  <si>
+    <t>Embraer S.A.</t>
+  </si>
+  <si>
+    <t>Luiz Gustavo Nitta Dos Santos</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DOS CAMPOS</t>
+  </si>
+  <si>
+    <t>02ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t>R$               93.500,00</t>
+  </si>
+  <si>
+    <t>Grupo B2</t>
+  </si>
+  <si>
+    <t>VCR</t>
+  </si>
+  <si>
+    <t>BCF</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>1000703-80.2026.5.02.0434</t>
+  </si>
+  <si>
+    <t>Welber Lepore</t>
+  </si>
+  <si>
+    <t>SANTO ANDRÉ</t>
+  </si>
+  <si>
+    <t>R$             500.000,00</t>
+  </si>
+  <si>
+    <t>JPE</t>
+  </si>
+  <si>
+    <t>RFE</t>
+  </si>
+  <si>
+    <t>0011497-91.2024.5.15.0045</t>
+  </si>
+  <si>
+    <t>Sociedade Fogás Ltda</t>
+  </si>
+  <si>
+    <t>Willian Januario Ferreira</t>
+  </si>
+  <si>
+    <t>R$             320.364,80</t>
+  </si>
+  <si>
+    <t>RCF</t>
+  </si>
+  <si>
+    <t>0011213-20.2025.5.15.0087</t>
+  </si>
+  <si>
+    <t>Syngenta Proteção De Cultivos Ltda.</t>
+  </si>
+  <si>
+    <t>Adelvan Barbosa Mendes</t>
+  </si>
+  <si>
+    <t>PAULÍNIA</t>
+  </si>
+  <si>
+    <t>01ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$                 4.305,55</t>
+  </si>
+  <si>
+    <t>Correspondente - Carlos Florian</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Dra. Eliane Mendes, (15) 99949-8727</t>
+  </si>
+  <si>
+    <t>Audiência de Instrução - Semipresencial</t>
+  </si>
+  <si>
+    <t>0011639-67.2025.5.15.0043</t>
+  </si>
+  <si>
+    <t>Marcos Aparecido Martins</t>
+  </si>
+  <si>
+    <t>R$             102.072,18</t>
+  </si>
+  <si>
+    <t>ANB</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1 ID da reunião: 838 7184 7087 Senha: TRT15</t>
+  </si>
+  <si>
+    <t>Audiência Inicial - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010254-83.2026.5.15.0032</t>
+  </si>
+  <si>
+    <t>Telefonica Brasil S.A.</t>
+  </si>
+  <si>
+    <t>Fabiana Gambetta de Souza</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>VARA ÚNICA</t>
+  </si>
+  <si>
+    <t>R$          1.747.335,00</t>
+  </si>
+  <si>
+    <t>TFR</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
+  </si>
+  <si>
+    <t>0010126-72.2024.5.15.0084</t>
+  </si>
+  <si>
+    <t>Sergio Monteiro</t>
+  </si>
+  <si>
+    <t>04ª VARA DO TRABALHO</t>
+  </si>
+  <si>
+    <t>R$             229.387,00</t>
+  </si>
+  <si>
+    <t>1000430-23.2026.5.02.0363</t>
+  </si>
+  <si>
+    <t>Erivaldo Barbosa De Souza</t>
+  </si>
+  <si>
+    <t>MAUÁ</t>
+  </si>
+  <si>
+    <t>R$             428.326,17</t>
+  </si>
+  <si>
+    <t>GSM</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Audiência Una - Presencial</t>
+  </si>
+  <si>
+    <t>1001217-05.2026.5.02.0411</t>
+  </si>
+  <si>
+    <t>Companhia Brasileira De Cartuchos</t>
+  </si>
+  <si>
+    <t>Diego Marcos Gomes</t>
+  </si>
+  <si>
+    <t>RIBEIRÃO PIRES</t>
+  </si>
+  <si>
+    <t>R$               35.831,63</t>
+  </si>
+  <si>
+    <t>Grupo B3</t>
+  </si>
+  <si>
+    <t>LMI</t>
+  </si>
+  <si>
+    <t>0011021-83.2026.5.15.0077</t>
+  </si>
+  <si>
+    <t>Valdirene Maria Bispo De Santana</t>
+  </si>
+  <si>
+    <t>INDAIATUBA</t>
+  </si>
+  <si>
+    <t>R$             232.705,51</t>
+  </si>
+  <si>
+    <t>JPL</t>
+  </si>
+  <si>
+    <t>https://trt15-jus-br.zoom.us/j/88215751954?pwd=GWf0av1x8hFikMFre3DVbJa2NJn80H.1</t>
+  </si>
+  <si>
+    <t>Audiência de Conciliação - Telepresencial</t>
+  </si>
+  <si>
+    <t>0000955-98.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Spic Brasil Energia Participacoes S.A.</t>
+  </si>
+  <si>
+    <t>Antonio Marques Ferreira</t>
+  </si>
+  <si>
+    <t>QUIRINÓPOLIS</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>Conhecimento</t>
+  </si>
+  <si>
+    <t>R$               45.609,10</t>
+  </si>
+  <si>
+    <t>ECO</t>
+  </si>
+  <si>
+    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
+  </si>
+  <si>
+    <t>0000954-16.2026.5.18.0129</t>
+  </si>
+  <si>
+    <t>Genesio Carolino de Souza</t>
+  </si>
+  <si>
+    <t>1000911-89.2026.5.02.0361</t>
+  </si>
+  <si>
+    <t>Jose Leite De Sousa</t>
+  </si>
+  <si>
+    <t>R$             424.757,26</t>
+  </si>
+  <si>
+    <t>Sessão de Julgamento TRT - Presencial</t>
+  </si>
+  <si>
+    <t>1001902-80.2025.5.02.0432</t>
+  </si>
+  <si>
+    <t>Rodrigo Ramiro Da Silva</t>
+  </si>
+  <si>
+    <t>17ª TURMA</t>
+  </si>
+  <si>
+    <t>Recursal</t>
+  </si>
+  <si>
+    <t>R$             235.838,22</t>
+  </si>
+  <si>
+    <t>0000270-46.2026.5.09.0322</t>
+  </si>
+  <si>
+    <t>Fertilizantes Heringer S.A.</t>
+  </si>
+  <si>
+    <t>Gabriel Da Silva Pinheiro</t>
+  </si>
+  <si>
+    <t>PARANAGUÁ</t>
+  </si>
+  <si>
+    <t>R$               81.500,00</t>
+  </si>
+  <si>
+    <t>Grupo E2</t>
+  </si>
+  <si>
+    <t>RRU</t>
+  </si>
+  <si>
+    <t>Presencial - Carlos José Luiz lisbonten@gmail.com (41)9152-4057</t>
+  </si>
+  <si>
+    <t>Audiência MPT - Telepresencial</t>
+  </si>
+  <si>
+    <t>000013.2008.15.005/5</t>
+  </si>
+  <si>
+    <t>Viterra Bioenergia S.A.</t>
+  </si>
+  <si>
+    <t>Ministério Público Do Trabalho</t>
+  </si>
+  <si>
+    <t>PRESIDENTE PRUDENTE</t>
+  </si>
+  <si>
+    <t>PROCURADORIA REGIONAL DO TRABALHO</t>
+  </si>
+  <si>
+    <t>Ação Civil Pública</t>
+  </si>
+  <si>
+    <t>Procuradoria Regional do Trabalho</t>
+  </si>
+  <si>
+    <t>R$                            -  </t>
+  </si>
+  <si>
+    <t>AAP</t>
+  </si>
+  <si>
+    <t>https://link.mpt.mp.br/xveNFA1</t>
+  </si>
+  <si>
+    <t>0010380-36.2026.5.03.0140</t>
+  </si>
+  <si>
+    <t>Sistenge Construções E Comércio Ltda.</t>
+  </si>
+  <si>
+    <t>Alex Alves Da Silva Batista</t>
+  </si>
+  <si>
+    <t>CONTAGEM</t>
   </si>
   <si>
     <t>MG</t>
   </si>
   <si>
-    <t>VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Conhecimento</t>
-  </si>
-  <si>
-    <t>Reclamação Trabalhista</t>
-  </si>
-  <si>
-    <t>CENTRAL</t>
-  </si>
-  <si>
-    <t>R$             143.152,18</t>
-  </si>
-  <si>
-    <t>Grupo E2</t>
+    <t>R$             114.705,18</t>
   </si>
   <si>
     <t>BBO</t>
   </si>
   <si>
-    <t>LWP</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.araxa</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Presencial</t>
-  </si>
-  <si>
-    <t>0010471-74.2026.5.15.0017</t>
-  </si>
-  <si>
-    <t>Moema Bioenergia S.A. - Moema</t>
-  </si>
-  <si>
-    <t>Wivison Alves Melo</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DO RIO PRETO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>01ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>Instrução</t>
-  </si>
-  <si>
-    <t>R$             317.975,40</t>
-  </si>
-  <si>
-    <t>Correspondente - doc9</t>
-  </si>
-  <si>
-    <t>CAL</t>
-  </si>
-  <si>
-    <t>Presencial | Advogada - Kelly Cristina Perez kelly.perez@terra.com.br (17) 99111-4699</t>
-  </si>
-  <si>
-    <t>Audiência de Instrução - Semipresencial</t>
-  </si>
-  <si>
-    <t>0000014-47.2026.5.09.0664</t>
-  </si>
-  <si>
-    <t>Companhia Act De Participações E Companhia Aix De Participações</t>
-  </si>
-  <si>
-    <t>Rafael Igor Bordini</t>
-  </si>
-  <si>
-    <t>LONDRINA</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>05ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$               58.000,00</t>
-  </si>
-  <si>
-    <t>Grupo C</t>
-  </si>
-  <si>
-    <t>VSI</t>
-  </si>
-  <si>
-    <t>https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1 ID da reunião: 873 5191 4639 Senha: 997272</t>
-  </si>
-  <si>
-    <t>0010966-59.2026.5.03.0080</t>
-  </si>
-  <si>
-    <t>Salitre Fertilizantes Ltda.</t>
-  </si>
-  <si>
-    <t>Raniel Luis Martins</t>
-  </si>
-  <si>
-    <t>PATROCÍNIO</t>
-  </si>
-  <si>
-    <t>R$               71.405,55</t>
-  </si>
-  <si>
-    <t>RRU</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vt.patrocinio</t>
-  </si>
-  <si>
-    <t>Audiência Una - Presencial</t>
-  </si>
-  <si>
-    <t>1001538-77.2026.5.02.0431</t>
-  </si>
-  <si>
-    <t>Bridgestone Do Brasil Indústria E Comércio Ltda.</t>
-  </si>
-  <si>
-    <t>Gilson Siqueira Silva</t>
-  </si>
-  <si>
-    <t>SANTO ANDRÉ</t>
-  </si>
-  <si>
-    <t>R$             437.883,24</t>
-  </si>
-  <si>
-    <t>Grupo B1</t>
-  </si>
-  <si>
-    <t>GSM</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>0000018-84.2026.5.09.0664</t>
-  </si>
-  <si>
-    <t>R$             538.600,00</t>
-  </si>
-  <si>
-    <t>0010056-60.2025.5.15.0071</t>
-  </si>
-  <si>
-    <t>Mahle Metal Leve S.A.</t>
-  </si>
-  <si>
-    <t>Reginaldo Jose De Souza</t>
-  </si>
-  <si>
-    <t>MOGI GUAÇU</t>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>https://trt3-jus-br.zoom.us/my/vt1.contagem  id da reunião: 951 137 6811</t>
+  </si>
+  <si>
+    <t>0010292-31.2026.5.03.0032</t>
+  </si>
+  <si>
+    <t>Deivid Dos Santos Purcina</t>
+  </si>
+  <si>
+    <t>R$             102.504,89</t>
+  </si>
+  <si>
+    <t>Presencial | Advogada - Gelseli Candido da Silva Ribeiro gelseli45@gmail.com (31) 99219306</t>
+  </si>
+  <si>
+    <t>Audiência Instrução - Telepresencial</t>
+  </si>
+  <si>
+    <t>0010591-18.2026.5.15.0050</t>
+  </si>
+  <si>
+    <t>Allyson Hian Ladeia Lira De Souza</t>
+  </si>
+  <si>
+    <t>DRACENA</t>
+  </si>
+  <si>
+    <t>R$               63.021,36</t>
+  </si>
+  <si>
+    <t>https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09 ID da reunião: 875 2756 4652 Senha de acesso: 246680</t>
+  </si>
+  <si>
+    <t>1000269-26.2018.5.02.0320</t>
+  </si>
+  <si>
+    <t>Rosangela Aparecida Cassiano Silva Pinto</t>
+  </si>
+  <si>
+    <t>GUARULHOS</t>
+  </si>
+  <si>
+    <t>CEJUSC GUARULHOS</t>
+  </si>
+  <si>
+    <t>Execução</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>R$             360.271,60</t>
-  </si>
-  <si>
-    <t>Grupo E1</t>
-  </si>
-  <si>
-    <t>Correspondente - Ana</t>
-  </si>
-  <si>
-    <t>PSI</t>
-  </si>
-  <si>
-    <t>1000145-14.2026.5.02.0433</t>
-  </si>
-  <si>
-    <t>Rogerio Aparecido Gava</t>
-  </si>
-  <si>
-    <t>03ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$          1.138.821,89</t>
-  </si>
-  <si>
-    <t>JPE</t>
-  </si>
-  <si>
-    <t>Audiência Instrução - Telepresencial</t>
-  </si>
-  <si>
-    <t>0010028-86.2026.5.15.0094</t>
-  </si>
-  <si>
-    <t>Wesley Monteiro Franca Da Silva</t>
-  </si>
-  <si>
-    <t>CAMPINAS</t>
-  </si>
-  <si>
-    <t>07ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             187.934,79</t>
-  </si>
-  <si>
-    <t>BSO</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09 ID da reunião: 452 528 5196 Senha de acesso: 702632</t>
-  </si>
-  <si>
-    <t>Audiência Inicial -  Presencial</t>
-  </si>
-  <si>
-    <t>1001539-50.2026.5.02.0435</t>
-  </si>
-  <si>
-    <t>Maciano Almeida Soares</t>
-  </si>
-  <si>
-    <t>R$             361.934,80</t>
-  </si>
-  <si>
-    <t>Correspondente - Hebert</t>
-  </si>
-  <si>
-    <t>RFE</t>
-  </si>
-  <si>
-    <t>Companhia Brasileira De Cartuchos</t>
-  </si>
-  <si>
-    <t>Grupo B3</t>
-  </si>
-  <si>
-    <t>LMI</t>
-  </si>
-  <si>
-    <t>Audiência Una - Telepresencial</t>
-  </si>
-  <si>
-    <t>1001377-21.2026.5.02.0608</t>
-  </si>
-  <si>
-    <t>Cepam Panificadora E Restaurante Ltda</t>
-  </si>
-  <si>
-    <t>Maria Valdirene Lima Da Silva</t>
-  </si>
-  <si>
-    <t>SÃO PAULO - ZONA LESTE</t>
-  </si>
-  <si>
-    <t>08ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>ZONA LESTE</t>
-  </si>
-  <si>
-    <t>R$             102.760,38</t>
-  </si>
-  <si>
-    <t>0001073-40.2026.5.08.0101</t>
-  </si>
-  <si>
-    <t>Fertilizantes Tocantins S.A</t>
-  </si>
-  <si>
-    <t>Bruno Wallyson Da Silva Azevedo</t>
-  </si>
-  <si>
-    <t>ABAETETUBA</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>R$             155.483,58</t>
-  </si>
-  <si>
-    <t>RYL</t>
-  </si>
-  <si>
-    <t>https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09 ID da Reunião: 850 5396 9243 Senha: 1VTAbaete</t>
-  </si>
-  <si>
-    <t>1000910-22.2025.5.02.0432</t>
-  </si>
-  <si>
-    <t>Felipe Da Silva Evangelista</t>
-  </si>
-  <si>
-    <t>02ª VARA DO TRABALHO</t>
-  </si>
-  <si>
-    <t>R$             183.690,60</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Audiência de Conciliação - Telepresencial</t>
-  </si>
-  <si>
-    <t>0211600-32.2007.5.15.0071</t>
-  </si>
-  <si>
-    <t>Tereza Fernandes</t>
-  </si>
-  <si>
-    <t>CEJUSC TST</t>
-  </si>
-  <si>
-    <t>3ª Instância</t>
-  </si>
-  <si>
-    <t>R$               18.360,12</t>
-  </si>
-  <si>
-    <t>bit.ly/Cejusc2026</t>
-  </si>
-  <si>
-    <t>0000956-83.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Spic Brasil Energia Participacoes S.A.</t>
-  </si>
-  <si>
-    <t>Sinval Palhares da Silva</t>
-  </si>
-  <si>
-    <t>QUIRINÓPOLIS</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>R$               45.609,10</t>
-  </si>
-  <si>
-    <t>ECO</t>
-  </si>
-  <si>
-    <t>https://trt18-jus-br.zoom.us/my/cejuscdigital.manha</t>
-  </si>
-  <si>
-    <t>0000991-43.2026.5.18.0129</t>
-  </si>
-  <si>
-    <t>Messias Vitor Dos Santos</t>
-  </si>
-  <si>
-    <t>0010316-75.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Itapagipe Bioenergia Ltda.</t>
-  </si>
-  <si>
-    <t>Rogerio Nunes Bernardino</t>
-  </si>
-  <si>
-    <t>FRUTAL</t>
-  </si>
-  <si>
-    <t>R$             214.662,00</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>https://trt3-jus-br.zoom.us/my/vtfrutal</t>
-  </si>
-  <si>
-    <t>0010328-89.2026.5.03.0156</t>
-  </si>
-  <si>
-    <t>Valdomiro Carvalho De Souza</t>
-  </si>
-  <si>
-    <t>R$             161.186,00</t>
-  </si>
-  <si>
-    <t>0010394-11.2026.5.15.0132</t>
-  </si>
-  <si>
-    <t>Embraer S.A.</t>
-  </si>
-  <si>
-    <t>Gilson Brito Soares</t>
-  </si>
-  <si>
-    <t>SÃO JOSÉ DOS CAMPOS</t>
-  </si>
-  <si>
-    <t>R$             150.000,00</t>
-  </si>
-  <si>
-    <t>Grupo B2</t>
-  </si>
-  <si>
-    <t>VCR</t>
-  </si>
-  <si>
-    <t>ANB</t>
-  </si>
-  <si>
-    <t>0011493-69.2022.5.15.0095</t>
-  </si>
-  <si>
-    <t>Jose Roberto Francisco</t>
-  </si>
-  <si>
-    <t>CEJUSC CAMPINAS</t>
-  </si>
-  <si>
-    <t>Execução</t>
-  </si>
-  <si>
-    <t>R$             157.477,74</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/89925839124?pwd=HehXMRH0LyTAyjb9t6axbYz7RHoBqz.1</t>
-  </si>
-  <si>
-    <t>0011032-62.2026.5.15.0126</t>
-  </si>
-  <si>
-    <t>Syngenta Proteção De Cultivos Ltda.</t>
-  </si>
-  <si>
-    <t>Francisco Almeida Lima</t>
-  </si>
-  <si>
-    <t>PAULÍNIA</t>
-  </si>
-  <si>
-    <t>1ª Instância</t>
-  </si>
-  <si>
-    <t>R$               32.183,40</t>
-  </si>
-  <si>
-    <t>VRO</t>
-  </si>
-  <si>
-    <t>GVM</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1 ID da reunião: 830 5910 4477 Senha: 005974</t>
-  </si>
-  <si>
-    <t>0011233-12.2026.5.15.0043</t>
-  </si>
-  <si>
-    <t>Jose Fabio Silva Dos Santos</t>
-  </si>
-  <si>
-    <t>R$               80.917,00</t>
-  </si>
-  <si>
-    <t>JPL</t>
-  </si>
-  <si>
-    <t>https://trt15-jus-br.zoom.us/j/7789578906?pwd=RlVpOTVlK1Y5Sm96WDlrNmczYklHQT09 Id: 778 957 8906 Senha: 101200</t>
+    <t>R$               27.294,86</t>
+  </si>
+  <si>
+    <t>TLI</t>
+  </si>
+  <si>
+    <t>https://trt2-jus-br.zoom.us/j/81052513141?pwd=OWZwN1k3RUNBdFZSWU5OR2d6aE4xUT09 ID da reunião: 810 5251 3141 Senha de acesso: 1212</t>
   </si>
 </sst>
 </file>
@@ -613,12 +678,10 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <color rgb="FF467886"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -675,14 +738,16 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -691,18 +756,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,12 +791,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1062,8 +1124,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFCE559-4AF4-4D62-8FC3-404FC081B65D}">
-  <dimension ref="A1:R24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2D74DD-DFB2-44BA-AD0D-3BE59E9A8464}">
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
@@ -1071,20 +1133,21 @@
     <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="117" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="136.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1140,12 +1203,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>105859</v>
+        <v>102127</v>
       </c>
       <c r="B2" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C2" s="6">
         <v>0.33333333333333331</v>
@@ -1192,19 +1255,19 @@
       <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>104285</v>
+        <v>104547</v>
       </c>
       <c r="B3" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3" s="6">
-        <v>0.35416666666666669</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>33</v>
@@ -1240,48 +1303,48 @@
         <v>41</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>103754</v>
+        <v>105203</v>
       </c>
       <c r="B4" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C4" s="6">
-        <v>0.36458333333333331</v>
+        <v>0.34930555555555554</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>40</v>
@@ -1293,51 +1356,51 @@
         <v>27</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>55</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>105905</v>
+        <v>103762</v>
       </c>
       <c r="B5" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C5" s="6">
-        <v>0.37152777777777779</v>
+        <v>0.35902777777777778</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>40</v>
@@ -1349,54 +1412,54 @@
         <v>27</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>103233</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="7" t="s">
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>105740</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>26</v>
@@ -1405,51 +1468,51 @@
         <v>27</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>104765</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="F7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
-        <v>103738</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>40</v>
@@ -1461,33 +1524,33 @@
         <v>27</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>55</v>
+      <c r="R7" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>99917</v>
+        <v>101073</v>
       </c>
       <c r="B8" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C8" s="6">
-        <v>0.40277777777777779</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>74</v>
@@ -1499,13 +1562,13 @@
         <v>76</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>40</v>
@@ -1514,57 +1577,57 @@
         <v>26</v>
       </c>
       <c r="M8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="Q8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>101929</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>103916</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>26</v>
@@ -1573,51 +1636,51 @@
         <v>27</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="10" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>103752</v>
+        <v>101921</v>
       </c>
       <c r="B10" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C10" s="6">
         <v>0.43055555555555558</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>40</v>
@@ -1629,51 +1692,51 @@
         <v>27</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>104629</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="R10" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>105796</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.4375</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="I11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>40</v>
@@ -1688,51 +1751,51 @@
         <v>99</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="P11" s="7" t="s">
         <v>100</v>
       </c>
       <c r="Q11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="R11" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="R11" s="8" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="12" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>105735</v>
+        <v>97164</v>
       </c>
       <c r="B12" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C12" s="6">
-        <v>0.4375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>26</v>
@@ -1741,51 +1804,51 @@
         <v>27</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>71</v>
+        <v>91</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>105406</v>
+        <v>104652</v>
       </c>
       <c r="B13" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C13" s="6">
         <v>0.4513888888888889</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>106</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>40</v>
@@ -1794,36 +1857,36 @@
         <v>26</v>
       </c>
       <c r="M13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="R13" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>105880</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
-        <v>105386</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>113</v>
@@ -1838,13 +1901,13 @@
         <v>116</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>26</v>
@@ -1853,10 +1916,10 @@
         <v>27</v>
       </c>
       <c r="N14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>119</v>
@@ -1864,43 +1927,43 @@
       <c r="Q14" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="R14" s="8" t="s">
-        <v>120</v>
+      <c r="R14" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>101259</v>
+        <v>104473</v>
       </c>
       <c r="B15" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C15" s="6">
-        <v>0.46180555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="I15" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>26</v>
@@ -1909,30 +1972,30 @@
         <v>27</v>
       </c>
       <c r="N15" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="Q15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="R15" s="8" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>72686</v>
+        <v>105816</v>
       </c>
       <c r="B16" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C16" s="6">
-        <v>0.46597222222222223</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>126</v>
@@ -1941,22 +2004,22 @@
         <v>127</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>26</v>
@@ -1965,54 +2028,54 @@
         <v>27</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>105822</v>
+        <v>105819</v>
       </c>
       <c r="B17" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C17" s="6">
-        <v>0.47222222222222221</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>126</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>26</v>
@@ -2021,51 +2084,51 @@
         <v>27</v>
       </c>
       <c r="N17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>105464</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P17" s="7" t="s">
+      <c r="F18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="Q17" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
-        <v>105933</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>142</v>
-      </c>
       <c r="H18" s="7" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>40</v>
@@ -2076,55 +2139,55 @@
       <c r="M18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N18" s="7">
-        <v>45609.1</v>
+      <c r="N18" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>140</v>
+        <v>55</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>104775</v>
+        <v>102935</v>
       </c>
       <c r="B19" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C19" s="6">
-        <v>0.54861111111111116</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="H19" s="7" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>26</v>
@@ -2133,51 +2196,51 @@
         <v>27</v>
       </c>
       <c r="N19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>104730</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="O19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P19" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="Q19" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="R19" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
-        <v>104776</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.59027777777777779</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="I20" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>40</v>
@@ -2189,110 +2252,110 @@
         <v>27</v>
       </c>
       <c r="N20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>150</v>
+      <c r="R20" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>104370</v>
+        <v>105817</v>
       </c>
       <c r="B21" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C21" s="6">
-        <v>0.61458333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>40</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>96644</v>
+        <v>104705</v>
       </c>
       <c r="B22" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C22" s="6">
-        <v>0.6333333333333333</v>
+        <v>0.58402777777777781</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>65</v>
+        <v>167</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>26</v>
@@ -2301,54 +2364,54 @@
         <v>27</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="P22" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>104245</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="Q22" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="R22" s="8" t="s">
+      <c r="E23" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4">
-        <v>105462</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46274</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="I23" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H23" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="J23" s="7" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>26</v>
@@ -2357,54 +2420,54 @@
         <v>27</v>
       </c>
       <c r="N23" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>176</v>
+      <c r="R23" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>105275</v>
+        <v>104922</v>
       </c>
       <c r="B24" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C24" s="6">
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>26</v>
@@ -2413,39 +2476,94 @@
         <v>27</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O24" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>66355</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>181</v>
+      <c r="G25" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{9BB30BC5-44AD-4A42-8883-0E049C6B8289}"/>
-    <hyperlink ref="R3" r:id="rId2" display="mailto:kelly.perez@terra.com.br" xr:uid="{6E3FAE6C-A432-4ED8-8338-53E338307DF2}"/>
-    <hyperlink ref="R4" r:id="rId3" display="https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1%20ID%20da%20reunião:%20873%205191%204639%20Senha:%20997272" xr:uid="{B6BADF55-607E-4995-AEB5-6F853156AF5B}"/>
-    <hyperlink ref="R5" r:id="rId4" xr:uid="{D303B6F2-66EF-4512-BB2F-90049E36973E}"/>
-    <hyperlink ref="R7" r:id="rId5" display="https://trt9-jus-br.zoom.us/j/87351914639?pwd=tOMbWCmQ9cg2BOrqRMt0wQjiQbHLyL.1%20ID%20da%20reunião:%20873%205191%204639%20Senha:%20997272" xr:uid="{E33D51CF-6773-4935-9E19-2F62DBEB9BF0}"/>
-    <hyperlink ref="R10" r:id="rId6" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{B4D172A7-8AA3-4922-83ED-9FFB73E4A370}"/>
-    <hyperlink ref="R14" r:id="rId7" display="https://trt8-jus-br.zoom.us/j/85053969243?pwd=RVArVU1FbVNNeFhZMVdxd2x0dEpkdz09%20ID%20da%20Reunião:%20850%205396%209243%20Senha:%201VTAbaete" xr:uid="{349DE195-AFB1-4605-9345-FBACD79E5170}"/>
-    <hyperlink ref="R17" r:id="rId8" xr:uid="{7041F983-C504-4D21-867D-B47791B4D477}"/>
-    <hyperlink ref="R18" r:id="rId9" xr:uid="{AAC53428-E28A-4C85-89F0-82631DD506CB}"/>
-    <hyperlink ref="R19" r:id="rId10" xr:uid="{02C4FCBB-9D54-4350-A00B-607CBE6BEBD2}"/>
-    <hyperlink ref="R20" r:id="rId11" xr:uid="{2FDDEC29-9C26-4510-BCF3-81AA329977A1}"/>
-    <hyperlink ref="R22" r:id="rId12" xr:uid="{093B09E2-7A05-49ED-8B04-DBBD2E06822A}"/>
-    <hyperlink ref="R23" r:id="rId13" display="https://trt15-jus-br.zoom.us/j/83059104477?pwd=h7VDkteaYgzZ4FIU9CoepcQo5ErUHA.1%20ID%20da%20reunião:%20830%205910%204477%20Senha:%20005974" xr:uid="{3A2FF20F-758A-488C-9BE0-4A5D8A94CF1D}"/>
-    <hyperlink ref="R24" r:id="rId14" display="https://trt15-jus-br.zoom.us/j/7789578906?pwd=RlVpOTVlK1Y5Sm96WDlrNmczYklHQT09%20Id:%20778%20957%208906%20Senha:%20101200" xr:uid="{E740943B-E45B-442E-BCFF-28964FA3F17C}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{6EFA8E9F-C59D-49D2-97A9-47035D61B6B0}"/>
+    <hyperlink ref="R4" r:id="rId2" xr:uid="{54294A7B-A98D-4A22-B70A-D03C49B0AA7A}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{B6AA696A-C9BA-44B6-8708-561E285BCC2C}"/>
+    <hyperlink ref="R10" r:id="rId4" display="https://trt15-jus-br.zoom.us/j/83871847087?pwd=Ebt1CpRUX1UTa0fVvv9MzLp1q3Nviv.1%20ID%20da%20reunião:%20838%207184%207087%20Senha:%20TRT15" xr:uid="{95E9564A-3937-4976-99FB-CC71AFBCE5F2}"/>
+    <hyperlink ref="R11" r:id="rId5" display="https://trt15-jus-br.zoom.us/j/4525285196?pwd=cG1ieCtlVVdHZERxcVRTM2lzSGt3dz09%20ID%20da%20reunião:%20452%20528%205196%20Senha%20de%20acesso:%20702632" xr:uid="{7AD27C08-A580-4CCF-A35B-B40DEBD19780}"/>
+    <hyperlink ref="R15" r:id="rId6" xr:uid="{A43C92EE-A1DA-4389-97FE-A948489217B1}"/>
+    <hyperlink ref="R16" r:id="rId7" xr:uid="{E32B90FE-4C30-4C9B-8C73-9C9F9E951E6B}"/>
+    <hyperlink ref="R17" r:id="rId8" xr:uid="{26B08CFF-EF0B-4537-90EA-BC0B97BA68F1}"/>
+    <hyperlink ref="R20" r:id="rId9" display="mailto:lisbonten@gmail.com" xr:uid="{9095D122-A69A-44B0-B4D3-3EA8EBA61F78}"/>
+    <hyperlink ref="R21" r:id="rId10" xr:uid="{5180BE93-DE02-440F-B893-38BD30CA0961}"/>
+    <hyperlink ref="R22" r:id="rId11" display="https://trt3-jus-br.zoom.us/my/vt1.contagem  id da reunião: 951 137 6811" xr:uid="{6727428F-44D0-476D-9837-8068BD565468}"/>
+    <hyperlink ref="R23" r:id="rId12" display="mailto:gelseli45@gmail.com" xr:uid="{36B47A19-C3E1-4C99-B9C7-1F1C65EC2A3C}"/>
+    <hyperlink ref="R24" r:id="rId13" display="https://trt15-jus.br.zoom.us/j/87527564652?pwd=d3YrZ2diWXk5UjgzbmVkNExteWVMQT09%20ID%20da%20reunião:%20875%202756%204652%20Senha%20de%20acesso:%20246680" xr:uid="{3AF867D0-4803-4F73-81E9-7FB544EB202C}"/>
+    <hyperlink ref="R25" r:id="rId14" display="https://trt2-jus-br.zoom.us/j/81052513141?pwd=OWZwN1k3RUNBdFZSWU5OR2d6aE4xUT09%20ID%20da%20reunião:%20810%205251%203141%20Senha%20de%20acesso:%201212" xr:uid="{D25B88C6-8137-4550-87BE-D5D458A6ECA7}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId15"/>
 </worksheet>
 </file>